--- a/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
+++ b/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
@@ -486,7 +486,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>334340</v>
+        <v>334360</v>
       </c>
       <c r="E2" t="n">
         <v>172968</v>
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -683,13 +683,13 @@
         <v>7.442</v>
       </c>
       <c r="I2" t="n">
-        <v>9.026</v>
+        <v>9.026999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>0.6870000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>1.584</v>
+        <v>1.585</v>
       </c>
       <c r="L2" t="n">
         <v>6.38</v>
@@ -698,13 +698,13 @@
         <v>6.38</v>
       </c>
       <c r="N2" t="n">
-        <v>6.426</v>
+        <v>6.427</v>
       </c>
       <c r="O2" t="n">
         <v>0.445</v>
       </c>
       <c r="P2" t="n">
-        <v>-107.189</v>
+        <v>-107.199</v>
       </c>
       <c r="Q2" t="n">
         <v>-3.402</v>
@@ -765,16 +765,16 @@
         <v>5.158</v>
       </c>
       <c r="I3" t="n">
-        <v>5.598</v>
+        <v>5.596</v>
       </c>
       <c r="J3" t="n">
         <v>-1.412</v>
       </c>
       <c r="K3" t="n">
-        <v>0.44</v>
+        <v>0.438</v>
       </c>
       <c r="L3" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="M3" t="n">
         <v>0.571</v>
@@ -783,13 +783,13 @@
         <v>0.801</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.697</v>
+        <v>-0.695</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.336</v>
+        <v>-1.332</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.826</v>
+        <v>-0.825</v>
       </c>
       <c r="R3" t="n">
         <v>20.69</v>
@@ -847,16 +847,16 @@
         <v>4.563</v>
       </c>
       <c r="I4" t="n">
-        <v>4.955</v>
+        <v>4.956</v>
       </c>
       <c r="J4" t="n">
         <v>-0.502</v>
       </c>
       <c r="K4" t="n">
-        <v>0.392</v>
+        <v>0.393</v>
       </c>
       <c r="L4" t="n">
-        <v>0.577</v>
+        <v>0.578</v>
       </c>
       <c r="M4" t="n">
         <v>0.787</v>
@@ -865,10 +865,10 @@
         <v>0.9389999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.295</v>
+        <v>-0.296</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.107</v>
+        <v>-2.109</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.334</v>
@@ -929,13 +929,13 @@
         <v>12.839</v>
       </c>
       <c r="I5" t="n">
-        <v>11.766</v>
+        <v>11.767</v>
       </c>
       <c r="J5" t="n">
         <v>0.185</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.073</v>
+        <v>-1.072</v>
       </c>
       <c r="L5" t="n">
         <v>5.403</v>
@@ -950,10 +950,10 @@
         <v>-0.369</v>
       </c>
       <c r="P5" t="n">
-        <v>-277.026</v>
+        <v>-277.018</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.615</v>
+        <v>-0.616</v>
       </c>
       <c r="R5" t="n">
         <v>20.69</v>
@@ -1011,22 +1011,22 @@
         <v>2.979</v>
       </c>
       <c r="I6" t="n">
-        <v>105.437</v>
+        <v>105.449</v>
       </c>
       <c r="J6" t="n">
         <v>-52.655</v>
       </c>
       <c r="K6" t="n">
-        <v>102.458</v>
+        <v>102.47</v>
       </c>
       <c r="L6" t="n">
-        <v>42.783</v>
+        <v>42.785</v>
       </c>
       <c r="M6" t="n">
-        <v>60.716</v>
+        <v>60.718</v>
       </c>
       <c r="N6" t="n">
-        <v>67.65000000000001</v>
+        <v>67.65300000000001</v>
       </c>
       <c r="O6" t="n">
         <v>-0.323</v>
@@ -1175,19 +1175,19 @@
         <v>8.464</v>
       </c>
       <c r="I8" t="n">
-        <v>7.831</v>
+        <v>7.826</v>
       </c>
       <c r="J8" t="n">
         <v>0.39</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.633</v>
+        <v>-0.638</v>
       </c>
       <c r="L8" t="n">
-        <v>0.74</v>
+        <v>0.738</v>
       </c>
       <c r="M8" t="n">
-        <v>0.979</v>
+        <v>0.978</v>
       </c>
       <c r="N8" t="n">
         <v>1.249</v>
@@ -1196,10 +1196,10 @@
         <v>-0.493</v>
       </c>
       <c r="P8" t="n">
-        <v>-11.033</v>
+        <v>-11.022</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.896</v>
+        <v>-0.897</v>
       </c>
       <c r="R8" t="n">
         <v>31.034</v>
@@ -1257,13 +1257,13 @@
         <v>4.662</v>
       </c>
       <c r="I9" t="n">
-        <v>5.507</v>
+        <v>5.509</v>
       </c>
       <c r="J9" t="n">
         <v>0.72</v>
       </c>
       <c r="K9" t="n">
-        <v>0.845</v>
+        <v>0.847</v>
       </c>
       <c r="L9" t="n">
         <v>0.376</v>
@@ -1272,13 +1272,13 @@
         <v>0.633</v>
       </c>
       <c r="N9" t="n">
-        <v>0.707</v>
+        <v>0.708</v>
       </c>
       <c r="O9" t="n">
         <v>0.323</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.909</v>
+        <v>-0.91</v>
       </c>
       <c r="Q9" t="n">
         <v>0.318</v>
@@ -1339,16 +1339,16 @@
         <v>5.52</v>
       </c>
       <c r="I10" t="n">
-        <v>5.824</v>
+        <v>5.822</v>
       </c>
       <c r="J10" t="n">
         <v>-0.632</v>
       </c>
       <c r="K10" t="n">
-        <v>0.305</v>
+        <v>0.303</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M10" t="n">
         <v>0.639</v>
@@ -1357,13 +1357,13 @@
         <v>0.799</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.67</v>
+        <v>-0.669</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.048</v>
+        <v>-4.047</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="R10" t="n">
         <v>27.586</v>
@@ -1439,13 +1439,13 @@
         <v>0.469</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.386</v>
+        <v>-0.385</v>
       </c>
       <c r="P11" t="n">
         <v>-0.869</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.439</v>
+        <v>-0.438</v>
       </c>
       <c r="R11" t="n">
         <v>24.138</v>
@@ -1524,7 +1524,7 @@
         <v>0.27</v>
       </c>
       <c r="P12" t="n">
-        <v>-9.836</v>
+        <v>-9.837</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.806</v>
@@ -1585,13 +1585,13 @@
         <v>5.663</v>
       </c>
       <c r="I13" t="n">
-        <v>7.072</v>
+        <v>7.073</v>
       </c>
       <c r="J13" t="n">
         <v>0.78</v>
       </c>
       <c r="K13" t="n">
-        <v>1.409</v>
+        <v>1.41</v>
       </c>
       <c r="L13" t="n">
         <v>0.263</v>
@@ -1600,16 +1600,16 @@
         <v>0.804</v>
       </c>
       <c r="N13" t="n">
-        <v>0.902</v>
+        <v>0.903</v>
       </c>
       <c r="O13" t="n">
         <v>0.166</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.863</v>
+        <v>-3.868</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.327</v>
+        <v>-0.328</v>
       </c>
       <c r="R13" t="n">
         <v>51.724</v>
@@ -1632,7 +1632,7 @@
         <v>0.781</v>
       </c>
       <c r="X13" t="n">
-        <v>2.281</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="14">
@@ -1746,34 +1746,34 @@
         <v>5.06</v>
       </c>
       <c r="H15" t="n">
-        <v>5.57</v>
+        <v>5.573</v>
       </c>
       <c r="I15" t="n">
-        <v>6.493</v>
+        <v>6.488</v>
       </c>
       <c r="J15" t="n">
         <v>0.28</v>
       </c>
       <c r="K15" t="n">
-        <v>0.922</v>
+        <v>0.915</v>
       </c>
       <c r="L15" t="n">
         <v>0.273</v>
       </c>
       <c r="M15" t="n">
-        <v>0.742</v>
+        <v>0.741</v>
       </c>
       <c r="N15" t="n">
-        <v>0.861</v>
+        <v>0.859</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.581</v>
+        <v>-0.58</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.805</v>
+        <v>-1.796</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.596</v>
+        <v>-0.597</v>
       </c>
       <c r="R15" t="n">
         <v>24.138</v>
@@ -1831,34 +1831,34 @@
         <v>6.803</v>
       </c>
       <c r="I16" t="n">
-        <v>8.217000000000001</v>
+        <v>8.215999999999999</v>
       </c>
       <c r="J16" t="n">
         <v>-0.825</v>
       </c>
       <c r="K16" t="n">
-        <v>1.414</v>
+        <v>1.413</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.133</v>
+        <v>-0.134</v>
       </c>
       <c r="M16" t="n">
-        <v>0.852</v>
+        <v>0.851</v>
       </c>
       <c r="N16" t="n">
-        <v>0.978</v>
+        <v>0.977</v>
       </c>
       <c r="O16" t="n">
         <v>-0.503</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.998</v>
+        <v>-1.991</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.503</v>
       </c>
       <c r="R16" t="n">
-        <v>13.793</v>
+        <v>17.241</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>3.945</v>
       </c>
       <c r="I17" t="n">
-        <v>3.976</v>
+        <v>3.977</v>
       </c>
       <c r="J17" t="n">
         <v>-0.58</v>
@@ -1922,22 +1922,22 @@
         <v>0.031</v>
       </c>
       <c r="L17" t="n">
-        <v>0.723</v>
+        <v>0.725</v>
       </c>
       <c r="M17" t="n">
-        <v>0.775</v>
+        <v>0.777</v>
       </c>
       <c r="N17" t="n">
-        <v>1.108</v>
+        <v>1.11</v>
       </c>
       <c r="O17" t="n">
-        <v>0.256</v>
+        <v>0.253</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.724</v>
+        <v>-3.741</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.035</v>
+        <v>0.033</v>
       </c>
       <c r="R17" t="n">
         <v>44.828</v>
@@ -2001,7 +2001,7 @@
         <v>-0.795</v>
       </c>
       <c r="K18" t="n">
-        <v>0.299</v>
+        <v>0.3</v>
       </c>
       <c r="L18" t="n">
         <v>0.106</v>
@@ -2013,13 +2013,13 @@
         <v>0.521</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.266</v>
+        <v>-0.265</v>
       </c>
       <c r="P18" t="n">
         <v>-0.411</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.408</v>
+        <v>-0.407</v>
       </c>
       <c r="R18" t="n">
         <v>24.138</v>
@@ -2077,13 +2077,13 @@
         <v>2.466</v>
       </c>
       <c r="I19" t="n">
-        <v>2.878</v>
+        <v>2.875</v>
       </c>
       <c r="J19" t="n">
         <v>-0.153</v>
       </c>
       <c r="K19" t="n">
-        <v>0.412</v>
+        <v>0.41</v>
       </c>
       <c r="L19" t="n">
         <v>0.062</v>
@@ -2092,16 +2092,16 @@
         <v>0.576</v>
       </c>
       <c r="N19" t="n">
-        <v>0.651</v>
+        <v>0.65</v>
       </c>
       <c r="O19" t="n">
         <v>-0.759</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.303</v>
+        <v>-1.299</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.803</v>
+        <v>-0.804</v>
       </c>
       <c r="R19" t="n">
         <v>20.69</v>
@@ -2241,13 +2241,13 @@
         <v>129.287</v>
       </c>
       <c r="I21" t="n">
-        <v>128.806</v>
+        <v>128.807</v>
       </c>
       <c r="J21" t="n">
         <v>-0.34</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.481</v>
+        <v>-0.48</v>
       </c>
       <c r="L21" t="n">
         <v>-0.006</v>
@@ -2262,7 +2262,7 @@
         <v>0.661</v>
       </c>
       <c r="P21" t="n">
-        <v>0.429</v>
+        <v>0.428</v>
       </c>
       <c r="Q21" t="n">
         <v>0.451</v>
@@ -3982,10 +3982,10 @@
         <v>10</v>
       </c>
       <c r="G24" t="n">
-        <v>0.782051282051282</v>
+        <v>0.7822064056939502</v>
       </c>
       <c r="H24" t="n">
-        <v>9.21974358974359</v>
+        <v>9.221762989323842</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -4004,16 +4004,16 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>6.66474358974359</v>
+        <v>6.666762989323843</v>
       </c>
       <c r="N24" t="n">
-        <v>6.66474358974359</v>
+        <v>6.666762989323843</v>
       </c>
       <c r="O24" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P24" t="n">
-        <v>1.945976754117233</v>
+        <v>1.947996153697485</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4053,10 +4053,10 @@
         <v>10</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7891737891737892</v>
+        <v>0.7893238434163701</v>
       </c>
       <c r="H25" t="n">
-        <v>9.291809116809118</v>
+        <v>9.293932384341637</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -4075,16 +4075,16 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>7.011809116809118</v>
+        <v>7.013932384341638</v>
       </c>
       <c r="N25" t="n">
-        <v>7.011809116809118</v>
+        <v>7.013932384341638</v>
       </c>
       <c r="O25" t="n">
         <v>-0.2750000000000004</v>
       </c>
       <c r="P25" t="n">
-        <v>0.07206552706552749</v>
+        <v>0.07216939501779507</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4124,10 +4124,10 @@
         <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7927350427350427</v>
+        <v>0.79288256227758</v>
       </c>
       <c r="H26" t="n">
-        <v>9.308440170940171</v>
+        <v>9.308857651245551</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -4146,16 +4146,16 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>7.235940170940172</v>
+        <v>7.236357651245552</v>
       </c>
       <c r="N26" t="n">
-        <v>7.235940170940172</v>
+        <v>7.236357651245552</v>
       </c>
       <c r="O26" t="n">
         <v>-0.2075</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0166310541310537</v>
+        <v>0.01492526690391394</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4195,10 +4195,10 @@
         <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7856125356125356</v>
+        <v>0.7857651245551601</v>
       </c>
       <c r="H27" t="n">
-        <v>9.267880341880343</v>
+        <v>9.268916725978647</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4217,16 +4217,16 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>7.382880341880343</v>
+        <v>7.383916725978647</v>
       </c>
       <c r="N27" t="n">
-        <v>7.382880341880343</v>
+        <v>7.383916725978647</v>
       </c>
       <c r="O27" t="n">
         <v>-0.1874999999999998</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.0405598290598288</v>
+        <v>-0.03994092526690451</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4266,10 +4266,10 @@
         <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7799145299145299</v>
+        <v>0.7800711743772242</v>
       </c>
       <c r="H28" t="n">
-        <v>9.202158119658119</v>
+        <v>9.202601423487543</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4288,16 +4288,16 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>7.412158119658119</v>
+        <v>7.412601423487543</v>
       </c>
       <c r="N28" t="n">
-        <v>7.412158119658119</v>
+        <v>7.412601423487543</v>
       </c>
       <c r="O28" t="n">
         <v>-0.09499999999999997</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.06572222222222379</v>
+        <v>-0.06631530249110362</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4337,10 +4337,10 @@
         <v>10</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7706552706552706</v>
+        <v>0.7708185053380783</v>
       </c>
       <c r="H29" t="n">
-        <v>9.094336182336182</v>
+        <v>9.094982918149466</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4359,16 +4359,16 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>7.349336182336182</v>
+        <v>7.349982918149466</v>
       </c>
       <c r="N29" t="n">
-        <v>7.349336182336182</v>
+        <v>7.349982918149466</v>
       </c>
       <c r="O29" t="n">
         <v>-0.04499999999999993</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.1078219373219369</v>
+        <v>-0.1076185053380776</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4408,10 +4408,10 @@
         <v>10</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7628205128205128</v>
+        <v>0.7629893238434163</v>
       </c>
       <c r="H30" t="n">
-        <v>9.073294871794872</v>
+        <v>9.073963701067616</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4430,16 +4430,16 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>7.398294871794872</v>
+        <v>7.398963701067616</v>
       </c>
       <c r="N30" t="n">
-        <v>7.398294871794872</v>
+        <v>7.398963701067616</v>
       </c>
       <c r="O30" t="n">
         <v>-0.07000000000000006</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.02104131054131031</v>
+        <v>-0.02101921708185017</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4479,10 +4479,10 @@
         <v>10</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7564102564102564</v>
+        <v>0.7565836298932385</v>
       </c>
       <c r="H31" t="n">
-        <v>9.026282051282051</v>
+        <v>9.027263345195729</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4501,16 +4501,16 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>7.366282051282051</v>
+        <v>7.367263345195729</v>
       </c>
       <c r="N31" t="n">
-        <v>7.366282051282051</v>
+        <v>7.367263345195729</v>
       </c>
       <c r="O31" t="n">
         <v>-0.01500000000000012</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.04701282051282085</v>
+        <v>-0.04670035587188615</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -6106,10 +6106,10 @@
         <v>10</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6189458689458689</v>
+        <v>0.6185053380782918</v>
       </c>
       <c r="H54" t="n">
-        <v>5.076877967711301</v>
+        <v>5.075043890865955</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -6128,16 +6128,16 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.7593779677113002</v>
+        <v>0.7575438908659544</v>
       </c>
       <c r="N54" t="n">
-        <v>0.7593779677113002</v>
+        <v>0.7575438908659544</v>
       </c>
       <c r="O54" t="n">
         <v>-0.02249999999999908</v>
       </c>
       <c r="P54" t="n">
-        <v>0.2001684576944047</v>
+        <v>0.198334380849059</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -6177,10 +6177,10 @@
         <v>10</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6182336182336182</v>
+        <v>0.6177935943060499</v>
       </c>
       <c r="H55" t="n">
-        <v>5.073912630579297</v>
+        <v>5.072080664294187</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -6199,16 +6199,16 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>1.008912630579297</v>
+        <v>1.007080664294187</v>
       </c>
       <c r="N55" t="n">
-        <v>1.008912630579297</v>
+        <v>1.007080664294187</v>
       </c>
       <c r="O55" t="n">
         <v>-0.2525000000000004</v>
       </c>
       <c r="P55" t="n">
-        <v>-0.002965337132003754</v>
+        <v>-0.002963226571767841</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -6248,10 +6248,10 @@
         <v>10</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6203703703703703</v>
+        <v>0.6199288256227758</v>
       </c>
       <c r="H56" t="n">
-        <v>5.081685185185185</v>
+        <v>5.080582206405694</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -6270,16 +6270,16 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>1.276685185185185</v>
+        <v>1.275582206405694</v>
       </c>
       <c r="N56" t="n">
-        <v>1.276685185185185</v>
+        <v>1.275582206405694</v>
       </c>
       <c r="O56" t="n">
         <v>-0.2600000000000002</v>
       </c>
       <c r="P56" t="n">
-        <v>0.007772554605887549</v>
+        <v>0.008501542111506666</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -6319,10 +6319,10 @@
         <v>10</v>
       </c>
       <c r="G57" t="n">
-        <v>0.6310541310541311</v>
+        <v>0.6306049822064057</v>
       </c>
       <c r="H57" t="n">
-        <v>5.118074643874644</v>
+        <v>5.115004982206407</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -6341,16 +6341,16 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>1.318074643874644</v>
+        <v>1.315004982206407</v>
       </c>
       <c r="N57" t="n">
-        <v>1.318074643874644</v>
+        <v>1.315004982206407</v>
       </c>
       <c r="O57" t="n">
         <v>-0.005000000000000338</v>
       </c>
       <c r="P57" t="n">
-        <v>0.03638945868945953</v>
+        <v>0.03442277580071273</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -6390,10 +6390,10 @@
         <v>10</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6661921708185053</v>
       </c>
       <c r="H58" t="n">
-        <v>5.176060606060606</v>
+        <v>5.175521837593012</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6412,16 +6412,16 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>1.411060606060606</v>
+        <v>1.410521837593012</v>
       </c>
       <c r="N58" t="n">
-        <v>1.411060606060606</v>
+        <v>1.410521837593012</v>
       </c>
       <c r="O58" t="n">
         <v>-0.0349999999999997</v>
       </c>
       <c r="P58" t="n">
-        <v>0.05798596218596153</v>
+        <v>0.0605168553866049</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -6461,10 +6461,10 @@
         <v>10</v>
       </c>
       <c r="G59" t="n">
-        <v>0.7264957264957265</v>
+        <v>0.7259786476868327</v>
       </c>
       <c r="H59" t="n">
-        <v>5.318112332112332</v>
+        <v>5.315978647686832</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6483,16 +6483,16 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>1.608112332112332</v>
+        <v>1.605978647686833</v>
       </c>
       <c r="N59" t="n">
-        <v>1.608112332112332</v>
+        <v>1.605978647686833</v>
       </c>
       <c r="O59" t="n">
         <v>-0.05500000000000016</v>
       </c>
       <c r="P59" t="n">
-        <v>0.1420517260517258</v>
+        <v>0.1404568100938208</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -6532,10 +6532,10 @@
         <v>10</v>
       </c>
       <c r="G60" t="n">
-        <v>0.7891737891737892</v>
+        <v>0.7886120996441282</v>
       </c>
       <c r="H60" t="n">
-        <v>5.459195156695157</v>
+        <v>5.45744128113879</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -6554,16 +6554,16 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>1.909195156695157</v>
+        <v>1.90744128113879</v>
       </c>
       <c r="N60" t="n">
-        <v>1.909195156695157</v>
+        <v>1.90744128113879</v>
       </c>
       <c r="O60" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P60" t="n">
-        <v>0.1410828245828251</v>
+        <v>0.1414626334519573</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -6603,10 +6603,10 @@
         <v>10</v>
       </c>
       <c r="G61" t="n">
-        <v>0.8262108262108262</v>
+        <v>0.8256227758007118</v>
       </c>
       <c r="H61" t="n">
-        <v>5.597874643874643</v>
+        <v>5.596405693950178</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -6625,16 +6625,16 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>1.997874643874643</v>
+        <v>1.996405693950178</v>
       </c>
       <c r="N61" t="n">
-        <v>1.997874643874643</v>
+        <v>1.996405693950178</v>
       </c>
       <c r="O61" t="n">
         <v>0.05000000000000027</v>
       </c>
       <c r="P61" t="n">
-        <v>0.1386794871794867</v>
+        <v>0.1389644128113883</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8230,10 +8230,10 @@
         <v>10</v>
       </c>
       <c r="G84" t="n">
-        <v>0.7264957264957265</v>
+        <v>0.7266903914590748</v>
       </c>
       <c r="H84" t="n">
-        <v>5.099658119658119</v>
+        <v>5.100270462633452</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -8252,16 +8252,16 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>1.504658119658119</v>
+        <v>1.505270462633451</v>
       </c>
       <c r="N84" t="n">
-        <v>1.504658119658119</v>
+        <v>1.505270462633451</v>
       </c>
       <c r="O84" t="n">
         <v>-0.2124999999999999</v>
       </c>
       <c r="P84" t="n">
-        <v>-0.4802549867864867</v>
+        <v>-0.4796426438111538</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -8301,10 +8301,10 @@
         <v>10</v>
       </c>
       <c r="G85" t="n">
-        <v>0.7122507122507122</v>
+        <v>0.7124555160142348</v>
       </c>
       <c r="H85" t="n">
-        <v>5.056809116809116</v>
+        <v>5.057992882562277</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -8323,16 +8323,16 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>1.006809116809117</v>
+        <v>1.007992882562277</v>
       </c>
       <c r="N85" t="n">
-        <v>1.006809116809117</v>
+        <v>1.007992882562277</v>
       </c>
       <c r="O85" t="n">
         <v>0.4549999999999996</v>
       </c>
       <c r="P85" t="n">
-        <v>-0.04284900284900228</v>
+        <v>-0.04227758007117455</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -8372,10 +8372,10 @@
         <v>10</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6930199430199431</v>
+        <v>0.6932384341637011</v>
       </c>
       <c r="H86" t="n">
-        <v>4.961310541310541</v>
+        <v>4.963836298932385</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -8394,16 +8394,16 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>0.8313105413105415</v>
+        <v>0.8338362989323853</v>
       </c>
       <c r="N86" t="n">
-        <v>0.8313105413105415</v>
+        <v>0.8338362989323853</v>
       </c>
       <c r="O86" t="n">
         <v>0.08000000000000007</v>
       </c>
       <c r="P86" t="n">
-        <v>-0.0954985754985751</v>
+        <v>-0.09415658362989188</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -8443,10 +8443,10 @@
         <v>10</v>
       </c>
       <c r="G87" t="n">
-        <v>0.6866096866096866</v>
+        <v>0.6868327402135231</v>
       </c>
       <c r="H87" t="n">
-        <v>4.946353276353276</v>
+        <v>4.946765836298932</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -8465,16 +8465,16 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>0.3638532763532769</v>
+        <v>0.3642658362989328</v>
       </c>
       <c r="N87" t="n">
-        <v>0.3638532763532769</v>
+        <v>0.3642658362989328</v>
       </c>
       <c r="O87" t="n">
         <v>0.4524999999999997</v>
       </c>
       <c r="P87" t="n">
-        <v>-0.0149572649572649</v>
+        <v>-0.0170704626334528</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -8514,10 +8514,10 @@
         <v>10</v>
       </c>
       <c r="G88" t="n">
-        <v>0.7058404558404558</v>
+        <v>0.706049822064057</v>
       </c>
       <c r="H88" t="n">
-        <v>5.035709401709402</v>
+        <v>5.037161565836299</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -8536,16 +8536,16 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>0.9732094017094015</v>
+        <v>0.9746615658362989</v>
       </c>
       <c r="N88" t="n">
-        <v>0.9732094017094015</v>
+        <v>0.9746615658362989</v>
       </c>
       <c r="O88" t="n">
         <v>-0.5199999999999996</v>
       </c>
       <c r="P88" t="n">
-        <v>0.08935612535612503</v>
+        <v>0.09039572953736652</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -8585,10 +8585,10 @@
         <v>10</v>
       </c>
       <c r="G89" t="n">
-        <v>0.7136752136752137</v>
+        <v>0.7138790035587189</v>
       </c>
       <c r="H89" t="n">
-        <v>5.068008547008547</v>
+        <v>5.068244128113879</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -8607,16 +8607,16 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>1.455508547008547</v>
+        <v>1.455744128113879</v>
       </c>
       <c r="N89" t="n">
-        <v>1.455508547008547</v>
+        <v>1.455744128113879</v>
       </c>
       <c r="O89" t="n">
         <v>-0.4500000000000002</v>
       </c>
       <c r="P89" t="n">
-        <v>0.03229914529914524</v>
+        <v>0.03108256227757966</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -8656,10 +8656,10 @@
         <v>10</v>
       </c>
       <c r="G90" t="n">
-        <v>0.7086894586894587</v>
+        <v>0.7088967971530249</v>
       </c>
       <c r="H90" t="n">
-        <v>5.045592022792023</v>
+        <v>5.045975516014234</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -8678,16 +8678,16 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>1.663092022792023</v>
+        <v>1.663475516014234</v>
       </c>
       <c r="N90" t="n">
-        <v>1.663092022792023</v>
+        <v>1.663475516014234</v>
       </c>
       <c r="O90" t="n">
         <v>-0.23</v>
       </c>
       <c r="P90" t="n">
-        <v>-0.02241652421652418</v>
+        <v>-0.02226861209964426</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -8727,10 +8727,10 @@
         <v>10</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6908831908831908</v>
+        <v>0.6911032028469751</v>
       </c>
       <c r="H91" t="n">
-        <v>4.955321937321937</v>
+        <v>4.955830604982206</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -8749,16 +8749,16 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>1.775321937321937</v>
+        <v>1.775830604982206</v>
       </c>
       <c r="N91" t="n">
-        <v>1.775321937321937</v>
+        <v>1.775830604982206</v>
       </c>
       <c r="O91" t="n">
         <v>-0.2024999999999997</v>
       </c>
       <c r="P91" t="n">
-        <v>-0.09027008547008553</v>
+        <v>-0.09014491103202804</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -10354,10 +10354,10 @@
         <v>10</v>
       </c>
       <c r="G114" t="n">
-        <v>0.6381766381766382</v>
+        <v>0.6377224199288256</v>
       </c>
       <c r="H114" t="n">
-        <v>11.72822792022792</v>
+        <v>11.72595017793594</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -10376,16 +10376,16 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>5.058227920227921</v>
+        <v>5.055950177935943</v>
       </c>
       <c r="N114" t="n">
-        <v>5.058227920227921</v>
+        <v>5.055950177935943</v>
       </c>
       <c r="O114" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P114" t="n">
-        <v>-1.099858611270994</v>
+        <v>-1.102136353562972</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -10425,10 +10425,10 @@
         <v>10</v>
       </c>
       <c r="G115" t="n">
-        <v>0.636039886039886</v>
+        <v>0.6355871886120996</v>
       </c>
       <c r="H115" t="n">
-        <v>11.71968625356125</v>
+        <v>11.71950177935943</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -10447,16 +10447,16 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>5.179686253561255</v>
+        <v>5.179501779359431</v>
       </c>
       <c r="N115" t="n">
-        <v>5.179686253561255</v>
+        <v>5.179501779359431</v>
       </c>
       <c r="O115" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P115" t="n">
-        <v>-0.008541666666666003</v>
+        <v>-0.006448398576511138</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -10496,10 +10496,10 @@
         <v>10</v>
       </c>
       <c r="G116" t="n">
-        <v>0.6353276353276354</v>
+        <v>0.6348754448398577</v>
       </c>
       <c r="H116" t="n">
-        <v>11.71939601139601</v>
+        <v>11.71921174377224</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -10518,16 +10518,16 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>5.084396011396013</v>
+        <v>5.084211743772242</v>
       </c>
       <c r="N116" t="n">
-        <v>5.084396011396013</v>
+        <v>5.084211743772242</v>
       </c>
       <c r="O116" t="n">
         <v>0.09499999999999975</v>
       </c>
       <c r="P116" t="n">
-        <v>-0.0002902421652422049</v>
+        <v>-0.0002900355871897631</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -10567,10 +10567,10 @@
         <v>10</v>
       </c>
       <c r="G117" t="n">
-        <v>0.6374643874643875</v>
+        <v>0.6370106761565836</v>
       </c>
       <c r="H117" t="n">
-        <v>11.72426780626781</v>
+        <v>11.72130960854093</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -10589,16 +10589,16 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>5.039267806267808</v>
+        <v>5.036309608540926</v>
       </c>
       <c r="N117" t="n">
-        <v>5.039267806267808</v>
+        <v>5.036309608540926</v>
       </c>
       <c r="O117" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P117" t="n">
-        <v>0.004871794871794677</v>
+        <v>0.002097864768684232</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -10638,10 +10638,10 @@
         <v>10</v>
       </c>
       <c r="G118" t="n">
-        <v>0.6424501424501424</v>
+        <v>0.6419928825622776</v>
       </c>
       <c r="H118" t="n">
-        <v>11.74859686609687</v>
+        <v>11.74822419928826</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -10660,16 +10660,16 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>5.218596866096867</v>
+        <v>5.218224199288256</v>
       </c>
       <c r="N118" t="n">
-        <v>5.218596866096867</v>
+        <v>5.218224199288256</v>
       </c>
       <c r="O118" t="n">
         <v>-0.1550000000000002</v>
       </c>
       <c r="P118" t="n">
-        <v>0.02432905982905886</v>
+        <v>0.02691459074732983</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -10709,10 +10709,10 @@
         <v>10</v>
       </c>
       <c r="G119" t="n">
-        <v>0.6452991452991453</v>
+        <v>0.6455516014234876</v>
       </c>
       <c r="H119" t="n">
-        <v>11.75459401709402</v>
+        <v>11.75562277580071</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -10731,16 +10731,16 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>5.479594017094019</v>
+        <v>5.480622775800713</v>
       </c>
       <c r="N119" t="n">
-        <v>5.479594017094019</v>
+        <v>5.480622775800713</v>
       </c>
       <c r="O119" t="n">
         <v>-0.2550000000000008</v>
       </c>
       <c r="P119" t="n">
-        <v>0.005997150997151479</v>
+        <v>0.00739857651245579</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -10780,10 +10780,10 @@
         <v>10</v>
       </c>
       <c r="G120" t="n">
-        <v>0.6474358974358975</v>
+        <v>0.6476868327402135</v>
       </c>
       <c r="H120" t="n">
-        <v>11.76330128205128</v>
+        <v>11.76432384341637</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -10802,16 +10802,16 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>5.693301282051283</v>
+        <v>5.694323843416371</v>
       </c>
       <c r="N120" t="n">
-        <v>5.693301282051283</v>
+        <v>5.694323843416371</v>
       </c>
       <c r="O120" t="n">
         <v>-0.2049999999999992</v>
       </c>
       <c r="P120" t="n">
-        <v>0.008707264957264371</v>
+        <v>0.008701067615659142</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -10851,10 +10851,10 @@
         <v>10</v>
       </c>
       <c r="G121" t="n">
-        <v>0.6481481481481481</v>
+        <v>0.6483985765124555</v>
       </c>
       <c r="H121" t="n">
-        <v>11.7662037037037</v>
+        <v>11.76722419928826</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -10873,16 +10873,16 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>5.866203703703702</v>
+        <v>5.867224199288255</v>
       </c>
       <c r="N121" t="n">
-        <v>5.866203703703702</v>
+        <v>5.867224199288255</v>
       </c>
       <c r="O121" t="n">
         <v>-0.169999999999999</v>
       </c>
       <c r="P121" t="n">
-        <v>0.002902421652420273</v>
+        <v>0.002900355871885196</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -12478,10 +12478,10 @@
         <v>10</v>
       </c>
       <c r="G144" t="n">
-        <v>0.3974358974358974</v>
+        <v>0.397864768683274</v>
       </c>
       <c r="H144" t="n">
-        <v>109.2730341880342</v>
+        <v>109.2741992882562</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -12500,16 +12500,16 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>104.9330341880342</v>
+        <v>104.9341992882562</v>
       </c>
       <c r="N144" t="n">
-        <v>104.9330341880342</v>
+        <v>104.9341992882562</v>
       </c>
       <c r="O144" t="n">
         <v>-52.655</v>
       </c>
       <c r="P144" t="n">
-        <v>-0.2560534296341643</v>
+        <v>-0.2548883294121254</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
@@ -12549,10 +12549,10 @@
         <v>10</v>
       </c>
       <c r="G145" t="n">
-        <v>0.344017094017094</v>
+        <v>0.3444839857651246</v>
       </c>
       <c r="H145" t="n">
-        <v>108.9149572649573</v>
+        <v>108.9301779359431</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -12571,16 +12571,16 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>104.7249572649573</v>
+        <v>104.7401779359431</v>
       </c>
       <c r="N145" t="n">
-        <v>104.7249572649573</v>
+        <v>104.7401779359431</v>
       </c>
       <c r="O145" t="n">
         <v>-0.1499999999999995</v>
       </c>
       <c r="P145" t="n">
-        <v>-0.3580769230769221</v>
+        <v>-0.3440213523131632</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -12620,10 +12620,10 @@
         <v>10</v>
       </c>
       <c r="G146" t="n">
-        <v>0.3012820512820513</v>
+        <v>0.301779359430605</v>
       </c>
       <c r="H146" t="n">
-        <v>108.4884829059829</v>
+        <v>108.4898339264531</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -12642,16 +12642,16 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>104.3484829059829</v>
+        <v>104.3498339264531</v>
       </c>
       <c r="N146" t="n">
-        <v>104.3484829059829</v>
+        <v>104.3498339264531</v>
       </c>
       <c r="O146" t="n">
         <v>-0.05000000000000071</v>
       </c>
       <c r="P146" t="n">
-        <v>-0.4264743589743603</v>
+        <v>-0.4403440094899196</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -12691,10 +12691,10 @@
         <v>10</v>
       </c>
       <c r="G147" t="n">
-        <v>0.25997150997151</v>
+        <v>0.2604982206405694</v>
       </c>
       <c r="H147" t="n">
-        <v>108.0487678062678</v>
+        <v>108.054590747331</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -12713,16 +12713,16 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>103.9787678062678</v>
+        <v>103.984590747331</v>
       </c>
       <c r="N147" t="n">
-        <v>103.9787678062678</v>
+        <v>103.984590747331</v>
       </c>
       <c r="O147" t="n">
         <v>-0.0699999999999994</v>
       </c>
       <c r="P147" t="n">
-        <v>-0.4397150997151016</v>
+        <v>-0.4352431791221818</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -12762,10 +12762,10 @@
         <v>10</v>
       </c>
       <c r="G148" t="n">
-        <v>0.2272079772079772</v>
+        <v>0.2277580071174377</v>
       </c>
       <c r="H148" t="n">
-        <v>107.671745014245</v>
+        <v>107.6762277580071</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -12784,16 +12784,16 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>103.611745014245</v>
+        <v>103.6162277580071</v>
       </c>
       <c r="N148" t="n">
-        <v>103.611745014245</v>
+        <v>103.6162277580071</v>
       </c>
       <c r="O148" t="n">
         <v>-0.01000000000000068</v>
       </c>
       <c r="P148" t="n">
-        <v>-0.3770227920227853</v>
+        <v>-0.3783629893238469</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -12833,10 +12833,10 @@
         <v>10</v>
       </c>
       <c r="G149" t="n">
-        <v>0.2165242165242165</v>
+        <v>0.2170818505338078</v>
       </c>
       <c r="H149" t="n">
-        <v>107.4693447293447</v>
+        <v>107.4784341637011</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -12855,16 +12855,16 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>103.4793447293447</v>
+        <v>103.4884341637011</v>
       </c>
       <c r="N149" t="n">
-        <v>103.4793447293447</v>
+        <v>103.4884341637011</v>
       </c>
       <c r="O149" t="n">
         <v>-0.0699999999999994</v>
       </c>
       <c r="P149" t="n">
-        <v>-0.2024002849002926</v>
+        <v>-0.1977935943060487</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -12904,10 +12904,10 @@
         <v>10</v>
       </c>
       <c r="G150" t="n">
-        <v>0.2022792022792023</v>
+        <v>0.202846975088968</v>
       </c>
       <c r="H150" t="n">
-        <v>106.997150997151</v>
+        <v>107.0064056939502</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -12926,16 +12926,16 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>103.047150997151</v>
+        <v>103.0564056939502</v>
       </c>
       <c r="N150" t="n">
-        <v>103.047150997151</v>
+        <v>103.0564056939502</v>
       </c>
       <c r="O150" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P150" t="n">
-        <v>-0.4721937321937304</v>
+        <v>-0.4720284697508816</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -12975,10 +12975,10 @@
         <v>10</v>
       </c>
       <c r="G151" t="n">
-        <v>0.1652421652421652</v>
+        <v>0.1658362989323843</v>
       </c>
       <c r="H151" t="n">
-        <v>105.4367236467236</v>
+        <v>105.4493950177936</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -12997,16 +12997,16 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>101.4867236467236</v>
+        <v>101.4993950177936</v>
       </c>
       <c r="N151" t="n">
-        <v>101.4867236467236</v>
+        <v>101.4993950177936</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
       </c>
       <c r="P151" t="n">
-        <v>-1.560427350427346</v>
+        <v>-1.557010676156594</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
@@ -14880,10 +14880,10 @@
         <v>10</v>
       </c>
       <c r="G178" t="n">
-        <v>0.6723646723646723</v>
+        <v>0.6718861209964413</v>
       </c>
       <c r="H178" t="n">
-        <v>6.728757122507123</v>
+        <v>6.72651690391459</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -14902,16 +14902,16 @@
         <v>1</v>
       </c>
       <c r="M178" t="n">
-        <v>-0.2262428774928775</v>
+        <v>-0.2284830960854096</v>
       </c>
       <c r="N178" t="n">
-        <v>0.2262428774928775</v>
+        <v>0.2284830960854096</v>
       </c>
       <c r="O178" t="n">
         <v>-0.0649999999999995</v>
       </c>
       <c r="P178" t="n">
-        <v>0.2092151239553486</v>
+        <v>0.2069749053628165</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
@@ -14951,10 +14951,10 @@
         <v>10</v>
       </c>
       <c r="G179" t="n">
-        <v>0.6844729344729344</v>
+        <v>0.6839857651245551</v>
       </c>
       <c r="H179" t="n">
-        <v>6.8079534662868</v>
+        <v>6.806215895610913</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -14973,16 +14973,16 @@
         <v>1</v>
       </c>
       <c r="M179" t="n">
-        <v>-0.1220465337132</v>
+        <v>-0.1237841043890864</v>
       </c>
       <c r="N179" t="n">
-        <v>0.1220465337132</v>
+        <v>0.1237841043890864</v>
       </c>
       <c r="O179" t="n">
         <v>-0.02500000000000036</v>
       </c>
       <c r="P179" t="n">
-        <v>0.07919634377967721</v>
+        <v>0.07969899169632289</v>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
@@ -15022,10 +15022,10 @@
         <v>10</v>
       </c>
       <c r="G180" t="n">
-        <v>0.7029914529914529</v>
+        <v>0.702491103202847</v>
       </c>
       <c r="H180" t="n">
-        <v>6.903668091168091</v>
+        <v>6.902775800711744</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -15044,16 +15044,16 @@
         <v>1</v>
       </c>
       <c r="M180" t="n">
-        <v>-0.006331908831908706</v>
+        <v>-0.007224199288256017</v>
       </c>
       <c r="N180" t="n">
-        <v>0.006331908831908706</v>
+        <v>0.007224199288256017</v>
       </c>
       <c r="O180" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P180" t="n">
-        <v>0.09571462488129168</v>
+        <v>0.09655990510083079</v>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
@@ -15093,10 +15093,10 @@
         <v>10</v>
       </c>
       <c r="G181" t="n">
-        <v>0.7250712250712251</v>
+        <v>0.7245551601423488</v>
       </c>
       <c r="H181" t="n">
-        <v>6.959855175688509</v>
+        <v>6.959395017793594</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -15115,16 +15115,16 @@
         <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>0.02985517568850948</v>
+        <v>0.02939501779359421</v>
       </c>
       <c r="N181" t="n">
-        <v>0.02985517568850948</v>
+        <v>0.02939501779359421</v>
       </c>
       <c r="O181" t="n">
         <v>0.01999999999999957</v>
       </c>
       <c r="P181" t="n">
-        <v>0.05618708452041776</v>
+        <v>0.0566192170818498</v>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
@@ -15164,10 +15164,10 @@
         <v>10</v>
       </c>
       <c r="G182" t="n">
-        <v>0.7606837606837606</v>
+        <v>0.7601423487544484</v>
       </c>
       <c r="H182" t="n">
-        <v>7.199145299145298</v>
+        <v>7.191903914590748</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -15186,16 +15186,16 @@
         <v>1</v>
       </c>
       <c r="M182" t="n">
-        <v>0.2791452991452985</v>
+        <v>0.271903914590748</v>
       </c>
       <c r="N182" t="n">
-        <v>0.2791452991452985</v>
+        <v>0.271903914590748</v>
       </c>
       <c r="O182" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P182" t="n">
-        <v>0.2392901234567892</v>
+        <v>0.232508896797154</v>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
@@ -15235,10 +15235,10 @@
         <v>10</v>
       </c>
       <c r="G183" t="n">
-        <v>0.7877492877492878</v>
+        <v>0.7871886120996441</v>
       </c>
       <c r="H183" t="n">
-        <v>7.515175925925926</v>
+        <v>7.48982918149466</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -15257,16 +15257,16 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>0.615175925925926</v>
+        <v>0.5898291814946592</v>
       </c>
       <c r="N183" t="n">
-        <v>0.615175925925926</v>
+        <v>0.5898291814946592</v>
       </c>
       <c r="O183" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P183" t="n">
-        <v>0.3160306267806279</v>
+        <v>0.2979252669039116</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
@@ -15306,10 +15306,10 @@
         <v>10</v>
       </c>
       <c r="G184" t="n">
-        <v>0.8198005698005698</v>
+        <v>0.8192170818505338</v>
       </c>
       <c r="H184" t="n">
-        <v>7.831492877492877</v>
+        <v>7.826498220640569</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -15328,16 +15328,16 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>0.9214928774928772</v>
+        <v>0.9164982206405687</v>
       </c>
       <c r="N184" t="n">
-        <v>0.9214928774928772</v>
+        <v>0.9164982206405687</v>
       </c>
       <c r="O184" t="n">
         <v>0.009999999999999787</v>
       </c>
       <c r="P184" t="n">
-        <v>0.3163169515669511</v>
+        <v>0.3366690391459093</v>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
@@ -16933,10 +16933,10 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>0.1816239316239316</v>
+        <v>0.1814946619217082</v>
       </c>
       <c r="H207" t="n">
-        <v>4.22642094017094</v>
+        <v>4.226307829181494</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -16955,16 +16955,16 @@
         <v>1</v>
       </c>
       <c r="M207" t="n">
-        <v>-0.536079059829059</v>
+        <v>-0.5361921708185049</v>
       </c>
       <c r="N207" t="n">
-        <v>0.536079059829059</v>
+        <v>0.5361921708185049</v>
       </c>
       <c r="O207" t="n">
         <v>0.1574999999999989</v>
       </c>
       <c r="P207" t="n">
-        <v>-0.6620834045068289</v>
+        <v>-0.6621965154962748</v>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
@@ -17004,10 +17004,10 @@
         <v>10</v>
       </c>
       <c r="G208" t="n">
-        <v>0.193019943019943</v>
+        <v>0.1928825622775801</v>
       </c>
       <c r="H208" t="n">
-        <v>4.291139601139601</v>
+        <v>4.290177935943061</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -17026,16 +17026,16 @@
         <v>1</v>
       </c>
       <c r="M208" t="n">
-        <v>-0.3788603988603985</v>
+        <v>-0.3798220640569392</v>
       </c>
       <c r="N208" t="n">
-        <v>0.3788603988603985</v>
+        <v>0.3798220640569392</v>
       </c>
       <c r="O208" t="n">
         <v>-0.09249999999999936</v>
       </c>
       <c r="P208" t="n">
-        <v>0.06471866096866119</v>
+        <v>0.06387010676156635</v>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
@@ -17075,10 +17075,10 @@
         <v>10</v>
       </c>
       <c r="G209" t="n">
-        <v>0.2293447293447294</v>
+        <v>0.2291814946619217</v>
       </c>
       <c r="H209" t="n">
-        <v>4.59088319088319</v>
+        <v>4.590169039145906</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -17097,16 +17097,16 @@
         <v>1</v>
       </c>
       <c r="M209" t="n">
-        <v>0.09088319088318997</v>
+        <v>0.09016903914590646</v>
       </c>
       <c r="N209" t="n">
-        <v>0.09088319088318997</v>
+        <v>0.09016903914590646</v>
       </c>
       <c r="O209" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P209" t="n">
-        <v>0.2997435897435885</v>
+        <v>0.2999911032028457</v>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
@@ -17146,10 +17146,10 @@
         <v>10</v>
       </c>
       <c r="G210" t="n">
-        <v>0.3041310541310541</v>
+        <v>0.303914590747331</v>
       </c>
       <c r="H210" t="n">
-        <v>5.063965099715099</v>
+        <v>5.062866548042704</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -17168,16 +17168,16 @@
         <v>1</v>
       </c>
       <c r="M210" t="n">
-        <v>0.5664650997150993</v>
+        <v>0.5653665480427046</v>
       </c>
       <c r="N210" t="n">
-        <v>0.5664650997150993</v>
+        <v>0.5653665480427046</v>
       </c>
       <c r="O210" t="n">
         <v>-0.002500000000000391</v>
       </c>
       <c r="P210" t="n">
-        <v>0.4730819088319089</v>
+        <v>0.4726975088967977</v>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
@@ -17217,10 +17217,10 @@
         <v>10</v>
       </c>
       <c r="G211" t="n">
-        <v>0.3717948717948718</v>
+        <v>0.3722419928825623</v>
       </c>
       <c r="H211" t="n">
-        <v>5.442384615384616</v>
+        <v>5.442854092526691</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -17239,16 +17239,16 @@
         <v>1</v>
       </c>
       <c r="M211" t="n">
-        <v>0.8548846153846172</v>
+        <v>0.8553540925266923</v>
       </c>
       <c r="N211" t="n">
-        <v>0.8548846153846172</v>
+        <v>0.8553540925266923</v>
       </c>
       <c r="O211" t="n">
         <v>0.08999999999999897</v>
       </c>
       <c r="P211" t="n">
-        <v>0.3784195156695169</v>
+        <v>0.3799875444839866</v>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
@@ -17288,10 +17288,10 @@
         <v>10</v>
       </c>
       <c r="G212" t="n">
-        <v>0.4088319088319088</v>
+        <v>0.4092526690391459</v>
       </c>
       <c r="H212" t="n">
-        <v>5.598911680911681</v>
+        <v>5.60038434163701</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -17310,16 +17310,16 @@
         <v>1</v>
       </c>
       <c r="M212" t="n">
-        <v>0.6664116809116809</v>
+        <v>0.6678843416370102</v>
       </c>
       <c r="N212" t="n">
-        <v>0.6664116809116809</v>
+        <v>0.6678843416370102</v>
       </c>
       <c r="O212" t="n">
         <v>0.3450000000000015</v>
       </c>
       <c r="P212" t="n">
-        <v>0.1565270655270652</v>
+        <v>0.1575302491103194</v>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
@@ -17359,10 +17359,10 @@
         <v>10</v>
       </c>
       <c r="G213" t="n">
-        <v>0.4045584045584046</v>
+        <v>0.4049822064056939</v>
       </c>
       <c r="H213" t="n">
-        <v>5.590954415954416</v>
+        <v>5.592437722419929</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -17381,16 +17381,16 @@
         <v>1</v>
       </c>
       <c r="M213" t="n">
-        <v>0.9109544159544161</v>
+        <v>0.9124377224199289</v>
       </c>
       <c r="N213" t="n">
-        <v>0.9109544159544161</v>
+        <v>0.9124377224199289</v>
       </c>
       <c r="O213" t="n">
         <v>-0.2525000000000004</v>
       </c>
       <c r="P213" t="n">
-        <v>-0.007957264957265231</v>
+        <v>-0.007946619217081619</v>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
@@ -17430,10 +17430,10 @@
         <v>10</v>
       </c>
       <c r="G214" t="n">
-        <v>0.3839031339031339</v>
+        <v>0.3843416370106761</v>
       </c>
       <c r="H214" t="n">
-        <v>5.506759259259259</v>
+        <v>5.508754448398576</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -17452,16 +17452,16 @@
         <v>1</v>
       </c>
       <c r="M214" t="n">
-        <v>1.036759259259259</v>
+        <v>1.038754448398576</v>
       </c>
       <c r="N214" t="n">
-        <v>1.036759259259259</v>
+        <v>1.038754448398576</v>
       </c>
       <c r="O214" t="n">
         <v>-0.21</v>
       </c>
       <c r="P214" t="n">
-        <v>-0.08419515669515665</v>
+        <v>-0.08368327402135289</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -19057,10 +19057,10 @@
         <v>10</v>
       </c>
       <c r="G237" t="n">
-        <v>0.6752136752136753</v>
+        <v>0.6747330960854092</v>
       </c>
       <c r="H237" t="n">
-        <v>5.168504273504274</v>
+        <v>5.168157295373666</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
@@ -19079,16 +19079,16 @@
         <v>1</v>
       </c>
       <c r="M237" t="n">
-        <v>-0.3339957264957265</v>
+        <v>-0.3343427046263345</v>
       </c>
       <c r="N237" t="n">
-        <v>0.3339957264957265</v>
+        <v>0.3343427046263345</v>
       </c>
       <c r="O237" t="n">
         <v>-0.1549999999999994</v>
       </c>
       <c r="P237" t="n">
-        <v>0.03986560587212296</v>
+        <v>0.03951862774151493</v>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
@@ -19128,10 +19128,10 @@
         <v>10</v>
       </c>
       <c r="G238" t="n">
-        <v>0.655982905982906</v>
+        <v>0.6555160142348755</v>
       </c>
       <c r="H238" t="n">
-        <v>5.111239316239317</v>
+        <v>5.11056512455516</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -19150,16 +19150,16 @@
         <v>1</v>
       </c>
       <c r="M238" t="n">
-        <v>-0.3437606837606832</v>
+        <v>-0.3444348754448399</v>
       </c>
       <c r="N238" t="n">
-        <v>0.3437606837606832</v>
+        <v>0.3444348754448399</v>
       </c>
       <c r="O238" t="n">
         <v>-0.04750000000000032</v>
       </c>
       <c r="P238" t="n">
-        <v>-0.05726495726495706</v>
+        <v>-0.05759217081850565</v>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
@@ -19199,10 +19199,10 @@
         <v>10</v>
       </c>
       <c r="G239" t="n">
-        <v>0.6502849002849003</v>
+        <v>0.6498220640569395</v>
       </c>
       <c r="H239" t="n">
-        <v>5.094068376068376</v>
+        <v>5.090058362989324</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -19221,16 +19221,16 @@
         <v>1</v>
       </c>
       <c r="M239" t="n">
-        <v>-0.2934316239316246</v>
+        <v>-0.2974416370106763</v>
       </c>
       <c r="N239" t="n">
-        <v>0.2934316239316246</v>
+        <v>0.2974416370106763</v>
       </c>
       <c r="O239" t="n">
         <v>-0.06749999999999989</v>
       </c>
       <c r="P239" t="n">
-        <v>-0.01717094017094123</v>
+        <v>-0.02050676156583631</v>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
@@ -19270,10 +19270,10 @@
         <v>10</v>
       </c>
       <c r="G240" t="n">
-        <v>0.6531339031339032</v>
+        <v>0.6526690391459075</v>
       </c>
       <c r="H240" t="n">
-        <v>5.105208926875593</v>
+        <v>5.104090154211151</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
@@ -19292,16 +19292,16 @@
         <v>1</v>
       </c>
       <c r="M240" t="n">
-        <v>-0.1772910731244073</v>
+        <v>-0.1784098457888499</v>
       </c>
       <c r="N240" t="n">
-        <v>0.1772910731244073</v>
+        <v>0.1784098457888499</v>
       </c>
       <c r="O240" t="n">
         <v>-0.1049999999999995</v>
       </c>
       <c r="P240" t="n">
-        <v>0.01114055080721776</v>
+        <v>0.01403179122182685</v>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
@@ -19341,10 +19341,10 @@
         <v>10</v>
       </c>
       <c r="G241" t="n">
-        <v>0.6680911680911681</v>
+        <v>0.6676156583629893</v>
       </c>
       <c r="H241" t="n">
-        <v>5.152723646723647</v>
+        <v>5.152037010676157</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
@@ -19363,16 +19363,16 @@
         <v>1</v>
       </c>
       <c r="M241" t="n">
-        <v>-0.02977635327635308</v>
+        <v>-0.03046298932384328</v>
       </c>
       <c r="N241" t="n">
-        <v>0.02977635327635308</v>
+        <v>0.03046298932384328</v>
       </c>
       <c r="O241" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P241" t="n">
-        <v>0.04751471984805367</v>
+        <v>0.04794685646500607</v>
       </c>
       <c r="Q241" t="inlineStr">
         <is>
@@ -19412,10 +19412,10 @@
         <v>10</v>
       </c>
       <c r="G242" t="n">
-        <v>0.7136752136752137</v>
+        <v>0.7131672597864769</v>
       </c>
       <c r="H242" t="n">
-        <v>5.326367521367522</v>
+        <v>5.324533807829182</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
@@ -19434,16 +19434,16 @@
         <v>1</v>
       </c>
       <c r="M242" t="n">
-        <v>0.2038675213675223</v>
+        <v>0.2020338078291823</v>
       </c>
       <c r="N242" t="n">
-        <v>0.2038675213675223</v>
+        <v>0.2020338078291823</v>
       </c>
       <c r="O242" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P242" t="n">
-        <v>0.1736438746438749</v>
+        <v>0.1724967971530251</v>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
@@ -19483,10 +19483,10 @@
         <v>10</v>
       </c>
       <c r="G243" t="n">
-        <v>0.7613960113960114</v>
+        <v>0.7608540925266903</v>
       </c>
       <c r="H243" t="n">
-        <v>5.637279202279202</v>
+        <v>5.633366548042704</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -19505,16 +19505,16 @@
         <v>1</v>
       </c>
       <c r="M243" t="n">
-        <v>0.4547792022792025</v>
+        <v>0.450866548042705</v>
       </c>
       <c r="N243" t="n">
-        <v>0.4547792022792025</v>
+        <v>0.450866548042705</v>
       </c>
       <c r="O243" t="n">
         <v>0.05999999999999961</v>
       </c>
       <c r="P243" t="n">
-        <v>0.3109116809116799</v>
+        <v>0.3088327402135222</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
@@ -19554,10 +19554,10 @@
         <v>10</v>
       </c>
       <c r="G244" t="n">
-        <v>0.792022792022792</v>
+        <v>0.7914590747330961</v>
       </c>
       <c r="H244" t="n">
-        <v>5.82420227920228</v>
+        <v>5.822167259786477</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -19576,16 +19576,16 @@
         <v>1</v>
       </c>
       <c r="M244" t="n">
-        <v>0.5442022792022794</v>
+        <v>0.5421672597864768</v>
       </c>
       <c r="N244" t="n">
-        <v>0.5442022792022794</v>
+        <v>0.5421672597864768</v>
       </c>
       <c r="O244" t="n">
         <v>0.09750000000000103</v>
       </c>
       <c r="P244" t="n">
-        <v>0.1869230769230779</v>
+        <v>0.1888007117437729</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -21181,10 +21181,10 @@
         <v>10</v>
       </c>
       <c r="G267" t="n">
-        <v>0.7350427350427351</v>
+        <v>0.7352313167259786</v>
       </c>
       <c r="H267" t="n">
-        <v>10.37531603418804</v>
+        <v>10.37646739928826</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
@@ -21203,16 +21203,16 @@
         <v>1</v>
       </c>
       <c r="M267" t="n">
-        <v>-0.1171839658119644</v>
+        <v>-0.1160326007117423</v>
       </c>
       <c r="N267" t="n">
-        <v>0.1171839658119644</v>
+        <v>0.1160326007117423</v>
       </c>
       <c r="O267" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P267" t="n">
-        <v>0.6444454542604472</v>
+        <v>0.6455968193606694</v>
       </c>
       <c r="Q267" t="inlineStr">
         <is>
@@ -21252,10 +21252,10 @@
         <v>10</v>
       </c>
       <c r="G268" t="n">
-        <v>0.7329059829059829</v>
+        <v>0.7330960854092526</v>
       </c>
       <c r="H268" t="n">
-        <v>10.36982925094017</v>
+        <v>10.37047170989324</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
@@ -21274,16 +21274,16 @@
         <v>1</v>
       </c>
       <c r="M268" t="n">
-        <v>-0.002670749059831223</v>
+        <v>-0.002028290106762753</v>
       </c>
       <c r="N268" t="n">
-        <v>0.002670749059831223</v>
+        <v>0.002028290106762753</v>
       </c>
       <c r="O268" t="n">
         <v>-0.1199999999999992</v>
       </c>
       <c r="P268" t="n">
-        <v>-0.005486783247866001</v>
+        <v>-0.00599568939501971</v>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
@@ -21323,10 +21323,10 @@
         <v>10</v>
       </c>
       <c r="G269" t="n">
-        <v>0.7364672364672364</v>
+        <v>0.7366548042704626</v>
       </c>
       <c r="H269" t="n">
-        <v>10.38454063817664</v>
+        <v>10.38581193907473</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
@@ -21345,16 +21345,16 @@
         <v>1</v>
       </c>
       <c r="M269" t="n">
-        <v>0.1145406381766385</v>
+        <v>0.1158119390747334</v>
       </c>
       <c r="N269" t="n">
-        <v>0.1145406381766385</v>
+        <v>0.1158119390747334</v>
       </c>
       <c r="O269" t="n">
         <v>-0.1025000000000009</v>
       </c>
       <c r="P269" t="n">
-        <v>0.01471138723646881</v>
+        <v>0.01534022918149525</v>
       </c>
       <c r="Q269" t="inlineStr">
         <is>
@@ -21394,10 +21394,10 @@
         <v>10</v>
       </c>
       <c r="G270" t="n">
-        <v>0.7407407407407407</v>
+        <v>0.7409252669039146</v>
       </c>
       <c r="H270" t="n">
-        <v>10.40033111842593</v>
+        <v>10.40048796740747</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
@@ -21416,16 +21416,16 @@
         <v>1</v>
       </c>
       <c r="M270" t="n">
-        <v>0.2703311184259256</v>
+        <v>0.2704879674074725</v>
       </c>
       <c r="N270" t="n">
-        <v>0.2703311184259256</v>
+        <v>0.2704879674074725</v>
       </c>
       <c r="O270" t="n">
         <v>-0.1399999999999988</v>
       </c>
       <c r="P270" t="n">
-        <v>0.01579048024928831</v>
+        <v>0.01467602833274029</v>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
@@ -21465,10 +21465,10 @@
         <v>10</v>
       </c>
       <c r="G271" t="n">
-        <v>0.75</v>
+        <v>0.7501779359430605</v>
       </c>
       <c r="H271" t="n">
-        <v>10.42040808</v>
+        <v>10.42101525733808</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
@@ -21487,16 +21487,16 @@
         <v>1</v>
       </c>
       <c r="M271" t="n">
-        <v>0.3879080800000008</v>
+        <v>0.3885152573380779</v>
       </c>
       <c r="N271" t="n">
-        <v>0.3879080800000008</v>
+        <v>0.3885152573380779</v>
       </c>
       <c r="O271" t="n">
         <v>-0.09750000000000014</v>
       </c>
       <c r="P271" t="n">
-        <v>0.02007696157407501</v>
+        <v>0.02052728993060526</v>
       </c>
       <c r="Q271" t="inlineStr">
         <is>
@@ -21536,10 +21536,10 @@
         <v>10</v>
       </c>
       <c r="G272" t="n">
-        <v>0.7592592592592593</v>
+        <v>0.7594306049822064</v>
       </c>
       <c r="H272" t="n">
-        <v>10.45010620285926</v>
+        <v>10.45022376690306</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
@@ -21558,16 +21558,16 @@
         <v>1</v>
       </c>
       <c r="M272" t="n">
-        <v>0.5301062028592582</v>
+        <v>0.5302237669030596</v>
       </c>
       <c r="N272" t="n">
-        <v>0.5301062028592582</v>
+        <v>0.5302237669030596</v>
       </c>
       <c r="O272" t="n">
         <v>-0.1125000000000007</v>
       </c>
       <c r="P272" t="n">
-        <v>0.02969812285925677</v>
+        <v>0.029208509564981</v>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
@@ -21607,10 +21607,10 @@
         <v>10</v>
       </c>
       <c r="G273" t="n">
-        <v>0.7585470085470085</v>
+        <v>0.7587188612099645</v>
       </c>
       <c r="H273" t="n">
-        <v>10.44961751208547</v>
+        <v>10.44973542395189</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -21629,16 +21629,16 @@
         <v>1</v>
       </c>
       <c r="M273" t="n">
-        <v>0.6421175120854716</v>
+        <v>0.6422354239518864</v>
       </c>
       <c r="N273" t="n">
-        <v>0.6421175120854716</v>
+        <v>0.6422354239518864</v>
       </c>
       <c r="O273" t="n">
         <v>-0.1125000000000007</v>
       </c>
       <c r="P273" t="n">
-        <v>-0.0004886907737873258</v>
+        <v>-0.0004883429511739479</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -21678,10 +21678,10 @@
         <v>10</v>
       </c>
       <c r="G274" t="n">
-        <v>0.7428774928774928</v>
+        <v>0.7430604982206406</v>
       </c>
       <c r="H274" t="n">
-        <v>10.40297975323837</v>
+        <v>10.40339492722183</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -21700,16 +21700,16 @@
         <v>1</v>
       </c>
       <c r="M274" t="n">
-        <v>0.7129797532383666</v>
+        <v>0.7133949272218274</v>
       </c>
       <c r="N274" t="n">
-        <v>0.7129797532383666</v>
+        <v>0.7133949272218274</v>
       </c>
       <c r="O274" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P274" t="n">
-        <v>-0.04663775884710475</v>
+        <v>-0.04634049673005869</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -23305,10 +23305,10 @@
         <v>10</v>
       </c>
       <c r="G297" t="n">
-        <v>0.9017094017094017</v>
+        <v>0.9017793594306049</v>
       </c>
       <c r="H297" t="n">
-        <v>7.008666666666667</v>
+        <v>7.008939501779359</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
@@ -23327,16 +23327,16 @@
         <v>1</v>
       </c>
       <c r="M297" t="n">
-        <v>4.128666666666667</v>
+        <v>4.128939501779359</v>
       </c>
       <c r="N297" t="n">
-        <v>4.128666666666667</v>
+        <v>4.128939501779359</v>
       </c>
       <c r="O297" t="n">
         <v>-0.1899999999999999</v>
       </c>
       <c r="P297" t="n">
-        <v>-0.04425295679459396</v>
+        <v>-0.04398012168190135</v>
       </c>
       <c r="Q297" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>10</v>
       </c>
       <c r="G298" t="n">
-        <v>0.7970085470085471</v>
+        <v>0.797153024911032</v>
       </c>
       <c r="H298" t="n">
-        <v>6.255333333333334</v>
+        <v>6.255558718861209</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
@@ -23398,16 +23398,16 @@
         <v>1</v>
       </c>
       <c r="M298" t="n">
-        <v>3.505333333333334</v>
+        <v>3.505558718861209</v>
       </c>
       <c r="N298" t="n">
-        <v>3.505333333333334</v>
+        <v>3.505558718861209</v>
       </c>
       <c r="O298" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P298" t="n">
-        <v>-0.753333333333333</v>
+        <v>-0.7533807829181498</v>
       </c>
       <c r="Q298" t="inlineStr">
         <is>
@@ -23447,10 +23447,10 @@
         <v>10</v>
       </c>
       <c r="G299" t="n">
-        <v>0.6246438746438746</v>
+        <v>0.6249110320284698</v>
       </c>
       <c r="H299" t="n">
-        <v>4.884027777777778</v>
+        <v>4.884288256227758</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
@@ -23469,16 +23469,16 @@
         <v>1</v>
       </c>
       <c r="M299" t="n">
-        <v>2.199027777777778</v>
+        <v>2.199288256227758</v>
       </c>
       <c r="N299" t="n">
-        <v>2.199027777777778</v>
+        <v>2.199288256227758</v>
       </c>
       <c r="O299" t="n">
         <v>-0.06499999999999995</v>
       </c>
       <c r="P299" t="n">
-        <v>-1.371305555555556</v>
+        <v>-1.371270462633452</v>
       </c>
       <c r="Q299" t="inlineStr">
         <is>
@@ -23518,10 +23518,10 @@
         <v>10</v>
       </c>
       <c r="G300" t="n">
-        <v>0.4494301994301994</v>
+        <v>0.4498220640569395</v>
       </c>
       <c r="H300" t="n">
-        <v>4.033194444444445</v>
+        <v>4.033576512455516</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
@@ -23540,16 +23540,16 @@
         <v>1</v>
       </c>
       <c r="M300" t="n">
-        <v>1.418194444444445</v>
+        <v>1.418576512455516</v>
       </c>
       <c r="N300" t="n">
-        <v>1.418194444444445</v>
+        <v>1.418576512455516</v>
       </c>
       <c r="O300" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P300" t="n">
-        <v>-0.8508333333333331</v>
+        <v>-0.8507117437722416</v>
       </c>
       <c r="Q300" t="inlineStr">
         <is>
@@ -23589,10 +23589,10 @@
         <v>10</v>
       </c>
       <c r="G301" t="n">
-        <v>0.334045584045584</v>
+        <v>0.3345195729537366</v>
       </c>
       <c r="H301" t="n">
-        <v>3.910277777777778</v>
+        <v>3.910462633451957</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
@@ -23611,16 +23611,16 @@
         <v>1</v>
       </c>
       <c r="M301" t="n">
-        <v>1.345277777777778</v>
+        <v>1.345462633451957</v>
       </c>
       <c r="N301" t="n">
-        <v>1.345277777777778</v>
+        <v>1.345462633451957</v>
       </c>
       <c r="O301" t="n">
         <v>-0.05000000000000027</v>
       </c>
       <c r="P301" t="n">
-        <v>-0.1229166666666668</v>
+        <v>-0.1231138790035589</v>
       </c>
       <c r="Q301" t="inlineStr">
         <is>
@@ -23660,10 +23660,10 @@
         <v>10</v>
       </c>
       <c r="G302" t="n">
-        <v>0.3347578347578348</v>
+        <v>0.3352313167259787</v>
       </c>
       <c r="H302" t="n">
-        <v>3.910555555555556</v>
+        <v>3.910740213523132</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
@@ -23682,16 +23682,16 @@
         <v>1</v>
       </c>
       <c r="M302" t="n">
-        <v>1.395555555555556</v>
+        <v>1.395740213523132</v>
       </c>
       <c r="N302" t="n">
-        <v>1.395555555555556</v>
+        <v>1.395740213523132</v>
       </c>
       <c r="O302" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P302" t="n">
-        <v>0.0002777777777778212</v>
+        <v>0.0002775800711742882</v>
       </c>
       <c r="Q302" t="inlineStr">
         <is>
@@ -23731,10 +23731,10 @@
         <v>10</v>
       </c>
       <c r="G303" t="n">
-        <v>0.3710826210826211</v>
+        <v>0.3715302491103203</v>
       </c>
       <c r="H303" t="n">
-        <v>3.936083333333333</v>
+        <v>3.936345195729538</v>
       </c>
       <c r="I303" t="inlineStr">
         <is>
@@ -23753,16 +23753,16 @@
         <v>1</v>
       </c>
       <c r="M303" t="n">
-        <v>1.486083333333333</v>
+        <v>1.486345195729537</v>
       </c>
       <c r="N303" t="n">
-        <v>1.486083333333333</v>
+        <v>1.486345195729537</v>
       </c>
       <c r="O303" t="n">
         <v>-0.06499999999999995</v>
       </c>
       <c r="P303" t="n">
-        <v>0.02552777777777759</v>
+        <v>0.02560498220640595</v>
       </c>
       <c r="Q303" t="inlineStr">
         <is>
@@ -23802,10 +23802,10 @@
         <v>10</v>
       </c>
       <c r="G304" t="n">
-        <v>0.3454415954415954</v>
+        <v>0.3459074733096085</v>
       </c>
       <c r="H304" t="n">
-        <v>3.920527777777778</v>
+        <v>3.921163701067615</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
@@ -23824,16 +23824,16 @@
         <v>1</v>
       </c>
       <c r="M304" t="n">
-        <v>1.530527777777777</v>
+        <v>1.531163701067615</v>
       </c>
       <c r="N304" t="n">
-        <v>1.530527777777777</v>
+        <v>1.531163701067615</v>
       </c>
       <c r="O304" t="n">
         <v>-0.06000000000000005</v>
       </c>
       <c r="P304" t="n">
-        <v>-0.01555555555555577</v>
+        <v>-0.0151814946619222</v>
       </c>
       <c r="Q304" t="inlineStr">
         <is>
@@ -25429,10 +25429,10 @@
         <v>10</v>
       </c>
       <c r="G327" t="n">
-        <v>0.9123931623931624</v>
+        <v>0.9124555160142349</v>
       </c>
       <c r="H327" t="n">
-        <v>7.300106837606838</v>
+        <v>7.300846975088969</v>
       </c>
       <c r="I327" t="inlineStr">
         <is>
@@ -25451,16 +25451,16 @@
         <v>1</v>
       </c>
       <c r="M327" t="n">
-        <v>1.520106837606837</v>
+        <v>1.520846975088968</v>
       </c>
       <c r="N327" t="n">
-        <v>1.520106837606837</v>
+        <v>1.520846975088968</v>
       </c>
       <c r="O327" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P327" t="n">
-        <v>2.162335898673697</v>
+        <v>2.163076036155828</v>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
@@ -25500,10 +25500,10 @@
         <v>10</v>
       </c>
       <c r="G328" t="n">
-        <v>0.9052706552706553</v>
+        <v>0.9053380782918149</v>
       </c>
       <c r="H328" t="n">
-        <v>7.226688034188037</v>
+        <v>7.22908896797153</v>
       </c>
       <c r="I328" t="inlineStr">
         <is>
@@ -25522,16 +25522,16 @@
         <v>1</v>
       </c>
       <c r="M328" t="n">
-        <v>1.469188034188036</v>
+        <v>1.471588967971529</v>
       </c>
       <c r="N328" t="n">
-        <v>1.469188034188036</v>
+        <v>1.471588967971529</v>
       </c>
       <c r="O328" t="n">
         <v>-0.02249999999999996</v>
       </c>
       <c r="P328" t="n">
-        <v>-0.07341880341880103</v>
+        <v>-0.07175800711743907</v>
       </c>
       <c r="Q328" t="inlineStr">
         <is>
@@ -25571,10 +25571,10 @@
         <v>10</v>
       </c>
       <c r="G329" t="n">
-        <v>0.8995726495726496</v>
+        <v>0.8996441281138789</v>
       </c>
       <c r="H329" t="n">
-        <v>7.165861378205129</v>
+        <v>7.166020462633453</v>
       </c>
       <c r="I329" t="inlineStr">
         <is>
@@ -25593,16 +25593,16 @@
         <v>1</v>
       </c>
       <c r="M329" t="n">
-        <v>1.415861378205129</v>
+        <v>1.416020462633453</v>
       </c>
       <c r="N329" t="n">
-        <v>1.415861378205129</v>
+        <v>1.416020462633453</v>
       </c>
       <c r="O329" t="n">
         <v>-0.007500000000000284</v>
       </c>
       <c r="P329" t="n">
-        <v>-0.0608266559829076</v>
+        <v>-0.06306850533807662</v>
       </c>
       <c r="Q329" t="inlineStr">
         <is>
@@ -25642,10 +25642,10 @@
         <v>10</v>
       </c>
       <c r="G330" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.8975088967971531</v>
       </c>
       <c r="H330" t="n">
-        <v>7.160641025641026</v>
+        <v>7.160857651245553</v>
       </c>
       <c r="I330" t="inlineStr">
         <is>
@@ -25664,16 +25664,16 @@
         <v>1</v>
       </c>
       <c r="M330" t="n">
-        <v>1.410641025641026</v>
+        <v>1.410857651245553</v>
       </c>
       <c r="N330" t="n">
-        <v>1.410641025641026</v>
+        <v>1.410857651245553</v>
       </c>
       <c r="O330" t="n">
         <v>0</v>
       </c>
       <c r="P330" t="n">
-        <v>-0.005220352564102804</v>
+        <v>-0.005162811387900312</v>
       </c>
       <c r="Q330" t="inlineStr">
         <is>
@@ -25713,10 +25713,10 @@
         <v>10</v>
       </c>
       <c r="G331" t="n">
-        <v>0.896011396011396</v>
+        <v>0.896085409252669</v>
       </c>
       <c r="H331" t="n">
-        <v>7.136092117758785</v>
+        <v>7.137556346381969</v>
       </c>
       <c r="I331" t="inlineStr">
         <is>
@@ -25735,16 +25735,16 @@
         <v>1</v>
       </c>
       <c r="M331" t="n">
-        <v>1.386092117758785</v>
+        <v>1.387556346381969</v>
       </c>
       <c r="N331" t="n">
-        <v>1.386092117758785</v>
+        <v>1.387556346381969</v>
       </c>
       <c r="O331" t="n">
         <v>0</v>
       </c>
       <c r="P331" t="n">
-        <v>-0.02454890788224073</v>
+        <v>-0.02330130486358328</v>
       </c>
       <c r="Q331" t="inlineStr">
         <is>
@@ -25784,10 +25784,10 @@
         <v>10</v>
       </c>
       <c r="G332" t="n">
-        <v>0.8945868945868946</v>
+        <v>0.894661921708185</v>
       </c>
       <c r="H332" t="n">
-        <v>7.107492877492878</v>
+        <v>7.109274021352314</v>
       </c>
       <c r="I332" t="inlineStr">
         <is>
@@ -25806,16 +25806,16 @@
         <v>1</v>
       </c>
       <c r="M332" t="n">
-        <v>1.357492877492878</v>
+        <v>1.359274021352314</v>
       </c>
       <c r="N332" t="n">
-        <v>1.357492877492878</v>
+        <v>1.359274021352314</v>
       </c>
       <c r="O332" t="n">
         <v>0</v>
       </c>
       <c r="P332" t="n">
-        <v>-0.02859924026590743</v>
+        <v>-0.02828232502965555</v>
       </c>
       <c r="Q332" t="inlineStr">
         <is>
@@ -25855,10 +25855,10 @@
         <v>10</v>
       </c>
       <c r="G333" t="n">
-        <v>0.8931623931623932</v>
+        <v>0.8932384341637011</v>
       </c>
       <c r="H333" t="n">
-        <v>7.081837606837608</v>
+        <v>7.082740213523132</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -25877,16 +25877,16 @@
         <v>1</v>
       </c>
       <c r="M333" t="n">
-        <v>1.331837606837608</v>
+        <v>1.332740213523132</v>
       </c>
       <c r="N333" t="n">
-        <v>1.331837606837608</v>
+        <v>1.332740213523132</v>
       </c>
       <c r="O333" t="n">
         <v>0</v>
       </c>
       <c r="P333" t="n">
-        <v>-0.02565527065527018</v>
+        <v>-0.02653380782918191</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -25926,10 +25926,10 @@
         <v>10</v>
       </c>
       <c r="G334" t="n">
-        <v>0.8917378917378918</v>
+        <v>0.8918149466192171</v>
       </c>
       <c r="H334" t="n">
-        <v>7.072464387464388</v>
+        <v>7.072921708185054</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -25948,16 +25948,16 @@
         <v>1</v>
       </c>
       <c r="M334" t="n">
-        <v>1.332464387464388</v>
+        <v>1.332921708185054</v>
       </c>
       <c r="N334" t="n">
-        <v>1.332464387464388</v>
+        <v>1.332921708185054</v>
       </c>
       <c r="O334" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P334" t="n">
-        <v>-0.00937321937322011</v>
+        <v>-0.009818505338078154</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -28121,10 +28121,10 @@
         <v>9</v>
       </c>
       <c r="G365" t="n">
-        <v>0.7994207096307024</v>
+        <v>0.8001448225923244</v>
       </c>
       <c r="H365" t="n">
-        <v>5.570463432295439</v>
+        <v>5.573217475259474</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -28143,10 +28143,10 @@
         <v>1</v>
       </c>
       <c r="M365" t="n">
-        <v>0.7904634322954385</v>
+        <v>0.7932174752594738</v>
       </c>
       <c r="N365" t="n">
-        <v>0.7904634322954385</v>
+        <v>0.7932174752594738</v>
       </c>
       <c r="O365" t="inlineStr"/>
       <c r="P365" t="inlineStr"/>
@@ -28186,10 +28186,10 @@
         <v>9</v>
       </c>
       <c r="G366" t="n">
-        <v>0.7871107892831282</v>
+        <v>0.7878349022447502</v>
       </c>
       <c r="H366" t="n">
-        <v>5.508093410572049</v>
+        <v>5.50891962346126</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -28208,16 +28208,16 @@
         <v>1</v>
       </c>
       <c r="M366" t="n">
-        <v>0.7205934105720475</v>
+        <v>0.7214196234612587</v>
       </c>
       <c r="N366" t="n">
-        <v>0.7205934105720475</v>
+        <v>0.7214196234612587</v>
       </c>
       <c r="O366" t="n">
         <v>0.007500000000001172</v>
       </c>
       <c r="P366" t="n">
-        <v>-0.06237002172338979</v>
+        <v>-0.06429785179821401</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>0.0149999999999979</v>
       </c>
       <c r="P367" t="n">
-        <v>-0.06264083997103498</v>
+        <v>-0.06346705286024612</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -28328,10 +28328,10 @@
         <v>9</v>
       </c>
       <c r="G368" t="n">
-        <v>0.7559739319333816</v>
+        <v>0.7566980448950036</v>
       </c>
       <c r="H368" t="n">
-        <v>5.386415640839971</v>
+        <v>5.388481173062997</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -28350,16 +28350,16 @@
         <v>1</v>
       </c>
       <c r="M368" t="n">
-        <v>0.5964156408399708</v>
+        <v>0.5984811730629973</v>
       </c>
       <c r="N368" t="n">
-        <v>0.5964156408399708</v>
+        <v>0.5984811730629973</v>
       </c>
       <c r="O368" t="n">
         <v>-0.01249999999999929</v>
       </c>
       <c r="P368" t="n">
-        <v>-0.05903692976104313</v>
+        <v>-0.05697139753801661</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>-0.004999999999999893</v>
       </c>
       <c r="P369" t="n">
-        <v>-0.02693772628530056</v>
+        <v>-0.02900325850832708</v>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>9</v>
       </c>
       <c r="D371" t="n">
-        <v>11700</v>
+        <v>11690</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>9</v>
       </c>
       <c r="D372" t="n">
-        <v>11596.4130859375</v>
+        <v>11591.4931640625</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>9</v>
       </c>
       <c r="D373" t="n">
-        <v>11510</v>
+        <v>11500</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -28683,10 +28683,10 @@
         <v>9</v>
       </c>
       <c r="G373" t="n">
-        <v>0.719768283852281</v>
+        <v>0.719044170890659</v>
       </c>
       <c r="H373" t="n">
-        <v>5.273139029688632</v>
+        <v>5.271073497465604</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -28705,16 +28705,16 @@
         <v>1</v>
       </c>
       <c r="M373" t="n">
-        <v>0.3581390296886315</v>
+        <v>0.3560734974656041</v>
       </c>
       <c r="N373" t="n">
-        <v>0.3581390296886315</v>
+        <v>0.3560734974656041</v>
       </c>
       <c r="O373" t="n">
         <v>-0.02750000000000075</v>
       </c>
       <c r="P373" t="n">
-        <v>-0.03338522809558242</v>
+        <v>-0.03545076031860983</v>
       </c>
       <c r="Q373" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>9</v>
       </c>
       <c r="D374" t="n">
-        <v>11414.107421875</v>
+        <v>11410</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>0.1200000000000001</v>
       </c>
       <c r="P374" t="n">
-        <v>-0.02056480811006534</v>
+        <v>-0.01849927588703792</v>
       </c>
       <c r="Q374" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>9</v>
       </c>
       <c r="D375" t="n">
-        <v>11330</v>
+        <v>11320.888671875</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -28825,10 +28825,10 @@
         <v>9</v>
       </c>
       <c r="G375" t="n">
-        <v>0.7002172338884866</v>
+        <v>0.6994931209268646</v>
       </c>
       <c r="H375" t="n">
-        <v>5.209869659666908</v>
+        <v>5.207804127443882</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -28847,16 +28847,16 @@
         <v>1</v>
       </c>
       <c r="M375" t="n">
-        <v>-0.1801303403330925</v>
+        <v>-0.182195872556119</v>
       </c>
       <c r="N375" t="n">
-        <v>0.1801303403330925</v>
+        <v>0.182195872556119</v>
       </c>
       <c r="O375" t="n">
         <v>0.3550000000000004</v>
       </c>
       <c r="P375" t="n">
-        <v>-0.04270456191165817</v>
+        <v>-0.04477009413468469</v>
       </c>
       <c r="Q375" t="inlineStr">
         <is>
@@ -28896,10 +28896,10 @@
         <v>9</v>
       </c>
       <c r="G376" t="n">
-        <v>0.6871832005792904</v>
+        <v>0.6879073135409124</v>
       </c>
       <c r="H376" t="n">
-        <v>5.152608254887762</v>
+        <v>5.159217958001449</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -28918,16 +28918,16 @@
         <v>1</v>
       </c>
       <c r="M376" t="n">
-        <v>-0.6148917451122378</v>
+        <v>-0.6082820419985513</v>
       </c>
       <c r="N376" t="n">
-        <v>0.6148917451122378</v>
+        <v>0.6082820419985513</v>
       </c>
       <c r="O376" t="n">
         <v>0.3774999999999995</v>
       </c>
       <c r="P376" t="n">
-        <v>-0.05726140477914576</v>
+        <v>-0.04858616944243277</v>
       </c>
       <c r="Q376" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
       </c>
       <c r="R376" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S376" t="b">
@@ -28956,7 +28956,7 @@
         <v>9</v>
       </c>
       <c r="D377" t="n">
-        <v>11107.5400390625</v>
+        <v>11107.4580078125</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>0.2025000000000006</v>
       </c>
       <c r="P377" t="n">
-        <v>-0.03340115858073833</v>
+        <v>-0.0400108616944248</v>
       </c>
       <c r="Q377" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>9</v>
       </c>
       <c r="D378" t="n">
-        <v>10973.126953125</v>
+        <v>10970</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>9</v>
       </c>
       <c r="D379" t="n">
-        <v>10939.720703125</v>
+        <v>10935.080078125</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -29180,10 +29180,10 @@
         <v>9</v>
       </c>
       <c r="G380" t="n">
-        <v>0.664011585807386</v>
+        <v>0.664735698769008</v>
       </c>
       <c r="H380" t="n">
-        <v>5.069093048515569</v>
+        <v>5.07231716147719</v>
       </c>
       <c r="I380" t="inlineStr">
         <is>
@@ -29202,16 +29202,16 @@
         <v>1</v>
       </c>
       <c r="M380" t="n">
-        <v>-1.265906951484431</v>
+        <v>-1.26268283852281</v>
       </c>
       <c r="N380" t="n">
-        <v>1.265906951484431</v>
+        <v>1.26268283852281</v>
       </c>
       <c r="O380" t="n">
         <v>0.002500000000000391</v>
       </c>
       <c r="P380" t="n">
-        <v>0.02134141926140565</v>
+        <v>0.02456553222302649</v>
       </c>
       <c r="Q380" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>9</v>
       </c>
       <c r="D381" t="n">
-        <v>11122.02734375</v>
+        <v>11120</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>-0.2450000000000001</v>
       </c>
       <c r="P381" t="n">
-        <v>0.06253475742215731</v>
+        <v>0.05931064446053647</v>
       </c>
       <c r="Q381" t="inlineStr">
         <is>
@@ -29322,10 +29322,10 @@
         <v>9</v>
       </c>
       <c r="G382" t="n">
-        <v>0.7031136857349747</v>
+        <v>0.7038377986965967</v>
       </c>
       <c r="H382" t="n">
-        <v>5.229126357711803</v>
+        <v>5.229539464156408</v>
       </c>
       <c r="I382" t="inlineStr">
         <is>
@@ -29344,16 +29344,16 @@
         <v>1</v>
       </c>
       <c r="M382" t="n">
-        <v>-0.5658736422881967</v>
+        <v>-0.5654605358435916</v>
       </c>
       <c r="N382" t="n">
-        <v>0.5658736422881967</v>
+        <v>0.5654605358435916</v>
       </c>
       <c r="O382" t="n">
         <v>-0.2949999999999999</v>
       </c>
       <c r="P382" t="n">
-        <v>0.09749855177407696</v>
+        <v>0.09791165821868208</v>
       </c>
       <c r="Q382" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>9</v>
       </c>
       <c r="D383" t="n">
-        <v>11560</v>
+        <v>11557.029296875</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>-0.2850000000000001</v>
       </c>
       <c r="P383" t="n">
-        <v>0.05908653149891396</v>
+        <v>0.05867342505430884</v>
       </c>
       <c r="Q383" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>9</v>
       </c>
       <c r="D386" t="n">
-        <v>11497.416015625</v>
+        <v>11490</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>10</v>
       </c>
       <c r="D387" t="n">
-        <v>11740</v>
+        <v>11730</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -29677,10 +29677,10 @@
         <v>10</v>
       </c>
       <c r="G387" t="n">
-        <v>0.6502849002849003</v>
+        <v>0.6498220640569395</v>
       </c>
       <c r="H387" t="n">
-        <v>5.882852564102564</v>
+        <v>5.880249110320285</v>
       </c>
       <c r="I387" t="inlineStr">
         <is>
@@ -29699,16 +29699,16 @@
         <v>1</v>
       </c>
       <c r="M387" t="n">
-        <v>0.9478525641025648</v>
+        <v>0.9452491103202849</v>
       </c>
       <c r="N387" t="n">
-        <v>0.9478525641025648</v>
+        <v>0.9452491103202849</v>
       </c>
       <c r="O387" t="n">
         <v>-0.1124999999999998</v>
       </c>
       <c r="P387" t="n">
-        <v>0.6138717530960474</v>
+        <v>0.6112682993137675</v>
       </c>
       <c r="Q387" t="inlineStr">
         <is>
@@ -29748,10 +29748,10 @@
         <v>10</v>
       </c>
       <c r="G388" t="n">
-        <v>0.6431623931623932</v>
+        <v>0.6427046263345195</v>
       </c>
       <c r="H388" t="n">
-        <v>5.847596153846154</v>
+        <v>5.846737841043891</v>
       </c>
       <c r="I388" t="inlineStr">
         <is>
@@ -29770,16 +29770,16 @@
         <v>1</v>
       </c>
       <c r="M388" t="n">
-        <v>0.945096153846154</v>
+        <v>0.9442378410438907</v>
       </c>
       <c r="N388" t="n">
-        <v>0.945096153846154</v>
+        <v>0.9442378410438907</v>
       </c>
       <c r="O388" t="n">
         <v>-0.03249999999999975</v>
       </c>
       <c r="P388" t="n">
-        <v>-0.03525641025641058</v>
+        <v>-0.03351126927639392</v>
       </c>
       <c r="Q388" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>10</v>
       </c>
       <c r="D389" t="n">
-        <v>11700</v>
+        <v>11680</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -29819,10 +29819,10 @@
         <v>10</v>
       </c>
       <c r="G389" t="n">
-        <v>0.6452991452991453</v>
+        <v>0.6448398576512455</v>
       </c>
       <c r="H389" t="n">
-        <v>5.857692307692308</v>
+        <v>5.853558718861209</v>
       </c>
       <c r="I389" t="inlineStr">
         <is>
@@ -29841,16 +29841,16 @@
         <v>1</v>
       </c>
       <c r="M389" t="n">
-        <v>1.010192307692308</v>
+        <v>1.006058718861209</v>
       </c>
       <c r="N389" t="n">
-        <v>1.010192307692308</v>
+        <v>1.006058718861209</v>
       </c>
       <c r="O389" t="n">
         <v>-0.05499999999999972</v>
       </c>
       <c r="P389" t="n">
-        <v>0.01009615384615437</v>
+        <v>0.00682087781731866</v>
       </c>
       <c r="Q389" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>10</v>
       </c>
       <c r="D390" t="n">
-        <v>11840</v>
+        <v>11830</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -29890,10 +29890,10 @@
         <v>10</v>
       </c>
       <c r="G390" t="n">
-        <v>0.6652421652421653</v>
+        <v>0.6626334519572954</v>
       </c>
       <c r="H390" t="n">
-        <v>5.918794871794872</v>
+        <v>5.909820877817319</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
@@ -29912,16 +29912,16 @@
         <v>1</v>
       </c>
       <c r="M390" t="n">
-        <v>1.211294871794872</v>
+        <v>1.20232087781732</v>
       </c>
       <c r="N390" t="n">
-        <v>1.211294871794872</v>
+        <v>1.20232087781732</v>
       </c>
       <c r="O390" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P390" t="n">
-        <v>0.06110256410256376</v>
+        <v>0.05626215895610986</v>
       </c>
       <c r="Q390" t="inlineStr">
         <is>
@@ -29961,10 +29961,10 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>0.7065527065527065</v>
+        <v>0.706049822064057</v>
       </c>
       <c r="H391" t="n">
-        <v>6.064358974358974</v>
+        <v>6.06153024911032</v>
       </c>
       <c r="I391" t="inlineStr">
         <is>
@@ -29983,16 +29983,16 @@
         <v>1</v>
       </c>
       <c r="M391" t="n">
-        <v>1.416858974358974</v>
+        <v>1.41403024911032</v>
       </c>
       <c r="N391" t="n">
-        <v>1.416858974358974</v>
+        <v>1.41403024911032</v>
       </c>
       <c r="O391" t="n">
         <v>-0.05999999999999961</v>
       </c>
       <c r="P391" t="n">
-        <v>0.1455641025641023</v>
+        <v>0.1517093712930011</v>
       </c>
       <c r="Q391" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>10</v>
       </c>
       <c r="D392" t="n">
-        <v>12550</v>
+        <v>12540</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -30032,10 +30032,10 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>0.7535612535612536</v>
+        <v>0.7530249110320285</v>
       </c>
       <c r="H392" t="n">
-        <v>6.276794871794872</v>
+        <v>6.275932892730046</v>
       </c>
       <c r="I392" t="inlineStr">
         <is>
@@ -30054,16 +30054,16 @@
         <v>1</v>
       </c>
       <c r="M392" t="n">
-        <v>1.489294871794872</v>
+        <v>1.488432892730046</v>
       </c>
       <c r="N392" t="n">
-        <v>1.489294871794872</v>
+        <v>1.488432892730046</v>
       </c>
       <c r="O392" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P392" t="n">
-        <v>0.2124358974358973</v>
+        <v>0.2144026436197253</v>
       </c>
       <c r="Q392" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>10</v>
       </c>
       <c r="D393" t="n">
-        <v>12930</v>
+        <v>12920</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
@@ -30103,10 +30103,10 @@
         <v>10</v>
       </c>
       <c r="G393" t="n">
-        <v>0.7863247863247863</v>
+        <v>0.7850533807829182</v>
       </c>
       <c r="H393" t="n">
-        <v>6.413269230769231</v>
+        <v>6.411481316725979</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -30125,16 +30125,16 @@
         <v>1</v>
       </c>
       <c r="M393" t="n">
-        <v>1.373269230769232</v>
+        <v>1.37148131672598</v>
       </c>
       <c r="N393" t="n">
-        <v>1.373269230769232</v>
+        <v>1.37148131672598</v>
       </c>
       <c r="O393" t="n">
         <v>0.2524999999999995</v>
       </c>
       <c r="P393" t="n">
-        <v>0.1364743589743593</v>
+        <v>0.1355484239959335</v>
       </c>
       <c r="Q393" t="inlineStr">
         <is>
@@ -30174,10 +30174,10 @@
         <v>10</v>
       </c>
       <c r="G394" t="n">
-        <v>0.8041310541310541</v>
+        <v>0.80355871886121</v>
       </c>
       <c r="H394" t="n">
-        <v>6.492532051282051</v>
+        <v>6.488024911032029</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -30196,16 +30196,16 @@
         <v>1</v>
       </c>
       <c r="M394" t="n">
-        <v>1.432532051282052</v>
+        <v>1.428024911032029</v>
       </c>
       <c r="N394" t="n">
-        <v>1.432532051282052</v>
+        <v>1.428024911032029</v>
       </c>
       <c r="O394" t="n">
         <v>0.02000000000000046</v>
       </c>
       <c r="P394" t="n">
-        <v>0.0792628205128203</v>
+        <v>0.07654359430604973</v>
       </c>
       <c r="Q394" t="inlineStr">
         <is>
@@ -31801,10 +31801,10 @@
         <v>10</v>
       </c>
       <c r="G417" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.6106761565836299</v>
       </c>
       <c r="H417" t="n">
-        <v>6.838</v>
+        <v>6.835500355871886</v>
       </c>
       <c r="I417" t="inlineStr">
         <is>
@@ -31823,16 +31823,16 @@
         <v>1</v>
       </c>
       <c r="M417" t="n">
-        <v>0.6779999999999999</v>
+        <v>0.6755003558718862</v>
       </c>
       <c r="N417" t="n">
-        <v>0.6779999999999999</v>
+        <v>0.6755003558718862</v>
       </c>
       <c r="O417" t="n">
         <v>-0.04250000000000043</v>
       </c>
       <c r="P417" t="n">
-        <v>0.4252483707458365</v>
+        <v>0.4227487266177228</v>
       </c>
       <c r="Q417" t="inlineStr">
         <is>
@@ -31872,10 +31872,10 @@
         <v>10</v>
       </c>
       <c r="G418" t="n">
-        <v>0.6339031339031339</v>
+        <v>0.6334519572953736</v>
       </c>
       <c r="H418" t="n">
-        <v>6.951595441595442</v>
+        <v>6.949110320284698</v>
       </c>
       <c r="I418" t="inlineStr">
         <is>
@@ -31894,16 +31894,16 @@
         <v>1</v>
       </c>
       <c r="M418" t="n">
-        <v>0.8065954415954426</v>
+        <v>0.804110320284698</v>
       </c>
       <c r="N418" t="n">
-        <v>0.8065954415954426</v>
+        <v>0.804110320284698</v>
       </c>
       <c r="O418" t="n">
         <v>-0.01500000000000057</v>
       </c>
       <c r="P418" t="n">
-        <v>0.1135954415954421</v>
+        <v>0.1136099644128112</v>
       </c>
       <c r="Q418" t="inlineStr">
         <is>
@@ -31943,10 +31943,10 @@
         <v>10</v>
       </c>
       <c r="G419" t="n">
-        <v>0.6951566951566952</v>
+        <v>0.6946619217081851</v>
       </c>
       <c r="H419" t="n">
-        <v>7.231977207977208</v>
+        <v>7.231607117437723</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>
@@ -31965,16 +31965,16 @@
         <v>1</v>
       </c>
       <c r="M419" t="n">
-        <v>1.029477207977209</v>
+        <v>1.029107117437723</v>
       </c>
       <c r="N419" t="n">
-        <v>1.029477207977209</v>
+        <v>1.029107117437723</v>
       </c>
       <c r="O419" t="n">
         <v>0.05750000000000011</v>
       </c>
       <c r="P419" t="n">
-        <v>0.2803817663817663</v>
+        <v>0.2824967971530254</v>
       </c>
       <c r="Q419" t="inlineStr">
         <is>
@@ -32014,10 +32014,10 @@
         <v>10</v>
       </c>
       <c r="G420" t="n">
-        <v>0.7685185185185185</v>
+        <v>0.7679715302491104</v>
       </c>
       <c r="H420" t="n">
-        <v>7.581703703703703</v>
+        <v>7.580885409252669</v>
       </c>
       <c r="I420" t="inlineStr">
         <is>
@@ -32036,16 +32036,16 @@
         <v>1</v>
       </c>
       <c r="M420" t="n">
-        <v>1.381703703703703</v>
+        <v>1.380885409252669</v>
       </c>
       <c r="N420" t="n">
-        <v>1.381703703703703</v>
+        <v>1.380885409252669</v>
       </c>
       <c r="O420" t="n">
         <v>-0.002499999999999503</v>
       </c>
       <c r="P420" t="n">
-        <v>0.3497264957264949</v>
+        <v>0.3492782918149464</v>
       </c>
       <c r="Q420" t="inlineStr">
         <is>
@@ -32085,10 +32085,10 @@
         <v>10</v>
       </c>
       <c r="G421" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.8199288256227758</v>
       </c>
       <c r="H421" t="n">
-        <v>7.861487179487179</v>
+        <v>7.860613523131673</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
@@ -32107,16 +32107,16 @@
         <v>1</v>
       </c>
       <c r="M421" t="n">
-        <v>1.721487179487179</v>
+        <v>1.720613523131672</v>
       </c>
       <c r="N421" t="n">
-        <v>1.721487179487179</v>
+        <v>1.720613523131672</v>
       </c>
       <c r="O421" t="n">
         <v>-0.05999999999999961</v>
       </c>
       <c r="P421" t="n">
-        <v>0.2797834757834758</v>
+        <v>0.2797281138790035</v>
       </c>
       <c r="Q421" t="inlineStr">
         <is>
@@ -32156,10 +32156,10 @@
         <v>10</v>
       </c>
       <c r="G422" t="n">
-        <v>0.8625356125356125</v>
+        <v>0.8619217081850534</v>
       </c>
       <c r="H422" t="n">
-        <v>8.095883190883189</v>
+        <v>8.091326690391458</v>
       </c>
       <c r="I422" t="inlineStr">
         <is>
@@ -32178,16 +32178,16 @@
         <v>1</v>
       </c>
       <c r="M422" t="n">
-        <v>1.85588319088319</v>
+        <v>1.851326690391459</v>
       </c>
       <c r="N422" t="n">
-        <v>1.85588319088319</v>
+        <v>1.851326690391459</v>
       </c>
       <c r="O422" t="n">
         <v>0.09999999999999876</v>
       </c>
       <c r="P422" t="n">
-        <v>0.2343960113960097</v>
+        <v>0.2307131672597853</v>
       </c>
       <c r="Q422" t="inlineStr">
         <is>
@@ -32227,10 +32227,10 @@
         <v>10</v>
       </c>
       <c r="G423" t="n">
-        <v>0.8774928774928775</v>
+        <v>0.8768683274021353</v>
       </c>
       <c r="H423" t="n">
-        <v>8.169116809116812</v>
+        <v>8.159487544483985</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -32249,16 +32249,16 @@
         <v>1</v>
       </c>
       <c r="M423" t="n">
-        <v>1.574116809116811</v>
+        <v>1.564487544483985</v>
       </c>
       <c r="N423" t="n">
-        <v>1.574116809116811</v>
+        <v>1.564487544483985</v>
       </c>
       <c r="O423" t="n">
         <v>0.3550000000000013</v>
       </c>
       <c r="P423" t="n">
-        <v>0.07323361823362262</v>
+        <v>0.06816085409252715</v>
       </c>
       <c r="Q423" t="inlineStr">
         <is>
@@ -32298,10 +32298,10 @@
         <v>10</v>
       </c>
       <c r="G424" t="n">
-        <v>0.8874643874643875</v>
+        <v>0.8868327402135231</v>
       </c>
       <c r="H424" t="n">
-        <v>8.216862298195633</v>
+        <v>8.215602372479241</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -32320,16 +32320,16 @@
         <v>1</v>
       </c>
       <c r="M424" t="n">
-        <v>1.506862298195633</v>
+        <v>1.505602372479241</v>
       </c>
       <c r="N424" t="n">
-        <v>1.506862298195633</v>
+        <v>1.505602372479241</v>
       </c>
       <c r="O424" t="n">
         <v>0.1149999999999993</v>
       </c>
       <c r="P424" t="n">
-        <v>0.04774548907882092</v>
+        <v>0.05611482799525547</v>
       </c>
       <c r="Q424" t="inlineStr">
         <is>
@@ -32338,11 +32338,11 @@
       </c>
       <c r="R424" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S424" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425">
@@ -33925,10 +33925,10 @@
         <v>10</v>
       </c>
       <c r="G447" t="n">
-        <v>0.6424501424501424</v>
+        <v>0.6427046263345195</v>
       </c>
       <c r="H447" t="n">
-        <v>6.145384615384614</v>
+        <v>6.146483985765124</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
@@ -33947,16 +33947,16 @@
         <v>1</v>
       </c>
       <c r="M447" t="n">
-        <v>2.385384615384615</v>
+        <v>2.386483985765124</v>
       </c>
       <c r="N447" t="n">
-        <v>2.385384615384615</v>
+        <v>2.386483985765124</v>
       </c>
       <c r="O447" t="n">
         <v>-0.4550000000000001</v>
       </c>
       <c r="P447" t="n">
-        <v>-0.04054876622291648</v>
+        <v>-0.03944939584240714</v>
       </c>
       <c r="Q447" t="inlineStr">
         <is>
@@ -33996,10 +33996,10 @@
         <v>10</v>
       </c>
       <c r="G448" t="n">
-        <v>0.4252136752136752</v>
+        <v>0.4256227758007117</v>
       </c>
       <c r="H448" t="n">
-        <v>5.434615384615385</v>
+        <v>5.43579359430605</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
@@ -34018,16 +34018,16 @@
         <v>1</v>
       </c>
       <c r="M448" t="n">
-        <v>1.894615384615385</v>
+        <v>1.89579359430605</v>
       </c>
       <c r="N448" t="n">
-        <v>1.894615384615385</v>
+        <v>1.89579359430605</v>
       </c>
       <c r="O448" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P448" t="n">
-        <v>-0.7107692307692295</v>
+        <v>-0.7106903914590736</v>
       </c>
       <c r="Q448" t="inlineStr">
         <is>
@@ -34067,10 +34067,10 @@
         <v>10</v>
       </c>
       <c r="G449" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.306049822064057</v>
       </c>
       <c r="H449" t="n">
-        <v>4.37</v>
+        <v>4.411281138790035</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
@@ -34089,16 +34089,16 @@
         <v>1</v>
       </c>
       <c r="M449" t="n">
-        <v>0.96</v>
+        <v>1.001281138790035</v>
       </c>
       <c r="N449" t="n">
-        <v>0.96</v>
+        <v>1.001281138790035</v>
       </c>
       <c r="O449" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P449" t="n">
-        <v>-1.064615384615385</v>
+        <v>-1.024512455516015</v>
       </c>
       <c r="Q449" t="inlineStr">
         <is>
@@ -34138,10 +34138,10 @@
         <v>10</v>
       </c>
       <c r="G450" t="n">
-        <v>0.2770655270655271</v>
+        <v>0.2775800711743772</v>
       </c>
       <c r="H450" t="n">
-        <v>4.011794871794871</v>
+        <v>4.017722419928825</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
@@ -34160,16 +34160,16 @@
         <v>1</v>
       </c>
       <c r="M450" t="n">
-        <v>0.6317948717948711</v>
+        <v>0.6377224199288252</v>
       </c>
       <c r="N450" t="n">
-        <v>0.6317948717948711</v>
+        <v>0.6377224199288252</v>
       </c>
       <c r="O450" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P450" t="n">
-        <v>-0.3582051282051291</v>
+        <v>-0.3935587188612102</v>
       </c>
       <c r="Q450" t="inlineStr">
         <is>
@@ -34209,10 +34209,10 @@
         <v>10</v>
       </c>
       <c r="G451" t="n">
-        <v>0.3233618233618233</v>
+        <v>0.3238434163701068</v>
       </c>
       <c r="H451" t="n">
-        <v>4.755213675213675</v>
+        <v>4.755444839857651</v>
       </c>
       <c r="I451" t="inlineStr">
         <is>
@@ -34231,16 +34231,16 @@
         <v>1</v>
       </c>
       <c r="M451" t="n">
-        <v>1.340213675213675</v>
+        <v>1.340444839857651</v>
       </c>
       <c r="N451" t="n">
-        <v>1.340213675213675</v>
+        <v>1.340444839857651</v>
       </c>
       <c r="O451" t="n">
         <v>0.03500000000000014</v>
       </c>
       <c r="P451" t="n">
-        <v>0.7434188034188036</v>
+        <v>0.7377224199288257</v>
       </c>
       <c r="Q451" t="inlineStr">
         <is>
@@ -34280,10 +34280,10 @@
         <v>10</v>
       </c>
       <c r="G452" t="n">
-        <v>0.3917378917378918</v>
+        <v>0.3921708185053381</v>
       </c>
       <c r="H452" t="n">
-        <v>5.282820512820513</v>
+        <v>5.287807829181495</v>
       </c>
       <c r="I452" t="inlineStr">
         <is>
@@ -34302,16 +34302,16 @@
         <v>1</v>
       </c>
       <c r="M452" t="n">
-        <v>1.817820512820513</v>
+        <v>1.822807829181495</v>
       </c>
       <c r="N452" t="n">
-        <v>1.817820512820513</v>
+        <v>1.822807829181495</v>
       </c>
       <c r="O452" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P452" t="n">
-        <v>0.5276068376068386</v>
+        <v>0.5323629893238442</v>
       </c>
       <c r="Q452" t="inlineStr">
         <is>
@@ -34351,10 +34351,10 @@
         <v>10</v>
       </c>
       <c r="G453" t="n">
-        <v>0.3653846153846154</v>
+        <v>0.3658362989323843</v>
       </c>
       <c r="H453" t="n">
-        <v>5.095384615384615</v>
+        <v>5.101238434163701</v>
       </c>
       <c r="I453" t="inlineStr">
         <is>
@@ -34373,16 +34373,16 @@
         <v>1</v>
       </c>
       <c r="M453" t="n">
-        <v>1.672884615384615</v>
+        <v>1.678738434163701</v>
       </c>
       <c r="N453" t="n">
-        <v>1.672884615384615</v>
+        <v>1.678738434163701</v>
       </c>
       <c r="O453" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P453" t="n">
-        <v>-0.1874358974358987</v>
+        <v>-0.186569395017794</v>
       </c>
       <c r="Q453" t="inlineStr">
         <is>
@@ -34422,10 +34422,10 @@
         <v>10</v>
       </c>
       <c r="G454" t="n">
-        <v>0.2713675213675213</v>
+        <v>0.2718861209964413</v>
       </c>
       <c r="H454" t="n">
-        <v>3.975769230769231</v>
+        <v>3.976516014234875</v>
       </c>
       <c r="I454" t="inlineStr">
         <is>
@@ -34444,16 +34444,16 @@
         <v>1</v>
       </c>
       <c r="M454" t="n">
-        <v>0.7557692307692303</v>
+        <v>0.756516014234875</v>
       </c>
       <c r="N454" t="n">
-        <v>0.7557692307692303</v>
+        <v>0.756516014234875</v>
       </c>
       <c r="O454" t="n">
         <v>-0.2024999999999997</v>
       </c>
       <c r="P454" t="n">
-        <v>-1.119615384615384</v>
+        <v>-1.124722419928826</v>
       </c>
       <c r="Q454" t="inlineStr">
         <is>
@@ -36049,10 +36049,10 @@
         <v>10</v>
       </c>
       <c r="G477" t="n">
-        <v>0.7450142450142451</v>
+        <v>0.7451957295373666</v>
       </c>
       <c r="H477" t="n">
-        <v>3.625156695156695</v>
+        <v>3.625879003558719</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -36071,16 +36071,16 @@
         <v>1</v>
       </c>
       <c r="M477" t="n">
-        <v>-0.1823433048433047</v>
+        <v>-0.1816209964412812</v>
       </c>
       <c r="N477" t="n">
-        <v>0.1823433048433047</v>
+        <v>0.1816209964412812</v>
       </c>
       <c r="O477" t="n">
         <v>-0.105</v>
       </c>
       <c r="P477" t="n">
-        <v>0.4705759565614747</v>
+        <v>0.4712982649634982</v>
       </c>
       <c r="Q477" t="inlineStr">
         <is>
@@ -36120,10 +36120,10 @@
         <v>10</v>
       </c>
       <c r="G478" t="n">
-        <v>0.7371794871794872</v>
+        <v>0.7373665480427046</v>
       </c>
       <c r="H478" t="n">
-        <v>3.598974358974359</v>
+        <v>3.599718861209964</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
@@ -36142,16 +36142,16 @@
         <v>1</v>
       </c>
       <c r="M478" t="n">
-        <v>-0.07352564102564063</v>
+        <v>-0.07278113879003545</v>
       </c>
       <c r="N478" t="n">
-        <v>0.07352564102564063</v>
+        <v>0.07278113879003545</v>
       </c>
       <c r="O478" t="n">
         <v>-0.1350000000000002</v>
       </c>
       <c r="P478" t="n">
-        <v>-0.02618233618233612</v>
+        <v>-0.02616014234875452</v>
       </c>
       <c r="Q478" t="inlineStr">
         <is>
@@ -36191,10 +36191,10 @@
         <v>10</v>
       </c>
       <c r="G479" t="n">
-        <v>0.7393162393162394</v>
+        <v>0.7395017793594306</v>
       </c>
       <c r="H479" t="n">
-        <v>3.607478632478633</v>
+        <v>3.608217081850534</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
@@ -36213,16 +36213,16 @@
         <v>1</v>
       </c>
       <c r="M479" t="n">
-        <v>0.04997863247863243</v>
+        <v>0.05071708185053403</v>
       </c>
       <c r="N479" t="n">
-        <v>0.04997863247863243</v>
+        <v>0.05071708185053403</v>
       </c>
       <c r="O479" t="n">
         <v>-0.1149999999999998</v>
       </c>
       <c r="P479" t="n">
-        <v>0.008504273504273296</v>
+        <v>0.008498220640569709</v>
       </c>
       <c r="Q479" t="inlineStr">
         <is>
@@ -36262,10 +36262,10 @@
         <v>10</v>
       </c>
       <c r="G480" t="n">
-        <v>0.7414529914529915</v>
+        <v>0.7416370106761566</v>
       </c>
       <c r="H480" t="n">
-        <v>3.613988603988604</v>
+        <v>3.614476868327402</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
@@ -36284,16 +36284,16 @@
         <v>1</v>
       </c>
       <c r="M480" t="n">
-        <v>0.2214886039886039</v>
+        <v>0.2219768683274022</v>
       </c>
       <c r="N480" t="n">
-        <v>0.2214886039886039</v>
+        <v>0.2219768683274022</v>
       </c>
       <c r="O480" t="n">
         <v>-0.165</v>
       </c>
       <c r="P480" t="n">
-        <v>0.006509971509971457</v>
+        <v>0.00625978647686809</v>
       </c>
       <c r="Q480" t="inlineStr">
         <is>
@@ -36333,10 +36333,10 @@
         <v>10</v>
       </c>
       <c r="G481" t="n">
-        <v>0.7478632478632479</v>
+        <v>0.7480427046263345</v>
       </c>
       <c r="H481" t="n">
-        <v>3.633247863247863</v>
+        <v>3.633604982206406</v>
       </c>
       <c r="I481" t="inlineStr">
         <is>
@@ -36355,16 +36355,16 @@
         <v>1</v>
       </c>
       <c r="M481" t="n">
-        <v>0.3707478632478631</v>
+        <v>0.3711049822064054</v>
       </c>
       <c r="N481" t="n">
-        <v>0.3707478632478631</v>
+        <v>0.3711049822064054</v>
       </c>
       <c r="O481" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P481" t="n">
-        <v>0.01925925925925931</v>
+        <v>0.01912811387900337</v>
       </c>
       <c r="Q481" t="inlineStr">
         <is>
@@ -36404,10 +36404,10 @@
         <v>10</v>
       </c>
       <c r="G482" t="n">
-        <v>0.7578347578347578</v>
+        <v>0.7580071174377224</v>
       </c>
       <c r="H482" t="n">
-        <v>3.670591168091168</v>
+        <v>3.670934163701068</v>
       </c>
       <c r="I482" t="inlineStr">
         <is>
@@ -36426,16 +36426,16 @@
         <v>1</v>
       </c>
       <c r="M482" t="n">
-        <v>0.5555911680911678</v>
+        <v>0.5559341637010675</v>
       </c>
       <c r="N482" t="n">
-        <v>0.5555911680911678</v>
+        <v>0.5559341637010675</v>
       </c>
       <c r="O482" t="n">
         <v>-0.1475</v>
       </c>
       <c r="P482" t="n">
-        <v>0.03734330484330473</v>
+        <v>0.03732918149466213</v>
       </c>
       <c r="Q482" t="inlineStr">
         <is>
@@ -36475,10 +36475,10 @@
         <v>10</v>
       </c>
       <c r="G483" t="n">
-        <v>0.7649572649572649</v>
+        <v>0.7651245551601423</v>
       </c>
       <c r="H483" t="n">
-        <v>3.704529914529914</v>
+        <v>3.705195729537367</v>
       </c>
       <c r="I483" t="inlineStr">
         <is>
@@ -36497,16 +36497,16 @@
         <v>1</v>
       </c>
       <c r="M483" t="n">
-        <v>0.8320299145299144</v>
+        <v>0.8326957295373667</v>
       </c>
       <c r="N483" t="n">
-        <v>0.8320299145299144</v>
+        <v>0.8326957295373667</v>
       </c>
       <c r="O483" t="n">
         <v>-0.2425000000000002</v>
       </c>
       <c r="P483" t="n">
-        <v>0.03393874643874639</v>
+        <v>0.03426156583629902</v>
       </c>
       <c r="Q483" t="inlineStr">
         <is>
@@ -36546,10 +36546,10 @@
         <v>10</v>
       </c>
       <c r="G484" t="n">
-        <v>0.7542735042735043</v>
+        <v>0.7544483985765125</v>
       </c>
       <c r="H484" t="n">
-        <v>3.660803418803419</v>
+        <v>3.661081850533808</v>
       </c>
       <c r="I484" t="inlineStr">
         <is>
@@ -36568,16 +36568,16 @@
         <v>1</v>
       </c>
       <c r="M484" t="n">
-        <v>0.9108034188034186</v>
+        <v>0.9110818505338076</v>
       </c>
       <c r="N484" t="n">
-        <v>0.9108034188034186</v>
+        <v>0.9110818505338076</v>
       </c>
       <c r="O484" t="n">
         <v>-0.1225000000000001</v>
       </c>
       <c r="P484" t="n">
-        <v>-0.04372649572649578</v>
+        <v>-0.04411387900355912</v>
       </c>
       <c r="Q484" t="inlineStr">
         <is>
@@ -38173,10 +38173,10 @@
         <v>10</v>
       </c>
       <c r="G507" t="n">
-        <v>0.7072649572649573</v>
+        <v>0.7067615658362989</v>
       </c>
       <c r="H507" t="n">
-        <v>2.645224358974359</v>
+        <v>2.642750889679715</v>
       </c>
       <c r="I507" t="inlineStr">
         <is>
@@ -38195,16 +38195,16 @@
         <v>1</v>
       </c>
       <c r="M507" t="n">
-        <v>0.495224358974359</v>
+        <v>0.4927508896797153</v>
       </c>
       <c r="N507" t="n">
-        <v>0.495224358974359</v>
+        <v>0.4927508896797153</v>
       </c>
       <c r="O507" t="n">
         <v>-0.1074999999999999</v>
       </c>
       <c r="P507" t="n">
-        <v>0.6226827224790661</v>
+        <v>0.6202092531844223</v>
       </c>
       <c r="Q507" t="inlineStr">
         <is>
@@ -38244,10 +38244,10 @@
         <v>10</v>
       </c>
       <c r="G508" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.693950177935943</v>
       </c>
       <c r="H508" t="n">
-        <v>2.5965625</v>
+        <v>2.595845195729538</v>
       </c>
       <c r="I508" t="inlineStr">
         <is>
@@ -38266,16 +38266,16 @@
         <v>1</v>
       </c>
       <c r="M508" t="n">
-        <v>0.5065625000000002</v>
+        <v>0.5058451957295378</v>
       </c>
       <c r="N508" t="n">
-        <v>0.5065625000000002</v>
+        <v>0.5058451957295378</v>
       </c>
       <c r="O508" t="n">
         <v>-0.06000000000000005</v>
       </c>
       <c r="P508" t="n">
-        <v>-0.04866185897435882</v>
+        <v>-0.04690569395017752</v>
       </c>
       <c r="Q508" t="inlineStr">
         <is>
@@ -38315,10 +38315,10 @@
         <v>10</v>
       </c>
       <c r="G509" t="n">
-        <v>0.6851851851851852</v>
+        <v>0.6846975088967971</v>
       </c>
       <c r="H509" t="n">
-        <v>2.561</v>
+        <v>2.559779359430605</v>
       </c>
       <c r="I509" t="inlineStr">
         <is>
@@ -38337,16 +38337,16 @@
         <v>1</v>
       </c>
       <c r="M509" t="n">
-        <v>0.5135000000000001</v>
+        <v>0.5122793594306052</v>
       </c>
       <c r="N509" t="n">
-        <v>0.5135000000000001</v>
+        <v>0.5122793594306052</v>
       </c>
       <c r="O509" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P509" t="n">
-        <v>-0.03556250000000016</v>
+        <v>-0.03606583629893256</v>
       </c>
       <c r="Q509" t="inlineStr">
         <is>
@@ -38386,10 +38386,10 @@
         <v>10</v>
       </c>
       <c r="G510" t="n">
-        <v>0.6830484330484331</v>
+        <v>0.6825622775800712</v>
       </c>
       <c r="H510" t="n">
-        <v>2.553397435897436</v>
+        <v>2.551516014234875</v>
       </c>
       <c r="I510" t="inlineStr">
         <is>
@@ -38408,16 +38408,16 @@
         <v>1</v>
       </c>
       <c r="M510" t="n">
-        <v>0.6808974358974362</v>
+        <v>0.6790160142348753</v>
       </c>
       <c r="N510" t="n">
-        <v>0.6808974358974362</v>
+        <v>0.6790160142348753</v>
       </c>
       <c r="O510" t="n">
         <v>-0.1749999999999998</v>
       </c>
       <c r="P510" t="n">
-        <v>-0.007602564102563658</v>
+        <v>-0.008263345195729688</v>
       </c>
       <c r="Q510" t="inlineStr">
         <is>
@@ -38457,10 +38457,10 @@
         <v>10</v>
       </c>
       <c r="G511" t="n">
-        <v>0.6894586894586895</v>
+        <v>0.6889679715302491</v>
       </c>
       <c r="H511" t="n">
-        <v>2.578076923076923</v>
+        <v>2.577364768683274</v>
       </c>
       <c r="I511" t="inlineStr">
         <is>
@@ -38479,16 +38479,16 @@
         <v>1</v>
       </c>
       <c r="M511" t="n">
-        <v>0.8105769230769231</v>
+        <v>0.8098647686832741</v>
       </c>
       <c r="N511" t="n">
-        <v>0.8105769230769231</v>
+        <v>0.8098647686832741</v>
       </c>
       <c r="O511" t="n">
         <v>-0.105</v>
       </c>
       <c r="P511" t="n">
-        <v>0.02467948717948687</v>
+        <v>0.02584875444839874</v>
       </c>
       <c r="Q511" t="inlineStr">
         <is>
@@ -38528,10 +38528,10 @@
         <v>10</v>
       </c>
       <c r="G512" t="n">
-        <v>0.7150997150997151</v>
+        <v>0.7145907473309608</v>
       </c>
       <c r="H512" t="n">
-        <v>2.677788461538462</v>
+        <v>2.677049822064057</v>
       </c>
       <c r="I512" t="inlineStr">
         <is>
@@ -38550,16 +38550,16 @@
         <v>1</v>
       </c>
       <c r="M512" t="n">
-        <v>0.9327884615384616</v>
+        <v>0.932049822064057</v>
       </c>
       <c r="N512" t="n">
-        <v>0.9327884615384616</v>
+        <v>0.932049822064057</v>
       </c>
       <c r="O512" t="n">
         <v>-0.02249999999999996</v>
       </c>
       <c r="P512" t="n">
-        <v>0.09971153846153857</v>
+        <v>0.09968505338078293</v>
       </c>
       <c r="Q512" t="inlineStr">
         <is>
@@ -38599,10 +38599,10 @@
         <v>10</v>
       </c>
       <c r="G513" t="n">
-        <v>0.7386039886039886</v>
+        <v>0.7380782918149467</v>
       </c>
       <c r="H513" t="n">
-        <v>2.767596153846153</v>
+        <v>2.764544483985765</v>
       </c>
       <c r="I513" t="inlineStr">
         <is>
@@ -38621,16 +38621,16 @@
         <v>1</v>
       </c>
       <c r="M513" t="n">
-        <v>0.9650961538461533</v>
+        <v>0.9620444839857651</v>
       </c>
       <c r="N513" t="n">
-        <v>0.9650961538461533</v>
+        <v>0.9620444839857651</v>
       </c>
       <c r="O513" t="n">
         <v>0.05749999999999988</v>
       </c>
       <c r="P513" t="n">
-        <v>0.08980769230769159</v>
+        <v>0.08749466192170807</v>
       </c>
       <c r="Q513" t="inlineStr">
         <is>
@@ -38670,10 +38670,10 @@
         <v>10</v>
       </c>
       <c r="G514" t="n">
-        <v>0.7678062678062678</v>
+        <v>0.7672597864768683</v>
       </c>
       <c r="H514" t="n">
-        <v>2.877836538461539</v>
+        <v>2.875457295373665</v>
       </c>
       <c r="I514" t="inlineStr">
         <is>
@@ -38692,16 +38692,16 @@
         <v>1</v>
       </c>
       <c r="M514" t="n">
-        <v>0.9778365384615388</v>
+        <v>0.9754572953736655</v>
       </c>
       <c r="N514" t="n">
-        <v>0.9778365384615388</v>
+        <v>0.9754572953736655</v>
       </c>
       <c r="O514" t="n">
         <v>0.09749999999999992</v>
       </c>
       <c r="P514" t="n">
-        <v>0.1102403846153854</v>
+        <v>0.1109128113879003</v>
       </c>
       <c r="Q514" t="inlineStr">
         <is>
@@ -42847,10 +42847,10 @@
         <v>10</v>
       </c>
       <c r="G573" t="n">
-        <v>0.1723646723646724</v>
+        <v>0.1722419928825623</v>
       </c>
       <c r="H573" t="n">
-        <v>128.5538888888889</v>
+        <v>128.5506832740214</v>
       </c>
       <c r="I573" t="inlineStr">
         <is>
@@ -42869,16 +42869,16 @@
         <v>1</v>
       </c>
       <c r="M573" t="n">
-        <v>-1.046111111111088</v>
+        <v>-1.049316725978628</v>
       </c>
       <c r="N573" t="n">
-        <v>1.046111111111088</v>
+        <v>1.049316725978628</v>
       </c>
       <c r="O573" t="n">
         <v>0.4499999999999886</v>
       </c>
       <c r="P573" t="n">
-        <v>-0.2422782906911323</v>
+        <v>-0.2454839055586717</v>
       </c>
       <c r="Q573" t="inlineStr">
         <is>
@@ -42918,10 +42918,10 @@
         <v>10</v>
       </c>
       <c r="G574" t="n">
-        <v>0.2407407407407407</v>
+        <v>0.2412811387900356</v>
       </c>
       <c r="H574" t="n">
-        <v>128.8056172839506</v>
+        <v>128.8071862396204</v>
       </c>
       <c r="I574" t="inlineStr">
         <is>
@@ -42940,16 +42940,16 @@
         <v>1</v>
       </c>
       <c r="M574" t="n">
-        <v>-0.6543827160493834</v>
+        <v>-0.6528137603795869</v>
       </c>
       <c r="N574" t="n">
-        <v>0.6543827160493834</v>
+        <v>0.6528137603795869</v>
       </c>
       <c r="O574" t="n">
         <v>-0.1399999999999864</v>
       </c>
       <c r="P574" t="n">
-        <v>0.2517283950617184</v>
+        <v>0.2565029655990543</v>
       </c>
       <c r="Q574" t="inlineStr">
         <is>
@@ -43092,12 +43092,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -43107,19 +43107,19 @@
         <v>8.326000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>8.779</v>
+        <v>8.568</v>
       </c>
       <c r="H2" t="n">
-        <v>9.329000000000001</v>
+        <v>9.069000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>8.879</v>
+        <v>8.853999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>8.724</v>
+        <v>8.648999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.155</v>
+        <v>-0.205</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>30</v>
       </c>
       <c r="O2" t="n">
-        <v>6.426</v>
+        <v>6.427</v>
       </c>
       <c r="P2" t="n">
         <v>6.38</v>
@@ -43168,38 +43168,38 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.679</v>
+        <v>5.628</v>
       </c>
       <c r="G3" t="n">
-        <v>5.781</v>
+        <v>5.768</v>
       </c>
       <c r="H3" t="n">
         <v>5.841</v>
       </c>
       <c r="I3" t="n">
-        <v>5.724</v>
+        <v>5.808</v>
       </c>
       <c r="J3" t="n">
-        <v>5.69</v>
+        <v>5.637</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.033</v>
+        <v>-0.171</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -43217,10 +43217,10 @@
         <v>0.571</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.826</v>
+        <v>-0.825</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -43244,34 +43244,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.547</v>
+        <v>4.47</v>
       </c>
       <c r="G4" t="n">
-        <v>4.885</v>
+        <v>4.84</v>
       </c>
       <c r="H4" t="n">
-        <v>5.048</v>
+        <v>5.12</v>
       </c>
       <c r="I4" t="n">
-        <v>4.936</v>
+        <v>4.95</v>
       </c>
       <c r="J4" t="n">
-        <v>4.791</v>
+        <v>4.803</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.146</v>
+        <v>-0.147</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>0.787</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.577</v>
+        <v>0.578</v>
       </c>
       <c r="R4" t="n">
         <v>-0.334</v>
@@ -43320,34 +43320,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.259</v>
+        <v>11.248</v>
       </c>
       <c r="G5" t="n">
-        <v>11.52</v>
+        <v>11.465</v>
       </c>
       <c r="H5" t="n">
-        <v>11.75</v>
+        <v>11.72</v>
       </c>
       <c r="I5" t="n">
-        <v>11.75</v>
+        <v>11.72</v>
       </c>
       <c r="J5" t="n">
-        <v>11.269</v>
+        <v>11.282</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.48</v>
+        <v>-0.438</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>5.403</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.615</v>
+        <v>-0.616</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -43396,38 +43396,38 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.585</v>
+        <v>2.522</v>
       </c>
       <c r="G6" t="n">
-        <v>37.579</v>
+        <v>37.902</v>
       </c>
       <c r="H6" t="n">
-        <v>108.28</v>
+        <v>111.228</v>
       </c>
       <c r="I6" t="n">
-        <v>56.368</v>
+        <v>53.861</v>
       </c>
       <c r="J6" t="n">
-        <v>55.627</v>
+        <v>109.606</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.741</v>
+        <v>55.745</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -43439,13 +43439,13 @@
         <v>30</v>
       </c>
       <c r="O6" t="n">
-        <v>67.65000000000001</v>
+        <v>67.65300000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>60.716</v>
+        <v>60.718</v>
       </c>
       <c r="Q6" t="n">
-        <v>42.783</v>
+        <v>42.785</v>
       </c>
       <c r="R6" t="n">
         <v>-0.804</v>
@@ -43472,38 +43472,38 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>9.301</v>
+        <v>9.272</v>
       </c>
       <c r="G7" t="n">
-        <v>9.374000000000001</v>
+        <v>9.368</v>
       </c>
       <c r="H7" t="n">
-        <v>9.451000000000001</v>
+        <v>9.455</v>
       </c>
       <c r="I7" t="n">
-        <v>9.339</v>
+        <v>9.347</v>
       </c>
       <c r="J7" t="n">
-        <v>9.301</v>
+        <v>9.273</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.037</v>
+        <v>-0.074</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -43548,38 +43548,38 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.196</v>
+        <v>8.339</v>
       </c>
       <c r="G8" t="n">
-        <v>8.425000000000001</v>
+        <v>8.442</v>
       </c>
       <c r="H8" t="n">
         <v>8.494999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>8.196</v>
+        <v>8.371</v>
       </c>
       <c r="J8" t="n">
-        <v>8.477</v>
+        <v>8.353999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.281</v>
+        <v>-0.017</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -43594,13 +43594,13 @@
         <v>1.249</v>
       </c>
       <c r="P8" t="n">
-        <v>0.979</v>
+        <v>0.978</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.74</v>
+        <v>0.738</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.896</v>
+        <v>-0.897</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -43624,12 +43624,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -43639,19 +43639,19 @@
         <v>4.644</v>
       </c>
       <c r="G9" t="n">
-        <v>5.065</v>
+        <v>5.092</v>
       </c>
       <c r="H9" t="n">
-        <v>5.83</v>
+        <v>5.913</v>
       </c>
       <c r="I9" t="n">
-        <v>5.314</v>
+        <v>5.194</v>
       </c>
       <c r="J9" t="n">
-        <v>5.681</v>
+        <v>5.746</v>
       </c>
       <c r="K9" t="n">
-        <v>0.367</v>
+        <v>0.552</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -43667,7 +43667,7 @@
         <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>0.707</v>
+        <v>0.708</v>
       </c>
       <c r="P9" t="n">
         <v>0.633</v>
@@ -43700,34 +43700,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.927</v>
+        <v>5.928</v>
       </c>
       <c r="G10" t="n">
-        <v>5.969</v>
+        <v>5.97</v>
       </c>
       <c r="H10" t="n">
-        <v>6.009</v>
+        <v>6.006</v>
       </c>
       <c r="I10" t="n">
-        <v>5.927</v>
+        <v>5.976</v>
       </c>
       <c r="J10" t="n">
         <v>5.928</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001</v>
+        <v>-0.048</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -43749,10 +43749,10 @@
         <v>0.639</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -43776,34 +43776,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.192</v>
+        <v>10.194</v>
       </c>
       <c r="G11" t="n">
-        <v>10.431</v>
+        <v>10.444</v>
       </c>
       <c r="H11" t="n">
-        <v>10.901</v>
+        <v>10.896</v>
       </c>
       <c r="I11" t="n">
-        <v>10.327</v>
+        <v>10.252</v>
       </c>
       <c r="J11" t="n">
-        <v>10.823</v>
+        <v>10.842</v>
       </c>
       <c r="K11" t="n">
-        <v>0.496</v>
+        <v>0.59</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -43828,7 +43828,7 @@
         <v>-0.053</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.439</v>
+        <v>-0.438</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -43852,38 +43852,38 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.517</v>
+        <v>2.378</v>
       </c>
       <c r="G12" t="n">
-        <v>3.391</v>
+        <v>3.306</v>
       </c>
       <c r="H12" t="n">
-        <v>3.937</v>
+        <v>5.934</v>
       </c>
       <c r="I12" t="n">
-        <v>3.769</v>
+        <v>3.489</v>
       </c>
       <c r="J12" t="n">
-        <v>3.003</v>
+        <v>3.777</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.766</v>
+        <v>0.288</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -43928,34 +43928,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.782</v>
+        <v>6.729</v>
       </c>
       <c r="G13" t="n">
-        <v>6.913</v>
+        <v>6.872</v>
       </c>
       <c r="H13" t="n">
-        <v>7.046</v>
+        <v>7.027</v>
       </c>
       <c r="I13" t="n">
-        <v>7.046</v>
+        <v>7.027</v>
       </c>
       <c r="J13" t="n">
-        <v>6.817</v>
+        <v>6.748</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.229</v>
+        <v>-0.279</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>0.902</v>
+        <v>0.903</v>
       </c>
       <c r="P13" t="n">
         <v>0.804</v>
@@ -43980,7 +43980,7 @@
         <v>0.263</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.327</v>
+        <v>-0.328</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -44004,34 +44004,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.74</v>
+        <v>10.545</v>
       </c>
       <c r="G14" t="n">
-        <v>10.939</v>
+        <v>10.865</v>
       </c>
       <c r="H14" t="n">
-        <v>11.122</v>
+        <v>11.082</v>
       </c>
       <c r="I14" t="n">
-        <v>11.122</v>
+        <v>11.082</v>
       </c>
       <c r="J14" t="n">
-        <v>10.789</v>
+        <v>10.681</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.333</v>
+        <v>-0.4</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -44080,34 +44080,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>4.853</v>
+        <v>4.715</v>
       </c>
       <c r="G15" t="n">
-        <v>5.118</v>
+        <v>4.865</v>
       </c>
       <c r="H15" t="n">
-        <v>5.205</v>
+        <v>5.031</v>
       </c>
       <c r="I15" t="n">
-        <v>4.853</v>
+        <v>4.715</v>
       </c>
       <c r="J15" t="n">
-        <v>5.198</v>
+        <v>5.014</v>
       </c>
       <c r="K15" t="n">
-        <v>0.345</v>
+        <v>0.298</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -44123,16 +44123,16 @@
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>0.861</v>
+        <v>0.859</v>
       </c>
       <c r="P15" t="n">
-        <v>0.742</v>
+        <v>0.741</v>
       </c>
       <c r="Q15" t="n">
         <v>0.273</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.596</v>
+        <v>-0.597</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -44156,34 +44156,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>8.007999999999999</v>
+        <v>8.002000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>8.144</v>
+        <v>8.114000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>8.228999999999999</v>
+        <v>8.217000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>8.228999999999999</v>
+        <v>8.217000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>8.036</v>
+        <v>8.007</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.193</v>
+        <v>-0.21</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -44199,13 +44199,13 @@
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>0.978</v>
+        <v>0.977</v>
       </c>
       <c r="P16" t="n">
-        <v>0.852</v>
+        <v>0.851</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.133</v>
+        <v>-0.134</v>
       </c>
       <c r="R16" t="n">
         <v>-0.503</v>
@@ -44232,34 +44232,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.563</v>
+        <v>2.123</v>
       </c>
       <c r="G17" t="n">
-        <v>3.847</v>
+        <v>3.903</v>
       </c>
       <c r="H17" t="n">
-        <v>5.426</v>
+        <v>7.314</v>
       </c>
       <c r="I17" t="n">
-        <v>3.616</v>
+        <v>3.683</v>
       </c>
       <c r="J17" t="n">
-        <v>3.88</v>
+        <v>5.082</v>
       </c>
       <c r="K17" t="n">
-        <v>0.264</v>
+        <v>1.399</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -44275,16 +44275,16 @@
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>1.108</v>
+        <v>1.11</v>
       </c>
       <c r="P17" t="n">
-        <v>0.775</v>
+        <v>0.777</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.723</v>
+        <v>0.725</v>
       </c>
       <c r="R17" t="n">
-        <v>0.035</v>
+        <v>0.033</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -44308,34 +44308,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.365</v>
+        <v>3.368</v>
       </c>
       <c r="G18" t="n">
-        <v>3.648</v>
+        <v>3.661</v>
       </c>
       <c r="H18" t="n">
-        <v>4.239</v>
+        <v>4.215</v>
       </c>
       <c r="I18" t="n">
-        <v>3.58</v>
+        <v>3.488</v>
       </c>
       <c r="J18" t="n">
-        <v>4.143</v>
+        <v>4.175</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>0.106</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.408</v>
+        <v>-0.407</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -44384,34 +44384,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.015</v>
+        <v>3.169</v>
       </c>
       <c r="G19" t="n">
-        <v>3.27</v>
+        <v>3.297</v>
       </c>
       <c r="H19" t="n">
-        <v>3.334</v>
+        <v>3.335</v>
       </c>
       <c r="I19" t="n">
-        <v>3.015</v>
+        <v>3.169</v>
       </c>
       <c r="J19" t="n">
-        <v>3.289</v>
+        <v>3.284</v>
       </c>
       <c r="K19" t="n">
-        <v>0.273</v>
+        <v>0.116</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>0.651</v>
+        <v>0.65</v>
       </c>
       <c r="P19" t="n">
         <v>0.576</v>
@@ -44436,7 +44436,7 @@
         <v>0.062</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.803</v>
+        <v>-0.804</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -44460,34 +44460,34 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>5.749</v>
+        <v>5.862</v>
       </c>
       <c r="G20" t="n">
-        <v>6.487</v>
+        <v>6.527</v>
       </c>
       <c r="H20" t="n">
-        <v>7.013</v>
+        <v>6.993</v>
       </c>
       <c r="I20" t="n">
-        <v>5.749</v>
+        <v>5.862</v>
       </c>
       <c r="J20" t="n">
-        <v>6.532</v>
+        <v>6.538</v>
       </c>
       <c r="K20" t="n">
-        <v>0.783</v>
+        <v>0.676</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -44536,12 +44536,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -44551,19 +44551,19 @@
         <v>128.582</v>
       </c>
       <c r="G21" t="n">
-        <v>128.959</v>
+        <v>129.007</v>
       </c>
       <c r="H21" t="n">
-        <v>129.78</v>
+        <v>130.077</v>
       </c>
       <c r="I21" t="n">
-        <v>128.749</v>
+        <v>128.68</v>
       </c>
       <c r="J21" t="n">
-        <v>129.509</v>
+        <v>129.435</v>
       </c>
       <c r="K21" t="n">
-        <v>0.76</v>
+        <v>0.756</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>

--- a/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
+++ b/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
@@ -486,7 +486,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>334360</v>
+        <v>334380</v>
       </c>
       <c r="E2" t="n">
         <v>172968</v>
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -683,13 +683,13 @@
         <v>7.442</v>
       </c>
       <c r="I2" t="n">
-        <v>9.026999999999999</v>
+        <v>9.028</v>
       </c>
       <c r="J2" t="n">
         <v>0.6870000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>1.585</v>
+        <v>1.586</v>
       </c>
       <c r="L2" t="n">
         <v>6.38</v>
@@ -704,7 +704,7 @@
         <v>0.445</v>
       </c>
       <c r="P2" t="n">
-        <v>-107.199</v>
+        <v>-107.21</v>
       </c>
       <c r="Q2" t="n">
         <v>-3.402</v>
@@ -765,31 +765,31 @@
         <v>5.158</v>
       </c>
       <c r="I3" t="n">
-        <v>5.596</v>
+        <v>5.595</v>
       </c>
       <c r="J3" t="n">
         <v>-1.412</v>
       </c>
       <c r="K3" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L3" t="n">
         <v>0.457</v>
       </c>
       <c r="M3" t="n">
-        <v>0.571</v>
+        <v>0.57</v>
       </c>
       <c r="N3" t="n">
-        <v>0.801</v>
+        <v>0.799</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.695</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.332</v>
+        <v>-1.325</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.825</v>
+        <v>-0.823</v>
       </c>
       <c r="R3" t="n">
         <v>20.69</v>
@@ -862,13 +862,13 @@
         <v>0.787</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O4" t="n">
         <v>-0.296</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.109</v>
+        <v>-2.111</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.334</v>
@@ -929,28 +929,28 @@
         <v>12.839</v>
       </c>
       <c r="I5" t="n">
-        <v>11.767</v>
+        <v>11.768</v>
       </c>
       <c r="J5" t="n">
         <v>0.185</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.072</v>
+        <v>-1.071</v>
       </c>
       <c r="L5" t="n">
-        <v>5.403</v>
+        <v>5.404</v>
       </c>
       <c r="M5" t="n">
-        <v>5.403</v>
+        <v>5.404</v>
       </c>
       <c r="N5" t="n">
         <v>5.438</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.369</v>
+        <v>-0.37</v>
       </c>
       <c r="P5" t="n">
-        <v>-277.018</v>
+        <v>-277.039</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.616</v>
@@ -1011,28 +1011,28 @@
         <v>2.979</v>
       </c>
       <c r="I6" t="n">
-        <v>105.449</v>
+        <v>105.478</v>
       </c>
       <c r="J6" t="n">
         <v>-52.655</v>
       </c>
       <c r="K6" t="n">
-        <v>102.47</v>
+        <v>102.499</v>
       </c>
       <c r="L6" t="n">
-        <v>42.785</v>
+        <v>42.788</v>
       </c>
       <c r="M6" t="n">
-        <v>60.718</v>
+        <v>60.721</v>
       </c>
       <c r="N6" t="n">
-        <v>67.65300000000001</v>
+        <v>67.657</v>
       </c>
       <c r="O6" t="n">
         <v>-0.323</v>
       </c>
       <c r="P6" t="n">
-        <v>-7.389</v>
+        <v>-7.39</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.804</v>
@@ -1175,28 +1175,28 @@
         <v>8.464</v>
       </c>
       <c r="I8" t="n">
-        <v>7.826</v>
+        <v>7.822</v>
       </c>
       <c r="J8" t="n">
         <v>0.39</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.638</v>
+        <v>-0.643</v>
       </c>
       <c r="L8" t="n">
-        <v>0.738</v>
+        <v>0.737</v>
       </c>
       <c r="M8" t="n">
-        <v>0.978</v>
+        <v>0.977</v>
       </c>
       <c r="N8" t="n">
-        <v>1.249</v>
+        <v>1.248</v>
       </c>
       <c r="O8" t="n">
         <v>-0.493</v>
       </c>
       <c r="P8" t="n">
-        <v>-11.022</v>
+        <v>-11.012</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.897</v>
@@ -1213,7 +1213,7 @@
         <v>6510</v>
       </c>
       <c r="U8" t="n">
-        <v>0.823</v>
+        <v>0.824</v>
       </c>
       <c r="V8" t="n">
         <v>0.649</v>
@@ -1257,13 +1257,13 @@
         <v>4.662</v>
       </c>
       <c r="I9" t="n">
-        <v>5.509</v>
+        <v>5.511</v>
       </c>
       <c r="J9" t="n">
         <v>0.72</v>
       </c>
       <c r="K9" t="n">
-        <v>0.847</v>
+        <v>0.849</v>
       </c>
       <c r="L9" t="n">
         <v>0.376</v>
@@ -1278,10 +1278,10 @@
         <v>0.323</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.91</v>
+        <v>-0.911</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.318</v>
+        <v>0.317</v>
       </c>
       <c r="R9" t="n">
         <v>20.69</v>
@@ -1339,13 +1339,13 @@
         <v>5.52</v>
       </c>
       <c r="I10" t="n">
-        <v>5.822</v>
+        <v>5.82</v>
       </c>
       <c r="J10" t="n">
         <v>-0.632</v>
       </c>
       <c r="K10" t="n">
-        <v>0.303</v>
+        <v>0.301</v>
       </c>
       <c r="L10" t="n">
         <v>-0.5600000000000001</v>
@@ -1357,7 +1357,7 @@
         <v>0.799</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.669</v>
+        <v>-0.668</v>
       </c>
       <c r="P10" t="n">
         <v>-4.047</v>
@@ -1421,7 +1421,7 @@
         <v>10.162</v>
       </c>
       <c r="I11" t="n">
-        <v>10.403</v>
+        <v>10.404</v>
       </c>
       <c r="J11" t="n">
         <v>-0.715</v>
@@ -1442,7 +1442,7 @@
         <v>-0.385</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.869</v>
+        <v>-0.87</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.438</v>
@@ -1503,19 +1503,19 @@
         <v>2.666</v>
       </c>
       <c r="I12" t="n">
-        <v>3.921</v>
+        <v>3.922</v>
       </c>
       <c r="J12" t="n">
         <v>-0.042</v>
       </c>
       <c r="K12" t="n">
-        <v>1.255</v>
+        <v>1.256</v>
       </c>
       <c r="L12" t="n">
         <v>1.076</v>
       </c>
       <c r="M12" t="n">
-        <v>1.12</v>
+        <v>1.121</v>
       </c>
       <c r="N12" t="n">
         <v>1.683</v>
@@ -1524,7 +1524,7 @@
         <v>0.27</v>
       </c>
       <c r="P12" t="n">
-        <v>-9.837</v>
+        <v>-9.839</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.806</v>
@@ -1594,10 +1594,10 @@
         <v>1.41</v>
       </c>
       <c r="L13" t="n">
-        <v>0.263</v>
+        <v>0.264</v>
       </c>
       <c r="M13" t="n">
-        <v>0.804</v>
+        <v>0.805</v>
       </c>
       <c r="N13" t="n">
         <v>0.903</v>
@@ -1606,7 +1606,7 @@
         <v>0.166</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.868</v>
+        <v>-3.872</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.328</v>
@@ -1749,16 +1749,16 @@
         <v>5.573</v>
       </c>
       <c r="I15" t="n">
-        <v>6.488</v>
+        <v>6.485</v>
       </c>
       <c r="J15" t="n">
         <v>0.28</v>
       </c>
       <c r="K15" t="n">
-        <v>0.915</v>
+        <v>0.912</v>
       </c>
       <c r="L15" t="n">
-        <v>0.273</v>
+        <v>0.272</v>
       </c>
       <c r="M15" t="n">
         <v>0.741</v>
@@ -1767,13 +1767,13 @@
         <v>0.859</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.58</v>
+        <v>-0.581</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.796</v>
+        <v>-1.795</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.597</v>
+        <v>-0.598</v>
       </c>
       <c r="R15" t="n">
         <v>24.138</v>
@@ -1831,19 +1831,19 @@
         <v>6.803</v>
       </c>
       <c r="I16" t="n">
-        <v>8.215999999999999</v>
+        <v>8.214</v>
       </c>
       <c r="J16" t="n">
         <v>-0.825</v>
       </c>
       <c r="K16" t="n">
-        <v>1.413</v>
+        <v>1.412</v>
       </c>
       <c r="L16" t="n">
         <v>-0.134</v>
       </c>
       <c r="M16" t="n">
-        <v>0.851</v>
+        <v>0.85</v>
       </c>
       <c r="N16" t="n">
         <v>0.977</v>
@@ -1852,7 +1852,7 @@
         <v>-0.503</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.991</v>
+        <v>-1.986</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.503</v>
@@ -1919,25 +1919,25 @@
         <v>-0.58</v>
       </c>
       <c r="K17" t="n">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
       <c r="L17" t="n">
-        <v>0.725</v>
+        <v>0.727</v>
       </c>
       <c r="M17" t="n">
-        <v>0.777</v>
+        <v>0.779</v>
       </c>
       <c r="N17" t="n">
-        <v>1.11</v>
+        <v>1.112</v>
       </c>
       <c r="O17" t="n">
-        <v>0.253</v>
+        <v>0.25</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.741</v>
+        <v>-3.759</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="R17" t="n">
         <v>44.828</v>
@@ -2004,13 +2004,13 @@
         <v>0.3</v>
       </c>
       <c r="L18" t="n">
-        <v>0.106</v>
+        <v>0.107</v>
       </c>
       <c r="M18" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="N18" t="n">
-        <v>0.521</v>
+        <v>0.522</v>
       </c>
       <c r="O18" t="n">
         <v>-0.265</v>
@@ -2077,31 +2077,31 @@
         <v>2.466</v>
       </c>
       <c r="I19" t="n">
-        <v>2.875</v>
+        <v>2.873</v>
       </c>
       <c r="J19" t="n">
         <v>-0.153</v>
       </c>
       <c r="K19" t="n">
-        <v>0.41</v>
+        <v>0.407</v>
       </c>
       <c r="L19" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="M19" t="n">
-        <v>0.576</v>
+        <v>0.575</v>
       </c>
       <c r="N19" t="n">
         <v>0.65</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.759</v>
+        <v>-0.76</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.299</v>
+        <v>-1.296</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.804</v>
+        <v>-0.805</v>
       </c>
       <c r="R19" t="n">
         <v>20.69</v>
@@ -2241,13 +2241,13 @@
         <v>129.287</v>
       </c>
       <c r="I21" t="n">
-        <v>128.807</v>
+        <v>128.809</v>
       </c>
       <c r="J21" t="n">
         <v>-0.34</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.48</v>
+        <v>-0.478</v>
       </c>
       <c r="L21" t="n">
         <v>-0.006</v>
@@ -3982,10 +3982,10 @@
         <v>10</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7822064056939502</v>
+        <v>0.7823613086770982</v>
       </c>
       <c r="H24" t="n">
-        <v>9.221762989323842</v>
+        <v>9.223779516358464</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -4004,16 +4004,16 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>6.666762989323843</v>
+        <v>6.668779516358464</v>
       </c>
       <c r="N24" t="n">
-        <v>6.666762989323843</v>
+        <v>6.668779516358464</v>
       </c>
       <c r="O24" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P24" t="n">
-        <v>1.947996153697485</v>
+        <v>1.950012680732106</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4053,10 +4053,10 @@
         <v>10</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7893238434163701</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="H25" t="n">
-        <v>9.293932384341637</v>
+        <v>9.296052631578949</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -4075,16 +4075,16 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>7.013932384341638</v>
+        <v>7.016052631578949</v>
       </c>
       <c r="N25" t="n">
-        <v>7.013932384341638</v>
+        <v>7.016052631578949</v>
       </c>
       <c r="O25" t="n">
         <v>-0.2750000000000004</v>
       </c>
       <c r="P25" t="n">
-        <v>0.07216939501779507</v>
+        <v>0.07227311522048474</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4124,10 +4124,10 @@
         <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>0.79288256227758</v>
+        <v>0.7930298719772404</v>
       </c>
       <c r="H26" t="n">
-        <v>9.308857651245551</v>
+        <v>9.309274537695591</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -4146,16 +4146,16 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>7.236357651245552</v>
+        <v>7.236774537695592</v>
       </c>
       <c r="N26" t="n">
-        <v>7.236357651245552</v>
+        <v>7.236774537695592</v>
       </c>
       <c r="O26" t="n">
         <v>-0.2075</v>
       </c>
       <c r="P26" t="n">
-        <v>0.01492526690391394</v>
+        <v>0.01322190611664276</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4195,10 +4195,10 @@
         <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7857651245551601</v>
+        <v>0.7859174964438123</v>
       </c>
       <c r="H27" t="n">
-        <v>9.268916725978647</v>
+        <v>9.269951635846374</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4217,16 +4217,16 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>7.383916725978647</v>
+        <v>7.384951635846374</v>
       </c>
       <c r="N27" t="n">
-        <v>7.383916725978647</v>
+        <v>7.384951635846374</v>
       </c>
       <c r="O27" t="n">
         <v>-0.1874999999999998</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.03994092526690451</v>
+        <v>-0.03932290184921783</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4266,10 +4266,10 @@
         <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7800711743772242</v>
+        <v>0.7802275960170697</v>
       </c>
       <c r="H28" t="n">
-        <v>9.202601423487543</v>
+        <v>9.203044096728307</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4288,16 +4288,16 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>7.412601423487543</v>
+        <v>7.413044096728307</v>
       </c>
       <c r="N28" t="n">
-        <v>7.412601423487543</v>
+        <v>7.413044096728307</v>
       </c>
       <c r="O28" t="n">
         <v>-0.09499999999999997</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.06631530249110362</v>
+        <v>-0.06690753911806624</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4337,10 +4337,10 @@
         <v>10</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7708185053380783</v>
+        <v>0.7709815078236131</v>
       </c>
       <c r="H29" t="n">
-        <v>9.094982918149466</v>
+        <v>9.095628733997154</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4359,16 +4359,16 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>7.349982918149466</v>
+        <v>7.350628733997154</v>
       </c>
       <c r="N29" t="n">
-        <v>7.349982918149466</v>
+        <v>7.350628733997154</v>
       </c>
       <c r="O29" t="n">
         <v>-0.04499999999999993</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.1076185053380776</v>
+        <v>-0.1074153627311532</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4408,10 +4408,10 @@
         <v>10</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7629893238434163</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="H30" t="n">
-        <v>9.073963701067616</v>
+        <v>9.074631578947368</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4430,16 +4430,16 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>7.398963701067616</v>
+        <v>7.399631578947369</v>
       </c>
       <c r="N30" t="n">
-        <v>7.398963701067616</v>
+        <v>7.399631578947369</v>
       </c>
       <c r="O30" t="n">
         <v>-0.07000000000000006</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.02101921708185017</v>
+        <v>-0.02099715504978583</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4479,10 +4479,10 @@
         <v>10</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7565836298932385</v>
+        <v>0.7567567567567568</v>
       </c>
       <c r="H31" t="n">
-        <v>9.027263345195729</v>
+        <v>9.028243243243244</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4501,16 +4501,16 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>7.367263345195729</v>
+        <v>7.368243243243244</v>
       </c>
       <c r="N31" t="n">
-        <v>7.367263345195729</v>
+        <v>7.368243243243244</v>
       </c>
       <c r="O31" t="n">
         <v>-0.01500000000000012</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.04670035587188615</v>
+        <v>-0.04638833570412437</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -6106,10 +6106,10 @@
         <v>10</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6185053380782918</v>
+        <v>0.6180654338549075</v>
       </c>
       <c r="H54" t="n">
-        <v>5.075043890865955</v>
+        <v>5.073212422949265</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -6128,16 +6128,16 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.7575438908659544</v>
+        <v>0.755712422949264</v>
       </c>
       <c r="N54" t="n">
-        <v>0.7575438908659544</v>
+        <v>0.755712422949264</v>
       </c>
       <c r="O54" t="n">
         <v>-0.02249999999999908</v>
       </c>
       <c r="P54" t="n">
-        <v>0.198334380849059</v>
+        <v>0.1965029129323685</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -6177,10 +6177,10 @@
         <v>10</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6177935943060499</v>
+        <v>0.6173541963015647</v>
       </c>
       <c r="H55" t="n">
-        <v>5.072080664294187</v>
+        <v>5.070251303935515</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -6199,16 +6199,16 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>1.007080664294187</v>
+        <v>1.005251303935514</v>
       </c>
       <c r="N55" t="n">
-        <v>1.007080664294187</v>
+        <v>1.005251303935514</v>
       </c>
       <c r="O55" t="n">
         <v>-0.2525000000000004</v>
       </c>
       <c r="P55" t="n">
-        <v>-0.002963226571767841</v>
+        <v>-0.002961119013749958</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -6248,10 +6248,10 @@
         <v>10</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6199288256227758</v>
+        <v>0.6194879089615932</v>
       </c>
       <c r="H56" t="n">
-        <v>5.080582206405694</v>
+        <v>5.079134660976766</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -6270,16 +6270,16 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>1.275582206405694</v>
+        <v>1.274134660976766</v>
       </c>
       <c r="N56" t="n">
-        <v>1.275582206405694</v>
+        <v>1.274134660976766</v>
       </c>
       <c r="O56" t="n">
         <v>-0.2600000000000002</v>
       </c>
       <c r="P56" t="n">
-        <v>0.008501542111506666</v>
+        <v>0.008883357041251649</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -6319,10 +6319,10 @@
         <v>10</v>
       </c>
       <c r="G57" t="n">
-        <v>0.6306049822064057</v>
+        <v>0.6301564722617354</v>
       </c>
       <c r="H57" t="n">
-        <v>5.115004982206407</v>
+        <v>5.110523470839261</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -6341,16 +6341,16 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>1.315004982206407</v>
+        <v>1.310523470839261</v>
       </c>
       <c r="N57" t="n">
-        <v>1.315004982206407</v>
+        <v>1.310523470839261</v>
       </c>
       <c r="O57" t="n">
         <v>-0.005000000000000338</v>
       </c>
       <c r="P57" t="n">
-        <v>0.03442277580071273</v>
+        <v>0.03138880986249415</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -6390,10 +6390,10 @@
         <v>10</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6661921708185053</v>
+        <v>0.6657183499288762</v>
       </c>
       <c r="H58" t="n">
-        <v>5.175521837593012</v>
+        <v>5.174983835510151</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6412,16 +6412,16 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>1.410521837593012</v>
+        <v>1.409983835510151</v>
       </c>
       <c r="N58" t="n">
-        <v>1.410521837593012</v>
+        <v>1.409983835510151</v>
       </c>
       <c r="O58" t="n">
         <v>-0.0349999999999997</v>
       </c>
       <c r="P58" t="n">
-        <v>0.0605168553866049</v>
+        <v>0.06446036467089034</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -6461,10 +6461,10 @@
         <v>10</v>
       </c>
       <c r="G59" t="n">
-        <v>0.7259786476868327</v>
+        <v>0.7254623044096729</v>
       </c>
       <c r="H59" t="n">
-        <v>5.315978647686832</v>
+        <v>5.310819345661451</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6483,16 +6483,16 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>1.605978647686833</v>
+        <v>1.600819345661451</v>
       </c>
       <c r="N59" t="n">
-        <v>1.605978647686833</v>
+        <v>1.600819345661451</v>
       </c>
       <c r="O59" t="n">
         <v>-0.05500000000000016</v>
       </c>
       <c r="P59" t="n">
-        <v>0.1404568100938208</v>
+        <v>0.1358355101513</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -6532,10 +6532,10 @@
         <v>10</v>
       </c>
       <c r="G60" t="n">
-        <v>0.7886120996441282</v>
+        <v>0.7880512091038406</v>
       </c>
       <c r="H60" t="n">
-        <v>5.45744128113879</v>
+        <v>5.455689900426743</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -6554,16 +6554,16 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>1.90744128113879</v>
+        <v>1.905689900426743</v>
       </c>
       <c r="N60" t="n">
-        <v>1.90744128113879</v>
+        <v>1.905689900426743</v>
       </c>
       <c r="O60" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P60" t="n">
-        <v>0.1414626334519573</v>
+        <v>0.1448705547652915</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -6603,10 +6603,10 @@
         <v>10</v>
       </c>
       <c r="G61" t="n">
-        <v>0.8256227758007118</v>
+        <v>0.8250355618776671</v>
       </c>
       <c r="H61" t="n">
-        <v>5.596405693950178</v>
+        <v>5.594938833570413</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -6625,16 +6625,16 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>1.996405693950178</v>
+        <v>1.994938833570413</v>
       </c>
       <c r="N61" t="n">
-        <v>1.996405693950178</v>
+        <v>1.994938833570413</v>
       </c>
       <c r="O61" t="n">
         <v>0.05000000000000027</v>
       </c>
       <c r="P61" t="n">
-        <v>0.1389644128113883</v>
+        <v>0.1392489331436702</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8230,10 +8230,10 @@
         <v>10</v>
       </c>
       <c r="G84" t="n">
-        <v>0.7266903914590748</v>
+        <v>0.7268847795163584</v>
       </c>
       <c r="H84" t="n">
-        <v>5.100270462633452</v>
+        <v>5.101394025604551</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -8252,16 +8252,16 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>1.505270462633451</v>
+        <v>1.506394025604551</v>
       </c>
       <c r="N84" t="n">
-        <v>1.505270462633451</v>
+        <v>1.506394025604551</v>
       </c>
       <c r="O84" t="n">
         <v>-0.2124999999999999</v>
       </c>
       <c r="P84" t="n">
-        <v>-0.4796426438111538</v>
+        <v>-0.4785190808400541</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -8301,10 +8301,10 @@
         <v>10</v>
       </c>
       <c r="G85" t="n">
-        <v>0.7124555160142348</v>
+        <v>0.7126600284495022</v>
       </c>
       <c r="H85" t="n">
-        <v>5.057992882562277</v>
+        <v>5.059174964438122</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -8323,16 +8323,16 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>1.007992882562277</v>
+        <v>1.009174964438122</v>
       </c>
       <c r="N85" t="n">
-        <v>1.007992882562277</v>
+        <v>1.009174964438122</v>
       </c>
       <c r="O85" t="n">
         <v>0.4549999999999996</v>
       </c>
       <c r="P85" t="n">
-        <v>-0.04227758007117455</v>
+        <v>-0.04221906116642948</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -8372,10 +8372,10 @@
         <v>10</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6932384341637011</v>
+        <v>0.6934566145092461</v>
       </c>
       <c r="H86" t="n">
-        <v>4.963836298932385</v>
+        <v>4.966358463726885</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -8394,16 +8394,16 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>0.8338362989323853</v>
+        <v>0.836358463726885</v>
       </c>
       <c r="N86" t="n">
-        <v>0.8338362989323853</v>
+        <v>0.836358463726885</v>
       </c>
       <c r="O86" t="n">
         <v>0.08000000000000007</v>
       </c>
       <c r="P86" t="n">
-        <v>-0.09415658362989188</v>
+        <v>-0.09281650071123693</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -8443,10 +8443,10 @@
         <v>10</v>
       </c>
       <c r="G87" t="n">
-        <v>0.6868327402135231</v>
+        <v>0.686344238975818</v>
       </c>
       <c r="H87" t="n">
-        <v>4.946765836298932</v>
+        <v>4.945862304409673</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -8465,16 +8465,16 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>0.3642658362989328</v>
+        <v>0.3633623044096739</v>
       </c>
       <c r="N87" t="n">
-        <v>0.3642658362989328</v>
+        <v>0.3633623044096739</v>
       </c>
       <c r="O87" t="n">
         <v>0.4524999999999997</v>
       </c>
       <c r="P87" t="n">
-        <v>-0.0170704626334528</v>
+        <v>-0.02049615931721149</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -8514,10 +8514,10 @@
         <v>10</v>
       </c>
       <c r="G88" t="n">
-        <v>0.706049822064057</v>
+        <v>0.7062588904694168</v>
       </c>
       <c r="H88" t="n">
-        <v>5.037161565836299</v>
+        <v>5.038611664295875</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -8536,16 +8536,16 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>0.9746615658362989</v>
+        <v>0.9761116642958747</v>
       </c>
       <c r="N88" t="n">
-        <v>0.9746615658362989</v>
+        <v>0.9761116642958747</v>
       </c>
       <c r="O88" t="n">
         <v>-0.5199999999999996</v>
       </c>
       <c r="P88" t="n">
-        <v>0.09039572953736652</v>
+        <v>0.09274935988620125</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -8585,10 +8585,10 @@
         <v>10</v>
       </c>
       <c r="G89" t="n">
-        <v>0.7138790035587189</v>
+        <v>0.7140825035561877</v>
       </c>
       <c r="H89" t="n">
-        <v>5.068244128113879</v>
+        <v>5.068479374110953</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -8607,16 +8607,16 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>1.455744128113879</v>
+        <v>1.455979374110953</v>
       </c>
       <c r="N89" t="n">
-        <v>1.455744128113879</v>
+        <v>1.455979374110953</v>
       </c>
       <c r="O89" t="n">
         <v>-0.4500000000000002</v>
       </c>
       <c r="P89" t="n">
-        <v>0.03108256227757966</v>
+        <v>0.02986770981507814</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -8656,10 +8656,10 @@
         <v>10</v>
       </c>
       <c r="G90" t="n">
-        <v>0.7088967971530249</v>
+        <v>0.7091038406827881</v>
       </c>
       <c r="H90" t="n">
-        <v>5.045975516014234</v>
+        <v>5.046358463726885</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -8678,16 +8678,16 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>1.663475516014234</v>
+        <v>1.663858463726885</v>
       </c>
       <c r="N90" t="n">
-        <v>1.663475516014234</v>
+        <v>1.663858463726885</v>
       </c>
       <c r="O90" t="n">
         <v>-0.23</v>
       </c>
       <c r="P90" t="n">
-        <v>-0.02226861209964426</v>
+        <v>-0.02212091038406783</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -8727,10 +8727,10 @@
         <v>10</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6911032028469751</v>
+        <v>0.6913229018492176</v>
       </c>
       <c r="H91" t="n">
-        <v>4.955830604982206</v>
+        <v>4.956338549075391</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -8749,16 +8749,16 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>1.775830604982206</v>
+        <v>1.776338549075391</v>
       </c>
       <c r="N91" t="n">
-        <v>1.775830604982206</v>
+        <v>1.776338549075391</v>
       </c>
       <c r="O91" t="n">
         <v>-0.2024999999999997</v>
       </c>
       <c r="P91" t="n">
-        <v>-0.09014491103202804</v>
+        <v>-0.09001991465149395</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -10354,10 +10354,10 @@
         <v>10</v>
       </c>
       <c r="G114" t="n">
-        <v>0.6377224199288256</v>
+        <v>0.6379800853485064</v>
       </c>
       <c r="H114" t="n">
-        <v>11.72595017793594</v>
+        <v>11.72763015647226</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -10376,16 +10376,16 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>5.055950177935943</v>
+        <v>5.057630156472262</v>
       </c>
       <c r="N114" t="n">
-        <v>5.055950177935943</v>
+        <v>5.057630156472262</v>
       </c>
       <c r="O114" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P114" t="n">
-        <v>-1.102136353562972</v>
+        <v>-1.100456375026653</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -10425,10 +10425,10 @@
         <v>10</v>
       </c>
       <c r="G115" t="n">
-        <v>0.6355871886120996</v>
+        <v>0.6351351351351351</v>
       </c>
       <c r="H115" t="n">
-        <v>11.71950177935943</v>
+        <v>11.71931756756757</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -10447,16 +10447,16 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>5.179501779359431</v>
+        <v>5.179317567567568</v>
       </c>
       <c r="N115" t="n">
-        <v>5.179501779359431</v>
+        <v>5.179317567567568</v>
       </c>
       <c r="O115" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P115" t="n">
-        <v>-0.006448398576511138</v>
+        <v>-0.008312588904693996</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -10496,10 +10496,10 @@
         <v>10</v>
       </c>
       <c r="G116" t="n">
-        <v>0.6348754448398577</v>
+        <v>0.6344238975817923</v>
       </c>
       <c r="H116" t="n">
-        <v>11.71921174377224</v>
+        <v>11.71902773826458</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -10518,16 +10518,16 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>5.084211743772242</v>
+        <v>5.084027738264581</v>
       </c>
       <c r="N116" t="n">
-        <v>5.084211743772242</v>
+        <v>5.084027738264581</v>
       </c>
       <c r="O116" t="n">
         <v>0.09499999999999975</v>
       </c>
       <c r="P116" t="n">
-        <v>-0.0002900355871897631</v>
+        <v>-0.0002898293029875987</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -10567,10 +10567,10 @@
         <v>10</v>
       </c>
       <c r="G117" t="n">
-        <v>0.6370106761565836</v>
+        <v>0.6372688477951636</v>
       </c>
       <c r="H117" t="n">
-        <v>11.72130960854093</v>
+        <v>11.72299288762447</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -10589,16 +10589,16 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>5.036309608540926</v>
+        <v>5.037992887624468</v>
       </c>
       <c r="N117" t="n">
-        <v>5.036309608540926</v>
+        <v>5.037992887624468</v>
       </c>
       <c r="O117" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P117" t="n">
-        <v>0.002097864768684232</v>
+        <v>0.003965149359887121</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -10638,10 +10638,10 @@
         <v>10</v>
       </c>
       <c r="G118" t="n">
-        <v>0.6419928825622776</v>
+        <v>0.6422475106685633</v>
       </c>
       <c r="H118" t="n">
-        <v>11.74822419928826</v>
+        <v>11.74843172119488</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -10660,16 +10660,16 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>5.218224199288256</v>
+        <v>5.218431721194879</v>
       </c>
       <c r="N118" t="n">
-        <v>5.218224199288256</v>
+        <v>5.218431721194879</v>
       </c>
       <c r="O118" t="n">
         <v>-0.1550000000000002</v>
       </c>
       <c r="P118" t="n">
-        <v>0.02691459074732983</v>
+        <v>0.02543883357041032</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -10709,10 +10709,10 @@
         <v>10</v>
       </c>
       <c r="G119" t="n">
-        <v>0.6455516014234876</v>
+        <v>0.6458036984352774</v>
       </c>
       <c r="H119" t="n">
-        <v>11.75562277580071</v>
+        <v>11.75665007112375</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -10731,16 +10731,16 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>5.480622775800713</v>
+        <v>5.481650071123756</v>
       </c>
       <c r="N119" t="n">
-        <v>5.480622775800713</v>
+        <v>5.481650071123756</v>
       </c>
       <c r="O119" t="n">
         <v>-0.2550000000000008</v>
       </c>
       <c r="P119" t="n">
-        <v>0.00739857651245579</v>
+        <v>0.008218349928876378</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -10780,10 +10780,10 @@
         <v>10</v>
       </c>
       <c r="G120" t="n">
-        <v>0.6476868327402135</v>
+        <v>0.6479374110953058</v>
       </c>
       <c r="H120" t="n">
-        <v>11.76432384341637</v>
+        <v>11.76534495021337</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -10802,16 +10802,16 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>5.694323843416371</v>
+        <v>5.695344950213371</v>
       </c>
       <c r="N120" t="n">
-        <v>5.694323843416371</v>
+        <v>5.695344950213371</v>
       </c>
       <c r="O120" t="n">
         <v>-0.2049999999999992</v>
       </c>
       <c r="P120" t="n">
-        <v>0.008701067615659142</v>
+        <v>0.008694879089615526</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -10851,10 +10851,10 @@
         <v>10</v>
       </c>
       <c r="G121" t="n">
-        <v>0.6483985765124555</v>
+        <v>0.6486486486486487</v>
       </c>
       <c r="H121" t="n">
-        <v>11.76722419928826</v>
+        <v>11.76824324324324</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -10873,16 +10873,16 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>5.867224199288255</v>
+        <v>5.868243243243242</v>
       </c>
       <c r="N121" t="n">
-        <v>5.867224199288255</v>
+        <v>5.868243243243242</v>
       </c>
       <c r="O121" t="n">
         <v>-0.169999999999999</v>
       </c>
       <c r="P121" t="n">
-        <v>0.002900355871885196</v>
+        <v>0.002898293029872434</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -12478,10 +12478,10 @@
         <v>10</v>
       </c>
       <c r="G144" t="n">
-        <v>0.397864768683274</v>
+        <v>0.3982930298719772</v>
       </c>
       <c r="H144" t="n">
-        <v>109.2741992882562</v>
+        <v>109.2753627311522</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -12500,16 +12500,16 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>104.9341992882562</v>
+        <v>104.9353627311522</v>
       </c>
       <c r="N144" t="n">
-        <v>104.9341992882562</v>
+        <v>104.9353627311522</v>
       </c>
       <c r="O144" t="n">
         <v>-52.655</v>
       </c>
       <c r="P144" t="n">
-        <v>-0.2548883294121254</v>
+        <v>-0.253724886516153</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
@@ -12549,10 +12549,10 @@
         <v>10</v>
       </c>
       <c r="G145" t="n">
-        <v>0.3444839857651246</v>
+        <v>0.344950213371266</v>
       </c>
       <c r="H145" t="n">
-        <v>108.9301779359431</v>
+        <v>108.9406721194879</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -12571,16 +12571,16 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>104.7401779359431</v>
+        <v>104.7506721194879</v>
       </c>
       <c r="N145" t="n">
-        <v>104.7401779359431</v>
+        <v>104.7506721194879</v>
       </c>
       <c r="O145" t="n">
         <v>-0.1499999999999995</v>
       </c>
       <c r="P145" t="n">
-        <v>-0.3440213523131632</v>
+        <v>-0.3346906116642856</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -12620,10 +12620,10 @@
         <v>10</v>
       </c>
       <c r="G146" t="n">
-        <v>0.301779359430605</v>
+        <v>0.302275960170697</v>
       </c>
       <c r="H146" t="n">
-        <v>108.4898339264531</v>
+        <v>108.4953236130868</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -12642,16 +12642,16 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>104.3498339264531</v>
+        <v>104.3553236130868</v>
       </c>
       <c r="N146" t="n">
-        <v>104.3498339264531</v>
+        <v>104.3553236130868</v>
       </c>
       <c r="O146" t="n">
         <v>-0.05000000000000071</v>
       </c>
       <c r="P146" t="n">
-        <v>-0.4403440094899196</v>
+        <v>-0.445348506401146</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -12691,10 +12691,10 @@
         <v>10</v>
       </c>
       <c r="G147" t="n">
-        <v>0.2604982206405694</v>
+        <v>0.2610241820768137</v>
       </c>
       <c r="H147" t="n">
-        <v>108.054590747331</v>
+        <v>108.061020625889</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -12713,16 +12713,16 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>103.984590747331</v>
+        <v>103.991020625889</v>
       </c>
       <c r="N147" t="n">
-        <v>103.984590747331</v>
+        <v>103.991020625889</v>
       </c>
       <c r="O147" t="n">
         <v>-0.0699999999999994</v>
       </c>
       <c r="P147" t="n">
-        <v>-0.4352431791221818</v>
+        <v>-0.4343029871977251</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -12762,10 +12762,10 @@
         <v>10</v>
       </c>
       <c r="G148" t="n">
-        <v>0.2277580071174377</v>
+        <v>0.2283072546230441</v>
       </c>
       <c r="H148" t="n">
-        <v>107.6762277580071</v>
+        <v>107.6807041251778</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -12784,16 +12784,16 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>103.6162277580071</v>
+        <v>103.6207041251778</v>
       </c>
       <c r="N148" t="n">
-        <v>103.6162277580071</v>
+        <v>103.6207041251778</v>
       </c>
       <c r="O148" t="n">
         <v>-0.01000000000000068</v>
       </c>
       <c r="P148" t="n">
-        <v>-0.3783629893238469</v>
+        <v>-0.3803165007112312</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -12833,10 +12833,10 @@
         <v>10</v>
       </c>
       <c r="G149" t="n">
-        <v>0.2170818505338078</v>
+        <v>0.2176386913229018</v>
       </c>
       <c r="H149" t="n">
-        <v>107.4784341637011</v>
+        <v>107.4875106685633</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -12855,16 +12855,16 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>103.4884341637011</v>
+        <v>103.4975106685633</v>
       </c>
       <c r="N149" t="n">
-        <v>103.4884341637011</v>
+        <v>103.4975106685633</v>
       </c>
       <c r="O149" t="n">
         <v>-0.0699999999999994</v>
       </c>
       <c r="P149" t="n">
-        <v>-0.1977935943060487</v>
+        <v>-0.1931934566145088</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -12904,10 +12904,10 @@
         <v>10</v>
       </c>
       <c r="G150" t="n">
-        <v>0.202846975088968</v>
+        <v>0.2034139402560455</v>
       </c>
       <c r="H150" t="n">
-        <v>107.0064056939502</v>
+        <v>107.0156472261735</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -12926,16 +12926,16 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>103.0564056939502</v>
+        <v>103.0656472261735</v>
       </c>
       <c r="N150" t="n">
-        <v>103.0564056939502</v>
+        <v>103.0656472261735</v>
       </c>
       <c r="O150" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P150" t="n">
-        <v>-0.4720284697508816</v>
+        <v>-0.4718634423897612</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -12975,10 +12975,10 @@
         <v>10</v>
       </c>
       <c r="G151" t="n">
-        <v>0.1658362989323843</v>
+        <v>0.1664295874822191</v>
       </c>
       <c r="H151" t="n">
-        <v>105.4493950177936</v>
+        <v>105.4784068278805</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -12997,16 +12997,16 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>101.4993950177936</v>
+        <v>101.5284068278805</v>
       </c>
       <c r="N151" t="n">
-        <v>101.4993950177936</v>
+        <v>101.5284068278805</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
       </c>
       <c r="P151" t="n">
-        <v>-1.557010676156594</v>
+        <v>-1.537240398293036</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
@@ -14880,10 +14880,10 @@
         <v>10</v>
       </c>
       <c r="G178" t="n">
-        <v>0.6718861209964413</v>
+        <v>0.6714082503556188</v>
       </c>
       <c r="H178" t="n">
-        <v>6.72651690391459</v>
+        <v>6.724279871977241</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -14902,16 +14902,16 @@
         <v>1</v>
       </c>
       <c r="M178" t="n">
-        <v>-0.2284830960854096</v>
+        <v>-0.2307201280227593</v>
       </c>
       <c r="N178" t="n">
-        <v>0.2284830960854096</v>
+        <v>0.2307201280227593</v>
       </c>
       <c r="O178" t="n">
         <v>-0.0649999999999995</v>
       </c>
       <c r="P178" t="n">
-        <v>0.2069749053628165</v>
+        <v>0.2047378734254668</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
@@ -14951,10 +14951,10 @@
         <v>10</v>
       </c>
       <c r="G179" t="n">
-        <v>0.6839857651245551</v>
+        <v>0.6834992887624467</v>
       </c>
       <c r="H179" t="n">
-        <v>6.806215895610913</v>
+        <v>6.80448079658606</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -14973,16 +14973,16 @@
         <v>1</v>
       </c>
       <c r="M179" t="n">
-        <v>-0.1237841043890864</v>
+        <v>-0.1255192034139396</v>
       </c>
       <c r="N179" t="n">
-        <v>0.1237841043890864</v>
+        <v>0.1255192034139396</v>
       </c>
       <c r="O179" t="n">
         <v>-0.02500000000000036</v>
       </c>
       <c r="P179" t="n">
-        <v>0.07969899169632289</v>
+        <v>0.08020092460881934</v>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
@@ -15022,10 +15022,10 @@
         <v>10</v>
       </c>
       <c r="G180" t="n">
-        <v>0.702491103202847</v>
+        <v>0.7019914651493598</v>
       </c>
       <c r="H180" t="n">
-        <v>6.902775800711744</v>
+        <v>6.901884779516359</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -15044,16 +15044,16 @@
         <v>1</v>
       </c>
       <c r="M180" t="n">
-        <v>-0.007224199288256017</v>
+        <v>-0.008115220483641217</v>
       </c>
       <c r="N180" t="n">
-        <v>0.007224199288256017</v>
+        <v>0.008115220483641217</v>
       </c>
       <c r="O180" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P180" t="n">
-        <v>0.09655990510083079</v>
+        <v>0.09740398293029884</v>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
@@ -15093,10 +15093,10 @@
         <v>10</v>
       </c>
       <c r="G181" t="n">
-        <v>0.7245551601423488</v>
+        <v>0.7240398293029872</v>
       </c>
       <c r="H181" t="n">
-        <v>6.959395017793594</v>
+        <v>6.95893551446183</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -15115,16 +15115,16 @@
         <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>0.02939501779359421</v>
+        <v>0.02893551446183018</v>
       </c>
       <c r="N181" t="n">
-        <v>0.02939501779359421</v>
+        <v>0.02893551446183018</v>
       </c>
       <c r="O181" t="n">
         <v>0.01999999999999957</v>
       </c>
       <c r="P181" t="n">
-        <v>0.0566192170818498</v>
+        <v>0.05705073494547097</v>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
@@ -15164,10 +15164,10 @@
         <v>10</v>
       </c>
       <c r="G182" t="n">
-        <v>0.7601423487544484</v>
+        <v>0.7596017069701281</v>
       </c>
       <c r="H182" t="n">
-        <v>7.191903914590748</v>
+        <v>7.184672830725463</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -15186,16 +15186,16 @@
         <v>1</v>
       </c>
       <c r="M182" t="n">
-        <v>0.271903914590748</v>
+        <v>0.2646728307254635</v>
       </c>
       <c r="N182" t="n">
-        <v>0.271903914590748</v>
+        <v>0.2646728307254635</v>
       </c>
       <c r="O182" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P182" t="n">
-        <v>0.232508896797154</v>
+        <v>0.2257373162636336</v>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
@@ -15235,10 +15235,10 @@
         <v>10</v>
       </c>
       <c r="G183" t="n">
-        <v>0.7871886120996441</v>
+        <v>0.786628733997155</v>
       </c>
       <c r="H183" t="n">
-        <v>7.48982918149466</v>
+        <v>7.465209815078237</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -15257,16 +15257,16 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>0.5898291814946592</v>
+        <v>0.5652098150782363</v>
       </c>
       <c r="N183" t="n">
-        <v>0.5898291814946592</v>
+        <v>0.5652098150782363</v>
       </c>
       <c r="O183" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P183" t="n">
-        <v>0.2979252669039116</v>
+        <v>0.2805369843527732</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
@@ -15306,10 +15306,10 @@
         <v>10</v>
       </c>
       <c r="G184" t="n">
-        <v>0.8192170818505338</v>
+        <v>0.8186344238975818</v>
       </c>
       <c r="H184" t="n">
-        <v>7.826498220640569</v>
+        <v>7.821541251778093</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -15328,16 +15328,16 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>0.9164982206405687</v>
+        <v>0.9115412517780932</v>
       </c>
       <c r="N184" t="n">
-        <v>0.9164982206405687</v>
+        <v>0.9115412517780932</v>
       </c>
       <c r="O184" t="n">
         <v>0.009999999999999787</v>
       </c>
       <c r="P184" t="n">
-        <v>0.3366690391459093</v>
+        <v>0.3563314366998567</v>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
@@ -16933,10 +16933,10 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>0.1814946619217082</v>
+        <v>0.1813655761024182</v>
       </c>
       <c r="H207" t="n">
-        <v>4.226307829181494</v>
+        <v>4.226194879089616</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -16955,16 +16955,16 @@
         <v>1</v>
       </c>
       <c r="M207" t="n">
-        <v>-0.5361921708185049</v>
+        <v>-0.5363051209103835</v>
       </c>
       <c r="N207" t="n">
-        <v>0.5361921708185049</v>
+        <v>0.5363051209103835</v>
       </c>
       <c r="O207" t="n">
         <v>0.1574999999999989</v>
       </c>
       <c r="P207" t="n">
-        <v>-0.6621965154962748</v>
+        <v>-0.6623094655881534</v>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
@@ -17004,10 +17004,10 @@
         <v>10</v>
       </c>
       <c r="G208" t="n">
-        <v>0.1928825622775801</v>
+        <v>0.1927453769559033</v>
       </c>
       <c r="H208" t="n">
-        <v>4.290177935943061</v>
+        <v>4.289217638691323</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -17026,16 +17026,16 @@
         <v>1</v>
       </c>
       <c r="M208" t="n">
-        <v>-0.3798220640569392</v>
+        <v>-0.3807823613086772</v>
       </c>
       <c r="N208" t="n">
-        <v>0.3798220640569392</v>
+        <v>0.3807823613086772</v>
       </c>
       <c r="O208" t="n">
         <v>-0.09249999999999936</v>
       </c>
       <c r="P208" t="n">
-        <v>0.06387010676156635</v>
+        <v>0.063022759601707</v>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
@@ -17075,10 +17075,10 @@
         <v>10</v>
       </c>
       <c r="G209" t="n">
-        <v>0.2291814946619217</v>
+        <v>0.2290184921763869</v>
       </c>
       <c r="H209" t="n">
-        <v>4.590169039145906</v>
+        <v>4.589455903271691</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -17097,16 +17097,16 @@
         <v>1</v>
       </c>
       <c r="M209" t="n">
-        <v>0.09016903914590646</v>
+        <v>0.08945590327169128</v>
       </c>
       <c r="N209" t="n">
-        <v>0.09016903914590646</v>
+        <v>0.08945590327169128</v>
       </c>
       <c r="O209" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P209" t="n">
-        <v>0.2999911032028457</v>
+        <v>0.3002382645803685</v>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
@@ -17146,10 +17146,10 @@
         <v>10</v>
       </c>
       <c r="G210" t="n">
-        <v>0.303914590747331</v>
+        <v>0.3036984352773827</v>
       </c>
       <c r="H210" t="n">
-        <v>5.062866548042704</v>
+        <v>5.061769559032716</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -17168,16 +17168,16 @@
         <v>1</v>
       </c>
       <c r="M210" t="n">
-        <v>0.5653665480427046</v>
+        <v>0.5642695590327165</v>
       </c>
       <c r="N210" t="n">
-        <v>0.5653665480427046</v>
+        <v>0.5642695590327165</v>
       </c>
       <c r="O210" t="n">
         <v>-0.002500000000000391</v>
       </c>
       <c r="P210" t="n">
-        <v>0.4726975088967977</v>
+        <v>0.4723136557610248</v>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
@@ -17217,10 +17217,10 @@
         <v>10</v>
       </c>
       <c r="G211" t="n">
-        <v>0.3722419928825623</v>
+        <v>0.3726884779516358</v>
       </c>
       <c r="H211" t="n">
-        <v>5.442854092526691</v>
+        <v>5.443322901849218</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -17239,16 +17239,16 @@
         <v>1</v>
       </c>
       <c r="M211" t="n">
-        <v>0.8553540925266923</v>
+        <v>0.8558229018492192</v>
       </c>
       <c r="N211" t="n">
-        <v>0.8553540925266923</v>
+        <v>0.8558229018492192</v>
       </c>
       <c r="O211" t="n">
         <v>0.08999999999999897</v>
       </c>
       <c r="P211" t="n">
-        <v>0.3799875444839866</v>
+        <v>0.3815533428165017</v>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
@@ -17288,10 +17288,10 @@
         <v>10</v>
       </c>
       <c r="G212" t="n">
-        <v>0.4092526690391459</v>
+        <v>0.4096728307254623</v>
       </c>
       <c r="H212" t="n">
-        <v>5.60038434163701</v>
+        <v>5.601854907539118</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -17310,16 +17310,16 @@
         <v>1</v>
       </c>
       <c r="M212" t="n">
-        <v>0.6678843416370102</v>
+        <v>0.6693549075391179</v>
       </c>
       <c r="N212" t="n">
-        <v>0.6678843416370102</v>
+        <v>0.6693549075391179</v>
       </c>
       <c r="O212" t="n">
         <v>0.3450000000000015</v>
       </c>
       <c r="P212" t="n">
-        <v>0.1575302491103194</v>
+        <v>0.1585320056899002</v>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
@@ -17359,10 +17359,10 @@
         <v>10</v>
       </c>
       <c r="G213" t="n">
-        <v>0.4049822064056939</v>
+        <v>0.4054054054054054</v>
       </c>
       <c r="H213" t="n">
-        <v>5.592437722419929</v>
+        <v>5.593918918918919</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -17381,16 +17381,16 @@
         <v>1</v>
       </c>
       <c r="M213" t="n">
-        <v>0.9124377224199289</v>
+        <v>0.9139189189189194</v>
       </c>
       <c r="N213" t="n">
-        <v>0.9124377224199289</v>
+        <v>0.9139189189189194</v>
       </c>
       <c r="O213" t="n">
         <v>-0.2525000000000004</v>
       </c>
       <c r="P213" t="n">
-        <v>-0.007946619217081619</v>
+        <v>-0.007935988620198842</v>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
@@ -17430,10 +17430,10 @@
         <v>10</v>
       </c>
       <c r="G214" t="n">
-        <v>0.3843416370106761</v>
+        <v>0.3847795163584637</v>
       </c>
       <c r="H214" t="n">
-        <v>5.508754448398576</v>
+        <v>5.51074679943101</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -17452,16 +17452,16 @@
         <v>1</v>
       </c>
       <c r="M214" t="n">
-        <v>1.038754448398576</v>
+        <v>1.04074679943101</v>
       </c>
       <c r="N214" t="n">
-        <v>1.038754448398576</v>
+        <v>1.04074679943101</v>
       </c>
       <c r="O214" t="n">
         <v>-0.21</v>
       </c>
       <c r="P214" t="n">
-        <v>-0.08368327402135289</v>
+        <v>-0.08317211948790959</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -19057,10 +19057,10 @@
         <v>10</v>
       </c>
       <c r="G237" t="n">
-        <v>0.6747330960854092</v>
+        <v>0.6742532005689901</v>
       </c>
       <c r="H237" t="n">
-        <v>5.168157295373666</v>
+        <v>5.166486486486487</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
@@ -19079,16 +19079,16 @@
         <v>1</v>
       </c>
       <c r="M237" t="n">
-        <v>-0.3343427046263345</v>
+        <v>-0.3360135135135138</v>
       </c>
       <c r="N237" t="n">
-        <v>0.3343427046263345</v>
+        <v>0.3360135135135138</v>
       </c>
       <c r="O237" t="n">
         <v>-0.1549999999999994</v>
       </c>
       <c r="P237" t="n">
-        <v>0.03951862774151493</v>
+        <v>0.03784781885433564</v>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
@@ -19128,10 +19128,10 @@
         <v>10</v>
       </c>
       <c r="G238" t="n">
-        <v>0.6555160142348755</v>
+        <v>0.655049786628734</v>
       </c>
       <c r="H238" t="n">
-        <v>5.11056512455516</v>
+        <v>5.10981981981982</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -19150,16 +19150,16 @@
         <v>1</v>
       </c>
       <c r="M238" t="n">
-        <v>-0.3444348754448399</v>
+        <v>-0.3451801801801802</v>
       </c>
       <c r="N238" t="n">
-        <v>0.3444348754448399</v>
+        <v>0.3451801801801802</v>
       </c>
       <c r="O238" t="n">
         <v>-0.04750000000000032</v>
       </c>
       <c r="P238" t="n">
-        <v>-0.05759217081850565</v>
+        <v>-0.05666666666666664</v>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
@@ -19199,10 +19199,10 @@
         <v>10</v>
       </c>
       <c r="G239" t="n">
-        <v>0.6498220640569395</v>
+        <v>0.6493598862019915</v>
       </c>
       <c r="H239" t="n">
-        <v>5.090058362989324</v>
+        <v>5.087513513513514</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -19221,16 +19221,16 @@
         <v>1</v>
       </c>
       <c r="M239" t="n">
-        <v>-0.2974416370106763</v>
+        <v>-0.2999864864864863</v>
       </c>
       <c r="N239" t="n">
-        <v>0.2974416370106763</v>
+        <v>0.2999864864864863</v>
       </c>
       <c r="O239" t="n">
         <v>-0.06749999999999989</v>
       </c>
       <c r="P239" t="n">
-        <v>-0.02050676156583631</v>
+        <v>-0.02230630630630603</v>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
@@ -19270,10 +19270,10 @@
         <v>10</v>
       </c>
       <c r="G240" t="n">
-        <v>0.6526690391459075</v>
+        <v>0.6522048364153628</v>
       </c>
       <c r="H240" t="n">
-        <v>5.104090154211151</v>
+        <v>5.102972972972973</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
@@ -19292,16 +19292,16 @@
         <v>1</v>
       </c>
       <c r="M240" t="n">
-        <v>-0.1784098457888499</v>
+        <v>-0.1795270270270279</v>
       </c>
       <c r="N240" t="n">
-        <v>0.1784098457888499</v>
+        <v>0.1795270270270279</v>
       </c>
       <c r="O240" t="n">
         <v>-0.1049999999999995</v>
       </c>
       <c r="P240" t="n">
-        <v>0.01403179122182685</v>
+        <v>0.01545945945945881</v>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
@@ -19341,10 +19341,10 @@
         <v>10</v>
       </c>
       <c r="G241" t="n">
-        <v>0.6676156583629893</v>
+        <v>0.6671408250355618</v>
       </c>
       <c r="H241" t="n">
-        <v>5.152037010676157</v>
+        <v>5.151351351351352</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
@@ -19363,16 +19363,16 @@
         <v>1</v>
       </c>
       <c r="M241" t="n">
-        <v>-0.03046298932384328</v>
+        <v>-0.03114864864864852</v>
       </c>
       <c r="N241" t="n">
-        <v>0.03046298932384328</v>
+        <v>0.03114864864864852</v>
       </c>
       <c r="O241" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P241" t="n">
-        <v>0.04794685646500607</v>
+        <v>0.04837837837837888</v>
       </c>
       <c r="Q241" t="inlineStr">
         <is>
@@ -19412,10 +19412,10 @@
         <v>10</v>
       </c>
       <c r="G242" t="n">
-        <v>0.7131672597864769</v>
+        <v>0.7126600284495022</v>
       </c>
       <c r="H242" t="n">
-        <v>5.324533807829182</v>
+        <v>5.322702702702703</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
@@ -19434,16 +19434,16 @@
         <v>1</v>
       </c>
       <c r="M242" t="n">
-        <v>0.2020338078291823</v>
+        <v>0.2002027027027031</v>
       </c>
       <c r="N242" t="n">
-        <v>0.2020338078291823</v>
+        <v>0.2002027027027031</v>
       </c>
       <c r="O242" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P242" t="n">
-        <v>0.1724967971530251</v>
+        <v>0.1713513513513512</v>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
@@ -19483,10 +19483,10 @@
         <v>10</v>
       </c>
       <c r="G243" t="n">
-        <v>0.7608540925266903</v>
+        <v>0.7603129445234709</v>
       </c>
       <c r="H243" t="n">
-        <v>5.633366548042704</v>
+        <v>5.62945945945946</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -19505,16 +19505,16 @@
         <v>1</v>
       </c>
       <c r="M243" t="n">
-        <v>0.450866548042705</v>
+        <v>0.4469594594594604</v>
       </c>
       <c r="N243" t="n">
-        <v>0.450866548042705</v>
+        <v>0.4469594594594604</v>
       </c>
       <c r="O243" t="n">
         <v>0.05999999999999961</v>
       </c>
       <c r="P243" t="n">
-        <v>0.3088327402135222</v>
+        <v>0.3067567567567568</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
@@ -19554,10 +19554,10 @@
         <v>10</v>
       </c>
       <c r="G244" t="n">
-        <v>0.7914590747330961</v>
+        <v>0.7908961593172119</v>
       </c>
       <c r="H244" t="n">
-        <v>5.822167259786477</v>
+        <v>5.820135135135136</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -19576,16 +19576,16 @@
         <v>1</v>
       </c>
       <c r="M244" t="n">
-        <v>0.5421672597864768</v>
+        <v>0.5401351351351353</v>
       </c>
       <c r="N244" t="n">
-        <v>0.5421672597864768</v>
+        <v>0.5401351351351353</v>
       </c>
       <c r="O244" t="n">
         <v>0.09750000000000103</v>
       </c>
       <c r="P244" t="n">
-        <v>0.1888007117437729</v>
+        <v>0.190675675675676</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -21181,10 +21181,10 @@
         <v>10</v>
       </c>
       <c r="G267" t="n">
-        <v>0.7352313167259786</v>
+        <v>0.7354196301564723</v>
       </c>
       <c r="H267" t="n">
-        <v>10.37646739928826</v>
+        <v>10.37761712660028</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
@@ -21203,16 +21203,16 @@
         <v>1</v>
       </c>
       <c r="M267" t="n">
-        <v>-0.1160326007117423</v>
+        <v>-0.1148828733997149</v>
       </c>
       <c r="N267" t="n">
-        <v>0.1160326007117423</v>
+        <v>0.1148828733997149</v>
       </c>
       <c r="O267" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P267" t="n">
-        <v>0.6455968193606694</v>
+        <v>0.6467465466726967</v>
       </c>
       <c r="Q267" t="inlineStr">
         <is>
@@ -21252,10 +21252,10 @@
         <v>10</v>
       </c>
       <c r="G268" t="n">
-        <v>0.7330960854092526</v>
+        <v>0.7332859174964438</v>
       </c>
       <c r="H268" t="n">
-        <v>10.37047170989324</v>
+        <v>10.37111325496444</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
@@ -21274,16 +21274,16 @@
         <v>1</v>
       </c>
       <c r="M268" t="n">
-        <v>-0.002028290106762753</v>
+        <v>-0.001386745035564019</v>
       </c>
       <c r="N268" t="n">
-        <v>0.002028290106762753</v>
+        <v>0.001386745035564019</v>
       </c>
       <c r="O268" t="n">
         <v>-0.1199999999999992</v>
       </c>
       <c r="P268" t="n">
-        <v>-0.00599568939501971</v>
+        <v>-0.006503871635848313</v>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
@@ -21323,10 +21323,10 @@
         <v>10</v>
       </c>
       <c r="G269" t="n">
-        <v>0.7366548042704626</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="H269" t="n">
-        <v>10.38581193907473</v>
+        <v>10.38708197473684</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
@@ -21345,16 +21345,16 @@
         <v>1</v>
       </c>
       <c r="M269" t="n">
-        <v>0.1158119390747334</v>
+        <v>0.1170819747368412</v>
       </c>
       <c r="N269" t="n">
-        <v>0.1158119390747334</v>
+        <v>0.1170819747368412</v>
       </c>
       <c r="O269" t="n">
         <v>-0.1025000000000009</v>
       </c>
       <c r="P269" t="n">
-        <v>0.01534022918149525</v>
+        <v>0.01596871977240433</v>
       </c>
       <c r="Q269" t="inlineStr">
         <is>
@@ -21394,10 +21394,10 @@
         <v>10</v>
       </c>
       <c r="G270" t="n">
-        <v>0.7409252669039146</v>
+        <v>0.7411095305832148</v>
       </c>
       <c r="H270" t="n">
-        <v>10.40048796740747</v>
+        <v>10.40064459327525</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
@@ -21416,16 +21416,16 @@
         <v>1</v>
       </c>
       <c r="M270" t="n">
-        <v>0.2704879674074725</v>
+        <v>0.2706445932752484</v>
       </c>
       <c r="N270" t="n">
-        <v>0.2704879674074725</v>
+        <v>0.2706445932752484</v>
       </c>
       <c r="O270" t="n">
         <v>-0.1399999999999988</v>
       </c>
       <c r="P270" t="n">
-        <v>0.01467602833274029</v>
+        <v>0.01356261853840834</v>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
@@ -21465,10 +21465,10 @@
         <v>10</v>
       </c>
       <c r="G271" t="n">
-        <v>0.7501779359430605</v>
+        <v>0.7503556187766715</v>
       </c>
       <c r="H271" t="n">
-        <v>10.42101525733808</v>
+        <v>10.42162157098151</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
@@ -21487,16 +21487,16 @@
         <v>1</v>
       </c>
       <c r="M271" t="n">
-        <v>0.3885152573380779</v>
+        <v>0.3891215709815086</v>
       </c>
       <c r="N271" t="n">
-        <v>0.3885152573380779</v>
+        <v>0.3891215709815086</v>
       </c>
       <c r="O271" t="n">
         <v>-0.09750000000000014</v>
       </c>
       <c r="P271" t="n">
-        <v>0.02052728993060526</v>
+        <v>0.02097697770626006</v>
       </c>
       <c r="Q271" t="inlineStr">
         <is>
@@ -21536,10 +21536,10 @@
         <v>10</v>
       </c>
       <c r="G272" t="n">
-        <v>0.7594306049822064</v>
+        <v>0.7596017069701281</v>
       </c>
       <c r="H272" t="n">
-        <v>10.45022376690306</v>
+        <v>10.45034116371493</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
@@ -21558,16 +21558,16 @@
         <v>1</v>
       </c>
       <c r="M272" t="n">
-        <v>0.5302237669030596</v>
+        <v>0.5303411637149349</v>
       </c>
       <c r="N272" t="n">
-        <v>0.5302237669030596</v>
+        <v>0.5303411637149349</v>
       </c>
       <c r="O272" t="n">
         <v>-0.1125000000000007</v>
       </c>
       <c r="P272" t="n">
-        <v>0.029208509564981</v>
+        <v>0.02871959273342561</v>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
@@ -21607,10 +21607,10 @@
         <v>10</v>
       </c>
       <c r="G273" t="n">
-        <v>0.7587188612099645</v>
+        <v>0.7588904694167852</v>
       </c>
       <c r="H273" t="n">
-        <v>10.44973542395189</v>
+        <v>10.44985316809161</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -21629,16 +21629,16 @@
         <v>1</v>
       </c>
       <c r="M273" t="n">
-        <v>0.6422354239518864</v>
+        <v>0.6423531680916081</v>
       </c>
       <c r="N273" t="n">
-        <v>0.6422354239518864</v>
+        <v>0.6423531680916081</v>
       </c>
       <c r="O273" t="n">
         <v>-0.1125000000000007</v>
       </c>
       <c r="P273" t="n">
-        <v>-0.0004883429511739479</v>
+        <v>-0.000487995623327464</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -21678,10 +21678,10 @@
         <v>10</v>
       </c>
       <c r="G274" t="n">
-        <v>0.7430604982206406</v>
+        <v>0.7432432432432432</v>
       </c>
       <c r="H274" t="n">
-        <v>10.40339492722183</v>
+        <v>10.40380951063063</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -21700,16 +21700,16 @@
         <v>1</v>
       </c>
       <c r="M274" t="n">
-        <v>0.7133949272218274</v>
+        <v>0.7138095106306306</v>
       </c>
       <c r="N274" t="n">
-        <v>0.7133949272218274</v>
+        <v>0.7138095106306306</v>
       </c>
       <c r="O274" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P274" t="n">
-        <v>-0.04634049673005869</v>
+        <v>-0.04604365746097727</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -23305,10 +23305,10 @@
         <v>10</v>
       </c>
       <c r="G297" t="n">
-        <v>0.9017793594306049</v>
+        <v>0.9018492176386913</v>
       </c>
       <c r="H297" t="n">
-        <v>7.008939501779359</v>
+        <v>7.009211948790895</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
@@ -23327,16 +23327,16 @@
         <v>1</v>
       </c>
       <c r="M297" t="n">
-        <v>4.128939501779359</v>
+        <v>4.129211948790895</v>
       </c>
       <c r="N297" t="n">
-        <v>4.128939501779359</v>
+        <v>4.129211948790895</v>
       </c>
       <c r="O297" t="n">
         <v>-0.1899999999999999</v>
       </c>
       <c r="P297" t="n">
-        <v>-0.04398012168190135</v>
+        <v>-0.04370767467036529</v>
       </c>
       <c r="Q297" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>10</v>
       </c>
       <c r="G298" t="n">
-        <v>0.797153024911032</v>
+        <v>0.7972972972972973</v>
       </c>
       <c r="H298" t="n">
-        <v>6.255558718861209</v>
+        <v>6.255783783783784</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
@@ -23398,16 +23398,16 @@
         <v>1</v>
       </c>
       <c r="M298" t="n">
-        <v>3.505558718861209</v>
+        <v>3.505783783783784</v>
       </c>
       <c r="N298" t="n">
-        <v>3.505558718861209</v>
+        <v>3.505783783783784</v>
       </c>
       <c r="O298" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P298" t="n">
-        <v>-0.7533807829181498</v>
+        <v>-0.7534281650071115</v>
       </c>
       <c r="Q298" t="inlineStr">
         <is>
@@ -23447,10 +23447,10 @@
         <v>10</v>
       </c>
       <c r="G299" t="n">
-        <v>0.6249110320284698</v>
+        <v>0.6251778093883357</v>
       </c>
       <c r="H299" t="n">
-        <v>4.884288256227758</v>
+        <v>4.884548364153627</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
@@ -23469,16 +23469,16 @@
         <v>1</v>
       </c>
       <c r="M299" t="n">
-        <v>2.199288256227758</v>
+        <v>2.199548364153627</v>
       </c>
       <c r="N299" t="n">
-        <v>2.199288256227758</v>
+        <v>2.199548364153627</v>
       </c>
       <c r="O299" t="n">
         <v>-0.06499999999999995</v>
       </c>
       <c r="P299" t="n">
-        <v>-1.371270462633452</v>
+        <v>-1.371235419630157</v>
       </c>
       <c r="Q299" t="inlineStr">
         <is>
@@ -23518,10 +23518,10 @@
         <v>10</v>
       </c>
       <c r="G300" t="n">
-        <v>0.4498220640569395</v>
+        <v>0.4502133712660029</v>
       </c>
       <c r="H300" t="n">
-        <v>4.033576512455516</v>
+        <v>4.033958036984353</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
@@ -23540,16 +23540,16 @@
         <v>1</v>
       </c>
       <c r="M300" t="n">
-        <v>1.418576512455516</v>
+        <v>1.418958036984352</v>
       </c>
       <c r="N300" t="n">
-        <v>1.418576512455516</v>
+        <v>1.418958036984352</v>
       </c>
       <c r="O300" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P300" t="n">
-        <v>-0.8507117437722416</v>
+        <v>-0.8505903271692743</v>
       </c>
       <c r="Q300" t="inlineStr">
         <is>
@@ -23589,10 +23589,10 @@
         <v>10</v>
       </c>
       <c r="G301" t="n">
-        <v>0.3345195729537366</v>
+        <v>0.3349928876244666</v>
       </c>
       <c r="H301" t="n">
-        <v>3.910462633451957</v>
+        <v>3.910647226173542</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
@@ -23611,16 +23611,16 @@
         <v>1</v>
       </c>
       <c r="M301" t="n">
-        <v>1.345462633451957</v>
+        <v>1.345647226173542</v>
       </c>
       <c r="N301" t="n">
-        <v>1.345462633451957</v>
+        <v>1.345647226173542</v>
       </c>
       <c r="O301" t="n">
         <v>-0.05000000000000027</v>
       </c>
       <c r="P301" t="n">
-        <v>-0.1231138790035589</v>
+        <v>-0.1233108108108105</v>
       </c>
       <c r="Q301" t="inlineStr">
         <is>
@@ -23660,10 +23660,10 @@
         <v>10</v>
       </c>
       <c r="G302" t="n">
-        <v>0.3352313167259787</v>
+        <v>0.3357041251778094</v>
       </c>
       <c r="H302" t="n">
-        <v>3.910740213523132</v>
+        <v>3.910924608819346</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
@@ -23682,16 +23682,16 @@
         <v>1</v>
       </c>
       <c r="M302" t="n">
-        <v>1.395740213523132</v>
+        <v>1.395924608819346</v>
       </c>
       <c r="N302" t="n">
-        <v>1.395740213523132</v>
+        <v>1.395924608819346</v>
       </c>
       <c r="O302" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P302" t="n">
-        <v>0.0002775800711742882</v>
+        <v>0.00027738264580357</v>
       </c>
       <c r="Q302" t="inlineStr">
         <is>
@@ -23731,10 +23731,10 @@
         <v>10</v>
       </c>
       <c r="G303" t="n">
-        <v>0.3715302491103203</v>
+        <v>0.3719772403982931</v>
       </c>
       <c r="H303" t="n">
-        <v>3.936345195729538</v>
+        <v>3.936606685633002</v>
       </c>
       <c r="I303" t="inlineStr">
         <is>
@@ -23753,16 +23753,16 @@
         <v>1</v>
       </c>
       <c r="M303" t="n">
-        <v>1.486345195729537</v>
+        <v>1.486606685633002</v>
       </c>
       <c r="N303" t="n">
-        <v>1.486345195729537</v>
+        <v>1.486606685633002</v>
       </c>
       <c r="O303" t="n">
         <v>-0.06499999999999995</v>
       </c>
       <c r="P303" t="n">
-        <v>0.02560498220640595</v>
+        <v>0.02568207681365609</v>
       </c>
       <c r="Q303" t="inlineStr">
         <is>
@@ -23802,10 +23802,10 @@
         <v>10</v>
       </c>
       <c r="G304" t="n">
-        <v>0.3459074733096085</v>
+        <v>0.3463726884779517</v>
       </c>
       <c r="H304" t="n">
-        <v>3.921163701067615</v>
+        <v>3.921798719772404</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
@@ -23824,16 +23824,16 @@
         <v>1</v>
       </c>
       <c r="M304" t="n">
-        <v>1.531163701067615</v>
+        <v>1.531798719772404</v>
       </c>
       <c r="N304" t="n">
-        <v>1.531163701067615</v>
+        <v>1.531798719772404</v>
       </c>
       <c r="O304" t="n">
         <v>-0.06000000000000005</v>
       </c>
       <c r="P304" t="n">
-        <v>-0.0151814946619222</v>
+        <v>-0.01480796586059796</v>
       </c>
       <c r="Q304" t="inlineStr">
         <is>
@@ -25429,10 +25429,10 @@
         <v>10</v>
       </c>
       <c r="G327" t="n">
-        <v>0.9124555160142349</v>
+        <v>0.9125177809388336</v>
       </c>
       <c r="H327" t="n">
-        <v>7.300846975088969</v>
+        <v>7.301586059743956</v>
       </c>
       <c r="I327" t="inlineStr">
         <is>
@@ -25451,16 +25451,16 @@
         <v>1</v>
       </c>
       <c r="M327" t="n">
-        <v>1.520846975088968</v>
+        <v>1.521586059743956</v>
       </c>
       <c r="N327" t="n">
-        <v>1.520846975088968</v>
+        <v>1.521586059743956</v>
       </c>
       <c r="O327" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P327" t="n">
-        <v>2.163076036155828</v>
+        <v>2.163815120810815</v>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
@@ -25500,10 +25500,10 @@
         <v>10</v>
       </c>
       <c r="G328" t="n">
-        <v>0.9053380782918149</v>
+        <v>0.9054054054054054</v>
       </c>
       <c r="H328" t="n">
-        <v>7.22908896797153</v>
+        <v>7.231486486486487</v>
       </c>
       <c r="I328" t="inlineStr">
         <is>
@@ -25522,16 +25522,16 @@
         <v>1</v>
       </c>
       <c r="M328" t="n">
-        <v>1.471588967971529</v>
+        <v>1.473986486486487</v>
       </c>
       <c r="N328" t="n">
-        <v>1.471588967971529</v>
+        <v>1.473986486486487</v>
       </c>
       <c r="O328" t="n">
         <v>-0.02249999999999996</v>
       </c>
       <c r="P328" t="n">
-        <v>-0.07175800711743907</v>
+        <v>-0.07009957325746896</v>
       </c>
       <c r="Q328" t="inlineStr">
         <is>
@@ -25571,10 +25571,10 @@
         <v>10</v>
       </c>
       <c r="G329" t="n">
-        <v>0.8996441281138789</v>
+        <v>0.8997155049786629</v>
       </c>
       <c r="H329" t="n">
-        <v>7.166020462633453</v>
+        <v>7.166179320768137</v>
       </c>
       <c r="I329" t="inlineStr">
         <is>
@@ -25593,16 +25593,16 @@
         <v>1</v>
       </c>
       <c r="M329" t="n">
-        <v>1.416020462633453</v>
+        <v>1.416179320768137</v>
       </c>
       <c r="N329" t="n">
-        <v>1.416020462633453</v>
+        <v>1.416179320768137</v>
       </c>
       <c r="O329" t="n">
         <v>-0.007500000000000284</v>
       </c>
       <c r="P329" t="n">
-        <v>-0.06306850533807662</v>
+        <v>-0.06530716571834994</v>
       </c>
       <c r="Q329" t="inlineStr">
         <is>
@@ -25642,10 +25642,10 @@
         <v>10</v>
       </c>
       <c r="G330" t="n">
-        <v>0.8975088967971531</v>
+        <v>0.8975817923186344</v>
       </c>
       <c r="H330" t="n">
-        <v>7.160857651245553</v>
+        <v>7.161073968705549</v>
       </c>
       <c r="I330" t="inlineStr">
         <is>
@@ -25664,16 +25664,16 @@
         <v>1</v>
       </c>
       <c r="M330" t="n">
-        <v>1.410857651245553</v>
+        <v>1.411073968705549</v>
       </c>
       <c r="N330" t="n">
-        <v>1.410857651245553</v>
+        <v>1.411073968705549</v>
       </c>
       <c r="O330" t="n">
         <v>0</v>
       </c>
       <c r="P330" t="n">
-        <v>-0.005162811387900312</v>
+        <v>-0.005105352062588331</v>
       </c>
       <c r="Q330" t="inlineStr">
         <is>
@@ -25713,10 +25713,10 @@
         <v>10</v>
       </c>
       <c r="G331" t="n">
-        <v>0.896085409252669</v>
+        <v>0.8961593172119487</v>
       </c>
       <c r="H331" t="n">
-        <v>7.137556346381969</v>
+        <v>7.139018492176387</v>
       </c>
       <c r="I331" t="inlineStr">
         <is>
@@ -25735,16 +25735,16 @@
         <v>1</v>
       </c>
       <c r="M331" t="n">
-        <v>1.387556346381969</v>
+        <v>1.389018492176387</v>
       </c>
       <c r="N331" t="n">
-        <v>1.387556346381969</v>
+        <v>1.389018492176387</v>
       </c>
       <c r="O331" t="n">
         <v>0</v>
       </c>
       <c r="P331" t="n">
-        <v>-0.02330130486358328</v>
+        <v>-0.02205547652916184</v>
       </c>
       <c r="Q331" t="inlineStr">
         <is>
@@ -25784,10 +25784,10 @@
         <v>10</v>
       </c>
       <c r="G332" t="n">
-        <v>0.894661921708185</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="H332" t="n">
-        <v>7.109274021352314</v>
+        <v>7.110877192982457</v>
       </c>
       <c r="I332" t="inlineStr">
         <is>
@@ -25806,16 +25806,16 @@
         <v>1</v>
       </c>
       <c r="M332" t="n">
-        <v>1.359274021352314</v>
+        <v>1.360877192982457</v>
       </c>
       <c r="N332" t="n">
-        <v>1.359274021352314</v>
+        <v>1.360877192982457</v>
       </c>
       <c r="O332" t="n">
         <v>0</v>
       </c>
       <c r="P332" t="n">
-        <v>-0.02828232502965555</v>
+        <v>-0.02814129919392983</v>
       </c>
       <c r="Q332" t="inlineStr">
         <is>
@@ -25855,10 +25855,10 @@
         <v>10</v>
       </c>
       <c r="G333" t="n">
-        <v>0.8932384341637011</v>
+        <v>0.8933143669985776</v>
       </c>
       <c r="H333" t="n">
-        <v>7.082740213523132</v>
+        <v>7.083641536273117</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -25877,16 +25877,16 @@
         <v>1</v>
       </c>
       <c r="M333" t="n">
-        <v>1.332740213523132</v>
+        <v>1.333641536273117</v>
       </c>
       <c r="N333" t="n">
-        <v>1.332740213523132</v>
+        <v>1.333641536273117</v>
       </c>
       <c r="O333" t="n">
         <v>0</v>
       </c>
       <c r="P333" t="n">
-        <v>-0.02653380782918191</v>
+        <v>-0.02723565670934036</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -25926,10 +25926,10 @@
         <v>10</v>
       </c>
       <c r="G334" t="n">
-        <v>0.8918149466192171</v>
+        <v>0.8918918918918919</v>
       </c>
       <c r="H334" t="n">
-        <v>7.072921708185054</v>
+        <v>7.073378378378378</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -25948,16 +25948,16 @@
         <v>1</v>
       </c>
       <c r="M334" t="n">
-        <v>1.332921708185054</v>
+        <v>1.333378378378378</v>
       </c>
       <c r="N334" t="n">
-        <v>1.332921708185054</v>
+        <v>1.333378378378378</v>
       </c>
       <c r="O334" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P334" t="n">
-        <v>-0.009818505338078154</v>
+        <v>-0.01026315789473831</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>9</v>
       </c>
       <c r="D366" t="n">
-        <v>12240</v>
+        <v>12238.1796875</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -28186,10 +28186,10 @@
         <v>9</v>
       </c>
       <c r="G366" t="n">
-        <v>0.7878349022447502</v>
+        <v>0.7863866763215062</v>
       </c>
       <c r="H366" t="n">
-        <v>5.50891962346126</v>
+        <v>5.507267197682839</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -28208,16 +28208,16 @@
         <v>1</v>
       </c>
       <c r="M366" t="n">
-        <v>0.7214196234612587</v>
+        <v>0.7197671976828373</v>
       </c>
       <c r="N366" t="n">
-        <v>0.7214196234612587</v>
+        <v>0.7197671976828373</v>
       </c>
       <c r="O366" t="n">
         <v>0.007500000000001172</v>
       </c>
       <c r="P366" t="n">
-        <v>-0.06429785179821401</v>
+        <v>-0.06595027757663541</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>9</v>
       </c>
       <c r="D367" t="n">
-        <v>12080</v>
+        <v>12079.1484375</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>0.0149999999999979</v>
       </c>
       <c r="P367" t="n">
-        <v>-0.06346705286024612</v>
+        <v>-0.06181462708182472</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -28317,7 +28317,7 @@
         <v>9</v>
       </c>
       <c r="D368" t="n">
-        <v>11960</v>
+        <v>11957.14453125</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -28328,10 +28328,10 @@
         <v>9</v>
       </c>
       <c r="G368" t="n">
-        <v>0.7566980448950036</v>
+        <v>0.7559739319333816</v>
       </c>
       <c r="H368" t="n">
-        <v>5.388481173062997</v>
+        <v>5.386415640839971</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -28350,16 +28350,16 @@
         <v>1</v>
       </c>
       <c r="M368" t="n">
-        <v>0.5984811730629973</v>
+        <v>0.5964156408399708</v>
       </c>
       <c r="N368" t="n">
-        <v>0.5984811730629973</v>
+        <v>0.5964156408399708</v>
       </c>
       <c r="O368" t="n">
         <v>-0.01249999999999929</v>
       </c>
       <c r="P368" t="n">
-        <v>-0.05697139753801661</v>
+        <v>-0.05903692976104313</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>9</v>
       </c>
       <c r="D369" t="n">
-        <v>11840</v>
+        <v>11837.7177734375</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -28399,10 +28399,10 @@
         <v>9</v>
       </c>
       <c r="G369" t="n">
-        <v>0.7480086893555394</v>
+        <v>0.7472845763939174</v>
       </c>
       <c r="H369" t="n">
-        <v>5.35947791455467</v>
+        <v>5.35865170166546</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -28421,16 +28421,16 @@
         <v>1</v>
       </c>
       <c r="M369" t="n">
-        <v>0.5744779145546701</v>
+        <v>0.5736517016654599</v>
       </c>
       <c r="N369" t="n">
-        <v>0.5744779145546701</v>
+        <v>0.5736517016654599</v>
       </c>
       <c r="O369" t="n">
         <v>-0.004999999999999893</v>
       </c>
       <c r="P369" t="n">
-        <v>-0.02900325850832708</v>
+        <v>-0.02776393917451081</v>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>9</v>
       </c>
       <c r="D370" t="n">
-        <v>11770</v>
+        <v>11750</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>0.08999999999999986</v>
       </c>
       <c r="P370" t="n">
-        <v>-0.03008834178131714</v>
+        <v>-0.02926212889210689</v>
       </c>
       <c r="Q370" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>9</v>
       </c>
       <c r="D371" t="n">
-        <v>11690</v>
+        <v>11686.0283203125</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>9</v>
       </c>
       <c r="D372" t="n">
-        <v>11591.4931640625</v>
+        <v>11591.37109375</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -28754,10 +28754,10 @@
         <v>9</v>
       </c>
       <c r="G374" t="n">
-        <v>0.7103548153511948</v>
+        <v>0.7110789283128168</v>
       </c>
       <c r="H374" t="n">
-        <v>5.252574221578566</v>
+        <v>5.25670528602462</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -28776,16 +28776,16 @@
         <v>1</v>
       </c>
       <c r="M374" t="n">
-        <v>0.2175742215785661</v>
+        <v>0.22170528602462</v>
       </c>
       <c r="N374" t="n">
-        <v>0.2175742215785661</v>
+        <v>0.22170528602462</v>
       </c>
       <c r="O374" t="n">
         <v>0.1200000000000001</v>
       </c>
       <c r="P374" t="n">
-        <v>-0.01849927588703792</v>
+        <v>-0.01436821144098399</v>
       </c>
       <c r="Q374" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>9</v>
       </c>
       <c r="D375" t="n">
-        <v>11320.888671875</v>
+        <v>11320</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>0.3550000000000004</v>
       </c>
       <c r="P375" t="n">
-        <v>-0.04477009413468469</v>
+        <v>-0.04890115858073862</v>
       </c>
       <c r="Q375" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>9</v>
       </c>
       <c r="D376" t="n">
-        <v>11220</v>
+        <v>11214.904296875</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -28896,10 +28896,10 @@
         <v>9</v>
       </c>
       <c r="G376" t="n">
-        <v>0.6879073135409124</v>
+        <v>0.6871832005792904</v>
       </c>
       <c r="H376" t="n">
-        <v>5.159217958001449</v>
+        <v>5.152608254887762</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -28918,16 +28918,16 @@
         <v>1</v>
       </c>
       <c r="M376" t="n">
-        <v>-0.6082820419985513</v>
+        <v>-0.6148917451122378</v>
       </c>
       <c r="N376" t="n">
-        <v>0.6082820419985513</v>
+        <v>0.6148917451122378</v>
       </c>
       <c r="O376" t="n">
         <v>0.3774999999999995</v>
       </c>
       <c r="P376" t="n">
-        <v>-0.04858616944243277</v>
+        <v>-0.05519587255611924</v>
       </c>
       <c r="Q376" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
       </c>
       <c r="R376" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S376" t="b">
@@ -28956,7 +28956,7 @@
         <v>9</v>
       </c>
       <c r="D377" t="n">
-        <v>11107.4580078125</v>
+        <v>11100</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>0.2025000000000006</v>
       </c>
       <c r="P377" t="n">
-        <v>-0.0400108616944248</v>
+        <v>-0.03340115858073833</v>
       </c>
       <c r="Q377" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>9</v>
       </c>
       <c r="D379" t="n">
-        <v>10935.080078125</v>
+        <v>10930</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>9</v>
       </c>
       <c r="D380" t="n">
-        <v>10970</v>
+        <v>10964.0595703125</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -29180,10 +29180,10 @@
         <v>9</v>
       </c>
       <c r="G380" t="n">
-        <v>0.664735698769008</v>
+        <v>0.664011585807386</v>
       </c>
       <c r="H380" t="n">
-        <v>5.07231716147719</v>
+        <v>5.069093048515569</v>
       </c>
       <c r="I380" t="inlineStr">
         <is>
@@ -29202,16 +29202,16 @@
         <v>1</v>
       </c>
       <c r="M380" t="n">
-        <v>-1.26268283852281</v>
+        <v>-1.265906951484431</v>
       </c>
       <c r="N380" t="n">
-        <v>1.26268283852281</v>
+        <v>1.265906951484431</v>
       </c>
       <c r="O380" t="n">
         <v>0.002500000000000391</v>
       </c>
       <c r="P380" t="n">
-        <v>0.02456553222302649</v>
+        <v>0.02134141926140565</v>
       </c>
       <c r="Q380" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>-0.2450000000000001</v>
       </c>
       <c r="P381" t="n">
-        <v>0.05931064446053647</v>
+        <v>0.06253475742215731</v>
       </c>
       <c r="Q381" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>9</v>
       </c>
       <c r="D383" t="n">
-        <v>11557.029296875</v>
+        <v>11550</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>9</v>
       </c>
       <c r="D384" t="n">
-        <v>11730</v>
+        <v>11725.8681640625</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>9</v>
       </c>
       <c r="D385" t="n">
-        <v>11660</v>
+        <v>11651.484375</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>9</v>
       </c>
       <c r="D386" t="n">
-        <v>11490</v>
+        <v>11480</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -29677,10 +29677,10 @@
         <v>10</v>
       </c>
       <c r="G387" t="n">
-        <v>0.6498220640569395</v>
+        <v>0.6500711237553343</v>
       </c>
       <c r="H387" t="n">
-        <v>5.880249110320285</v>
+        <v>5.881650071123755</v>
       </c>
       <c r="I387" t="inlineStr">
         <is>
@@ -29699,16 +29699,16 @@
         <v>1</v>
       </c>
       <c r="M387" t="n">
-        <v>0.9452491103202849</v>
+        <v>0.9466500711237558</v>
       </c>
       <c r="N387" t="n">
-        <v>0.9452491103202849</v>
+        <v>0.9466500711237558</v>
       </c>
       <c r="O387" t="n">
         <v>-0.1124999999999998</v>
       </c>
       <c r="P387" t="n">
-        <v>0.6112682993137675</v>
+        <v>0.6126692601172383</v>
       </c>
       <c r="Q387" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>10</v>
       </c>
       <c r="D388" t="n">
-        <v>11650</v>
+        <v>11640</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -29748,10 +29748,10 @@
         <v>10</v>
       </c>
       <c r="G388" t="n">
-        <v>0.6427046263345195</v>
+        <v>0.6422475106685633</v>
       </c>
       <c r="H388" t="n">
-        <v>5.846737841043891</v>
+        <v>5.845880749170223</v>
       </c>
       <c r="I388" t="inlineStr">
         <is>
@@ -29770,16 +29770,16 @@
         <v>1</v>
       </c>
       <c r="M388" t="n">
-        <v>0.9442378410438907</v>
+        <v>0.9433807491702231</v>
       </c>
       <c r="N388" t="n">
-        <v>0.9442378410438907</v>
+        <v>0.9433807491702231</v>
       </c>
       <c r="O388" t="n">
         <v>-0.03249999999999975</v>
       </c>
       <c r="P388" t="n">
-        <v>-0.03351126927639392</v>
+        <v>-0.03576932195353244</v>
       </c>
       <c r="Q388" t="inlineStr">
         <is>
@@ -29819,10 +29819,10 @@
         <v>10</v>
       </c>
       <c r="G389" t="n">
-        <v>0.6448398576512455</v>
+        <v>0.6443812233285917</v>
       </c>
       <c r="H389" t="n">
-        <v>5.853558718861209</v>
+        <v>5.849881460407776</v>
       </c>
       <c r="I389" t="inlineStr">
         <is>
@@ -29841,16 +29841,16 @@
         <v>1</v>
       </c>
       <c r="M389" t="n">
-        <v>1.006058718861209</v>
+        <v>1.002381460407776</v>
       </c>
       <c r="N389" t="n">
-        <v>1.006058718861209</v>
+        <v>1.002381460407776</v>
       </c>
       <c r="O389" t="n">
         <v>-0.05499999999999972</v>
       </c>
       <c r="P389" t="n">
-        <v>0.00682087781731866</v>
+        <v>0.004000711237552856</v>
       </c>
       <c r="Q389" t="inlineStr">
         <is>
@@ -29890,10 +29890,10 @@
         <v>10</v>
       </c>
       <c r="G390" t="n">
-        <v>0.6626334519572954</v>
+        <v>0.6621621621621622</v>
       </c>
       <c r="H390" t="n">
-        <v>5.909820877817319</v>
+        <v>5.909644144144145</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
@@ -29912,16 +29912,16 @@
         <v>1</v>
       </c>
       <c r="M390" t="n">
-        <v>1.20232087781732</v>
+        <v>1.202144144144145</v>
       </c>
       <c r="N390" t="n">
-        <v>1.20232087781732</v>
+        <v>1.202144144144145</v>
       </c>
       <c r="O390" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P390" t="n">
-        <v>0.05626215895610986</v>
+        <v>0.05976268373636895</v>
       </c>
       <c r="Q390" t="inlineStr">
         <is>
@@ -29961,10 +29961,10 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>0.706049822064057</v>
+        <v>0.7062588904694168</v>
       </c>
       <c r="H391" t="n">
-        <v>6.06153024911032</v>
+        <v>6.062706258890469</v>
       </c>
       <c r="I391" t="inlineStr">
         <is>
@@ -29983,16 +29983,16 @@
         <v>1</v>
       </c>
       <c r="M391" t="n">
-        <v>1.41403024911032</v>
+        <v>1.415206258890469</v>
       </c>
       <c r="N391" t="n">
-        <v>1.41403024911032</v>
+        <v>1.415206258890469</v>
       </c>
       <c r="O391" t="n">
         <v>-0.05999999999999961</v>
       </c>
       <c r="P391" t="n">
-        <v>0.1517093712930011</v>
+        <v>0.1530621147463247</v>
       </c>
       <c r="Q391" t="inlineStr">
         <is>
@@ -30032,10 +30032,10 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>0.7530249110320285</v>
+        <v>0.7524893314366998</v>
       </c>
       <c r="H392" t="n">
-        <v>6.275932892730046</v>
+        <v>6.275072139808982</v>
       </c>
       <c r="I392" t="inlineStr">
         <is>
@@ -30054,16 +30054,16 @@
         <v>1</v>
       </c>
       <c r="M392" t="n">
-        <v>1.488432892730046</v>
+        <v>1.487572139808982</v>
       </c>
       <c r="N392" t="n">
-        <v>1.488432892730046</v>
+        <v>1.487572139808982</v>
       </c>
       <c r="O392" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P392" t="n">
-        <v>0.2144026436197253</v>
+        <v>0.2123658809185125</v>
       </c>
       <c r="Q392" t="inlineStr">
         <is>
@@ -30103,10 +30103,10 @@
         <v>10</v>
       </c>
       <c r="G393" t="n">
-        <v>0.7850533807829182</v>
+        <v>0.7844950213371266</v>
       </c>
       <c r="H393" t="n">
-        <v>6.411481316725979</v>
+        <v>6.410696123755335</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -30125,16 +30125,16 @@
         <v>1</v>
       </c>
       <c r="M393" t="n">
-        <v>1.37148131672598</v>
+        <v>1.370696123755335</v>
       </c>
       <c r="N393" t="n">
-        <v>1.37148131672598</v>
+        <v>1.370696123755335</v>
       </c>
       <c r="O393" t="n">
         <v>0.2524999999999995</v>
       </c>
       <c r="P393" t="n">
-        <v>0.1355484239959335</v>
+        <v>0.1356239839463527</v>
       </c>
       <c r="Q393" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>10</v>
       </c>
       <c r="D394" t="n">
-        <v>13310</v>
+        <v>13289.060546875</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
@@ -30174,10 +30174,10 @@
         <v>10</v>
       </c>
       <c r="G394" t="n">
-        <v>0.80355871886121</v>
+        <v>0.8029871977240398</v>
       </c>
       <c r="H394" t="n">
-        <v>6.488024911032029</v>
+        <v>6.484802987197724</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -30196,16 +30196,16 @@
         <v>1</v>
       </c>
       <c r="M394" t="n">
-        <v>1.428024911032029</v>
+        <v>1.424802987197724</v>
       </c>
       <c r="N394" t="n">
-        <v>1.428024911032029</v>
+        <v>1.424802987197724</v>
       </c>
       <c r="O394" t="n">
         <v>0.02000000000000046</v>
       </c>
       <c r="P394" t="n">
-        <v>0.07654359430604973</v>
+        <v>0.07410686344238915</v>
       </c>
       <c r="Q394" t="inlineStr">
         <is>
@@ -31801,10 +31801,10 @@
         <v>10</v>
       </c>
       <c r="G417" t="n">
-        <v>0.6106761565836299</v>
+        <v>0.6102418207681366</v>
       </c>
       <c r="H417" t="n">
-        <v>6.835500355871886</v>
+        <v>6.833226173541963</v>
       </c>
       <c r="I417" t="inlineStr">
         <is>
@@ -31823,16 +31823,16 @@
         <v>1</v>
       </c>
       <c r="M417" t="n">
-        <v>0.6755003558718862</v>
+        <v>0.6732261735419627</v>
       </c>
       <c r="N417" t="n">
-        <v>0.6755003558718862</v>
+        <v>0.6732261735419627</v>
       </c>
       <c r="O417" t="n">
         <v>-0.04250000000000043</v>
       </c>
       <c r="P417" t="n">
-        <v>0.4227487266177228</v>
+        <v>0.4204745442877993</v>
       </c>
       <c r="Q417" t="inlineStr">
         <is>
@@ -31872,10 +31872,10 @@
         <v>10</v>
       </c>
       <c r="G418" t="n">
-        <v>0.6334519572953736</v>
+        <v>0.6330014224751067</v>
       </c>
       <c r="H418" t="n">
-        <v>6.949110320284698</v>
+        <v>6.947425320056899</v>
       </c>
       <c r="I418" t="inlineStr">
         <is>
@@ -31894,16 +31894,16 @@
         <v>1</v>
       </c>
       <c r="M418" t="n">
-        <v>0.804110320284698</v>
+        <v>0.8024253200568996</v>
       </c>
       <c r="N418" t="n">
-        <v>0.804110320284698</v>
+        <v>0.8024253200568996</v>
       </c>
       <c r="O418" t="n">
         <v>-0.01500000000000057</v>
       </c>
       <c r="P418" t="n">
-        <v>0.1136099644128112</v>
+        <v>0.1141991465149363</v>
       </c>
       <c r="Q418" t="inlineStr">
         <is>
@@ -31943,10 +31943,10 @@
         <v>10</v>
       </c>
       <c r="G419" t="n">
-        <v>0.6946619217081851</v>
+        <v>0.6941678520625889</v>
       </c>
       <c r="H419" t="n">
-        <v>7.231607117437723</v>
+        <v>7.231237553342817</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>
@@ -31965,16 +31965,16 @@
         <v>1</v>
       </c>
       <c r="M419" t="n">
-        <v>1.029107117437723</v>
+        <v>1.028737553342817</v>
       </c>
       <c r="N419" t="n">
-        <v>1.029107117437723</v>
+        <v>1.028737553342817</v>
       </c>
       <c r="O419" t="n">
         <v>0.05750000000000011</v>
       </c>
       <c r="P419" t="n">
-        <v>0.2824967971530254</v>
+        <v>0.2838122332859179</v>
       </c>
       <c r="Q419" t="inlineStr">
         <is>
@@ -32014,10 +32014,10 @@
         <v>10</v>
       </c>
       <c r="G420" t="n">
-        <v>0.7679715302491104</v>
+        <v>0.767425320056899</v>
       </c>
       <c r="H420" t="n">
-        <v>7.580885409252669</v>
+        <v>7.580068278805121</v>
       </c>
       <c r="I420" t="inlineStr">
         <is>
@@ -32036,16 +32036,16 @@
         <v>1</v>
       </c>
       <c r="M420" t="n">
-        <v>1.380885409252669</v>
+        <v>1.380068278805121</v>
       </c>
       <c r="N420" t="n">
-        <v>1.380885409252669</v>
+        <v>1.380068278805121</v>
       </c>
       <c r="O420" t="n">
         <v>-0.002499999999999503</v>
       </c>
       <c r="P420" t="n">
-        <v>0.3492782918149464</v>
+        <v>0.348830725462304</v>
       </c>
       <c r="Q420" t="inlineStr">
         <is>
@@ -32085,10 +32085,10 @@
         <v>10</v>
       </c>
       <c r="G421" t="n">
-        <v>0.8199288256227758</v>
+        <v>0.8193456614509246</v>
       </c>
       <c r="H421" t="n">
-        <v>7.860613523131673</v>
+        <v>7.858705547652916</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
@@ -32107,16 +32107,16 @@
         <v>1</v>
       </c>
       <c r="M421" t="n">
-        <v>1.720613523131672</v>
+        <v>1.718705547652916</v>
       </c>
       <c r="N421" t="n">
-        <v>1.720613523131672</v>
+        <v>1.718705547652916</v>
       </c>
       <c r="O421" t="n">
         <v>-0.05999999999999961</v>
       </c>
       <c r="P421" t="n">
-        <v>0.2797281138790035</v>
+        <v>0.2786372688477954</v>
       </c>
       <c r="Q421" t="inlineStr">
         <is>
@@ -32156,10 +32156,10 @@
         <v>10</v>
       </c>
       <c r="G422" t="n">
-        <v>0.8619217081850534</v>
+        <v>0.8613086770981507</v>
       </c>
       <c r="H422" t="n">
-        <v>8.091326690391458</v>
+        <v>8.085365576102419</v>
       </c>
       <c r="I422" t="inlineStr">
         <is>
@@ -32178,16 +32178,16 @@
         <v>1</v>
       </c>
       <c r="M422" t="n">
-        <v>1.851326690391459</v>
+        <v>1.845365576102419</v>
       </c>
       <c r="N422" t="n">
-        <v>1.851326690391459</v>
+        <v>1.845365576102419</v>
       </c>
       <c r="O422" t="n">
         <v>0.09999999999999876</v>
       </c>
       <c r="P422" t="n">
-        <v>0.2307131672597853</v>
+        <v>0.2266600284495022</v>
       </c>
       <c r="Q422" t="inlineStr">
         <is>
@@ -32227,10 +32227,10 @@
         <v>10</v>
       </c>
       <c r="G423" t="n">
-        <v>0.8768683274021353</v>
+        <v>0.8762446657183499</v>
       </c>
       <c r="H423" t="n">
-        <v>8.159487544483985</v>
+        <v>8.157155049786628</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -32249,16 +32249,16 @@
         <v>1</v>
       </c>
       <c r="M423" t="n">
-        <v>1.564487544483985</v>
+        <v>1.562155049786627</v>
       </c>
       <c r="N423" t="n">
-        <v>1.564487544483985</v>
+        <v>1.562155049786627</v>
       </c>
       <c r="O423" t="n">
         <v>0.3550000000000013</v>
       </c>
       <c r="P423" t="n">
-        <v>0.06816085409252715</v>
+        <v>0.07178947368420907</v>
       </c>
       <c r="Q423" t="inlineStr">
         <is>
@@ -32298,10 +32298,10 @@
         <v>10</v>
       </c>
       <c r="G424" t="n">
-        <v>0.8868327402135231</v>
+        <v>0.8862019914651493</v>
       </c>
       <c r="H424" t="n">
-        <v>8.215602372479241</v>
+        <v>8.214344238975817</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -32320,16 +32320,16 @@
         <v>1</v>
       </c>
       <c r="M424" t="n">
-        <v>1.505602372479241</v>
+        <v>1.504344238975817</v>
       </c>
       <c r="N424" t="n">
-        <v>1.505602372479241</v>
+        <v>1.504344238975817</v>
       </c>
       <c r="O424" t="n">
         <v>0.1149999999999993</v>
       </c>
       <c r="P424" t="n">
-        <v>0.05611482799525547</v>
+        <v>0.0571891891891898</v>
       </c>
       <c r="Q424" t="inlineStr">
         <is>
@@ -33925,10 +33925,10 @@
         <v>10</v>
       </c>
       <c r="G447" t="n">
-        <v>0.6427046263345195</v>
+        <v>0.6429587482219061</v>
       </c>
       <c r="H447" t="n">
-        <v>6.146483985765124</v>
+        <v>6.147581792318634</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
@@ -33947,16 +33947,16 @@
         <v>1</v>
       </c>
       <c r="M447" t="n">
-        <v>2.386483985765124</v>
+        <v>2.387581792318634</v>
       </c>
       <c r="N447" t="n">
-        <v>2.386483985765124</v>
+        <v>2.387581792318634</v>
       </c>
       <c r="O447" t="n">
         <v>-0.4550000000000001</v>
       </c>
       <c r="P447" t="n">
-        <v>-0.03944939584240714</v>
+        <v>-0.03835158928889726</v>
       </c>
       <c r="Q447" t="inlineStr">
         <is>
@@ -33996,10 +33996,10 @@
         <v>10</v>
       </c>
       <c r="G448" t="n">
-        <v>0.4256227758007117</v>
+        <v>0.4260312944523471</v>
       </c>
       <c r="H448" t="n">
-        <v>5.43579359430605</v>
+        <v>5.43697012802276</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
@@ -34018,16 +34018,16 @@
         <v>1</v>
       </c>
       <c r="M448" t="n">
-        <v>1.89579359430605</v>
+        <v>1.89697012802276</v>
       </c>
       <c r="N448" t="n">
-        <v>1.89579359430605</v>
+        <v>1.89697012802276</v>
       </c>
       <c r="O448" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P448" t="n">
-        <v>-0.7106903914590736</v>
+        <v>-0.7106116642958735</v>
       </c>
       <c r="Q448" t="inlineStr">
         <is>
@@ -34067,10 +34067,10 @@
         <v>10</v>
       </c>
       <c r="G449" t="n">
-        <v>0.306049822064057</v>
+        <v>0.3065433854907539</v>
       </c>
       <c r="H449" t="n">
-        <v>4.411281138790035</v>
+        <v>4.452503556187767</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
@@ -34089,16 +34089,16 @@
         <v>1</v>
       </c>
       <c r="M449" t="n">
-        <v>1.001281138790035</v>
+        <v>1.042503556187767</v>
       </c>
       <c r="N449" t="n">
-        <v>1.001281138790035</v>
+        <v>1.042503556187767</v>
       </c>
       <c r="O449" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P449" t="n">
-        <v>-1.024512455516015</v>
+        <v>-0.984466571834993</v>
       </c>
       <c r="Q449" t="inlineStr">
         <is>
@@ -34138,10 +34138,10 @@
         <v>10</v>
       </c>
       <c r="G450" t="n">
-        <v>0.2775800711743772</v>
+        <v>0.2780938833570413</v>
       </c>
       <c r="H450" t="n">
-        <v>4.017722419928825</v>
+        <v>4.020455192034139</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
@@ -34160,16 +34160,16 @@
         <v>1</v>
       </c>
       <c r="M450" t="n">
-        <v>0.6377224199288252</v>
+        <v>0.640455192034139</v>
       </c>
       <c r="N450" t="n">
-        <v>0.6377224199288252</v>
+        <v>0.640455192034139</v>
       </c>
       <c r="O450" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P450" t="n">
-        <v>-0.3935587188612102</v>
+        <v>-0.4320483641536281</v>
       </c>
       <c r="Q450" t="inlineStr">
         <is>
@@ -34209,10 +34209,10 @@
         <v>10</v>
       </c>
       <c r="G451" t="n">
-        <v>0.3238434163701068</v>
+        <v>0.3243243243243243</v>
       </c>
       <c r="H451" t="n">
-        <v>4.755444839857651</v>
+        <v>4.755675675675676</v>
       </c>
       <c r="I451" t="inlineStr">
         <is>
@@ -34231,16 +34231,16 @@
         <v>1</v>
       </c>
       <c r="M451" t="n">
-        <v>1.340444839857651</v>
+        <v>1.340675675675675</v>
       </c>
       <c r="N451" t="n">
-        <v>1.340444839857651</v>
+        <v>1.340675675675675</v>
       </c>
       <c r="O451" t="n">
         <v>0.03500000000000014</v>
       </c>
       <c r="P451" t="n">
-        <v>0.7377224199288257</v>
+        <v>0.7352204836415366</v>
       </c>
       <c r="Q451" t="inlineStr">
         <is>
@@ -34280,10 +34280,10 @@
         <v>10</v>
       </c>
       <c r="G452" t="n">
-        <v>0.3921708185053381</v>
+        <v>0.3926031294452347</v>
       </c>
       <c r="H452" t="n">
-        <v>5.287807829181495</v>
+        <v>5.292230440967283</v>
       </c>
       <c r="I452" t="inlineStr">
         <is>
@@ -34302,16 +34302,16 @@
         <v>1</v>
       </c>
       <c r="M452" t="n">
-        <v>1.822807829181495</v>
+        <v>1.827230440967283</v>
       </c>
       <c r="N452" t="n">
-        <v>1.822807829181495</v>
+        <v>1.827230440967283</v>
       </c>
       <c r="O452" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P452" t="n">
-        <v>0.5323629893238442</v>
+        <v>0.5365547652916076</v>
       </c>
       <c r="Q452" t="inlineStr">
         <is>
@@ -34351,10 +34351,10 @@
         <v>10</v>
       </c>
       <c r="G453" t="n">
-        <v>0.3658362989323843</v>
+        <v>0.3662873399715505</v>
       </c>
       <c r="H453" t="n">
-        <v>5.101238434163701</v>
+        <v>5.107083926031295</v>
       </c>
       <c r="I453" t="inlineStr">
         <is>
@@ -34373,16 +34373,16 @@
         <v>1</v>
       </c>
       <c r="M453" t="n">
-        <v>1.678738434163701</v>
+        <v>1.684583926031295</v>
       </c>
       <c r="N453" t="n">
-        <v>1.678738434163701</v>
+        <v>1.684583926031295</v>
       </c>
       <c r="O453" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P453" t="n">
-        <v>-0.186569395017794</v>
+        <v>-0.1851465149359885</v>
       </c>
       <c r="Q453" t="inlineStr">
         <is>
@@ -34422,10 +34422,10 @@
         <v>10</v>
       </c>
       <c r="G454" t="n">
-        <v>0.2718861209964413</v>
+        <v>0.2724039829302987</v>
       </c>
       <c r="H454" t="n">
-        <v>3.976516014234875</v>
+        <v>3.97726173541963</v>
       </c>
       <c r="I454" t="inlineStr">
         <is>
@@ -34444,16 +34444,16 @@
         <v>1</v>
       </c>
       <c r="M454" t="n">
-        <v>0.756516014234875</v>
+        <v>0.7572617354196298</v>
       </c>
       <c r="N454" t="n">
-        <v>0.756516014234875</v>
+        <v>0.7572617354196298</v>
       </c>
       <c r="O454" t="n">
         <v>-0.2024999999999997</v>
       </c>
       <c r="P454" t="n">
-        <v>-1.124722419928826</v>
+        <v>-1.129822190611665</v>
       </c>
       <c r="Q454" t="inlineStr">
         <is>
@@ -36049,10 +36049,10 @@
         <v>10</v>
       </c>
       <c r="G477" t="n">
-        <v>0.7451957295373666</v>
+        <v>0.7453769559032717</v>
       </c>
       <c r="H477" t="n">
-        <v>3.625879003558719</v>
+        <v>3.626600284495022</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -36071,16 +36071,16 @@
         <v>1</v>
       </c>
       <c r="M477" t="n">
-        <v>-0.1816209964412812</v>
+        <v>-0.1808997155049785</v>
       </c>
       <c r="N477" t="n">
-        <v>0.1816209964412812</v>
+        <v>0.1808997155049785</v>
       </c>
       <c r="O477" t="n">
         <v>-0.105</v>
       </c>
       <c r="P477" t="n">
-        <v>0.4712982649634982</v>
+        <v>0.4720195458998009</v>
       </c>
       <c r="Q477" t="inlineStr">
         <is>
@@ -36120,10 +36120,10 @@
         <v>10</v>
       </c>
       <c r="G478" t="n">
-        <v>0.7373665480427046</v>
+        <v>0.7375533428165008</v>
       </c>
       <c r="H478" t="n">
-        <v>3.599718861209964</v>
+        <v>3.600462304409673</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
@@ -36142,16 +36142,16 @@
         <v>1</v>
       </c>
       <c r="M478" t="n">
-        <v>-0.07278113879003545</v>
+        <v>-0.07203769559032658</v>
       </c>
       <c r="N478" t="n">
-        <v>0.07278113879003545</v>
+        <v>0.07203769559032658</v>
       </c>
       <c r="O478" t="n">
         <v>-0.1350000000000002</v>
       </c>
       <c r="P478" t="n">
-        <v>-0.02616014234875452</v>
+        <v>-0.02613798008534829</v>
       </c>
       <c r="Q478" t="inlineStr">
         <is>
@@ -36191,10 +36191,10 @@
         <v>10</v>
       </c>
       <c r="G479" t="n">
-        <v>0.7395017793594306</v>
+        <v>0.7396870554765291</v>
       </c>
       <c r="H479" t="n">
-        <v>3.608217081850534</v>
+        <v>3.608954480796586</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
@@ -36213,16 +36213,16 @@
         <v>1</v>
       </c>
       <c r="M479" t="n">
-        <v>0.05071708185053403</v>
+        <v>0.05145448079658577</v>
       </c>
       <c r="N479" t="n">
-        <v>0.05071708185053403</v>
+        <v>0.05145448079658577</v>
       </c>
       <c r="O479" t="n">
         <v>-0.1149999999999998</v>
       </c>
       <c r="P479" t="n">
-        <v>0.008498220640569709</v>
+        <v>0.008492176386912575</v>
       </c>
       <c r="Q479" t="inlineStr">
         <is>
@@ -36262,10 +36262,10 @@
         <v>10</v>
       </c>
       <c r="G480" t="n">
-        <v>0.7416370106761566</v>
+        <v>0.7418207681365576</v>
       </c>
       <c r="H480" t="n">
-        <v>3.614476868327402</v>
+        <v>3.614964438122333</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
@@ -36284,16 +36284,16 @@
         <v>1</v>
       </c>
       <c r="M480" t="n">
-        <v>0.2219768683274022</v>
+        <v>0.2224644381223331</v>
       </c>
       <c r="N480" t="n">
-        <v>0.2219768683274022</v>
+        <v>0.2224644381223331</v>
       </c>
       <c r="O480" t="n">
         <v>-0.165</v>
       </c>
       <c r="P480" t="n">
-        <v>0.00625978647686809</v>
+        <v>0.006009957325747273</v>
       </c>
       <c r="Q480" t="inlineStr">
         <is>
@@ -36333,10 +36333,10 @@
         <v>10</v>
       </c>
       <c r="G481" t="n">
-        <v>0.7480427046263345</v>
+        <v>0.748221906116643</v>
       </c>
       <c r="H481" t="n">
-        <v>3.633604982206406</v>
+        <v>3.63396159317212</v>
       </c>
       <c r="I481" t="inlineStr">
         <is>
@@ -36355,16 +36355,16 @@
         <v>1</v>
       </c>
       <c r="M481" t="n">
-        <v>0.3711049822064054</v>
+        <v>0.3714615931721195</v>
       </c>
       <c r="N481" t="n">
-        <v>0.3711049822064054</v>
+        <v>0.3714615931721195</v>
       </c>
       <c r="O481" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P481" t="n">
-        <v>0.01912811387900337</v>
+        <v>0.0189971550497865</v>
       </c>
       <c r="Q481" t="inlineStr">
         <is>
@@ -36404,10 +36404,10 @@
         <v>10</v>
       </c>
       <c r="G482" t="n">
-        <v>0.7580071174377224</v>
+        <v>0.7581792318634424</v>
       </c>
       <c r="H482" t="n">
-        <v>3.670934163701068</v>
+        <v>3.67127667140825</v>
       </c>
       <c r="I482" t="inlineStr">
         <is>
@@ -36426,16 +36426,16 @@
         <v>1</v>
       </c>
       <c r="M482" t="n">
-        <v>0.5559341637010675</v>
+        <v>0.5562766714082499</v>
       </c>
       <c r="N482" t="n">
-        <v>0.5559341637010675</v>
+        <v>0.5562766714082499</v>
       </c>
       <c r="O482" t="n">
         <v>-0.1475</v>
       </c>
       <c r="P482" t="n">
-        <v>0.03732918149466213</v>
+        <v>0.03731507823613045</v>
       </c>
       <c r="Q482" t="inlineStr">
         <is>
@@ -36475,10 +36475,10 @@
         <v>10</v>
       </c>
       <c r="G483" t="n">
-        <v>0.7651245551601423</v>
+        <v>0.7652916073968705</v>
       </c>
       <c r="H483" t="n">
-        <v>3.705195729537367</v>
+        <v>3.705860597439545</v>
       </c>
       <c r="I483" t="inlineStr">
         <is>
@@ -36497,16 +36497,16 @@
         <v>1</v>
       </c>
       <c r="M483" t="n">
-        <v>0.8326957295373667</v>
+        <v>0.8333605974395448</v>
       </c>
       <c r="N483" t="n">
-        <v>0.8326957295373667</v>
+        <v>0.8333605974395448</v>
       </c>
       <c r="O483" t="n">
         <v>-0.2425000000000002</v>
       </c>
       <c r="P483" t="n">
-        <v>0.03426156583629902</v>
+        <v>0.03458392603129479</v>
       </c>
       <c r="Q483" t="inlineStr">
         <is>
@@ -36546,10 +36546,10 @@
         <v>10</v>
       </c>
       <c r="G484" t="n">
-        <v>0.7544483985765125</v>
+        <v>0.7546230440967283</v>
       </c>
       <c r="H484" t="n">
-        <v>3.661081850533808</v>
+        <v>3.661359886201991</v>
       </c>
       <c r="I484" t="inlineStr">
         <is>
@@ -36568,16 +36568,16 @@
         <v>1</v>
       </c>
       <c r="M484" t="n">
-        <v>0.9110818505338076</v>
+        <v>0.9113598862019914</v>
       </c>
       <c r="N484" t="n">
-        <v>0.9110818505338076</v>
+        <v>0.9113598862019914</v>
       </c>
       <c r="O484" t="n">
         <v>-0.1225000000000001</v>
       </c>
       <c r="P484" t="n">
-        <v>-0.04411387900355912</v>
+        <v>-0.0445007112375535</v>
       </c>
       <c r="Q484" t="inlineStr">
         <is>
@@ -38173,10 +38173,10 @@
         <v>10</v>
       </c>
       <c r="G507" t="n">
-        <v>0.7067615658362989</v>
+        <v>0.7062588904694168</v>
       </c>
       <c r="H507" t="n">
-        <v>2.642750889679715</v>
+        <v>2.63988857278331</v>
       </c>
       <c r="I507" t="inlineStr">
         <is>
@@ -38195,16 +38195,16 @@
         <v>1</v>
       </c>
       <c r="M507" t="n">
-        <v>0.4927508896797153</v>
+        <v>0.4898885727833102</v>
       </c>
       <c r="N507" t="n">
-        <v>0.4927508896797153</v>
+        <v>0.4898885727833102</v>
       </c>
       <c r="O507" t="n">
         <v>-0.1074999999999999</v>
       </c>
       <c r="P507" t="n">
-        <v>0.6202092531844223</v>
+        <v>0.6173469362880173</v>
       </c>
       <c r="Q507" t="inlineStr">
         <is>
@@ -38244,10 +38244,10 @@
         <v>10</v>
       </c>
       <c r="G508" t="n">
-        <v>0.693950177935943</v>
+        <v>0.6934566145092461</v>
       </c>
       <c r="H508" t="n">
-        <v>2.595845195729538</v>
+        <v>2.595128911806543</v>
       </c>
       <c r="I508" t="inlineStr">
         <is>
@@ -38266,16 +38266,16 @@
         <v>1</v>
       </c>
       <c r="M508" t="n">
-        <v>0.5058451957295378</v>
+        <v>0.5051289118065436</v>
       </c>
       <c r="N508" t="n">
-        <v>0.5058451957295378</v>
+        <v>0.5051289118065436</v>
       </c>
       <c r="O508" t="n">
         <v>-0.06000000000000005</v>
       </c>
       <c r="P508" t="n">
-        <v>-0.04690569395017752</v>
+        <v>-0.04475966097676665</v>
       </c>
       <c r="Q508" t="inlineStr">
         <is>
@@ -38315,10 +38315,10 @@
         <v>10</v>
       </c>
       <c r="G509" t="n">
-        <v>0.6846975088967971</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="H509" t="n">
-        <v>2.559779359430605</v>
+        <v>2.557894736842106</v>
       </c>
       <c r="I509" t="inlineStr">
         <is>
@@ -38337,16 +38337,16 @@
         <v>1</v>
       </c>
       <c r="M509" t="n">
-        <v>0.5122793594306052</v>
+        <v>0.5103947368421058</v>
       </c>
       <c r="N509" t="n">
-        <v>0.5122793594306052</v>
+        <v>0.5103947368421058</v>
       </c>
       <c r="O509" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P509" t="n">
-        <v>-0.03606583629893256</v>
+        <v>-0.03723417496443782</v>
       </c>
       <c r="Q509" t="inlineStr">
         <is>
@@ -38386,10 +38386,10 @@
         <v>10</v>
       </c>
       <c r="G510" t="n">
-        <v>0.6825622775800712</v>
+        <v>0.682076813655761</v>
       </c>
       <c r="H510" t="n">
-        <v>2.551516014234875</v>
+        <v>2.549818634423898</v>
       </c>
       <c r="I510" t="inlineStr">
         <is>
@@ -38408,16 +38408,16 @@
         <v>1</v>
       </c>
       <c r="M510" t="n">
-        <v>0.6790160142348753</v>
+        <v>0.6773186344238975</v>
       </c>
       <c r="N510" t="n">
-        <v>0.6790160142348753</v>
+        <v>0.6773186344238975</v>
       </c>
       <c r="O510" t="n">
         <v>-0.1749999999999998</v>
       </c>
       <c r="P510" t="n">
-        <v>-0.008263345195729688</v>
+        <v>-0.008076102418208109</v>
       </c>
       <c r="Q510" t="inlineStr">
         <is>
@@ -38457,10 +38457,10 @@
         <v>10</v>
       </c>
       <c r="G511" t="n">
-        <v>0.6889679715302491</v>
+        <v>0.6884779516358464</v>
       </c>
       <c r="H511" t="n">
-        <v>2.577364768683274</v>
+        <v>2.576653627311522</v>
       </c>
       <c r="I511" t="inlineStr">
         <is>
@@ -38479,16 +38479,16 @@
         <v>1</v>
       </c>
       <c r="M511" t="n">
-        <v>0.8098647686832741</v>
+        <v>0.8091536273115221</v>
       </c>
       <c r="N511" t="n">
-        <v>0.8098647686832741</v>
+        <v>0.8091536273115221</v>
       </c>
       <c r="O511" t="n">
         <v>-0.105</v>
       </c>
       <c r="P511" t="n">
-        <v>0.02584875444839874</v>
+        <v>0.02683499288762459</v>
       </c>
       <c r="Q511" t="inlineStr">
         <is>
@@ -38528,10 +38528,10 @@
         <v>10</v>
       </c>
       <c r="G512" t="n">
-        <v>0.7145907473309608</v>
+        <v>0.7140825035561877</v>
       </c>
       <c r="H512" t="n">
-        <v>2.677049822064057</v>
+        <v>2.676312233285917</v>
       </c>
       <c r="I512" t="inlineStr">
         <is>
@@ -38550,16 +38550,16 @@
         <v>1</v>
       </c>
       <c r="M512" t="n">
-        <v>0.932049822064057</v>
+        <v>0.9313122332859174</v>
       </c>
       <c r="N512" t="n">
-        <v>0.932049822064057</v>
+        <v>0.9313122332859174</v>
       </c>
       <c r="O512" t="n">
         <v>-0.02249999999999996</v>
       </c>
       <c r="P512" t="n">
-        <v>0.09968505338078293</v>
+        <v>0.09965860597439535</v>
       </c>
       <c r="Q512" t="inlineStr">
         <is>
@@ -38599,10 +38599,10 @@
         <v>10</v>
       </c>
       <c r="G513" t="n">
-        <v>0.7380782918149467</v>
+        <v>0.7375533428165008</v>
       </c>
       <c r="H513" t="n">
-        <v>2.764544483985765</v>
+        <v>2.761497155049787</v>
       </c>
       <c r="I513" t="inlineStr">
         <is>
@@ -38621,16 +38621,16 @@
         <v>1</v>
       </c>
       <c r="M513" t="n">
-        <v>0.9620444839857651</v>
+        <v>0.9589971550497867</v>
       </c>
       <c r="N513" t="n">
-        <v>0.9620444839857651</v>
+        <v>0.9589971550497867</v>
       </c>
       <c r="O513" t="n">
         <v>0.05749999999999988</v>
       </c>
       <c r="P513" t="n">
-        <v>0.08749466192170807</v>
+        <v>0.08518492176386916</v>
       </c>
       <c r="Q513" t="inlineStr">
         <is>
@@ -38670,10 +38670,10 @@
         <v>10</v>
       </c>
       <c r="G514" t="n">
-        <v>0.7672597864768683</v>
+        <v>0.7667140825035562</v>
       </c>
       <c r="H514" t="n">
-        <v>2.875457295373665</v>
+        <v>2.873081436699858</v>
       </c>
       <c r="I514" t="inlineStr">
         <is>
@@ -38692,16 +38692,16 @@
         <v>1</v>
       </c>
       <c r="M514" t="n">
-        <v>0.9754572953736655</v>
+        <v>0.9730814366998581</v>
       </c>
       <c r="N514" t="n">
-        <v>0.9754572953736655</v>
+        <v>0.9730814366998581</v>
       </c>
       <c r="O514" t="n">
         <v>0.09749999999999992</v>
       </c>
       <c r="P514" t="n">
-        <v>0.1109128113879003</v>
+        <v>0.1115842816500714</v>
       </c>
       <c r="Q514" t="inlineStr">
         <is>
@@ -42847,10 +42847,10 @@
         <v>10</v>
       </c>
       <c r="G573" t="n">
-        <v>0.1722419928825623</v>
+        <v>0.1721194879089616</v>
       </c>
       <c r="H573" t="n">
-        <v>128.5506832740214</v>
+        <v>128.5494964438122</v>
       </c>
       <c r="I573" t="inlineStr">
         <is>
@@ -42869,16 +42869,16 @@
         <v>1</v>
       </c>
       <c r="M573" t="n">
-        <v>-1.049316725978628</v>
+        <v>-1.050503556187749</v>
       </c>
       <c r="N573" t="n">
-        <v>1.049316725978628</v>
+        <v>1.050503556187749</v>
       </c>
       <c r="O573" t="n">
         <v>0.4499999999999886</v>
       </c>
       <c r="P573" t="n">
-        <v>-0.2454839055586717</v>
+        <v>-0.2466707357677933</v>
       </c>
       <c r="Q573" t="inlineStr">
         <is>
@@ -42918,10 +42918,10 @@
         <v>10</v>
       </c>
       <c r="G574" t="n">
-        <v>0.2412811387900356</v>
+        <v>0.2418207681365576</v>
       </c>
       <c r="H574" t="n">
-        <v>128.8071862396204</v>
+        <v>128.8087529634898</v>
       </c>
       <c r="I574" t="inlineStr">
         <is>
@@ -42940,16 +42940,16 @@
         <v>1</v>
       </c>
       <c r="M574" t="n">
-        <v>-0.6528137603795869</v>
+        <v>-0.651247036510199</v>
       </c>
       <c r="N574" t="n">
-        <v>0.6528137603795869</v>
+        <v>0.651247036510199</v>
       </c>
       <c r="O574" t="n">
         <v>-0.1399999999999864</v>
       </c>
       <c r="P574" t="n">
-        <v>0.2565029655990543</v>
+        <v>0.2592565196775638</v>
       </c>
       <c r="Q574" t="inlineStr">
         <is>
@@ -43092,38 +43092,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.326000000000001</v>
+        <v>8.324</v>
       </c>
       <c r="G2" t="n">
-        <v>8.568</v>
+        <v>8.512</v>
       </c>
       <c r="H2" t="n">
-        <v>9.069000000000001</v>
+        <v>9.058999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>8.853999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="J2" t="n">
-        <v>8.648999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.205</v>
+        <v>-0.01</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -43168,34 +43168,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.628</v>
+        <v>5.621</v>
       </c>
       <c r="G3" t="n">
-        <v>5.768</v>
+        <v>5.747</v>
       </c>
       <c r="H3" t="n">
-        <v>5.841</v>
+        <v>5.842</v>
       </c>
       <c r="I3" t="n">
-        <v>5.808</v>
+        <v>5.826</v>
       </c>
       <c r="J3" t="n">
-        <v>5.637</v>
+        <v>5.621</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.171</v>
+        <v>-0.205</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -43211,16 +43211,16 @@
         <v>30</v>
       </c>
       <c r="O3" t="n">
-        <v>0.801</v>
+        <v>0.799</v>
       </c>
       <c r="P3" t="n">
-        <v>0.571</v>
+        <v>0.57</v>
       </c>
       <c r="Q3" t="n">
         <v>0.457</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.825</v>
+        <v>-0.823</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -43244,38 +43244,38 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.47</v>
+        <v>4.545</v>
       </c>
       <c r="G4" t="n">
-        <v>4.84</v>
+        <v>4.804</v>
       </c>
       <c r="H4" t="n">
-        <v>5.12</v>
+        <v>5.39</v>
       </c>
       <c r="I4" t="n">
-        <v>4.95</v>
+        <v>4.979</v>
       </c>
       <c r="J4" t="n">
-        <v>4.803</v>
+        <v>5.035</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.147</v>
+        <v>0.056</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -43287,7 +43287,7 @@
         <v>30</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P4" t="n">
         <v>0.787</v>
@@ -43320,34 +43320,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.248</v>
+        <v>11.224</v>
       </c>
       <c r="G5" t="n">
-        <v>11.465</v>
+        <v>11.411</v>
       </c>
       <c r="H5" t="n">
-        <v>11.72</v>
+        <v>11.688</v>
       </c>
       <c r="I5" t="n">
-        <v>11.72</v>
+        <v>11.688</v>
       </c>
       <c r="J5" t="n">
-        <v>11.282</v>
+        <v>11.247</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.438</v>
+        <v>-0.441</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -43366,10 +43366,10 @@
         <v>5.438</v>
       </c>
       <c r="P5" t="n">
-        <v>5.403</v>
+        <v>5.404</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.403</v>
+        <v>5.404</v>
       </c>
       <c r="R5" t="n">
         <v>-0.616</v>
@@ -43396,34 +43396,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.522</v>
+        <v>2.153</v>
       </c>
       <c r="G6" t="n">
-        <v>37.902</v>
+        <v>27.48</v>
       </c>
       <c r="H6" t="n">
-        <v>111.228</v>
+        <v>111.036</v>
       </c>
       <c r="I6" t="n">
-        <v>53.861</v>
+        <v>5.014</v>
       </c>
       <c r="J6" t="n">
-        <v>109.606</v>
+        <v>83.991</v>
       </c>
       <c r="K6" t="n">
-        <v>55.745</v>
+        <v>78.977</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -43439,13 +43439,13 @@
         <v>30</v>
       </c>
       <c r="O6" t="n">
-        <v>67.65300000000001</v>
+        <v>67.657</v>
       </c>
       <c r="P6" t="n">
-        <v>60.718</v>
+        <v>60.721</v>
       </c>
       <c r="Q6" t="n">
-        <v>42.785</v>
+        <v>42.788</v>
       </c>
       <c r="R6" t="n">
         <v>-0.804</v>
@@ -43472,34 +43472,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>9.272</v>
+        <v>9.234999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>9.368</v>
+        <v>9.358000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>9.455</v>
+        <v>9.457000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>9.347</v>
+        <v>9.363</v>
       </c>
       <c r="J7" t="n">
-        <v>9.273</v>
+        <v>9.236000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.074</v>
+        <v>-0.127</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -43548,38 +43548,38 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.339</v>
+        <v>8.164999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>8.442</v>
+        <v>8.420999999999999</v>
       </c>
       <c r="H8" t="n">
         <v>8.494999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>8.371</v>
+        <v>8.417999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>8.353999999999999</v>
+        <v>8.167999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.017</v>
+        <v>-0.25</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -43591,13 +43591,13 @@
         <v>30</v>
       </c>
       <c r="O8" t="n">
-        <v>1.249</v>
+        <v>1.248</v>
       </c>
       <c r="P8" t="n">
-        <v>0.978</v>
+        <v>0.977</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.738</v>
+        <v>0.737</v>
       </c>
       <c r="R8" t="n">
         <v>-0.897</v>
@@ -43624,12 +43624,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -43639,19 +43639,19 @@
         <v>4.644</v>
       </c>
       <c r="G9" t="n">
-        <v>5.092</v>
+        <v>5.08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.913</v>
+        <v>5.576</v>
       </c>
       <c r="I9" t="n">
-        <v>5.194</v>
+        <v>5.051</v>
       </c>
       <c r="J9" t="n">
-        <v>5.746</v>
+        <v>5.475</v>
       </c>
       <c r="K9" t="n">
-        <v>0.552</v>
+        <v>0.424</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
         <v>0.376</v>
       </c>
       <c r="R9" t="n">
-        <v>0.318</v>
+        <v>0.317</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -43700,38 +43700,38 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.928</v>
+        <v>5.927</v>
       </c>
       <c r="G10" t="n">
-        <v>5.97</v>
+        <v>5.964</v>
       </c>
       <c r="H10" t="n">
         <v>6.006</v>
       </c>
       <c r="I10" t="n">
-        <v>5.976</v>
+        <v>5.997</v>
       </c>
       <c r="J10" t="n">
         <v>5.928</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.048</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -43776,12 +43776,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -43791,19 +43791,19 @@
         <v>10.194</v>
       </c>
       <c r="G11" t="n">
-        <v>10.444</v>
+        <v>10.502</v>
       </c>
       <c r="H11" t="n">
-        <v>10.896</v>
+        <v>10.973</v>
       </c>
       <c r="I11" t="n">
-        <v>10.252</v>
+        <v>10.194</v>
       </c>
       <c r="J11" t="n">
-        <v>10.842</v>
+        <v>10.868</v>
       </c>
       <c r="K11" t="n">
-        <v>0.59</v>
+        <v>0.674</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -43852,34 +43852,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.378</v>
+        <v>2.376</v>
       </c>
       <c r="G12" t="n">
-        <v>3.306</v>
+        <v>3.093</v>
       </c>
       <c r="H12" t="n">
-        <v>5.934</v>
+        <v>6.609</v>
       </c>
       <c r="I12" t="n">
-        <v>3.489</v>
+        <v>3.264</v>
       </c>
       <c r="J12" t="n">
-        <v>3.777</v>
+        <v>4.41</v>
       </c>
       <c r="K12" t="n">
-        <v>0.288</v>
+        <v>1.146</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>1.683</v>
       </c>
       <c r="P12" t="n">
-        <v>1.12</v>
+        <v>1.121</v>
       </c>
       <c r="Q12" t="n">
         <v>1.076</v>
@@ -43928,34 +43928,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.729</v>
+        <v>6.717</v>
       </c>
       <c r="G13" t="n">
-        <v>6.872</v>
+        <v>6.828</v>
       </c>
       <c r="H13" t="n">
-        <v>7.027</v>
+        <v>6.921</v>
       </c>
       <c r="I13" t="n">
-        <v>7.027</v>
+        <v>6.92</v>
       </c>
       <c r="J13" t="n">
-        <v>6.748</v>
+        <v>6.721</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.279</v>
+        <v>-0.199</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -43974,10 +43974,10 @@
         <v>0.903</v>
       </c>
       <c r="P13" t="n">
-        <v>0.804</v>
+        <v>0.805</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.263</v>
+        <v>0.264</v>
       </c>
       <c r="R13" t="n">
         <v>-0.328</v>
@@ -44004,34 +44004,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.545</v>
+        <v>10.402</v>
       </c>
       <c r="G14" t="n">
-        <v>10.865</v>
+        <v>10.768</v>
       </c>
       <c r="H14" t="n">
-        <v>11.082</v>
+        <v>10.959</v>
       </c>
       <c r="I14" t="n">
-        <v>11.082</v>
+        <v>10.93</v>
       </c>
       <c r="J14" t="n">
-        <v>10.681</v>
+        <v>10.5</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4</v>
+        <v>-0.43</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -44080,34 +44080,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>4.715</v>
+        <v>4.561</v>
       </c>
       <c r="G15" t="n">
-        <v>4.865</v>
+        <v>4.622</v>
       </c>
       <c r="H15" t="n">
-        <v>5.031</v>
+        <v>4.71</v>
       </c>
       <c r="I15" t="n">
-        <v>4.715</v>
+        <v>4.561</v>
       </c>
       <c r="J15" t="n">
-        <v>5.014</v>
+        <v>4.696</v>
       </c>
       <c r="K15" t="n">
-        <v>0.298</v>
+        <v>0.134</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -44129,10 +44129,10 @@
         <v>0.741</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.273</v>
+        <v>0.272</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.597</v>
+        <v>-0.598</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -44156,34 +44156,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>8.002000000000001</v>
+        <v>7.98</v>
       </c>
       <c r="G16" t="n">
-        <v>8.114000000000001</v>
+        <v>8.087</v>
       </c>
       <c r="H16" t="n">
-        <v>8.217000000000001</v>
+        <v>8.195</v>
       </c>
       <c r="I16" t="n">
-        <v>8.217000000000001</v>
+        <v>8.195</v>
       </c>
       <c r="J16" t="n">
-        <v>8.007</v>
+        <v>7.987</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.21</v>
+        <v>-0.208</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>0.977</v>
       </c>
       <c r="P16" t="n">
-        <v>0.851</v>
+        <v>0.85</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.134</v>
@@ -44232,34 +44232,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.123</v>
+        <v>2.11</v>
       </c>
       <c r="G17" t="n">
-        <v>3.903</v>
+        <v>3.67</v>
       </c>
       <c r="H17" t="n">
-        <v>7.314</v>
+        <v>7.356</v>
       </c>
       <c r="I17" t="n">
-        <v>3.683</v>
+        <v>3.819</v>
       </c>
       <c r="J17" t="n">
-        <v>5.082</v>
+        <v>5.888</v>
       </c>
       <c r="K17" t="n">
-        <v>1.399</v>
+        <v>2.069</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -44275,16 +44275,16 @@
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>1.11</v>
+        <v>1.112</v>
       </c>
       <c r="P17" t="n">
-        <v>0.777</v>
+        <v>0.779</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.725</v>
+        <v>0.727</v>
       </c>
       <c r="R17" t="n">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -44308,34 +44308,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.368</v>
+        <v>3.367</v>
       </c>
       <c r="G18" t="n">
-        <v>3.661</v>
+        <v>3.73</v>
       </c>
       <c r="H18" t="n">
-        <v>4.215</v>
+        <v>4.259</v>
       </c>
       <c r="I18" t="n">
-        <v>3.488</v>
+        <v>3.386</v>
       </c>
       <c r="J18" t="n">
-        <v>4.175</v>
+        <v>4.213</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.827</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -44351,13 +44351,13 @@
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>0.521</v>
+        <v>0.522</v>
       </c>
       <c r="P18" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.106</v>
+        <v>0.107</v>
       </c>
       <c r="R18" t="n">
         <v>-0.407</v>
@@ -44384,38 +44384,38 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.169</v>
+        <v>3.276</v>
       </c>
       <c r="G19" t="n">
-        <v>3.297</v>
+        <v>3.308</v>
       </c>
       <c r="H19" t="n">
-        <v>3.335</v>
+        <v>3.336</v>
       </c>
       <c r="I19" t="n">
-        <v>3.169</v>
+        <v>3.29</v>
       </c>
       <c r="J19" t="n">
-        <v>3.284</v>
+        <v>3.28</v>
       </c>
       <c r="K19" t="n">
-        <v>0.116</v>
+        <v>-0.01</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -44430,13 +44430,13 @@
         <v>0.65</v>
       </c>
       <c r="P19" t="n">
-        <v>0.576</v>
+        <v>0.575</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.804</v>
+        <v>-0.805</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -44460,34 +44460,34 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>5.862</v>
+        <v>6.039</v>
       </c>
       <c r="G20" t="n">
-        <v>6.527</v>
+        <v>6.507</v>
       </c>
       <c r="H20" t="n">
-        <v>6.993</v>
+        <v>7.014</v>
       </c>
       <c r="I20" t="n">
-        <v>5.862</v>
+        <v>6.039</v>
       </c>
       <c r="J20" t="n">
-        <v>6.538</v>
+        <v>6.542</v>
       </c>
       <c r="K20" t="n">
-        <v>0.676</v>
+        <v>0.503</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -44536,12 +44536,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -44551,19 +44551,19 @@
         <v>128.582</v>
       </c>
       <c r="G21" t="n">
-        <v>129.007</v>
+        <v>128.947</v>
       </c>
       <c r="H21" t="n">
-        <v>130.077</v>
+        <v>129.491</v>
       </c>
       <c r="I21" t="n">
-        <v>128.68</v>
+        <v>128.596</v>
       </c>
       <c r="J21" t="n">
-        <v>129.435</v>
+        <v>129.266</v>
       </c>
       <c r="K21" t="n">
-        <v>0.756</v>
+        <v>0.67</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>

--- a/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
+++ b/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
@@ -489,7 +489,7 @@
         <v>334400</v>
       </c>
       <c r="E2" t="n">
-        <v>173039</v>
+        <v>173065</v>
       </c>
       <c r="F2" t="n">
         <v>573</v>
@@ -1977,52 +1977,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.545</v>
+        <v>3.155</v>
       </c>
       <c r="G18" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="H18" t="n">
-        <v>3.361</v>
+        <v>3.426</v>
       </c>
       <c r="I18" t="n">
-        <v>3.662</v>
+        <v>3.487</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.795</v>
+        <v>-0.635</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3</v>
+        <v>0.061</v>
       </c>
       <c r="L18" t="n">
-        <v>0.106</v>
+        <v>0.177</v>
       </c>
       <c r="M18" t="n">
-        <v>0.459</v>
+        <v>0.516</v>
       </c>
       <c r="N18" t="n">
-        <v>0.522</v>
+        <v>0.581</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.261</v>
+        <v>-0.318</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.408</v>
+        <v>-0.501</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.403</v>
+        <v>-0.465</v>
       </c>
       <c r="R18" t="n">
-        <v>20.69</v>
+        <v>24.138</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>10280</v>
+        <v>10282</v>
       </c>
       <c r="U18" t="n">
         <v>0.868</v>
@@ -2042,7 +2042,7 @@
         <v>0.847</v>
       </c>
       <c r="X18" t="n">
-        <v>1.681</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="19">
@@ -2059,52 +2059,52 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.052</v>
+        <v>1.878</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9</v>
+        <v>1.882</v>
       </c>
       <c r="H19" t="n">
-        <v>2.466</v>
+        <v>2.363</v>
       </c>
       <c r="I19" t="n">
-        <v>2.871</v>
+        <v>3.289</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.153</v>
+        <v>0.005</v>
       </c>
       <c r="K19" t="n">
-        <v>0.405</v>
+        <v>0.926</v>
       </c>
       <c r="L19" t="n">
-        <v>0.061</v>
+        <v>0.131</v>
       </c>
       <c r="M19" t="n">
-        <v>0.575</v>
+        <v>0.645</v>
       </c>
       <c r="N19" t="n">
-        <v>0.649</v>
+        <v>0.736</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.761</v>
+        <v>-0.671</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.292</v>
+        <v>-1.938</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.806</v>
+        <v>-0.679</v>
       </c>
       <c r="R19" t="n">
-        <v>20.69</v>
+        <v>24.138</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>14646</v>
+        <v>14649</v>
       </c>
       <c r="U19" t="n">
         <v>0.782</v>
@@ -2141,52 +2141,52 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>7.645</v>
+        <v>6.328</v>
       </c>
       <c r="G20" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>6.617</v>
+        <v>6.844</v>
       </c>
       <c r="I20" t="n">
-        <v>5.884</v>
+        <v>6.169</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.265</v>
+        <v>-0.327</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.733</v>
+        <v>-0.674</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.392</v>
+        <v>-0.396</v>
       </c>
       <c r="M20" t="n">
-        <v>0.584</v>
+        <v>0.532</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.776</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.356</v>
+        <v>-0.06</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.102</v>
+        <v>-1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.365</v>
+        <v>-0.062</v>
       </c>
       <c r="R20" t="n">
-        <v>13.793</v>
+        <v>31.034</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2194,19 +2194,19 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>2743</v>
+        <v>2752</v>
       </c>
       <c r="U20" t="n">
         <v>0.865</v>
       </c>
       <c r="V20" t="n">
-        <v>0.719</v>
+        <v>0.72</v>
       </c>
       <c r="W20" t="n">
         <v>0.858</v>
       </c>
       <c r="X20" t="n">
-        <v>1.751</v>
+        <v>1.748</v>
       </c>
     </row>
     <row r="21">
@@ -2223,52 +2223,52 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>129.8</v>
+        <v>127.65</v>
       </c>
       <c r="G21" t="n">
-        <v>129.46</v>
+        <v>128.96</v>
       </c>
       <c r="H21" t="n">
-        <v>129.287</v>
+        <v>128.032</v>
       </c>
       <c r="I21" t="n">
-        <v>128.81</v>
+        <v>128.59</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.34</v>
+        <v>1.31</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.477</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.006</v>
+        <v>0.03</v>
       </c>
       <c r="M21" t="n">
-        <v>0.573</v>
+        <v>0.484</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.614</v>
       </c>
       <c r="O21" t="n">
-        <v>0.661</v>
+        <v>0.514</v>
       </c>
       <c r="P21" t="n">
-        <v>0.428</v>
+        <v>0.244</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.451</v>
+        <v>0.403</v>
       </c>
       <c r="R21" t="n">
-        <v>48.276</v>
+        <v>41.379</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>10258</v>
+        <v>10267</v>
       </c>
       <c r="U21" t="n">
         <v>0.865</v>
@@ -2285,10 +2285,10 @@
         <v>0.731</v>
       </c>
       <c r="W21" t="n">
-        <v>0.864</v>
+        <v>0.865</v>
       </c>
       <c r="X21" t="n">
-        <v>1.046</v>
+        <v>1.045</v>
       </c>
     </row>
   </sheetData>
@@ -11160,7 +11160,7 @@
         <v>-0.04999999999999716</v>
       </c>
       <c r="P125" t="n">
-        <v>0.3373569876900737</v>
+        <v>0.3373569876900735</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>0.03000000000000114</v>
       </c>
       <c r="P126" t="n">
-        <v>0.342792662321991</v>
+        <v>0.3427926623219912</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>0.167994207096307</v>
       </c>
       <c r="H128" t="n">
-        <v>2.583207820419987</v>
+        <v>2.583207820419986</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         <v>0.0800000000000054</v>
       </c>
       <c r="P128" t="n">
-        <v>0.1232078204199869</v>
+        <v>0.1232078204199865</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>0.1000000000000014</v>
       </c>
       <c r="P129" t="n">
-        <v>0.325133960897896</v>
+        <v>0.3251339608978965</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>0.1199999999999974</v>
       </c>
       <c r="P130" t="n">
-        <v>0.6964156408399704</v>
+        <v>0.69641564083997</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>0.05500000000000682</v>
       </c>
       <c r="P131" t="n">
-        <v>0.5506179097272521</v>
+        <v>0.5506179097272526</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>0.333816075307748</v>
       </c>
       <c r="H137" t="n">
-        <v>3.167393193338161</v>
+        <v>3.167393193338162</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>0.04999999999999716</v>
       </c>
       <c r="P137" t="n">
-        <v>-0.1183236784938404</v>
+        <v>-0.11832367849384</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>0.4721216509775525</v>
       </c>
       <c r="H138" t="n">
-        <v>3.808108616944245</v>
+        <v>3.808108616944244</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>-0.04999999999999716</v>
       </c>
       <c r="P138" t="n">
-        <v>0.6407154236060837</v>
+        <v>0.6407154236060828</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>-0.1400000000000006</v>
       </c>
       <c r="P139" t="n">
-        <v>0.7518913830557574</v>
+        <v>0.7518913830557579</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>0.1670220326936745</v>
       </c>
       <c r="H150" t="n">
-        <v>3.062899786780384</v>
+        <v>3.062899786780383</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -12926,16 +12926,16 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-0.8771002132196162</v>
+        <v>-0.8771002132196166</v>
       </c>
       <c r="N150" t="n">
-        <v>0.8771002132196162</v>
+        <v>0.8771002132196166</v>
       </c>
       <c r="O150" t="n">
         <v>-0.01000000000000023</v>
       </c>
       <c r="P150" t="n">
-        <v>-0.2593390191897598</v>
+        <v>-0.2593390191897602</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>0.1000000000000001</v>
       </c>
       <c r="P151" t="n">
-        <v>-0.3328997867803833</v>
+        <v>-0.3328997867803829</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
@@ -34472,7 +34472,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -34482,7 +34482,7 @@
         <v>9</v>
       </c>
       <c r="D455" t="n">
-        <v>25664.40234375</v>
+        <v>25740</v>
       </c>
       <c r="E455" t="inlineStr">
         <is>
@@ -34493,10 +34493,10 @@
         <v>9</v>
       </c>
       <c r="G455" t="n">
-        <v>0.7740767559739319</v>
+        <v>0.7856625633598842</v>
       </c>
       <c r="H455" t="n">
-        <v>3.361491672700942</v>
+        <v>3.425952208544533</v>
       </c>
       <c r="I455" t="inlineStr">
         <is>
@@ -34509,16 +34509,16 @@
         </is>
       </c>
       <c r="K455" t="n">
-        <v>3.545</v>
+        <v>3.155</v>
       </c>
       <c r="L455" t="n">
         <v>1</v>
       </c>
       <c r="M455" t="n">
-        <v>-0.1835083272990583</v>
+        <v>0.2709522085445331</v>
       </c>
       <c r="N455" t="n">
-        <v>0.1835083272990583</v>
+        <v>0.2709522085445331</v>
       </c>
       <c r="O455" t="inlineStr"/>
       <c r="P455" t="inlineStr"/>
@@ -34537,7 +34537,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -34547,7 +34547,7 @@
         <v>9</v>
       </c>
       <c r="D456" t="n">
-        <v>25740</v>
+        <v>25710</v>
       </c>
       <c r="E456" t="inlineStr">
         <is>
@@ -34558,10 +34558,10 @@
         <v>9</v>
       </c>
       <c r="G456" t="n">
-        <v>0.7856625633598842</v>
+        <v>0.782766111513396</v>
       </c>
       <c r="H456" t="n">
-        <v>3.425952208544533</v>
+        <v>3.409891383055757</v>
       </c>
       <c r="I456" t="inlineStr">
         <is>
@@ -34574,22 +34574,22 @@
         </is>
       </c>
       <c r="K456" t="n">
-        <v>3.3575</v>
+        <v>2.9525</v>
       </c>
       <c r="L456" t="n">
         <v>1</v>
       </c>
       <c r="M456" t="n">
-        <v>0.06845220854453249</v>
+        <v>0.4573913830557568</v>
       </c>
       <c r="N456" t="n">
-        <v>0.06845220854453249</v>
+        <v>0.4573913830557568</v>
       </c>
       <c r="O456" t="n">
-        <v>-0.1874999999999996</v>
+        <v>-0.2024999999999997</v>
       </c>
       <c r="P456" t="n">
-        <v>0.06446053584359124</v>
+        <v>-0.01606082548877596</v>
       </c>
       <c r="Q456" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="R456" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S456" t="b">
@@ -34608,7 +34608,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -34618,7 +34618,7 @@
         <v>9</v>
       </c>
       <c r="D457" t="n">
-        <v>25740</v>
+        <v>25672.126953125</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
@@ -34629,10 +34629,10 @@
         <v>9</v>
       </c>
       <c r="G457" t="n">
-        <v>0.7856625633598842</v>
+        <v>0.776249094858798</v>
       </c>
       <c r="H457" t="n">
-        <v>3.425952208544533</v>
+        <v>3.373881245474294</v>
       </c>
       <c r="I457" t="inlineStr">
         <is>
@@ -34645,22 +34645,22 @@
         </is>
       </c>
       <c r="K457" t="n">
-        <v>3.155</v>
+        <v>2.7925</v>
       </c>
       <c r="L457" t="n">
         <v>1</v>
       </c>
       <c r="M457" t="n">
-        <v>0.2709522085445331</v>
+        <v>0.5813812454742942</v>
       </c>
       <c r="N457" t="n">
-        <v>0.2709522085445331</v>
+        <v>0.5813812454742942</v>
       </c>
       <c r="O457" t="n">
-        <v>-0.2025000000000006</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="P457" t="n">
-        <v>0</v>
+        <v>-0.03601013758146276</v>
       </c>
       <c r="Q457" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -34689,7 +34689,7 @@
         <v>9</v>
       </c>
       <c r="D458" t="n">
-        <v>25710</v>
+        <v>25670.3828125</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
@@ -34700,10 +34700,10 @@
         <v>9</v>
       </c>
       <c r="G458" t="n">
-        <v>0.782766111513396</v>
+        <v>0.775524981897176</v>
       </c>
       <c r="H458" t="n">
-        <v>3.409891383055757</v>
+        <v>3.369102099927589</v>
       </c>
       <c r="I458" t="inlineStr">
         <is>
@@ -34716,26 +34716,26 @@
         </is>
       </c>
       <c r="K458" t="n">
-        <v>2.9525</v>
+        <v>2.76</v>
       </c>
       <c r="L458" t="n">
         <v>1</v>
       </c>
       <c r="M458" t="n">
-        <v>0.4573913830557568</v>
+        <v>0.6091020999275893</v>
       </c>
       <c r="N458" t="n">
-        <v>0.4573913830557568</v>
+        <v>0.6091020999275893</v>
       </c>
       <c r="O458" t="n">
-        <v>-0.2024999999999997</v>
+        <v>-0.0325000000000002</v>
       </c>
       <c r="P458" t="n">
-        <v>-0.01606082548877596</v>
+        <v>-0.004779145546704999</v>
       </c>
       <c r="Q458" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R458" t="inlineStr">
@@ -34744,13 +34744,13 @@
         </is>
       </c>
       <c r="S458" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -34760,7 +34760,7 @@
         <v>9</v>
       </c>
       <c r="D459" t="n">
-        <v>25672.126953125</v>
+        <v>25700</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
@@ -34771,10 +34771,10 @@
         <v>9</v>
       </c>
       <c r="G459" t="n">
-        <v>0.776249094858798</v>
+        <v>0.777697320782042</v>
       </c>
       <c r="H459" t="n">
-        <v>3.373881245474294</v>
+        <v>3.38388848660391</v>
       </c>
       <c r="I459" t="inlineStr">
         <is>
@@ -34787,26 +34787,26 @@
         </is>
       </c>
       <c r="K459" t="n">
-        <v>2.7925</v>
+        <v>2.74</v>
       </c>
       <c r="L459" t="n">
         <v>1</v>
       </c>
       <c r="M459" t="n">
-        <v>0.5813812454742942</v>
+        <v>0.6438884866039101</v>
       </c>
       <c r="N459" t="n">
-        <v>0.5813812454742942</v>
+        <v>0.6438884866039101</v>
       </c>
       <c r="O459" t="n">
-        <v>-0.1600000000000001</v>
+        <v>-0.01999999999999957</v>
       </c>
       <c r="P459" t="n">
-        <v>-0.03601013758146276</v>
+        <v>0.01478638667632115</v>
       </c>
       <c r="Q459" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R459" t="inlineStr">
@@ -34815,13 +34815,13 @@
         </is>
       </c>
       <c r="S459" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -34831,7 +34831,7 @@
         <v>9</v>
       </c>
       <c r="D460" t="n">
-        <v>25670.3828125</v>
+        <v>25710</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
@@ -34842,10 +34842,10 @@
         <v>9</v>
       </c>
       <c r="G460" t="n">
-        <v>0.775524981897176</v>
+        <v>0.782766111513396</v>
       </c>
       <c r="H460" t="n">
-        <v>3.369102099927589</v>
+        <v>3.409891383055757</v>
       </c>
       <c r="I460" t="inlineStr">
         <is>
@@ -34858,22 +34858,22 @@
         </is>
       </c>
       <c r="K460" t="n">
-        <v>2.76</v>
+        <v>2.6925</v>
       </c>
       <c r="L460" t="n">
         <v>1</v>
       </c>
       <c r="M460" t="n">
-        <v>0.6091020999275893</v>
+        <v>0.717391383055757</v>
       </c>
       <c r="N460" t="n">
-        <v>0.6091020999275893</v>
+        <v>0.717391383055757</v>
       </c>
       <c r="O460" t="n">
-        <v>-0.0325000000000002</v>
+        <v>-0.04750000000000032</v>
       </c>
       <c r="P460" t="n">
-        <v>-0.004779145546704999</v>
+        <v>0.02600289645184661</v>
       </c>
       <c r="Q460" t="inlineStr">
         <is>
@@ -34892,7 +34892,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -34902,7 +34902,7 @@
         <v>9</v>
       </c>
       <c r="D461" t="n">
-        <v>25700</v>
+        <v>25710</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
@@ -34913,10 +34913,10 @@
         <v>9</v>
       </c>
       <c r="G461" t="n">
-        <v>0.777697320782042</v>
+        <v>0.782766111513396</v>
       </c>
       <c r="H461" t="n">
-        <v>3.38388848660391</v>
+        <v>3.409891383055757</v>
       </c>
       <c r="I461" t="inlineStr">
         <is>
@@ -34929,22 +34929,22 @@
         </is>
       </c>
       <c r="K461" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="L461" t="n">
         <v>1</v>
       </c>
       <c r="M461" t="n">
-        <v>0.6438884866039101</v>
+        <v>0.7498913830557568</v>
       </c>
       <c r="N461" t="n">
-        <v>0.6438884866039101</v>
+        <v>0.7498913830557568</v>
       </c>
       <c r="O461" t="n">
-        <v>-0.01999999999999957</v>
+        <v>-0.03249999999999975</v>
       </c>
       <c r="P461" t="n">
-        <v>0.01478638667632115</v>
+        <v>0</v>
       </c>
       <c r="Q461" t="inlineStr">
         <is>
@@ -34963,7 +34963,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -34973,7 +34973,7 @@
         <v>9</v>
       </c>
       <c r="D462" t="n">
-        <v>25710</v>
+        <v>25610.373046875</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
@@ -34984,10 +34984,10 @@
         <v>9</v>
       </c>
       <c r="G462" t="n">
-        <v>0.782766111513396</v>
+        <v>0.7704561911658219</v>
       </c>
       <c r="H462" t="n">
-        <v>3.409891383055757</v>
+        <v>3.345081824764663</v>
       </c>
       <c r="I462" t="inlineStr">
         <is>
@@ -35000,41 +35000,41 @@
         </is>
       </c>
       <c r="K462" t="n">
-        <v>2.6925</v>
+        <v>2.745</v>
       </c>
       <c r="L462" t="n">
         <v>1</v>
       </c>
       <c r="M462" t="n">
-        <v>0.717391383055757</v>
+        <v>0.6000818247646631</v>
       </c>
       <c r="N462" t="n">
-        <v>0.717391383055757</v>
+        <v>0.6000818247646631</v>
       </c>
       <c r="O462" t="n">
-        <v>-0.04750000000000032</v>
+        <v>0.08499999999999996</v>
       </c>
       <c r="P462" t="n">
-        <v>0.02600289645184661</v>
+        <v>-0.06480955829109369</v>
       </c>
       <c r="Q462" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="R462" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S462" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -35044,7 +35044,7 @@
         <v>9</v>
       </c>
       <c r="D463" t="n">
-        <v>25710</v>
+        <v>25492.7578125</v>
       </c>
       <c r="E463" t="inlineStr">
         <is>
@@ -35055,10 +35055,10 @@
         <v>9</v>
       </c>
       <c r="G463" t="n">
-        <v>0.782766111513396</v>
+        <v>0.7632150615496017</v>
       </c>
       <c r="H463" t="n">
-        <v>3.409891383055757</v>
+        <v>3.296908037653874</v>
       </c>
       <c r="I463" t="inlineStr">
         <is>
@@ -35071,41 +35071,41 @@
         </is>
       </c>
       <c r="K463" t="n">
-        <v>2.66</v>
+        <v>2.8175</v>
       </c>
       <c r="L463" t="n">
         <v>1</v>
       </c>
       <c r="M463" t="n">
-        <v>0.7498913830557568</v>
+        <v>0.4794080376538741</v>
       </c>
       <c r="N463" t="n">
-        <v>0.7498913830557568</v>
+        <v>0.4794080376538741</v>
       </c>
       <c r="O463" t="n">
-        <v>-0.03249999999999975</v>
+        <v>0.07249999999999979</v>
       </c>
       <c r="P463" t="n">
+        <v>-0.04817378711078923</v>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>Ascendente</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="S463" t="b">
         <v>0</v>
-      </c>
-      <c r="Q463" t="inlineStr">
-        <is>
-          <t>Estable</t>
-        </is>
-      </c>
-      <c r="R463" t="inlineStr">
-        <is>
-          <t>Estable</t>
-        </is>
-      </c>
-      <c r="S463" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -35115,7 +35115,7 @@
         <v>9</v>
       </c>
       <c r="D464" t="n">
-        <v>25610.373046875</v>
+        <v>25360</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
@@ -35126,10 +35126,10 @@
         <v>9</v>
       </c>
       <c r="G464" t="n">
-        <v>0.7704561911658219</v>
+        <v>0.7523533671252716</v>
       </c>
       <c r="H464" t="n">
-        <v>3.345081824764663</v>
+        <v>3.251752353367125</v>
       </c>
       <c r="I464" t="inlineStr">
         <is>
@@ -35142,22 +35142,22 @@
         </is>
       </c>
       <c r="K464" t="n">
-        <v>2.745</v>
+        <v>2.9425</v>
       </c>
       <c r="L464" t="n">
         <v>1</v>
       </c>
       <c r="M464" t="n">
-        <v>0.6000818247646631</v>
+        <v>0.3092523533671248</v>
       </c>
       <c r="N464" t="n">
-        <v>0.6000818247646631</v>
+        <v>0.3092523533671248</v>
       </c>
       <c r="O464" t="n">
-        <v>0.08499999999999996</v>
+        <v>0.1250000000000004</v>
       </c>
       <c r="P464" t="n">
-        <v>-0.06480955829109369</v>
+        <v>-0.04515568428674888</v>
       </c>
       <c r="Q464" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
       </c>
       <c r="R464" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S464" t="b">
@@ -35176,7 +35176,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -35186,7 +35186,7 @@
         <v>9</v>
       </c>
       <c r="D465" t="n">
-        <v>25492.7578125</v>
+        <v>25170</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
@@ -35197,10 +35197,10 @@
         <v>9</v>
       </c>
       <c r="G465" t="n">
-        <v>0.7632150615496017</v>
+        <v>0.7349746560463433</v>
       </c>
       <c r="H465" t="n">
-        <v>3.296908037653874</v>
+        <v>3.194668718320058</v>
       </c>
       <c r="I465" t="inlineStr">
         <is>
@@ -35213,22 +35213,22 @@
         </is>
       </c>
       <c r="K465" t="n">
-        <v>2.8175</v>
+        <v>3.1675</v>
       </c>
       <c r="L465" t="n">
         <v>1</v>
       </c>
       <c r="M465" t="n">
-        <v>0.4794080376538741</v>
+        <v>0.02716871832005774</v>
       </c>
       <c r="N465" t="n">
-        <v>0.4794080376538741</v>
+        <v>0.02716871832005774</v>
       </c>
       <c r="O465" t="n">
-        <v>0.07249999999999979</v>
+        <v>0.2250000000000001</v>
       </c>
       <c r="P465" t="n">
-        <v>-0.04817378711078923</v>
+        <v>-0.05708363504706693</v>
       </c>
       <c r="Q465" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
       </c>
       <c r="R465" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S465" t="b">
@@ -35247,7 +35247,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -35257,7 +35257,7 @@
         <v>9</v>
       </c>
       <c r="D466" t="n">
-        <v>25360</v>
+        <v>25100</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
@@ -35268,10 +35268,10 @@
         <v>9</v>
       </c>
       <c r="G466" t="n">
-        <v>0.7523533671252716</v>
+        <v>0.7255611875452571</v>
       </c>
       <c r="H466" t="n">
-        <v>3.251752353367125</v>
+        <v>3.169203475742216</v>
       </c>
       <c r="I466" t="inlineStr">
         <is>
@@ -35284,22 +35284,22 @@
         </is>
       </c>
       <c r="K466" t="n">
-        <v>2.9425</v>
+        <v>3.3125</v>
       </c>
       <c r="L466" t="n">
         <v>1</v>
       </c>
       <c r="M466" t="n">
-        <v>0.3092523533671248</v>
+        <v>-0.1432965242577842</v>
       </c>
       <c r="N466" t="n">
-        <v>0.3092523533671248</v>
+        <v>0.1432965242577842</v>
       </c>
       <c r="O466" t="n">
-        <v>0.1250000000000004</v>
+        <v>0.1449999999999996</v>
       </c>
       <c r="P466" t="n">
-        <v>-0.04515568428674888</v>
+        <v>-0.02546524257784233</v>
       </c>
       <c r="Q466" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -35328,7 +35328,7 @@
         <v>9</v>
       </c>
       <c r="D467" t="n">
-        <v>25170</v>
+        <v>25120</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
@@ -35339,10 +35339,10 @@
         <v>9</v>
       </c>
       <c r="G467" t="n">
-        <v>0.7349746560463433</v>
+        <v>0.7284576393917451</v>
       </c>
       <c r="H467" t="n">
-        <v>3.194668718320058</v>
+        <v>3.176821144098479</v>
       </c>
       <c r="I467" t="inlineStr">
         <is>
@@ -35355,22 +35355,22 @@
         </is>
       </c>
       <c r="K467" t="n">
-        <v>3.1675</v>
+        <v>3.5225</v>
       </c>
       <c r="L467" t="n">
         <v>1</v>
       </c>
       <c r="M467" t="n">
-        <v>0.02716871832005774</v>
+        <v>-0.3456788559015207</v>
       </c>
       <c r="N467" t="n">
-        <v>0.02716871832005774</v>
+        <v>0.3456788559015207</v>
       </c>
       <c r="O467" t="n">
-        <v>0.2250000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="P467" t="n">
-        <v>-0.05708363504706693</v>
+        <v>0.00761766835626343</v>
       </c>
       <c r="Q467" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
       </c>
       <c r="R467" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S467" t="b">
@@ -35389,7 +35389,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -35399,7 +35399,7 @@
         <v>9</v>
       </c>
       <c r="D468" t="n">
-        <v>25100</v>
+        <v>25200</v>
       </c>
       <c r="E468" t="inlineStr">
         <is>
@@ -35410,10 +35410,10 @@
         <v>9</v>
       </c>
       <c r="G468" t="n">
-        <v>0.7255611875452571</v>
+        <v>0.7393193338160753</v>
       </c>
       <c r="H468" t="n">
-        <v>3.169203475742216</v>
+        <v>3.20869659666908</v>
       </c>
       <c r="I468" t="inlineStr">
         <is>
@@ -35426,22 +35426,22 @@
         </is>
       </c>
       <c r="K468" t="n">
-        <v>3.3125</v>
+        <v>3.6875</v>
       </c>
       <c r="L468" t="n">
         <v>1</v>
       </c>
       <c r="M468" t="n">
-        <v>-0.1432965242577842</v>
+        <v>-0.4788034033309199</v>
       </c>
       <c r="N468" t="n">
-        <v>0.1432965242577842</v>
+        <v>0.4788034033309199</v>
       </c>
       <c r="O468" t="n">
-        <v>0.1449999999999996</v>
+        <v>0.165</v>
       </c>
       <c r="P468" t="n">
-        <v>-0.02546524257784233</v>
+        <v>0.03187545257060087</v>
       </c>
       <c r="Q468" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -35470,7 +35470,7 @@
         <v>9</v>
       </c>
       <c r="D469" t="n">
-        <v>25120</v>
+        <v>25280</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
@@ -35481,10 +35481,10 @@
         <v>9</v>
       </c>
       <c r="G469" t="n">
-        <v>0.7284576393917451</v>
+        <v>0.7443881245474294</v>
       </c>
       <c r="H469" t="n">
-        <v>3.176821144098479</v>
+        <v>3.230744388124548</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
@@ -35497,22 +35497,22 @@
         </is>
       </c>
       <c r="K469" t="n">
-        <v>3.5225</v>
+        <v>3.7675</v>
       </c>
       <c r="L469" t="n">
         <v>1</v>
       </c>
       <c r="M469" t="n">
-        <v>-0.3456788559015207</v>
+        <v>-0.536755611875452</v>
       </c>
       <c r="N469" t="n">
-        <v>0.3456788559015207</v>
+        <v>0.536755611875452</v>
       </c>
       <c r="O469" t="n">
-        <v>0.21</v>
+        <v>0.07999999999999963</v>
       </c>
       <c r="P469" t="n">
-        <v>0.00761766835626343</v>
+        <v>0.02204779145546754</v>
       </c>
       <c r="Q469" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -35541,7 +35541,7 @@
         <v>9</v>
       </c>
       <c r="D470" t="n">
-        <v>25200</v>
+        <v>25360</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
@@ -35552,10 +35552,10 @@
         <v>9</v>
       </c>
       <c r="G470" t="n">
-        <v>0.7393193338160753</v>
+        <v>0.7523533671252716</v>
       </c>
       <c r="H470" t="n">
-        <v>3.20869659666908</v>
+        <v>3.251752353367125</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
@@ -35568,22 +35568,22 @@
         </is>
       </c>
       <c r="K470" t="n">
-        <v>3.6875</v>
+        <v>3.8175</v>
       </c>
       <c r="L470" t="n">
         <v>1</v>
       </c>
       <c r="M470" t="n">
-        <v>-0.4788034033309199</v>
+        <v>-0.5657476466328748</v>
       </c>
       <c r="N470" t="n">
-        <v>0.4788034033309199</v>
+        <v>0.5657476466328748</v>
       </c>
       <c r="O470" t="n">
-        <v>0.165</v>
+        <v>0.05000000000000027</v>
       </c>
       <c r="P470" t="n">
-        <v>0.03187545257060087</v>
+        <v>0.02100796524257742</v>
       </c>
       <c r="Q470" t="inlineStr">
         <is>
@@ -35602,7 +35602,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -35612,7 +35612,7 @@
         <v>9</v>
       </c>
       <c r="D471" t="n">
-        <v>25280</v>
+        <v>25456.98828125</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
@@ -35623,10 +35623,10 @@
         <v>9</v>
       </c>
       <c r="G471" t="n">
-        <v>0.7443881245474294</v>
+        <v>0.7574221578566256</v>
       </c>
       <c r="H471" t="n">
-        <v>3.230744388124548</v>
+        <v>3.273787110789283</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
@@ -35639,22 +35639,22 @@
         </is>
       </c>
       <c r="K471" t="n">
-        <v>3.7675</v>
+        <v>3.9075</v>
       </c>
       <c r="L471" t="n">
         <v>1</v>
       </c>
       <c r="M471" t="n">
-        <v>-0.536755611875452</v>
+        <v>-0.6337128892107176</v>
       </c>
       <c r="N471" t="n">
-        <v>0.536755611875452</v>
+        <v>0.6337128892107176</v>
       </c>
       <c r="O471" t="n">
-        <v>0.07999999999999963</v>
+        <v>0.0900000000000003</v>
       </c>
       <c r="P471" t="n">
-        <v>0.02204779145546754</v>
+        <v>0.02203475742215755</v>
       </c>
       <c r="Q471" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -35683,7 +35683,7 @@
         <v>9</v>
       </c>
       <c r="D472" t="n">
-        <v>25360</v>
+        <v>25463.90625</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
@@ -35694,10 +35694,10 @@
         <v>9</v>
       </c>
       <c r="G472" t="n">
-        <v>0.7523533671252716</v>
+        <v>0.7595944967414917</v>
       </c>
       <c r="H472" t="n">
-        <v>3.251752353367125</v>
+        <v>3.284398986241854</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
@@ -35710,26 +35710,26 @@
         </is>
       </c>
       <c r="K472" t="n">
-        <v>3.8175</v>
+        <v>3.94</v>
       </c>
       <c r="L472" t="n">
         <v>1</v>
       </c>
       <c r="M472" t="n">
-        <v>-0.5657476466328748</v>
+        <v>-0.6556010137581461</v>
       </c>
       <c r="N472" t="n">
-        <v>0.5657476466328748</v>
+        <v>0.6556010137581461</v>
       </c>
       <c r="O472" t="n">
-        <v>0.05000000000000027</v>
+        <v>0.03249999999999975</v>
       </c>
       <c r="P472" t="n">
-        <v>0.02100796524257742</v>
+        <v>0.01061187545257125</v>
       </c>
       <c r="Q472" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R472" t="inlineStr">
@@ -35738,13 +35738,13 @@
         </is>
       </c>
       <c r="S472" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -35754,7 +35754,7 @@
         <v>9</v>
       </c>
       <c r="D473" t="n">
-        <v>25456.98828125</v>
+        <v>25300</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
@@ -35765,10 +35765,10 @@
         <v>9</v>
       </c>
       <c r="G473" t="n">
-        <v>0.7574221578566256</v>
+        <v>0.7465604634322954</v>
       </c>
       <c r="H473" t="n">
-        <v>3.273787110789283</v>
+        <v>3.238986241853729</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
@@ -35781,26 +35781,26 @@
         </is>
       </c>
       <c r="K473" t="n">
-        <v>3.9075</v>
+        <v>3.95</v>
       </c>
       <c r="L473" t="n">
         <v>1</v>
       </c>
       <c r="M473" t="n">
-        <v>-0.6337128892107176</v>
+        <v>-0.711013758146271</v>
       </c>
       <c r="N473" t="n">
-        <v>0.6337128892107176</v>
+        <v>0.711013758146271</v>
       </c>
       <c r="O473" t="n">
-        <v>0.0900000000000003</v>
+        <v>0.01000000000000023</v>
       </c>
       <c r="P473" t="n">
-        <v>0.02203475742215755</v>
+        <v>-0.0454127443881247</v>
       </c>
       <c r="Q473" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R473" t="inlineStr">
@@ -35809,13 +35809,13 @@
         </is>
       </c>
       <c r="S473" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -35825,7 +35825,7 @@
         <v>9</v>
       </c>
       <c r="D474" t="n">
-        <v>25463.90625</v>
+        <v>25075.537109375</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
@@ -35836,10 +35836,10 @@
         <v>9</v>
       </c>
       <c r="G474" t="n">
-        <v>0.7595944967414917</v>
+        <v>0.720492396813903</v>
       </c>
       <c r="H474" t="n">
-        <v>3.284398986241854</v>
+        <v>3.154580738595221</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
@@ -35852,22 +35852,22 @@
         </is>
       </c>
       <c r="K474" t="n">
-        <v>3.94</v>
+        <v>3.9125</v>
       </c>
       <c r="L474" t="n">
         <v>1</v>
       </c>
       <c r="M474" t="n">
-        <v>-0.6556010137581461</v>
+        <v>-0.7579192614047794</v>
       </c>
       <c r="N474" t="n">
-        <v>0.6556010137581461</v>
+        <v>0.7579192614047794</v>
       </c>
       <c r="O474" t="n">
-        <v>0.03249999999999975</v>
+        <v>-0.03750000000000009</v>
       </c>
       <c r="P474" t="n">
-        <v>0.01061187545257125</v>
+        <v>-0.08440550325850849</v>
       </c>
       <c r="Q474" t="inlineStr">
         <is>
@@ -35876,27 +35876,27 @@
       </c>
       <c r="R474" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S474" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B475" t="n">
         <v>9039635</v>
       </c>
       <c r="C475" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D475" t="n">
-        <v>25300</v>
+        <v>26520</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
@@ -35904,13 +35904,13 @@
         </is>
       </c>
       <c r="F475" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G475" t="n">
-        <v>0.7465604634322954</v>
+        <v>0.7455579246624022</v>
       </c>
       <c r="H475" t="n">
-        <v>3.238986241853729</v>
+        <v>3.624776119402985</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
@@ -35923,51 +35923,51 @@
         </is>
       </c>
       <c r="K475" t="n">
-        <v>3.95</v>
+        <v>3.8075</v>
       </c>
       <c r="L475" t="n">
         <v>1</v>
       </c>
       <c r="M475" t="n">
-        <v>-0.711013758146271</v>
+        <v>-0.1827238805970151</v>
       </c>
       <c r="N475" t="n">
-        <v>0.711013758146271</v>
+        <v>0.1827238805970151</v>
       </c>
       <c r="O475" t="n">
-        <v>0.01000000000000023</v>
+        <v>-0.105</v>
       </c>
       <c r="P475" t="n">
-        <v>-0.0454127443881247</v>
+        <v>0.4701953808077644</v>
       </c>
       <c r="Q475" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="R475" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S475" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B476" t="n">
         <v>9039635</v>
       </c>
       <c r="C476" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D476" t="n">
-        <v>25075.537109375</v>
+        <v>26412.142578125</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
@@ -35975,13 +35975,13 @@
         </is>
       </c>
       <c r="F476" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G476" t="n">
-        <v>0.720492396813903</v>
+        <v>0.7377398720682303</v>
       </c>
       <c r="H476" t="n">
-        <v>3.154580738595221</v>
+        <v>3.598582089552239</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
@@ -35994,31 +35994,31 @@
         </is>
       </c>
       <c r="K476" t="n">
-        <v>3.9125</v>
+        <v>3.6725</v>
       </c>
       <c r="L476" t="n">
         <v>1</v>
       </c>
       <c r="M476" t="n">
-        <v>-0.7579192614047794</v>
+        <v>-0.07391791044776141</v>
       </c>
       <c r="N476" t="n">
-        <v>0.7579192614047794</v>
+        <v>0.07391791044776141</v>
       </c>
       <c r="O476" t="n">
-        <v>-0.03750000000000009</v>
+        <v>-0.1349999999999998</v>
       </c>
       <c r="P476" t="n">
-        <v>-0.08440550325850849</v>
+        <v>-0.02619402985074615</v>
       </c>
       <c r="Q476" t="inlineStr">
         <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
           <t>Estable</t>
-        </is>
-      </c>
-      <c r="R476" t="inlineStr">
-        <is>
-          <t>Descendente</t>
         </is>
       </c>
       <c r="S476" t="b">
@@ -36028,7 +36028,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -36038,7 +36038,7 @@
         <v>10</v>
       </c>
       <c r="D477" t="n">
-        <v>26520</v>
+        <v>26420</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
@@ -36049,10 +36049,10 @@
         <v>10</v>
       </c>
       <c r="G477" t="n">
-        <v>0.7455579246624022</v>
+        <v>0.7398720682302772</v>
       </c>
       <c r="H477" t="n">
-        <v>3.627320540156361</v>
+        <v>3.607089552238806</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -36065,22 +36065,22 @@
         </is>
       </c>
       <c r="K477" t="n">
-        <v>3.8075</v>
+        <v>3.5575</v>
       </c>
       <c r="L477" t="n">
         <v>1</v>
       </c>
       <c r="M477" t="n">
-        <v>-0.180179459843639</v>
+        <v>0.0495895522388059</v>
       </c>
       <c r="N477" t="n">
-        <v>0.180179459843639</v>
+        <v>0.0495895522388059</v>
       </c>
       <c r="O477" t="n">
-        <v>-0.105</v>
+        <v>-0.1150000000000002</v>
       </c>
       <c r="P477" t="n">
-        <v>0.4727398015611404</v>
+        <v>0.008507462686567102</v>
       </c>
       <c r="Q477" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
       </c>
       <c r="R477" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S477" t="b">
@@ -36099,7 +36099,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -36109,7 +36109,7 @@
         <v>10</v>
       </c>
       <c r="D478" t="n">
-        <v>26412.142578125</v>
+        <v>26480</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
@@ -36120,10 +36120,10 @@
         <v>10</v>
       </c>
       <c r="G478" t="n">
-        <v>0.7377398720682303</v>
+        <v>0.7420042643923241</v>
       </c>
       <c r="H478" t="n">
-        <v>3.601204690831557</v>
+        <v>3.613731343283582</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
@@ -36136,22 +36136,22 @@
         </is>
       </c>
       <c r="K478" t="n">
-        <v>3.7</v>
+        <v>3.3925</v>
       </c>
       <c r="L478" t="n">
         <v>1</v>
       </c>
       <c r="M478" t="n">
-        <v>-0.09879530916844326</v>
+        <v>0.221231343283582</v>
       </c>
       <c r="N478" t="n">
-        <v>0.09879530916844326</v>
+        <v>0.221231343283582</v>
       </c>
       <c r="O478" t="n">
-        <v>-0.1074999999999999</v>
+        <v>-0.165</v>
       </c>
       <c r="P478" t="n">
-        <v>-0.02611584932480415</v>
+        <v>0.006641791044776024</v>
       </c>
       <c r="Q478" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -36180,7 +36180,7 @@
         <v>10</v>
       </c>
       <c r="D479" t="n">
-        <v>26420</v>
+        <v>26618.970703125</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
@@ -36191,10 +36191,10 @@
         <v>10</v>
       </c>
       <c r="G479" t="n">
-        <v>0.7398720682302772</v>
+        <v>0.7484008528784648</v>
       </c>
       <c r="H479" t="n">
-        <v>3.609690831556503</v>
+        <v>3.633059701492537</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
@@ -36207,22 +36207,22 @@
         </is>
       </c>
       <c r="K479" t="n">
-        <v>3.5575</v>
+        <v>3.2625</v>
       </c>
       <c r="L479" t="n">
         <v>1</v>
       </c>
       <c r="M479" t="n">
-        <v>0.05219083155650317</v>
+        <v>0.370559701492537</v>
       </c>
       <c r="N479" t="n">
-        <v>0.05219083155650317</v>
+        <v>0.370559701492537</v>
       </c>
       <c r="O479" t="n">
-        <v>-0.1425000000000001</v>
+        <v>-0.1299999999999999</v>
       </c>
       <c r="P479" t="n">
-        <v>0.008486140724946356</v>
+        <v>0.01932835820895518</v>
       </c>
       <c r="Q479" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -36251,7 +36251,7 @@
         <v>10</v>
       </c>
       <c r="D480" t="n">
-        <v>26480</v>
+        <v>26801.3828125</v>
       </c>
       <c r="E480" t="inlineStr">
         <is>
@@ -36262,10 +36262,10 @@
         <v>10</v>
       </c>
       <c r="G480" t="n">
-        <v>0.7420042643923241</v>
+        <v>0.7583511016346838</v>
       </c>
       <c r="H480" t="n">
-        <v>3.6154513148543</v>
+        <v>3.670410447761194</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
@@ -36278,22 +36278,22 @@
         </is>
       </c>
       <c r="K480" t="n">
-        <v>3.3925</v>
+        <v>3.115</v>
       </c>
       <c r="L480" t="n">
         <v>1</v>
       </c>
       <c r="M480" t="n">
-        <v>0.2229513148543001</v>
+        <v>0.5554104477611936</v>
       </c>
       <c r="N480" t="n">
-        <v>0.2229513148543001</v>
+        <v>0.5554104477611936</v>
       </c>
       <c r="O480" t="n">
-        <v>-0.165</v>
+        <v>-0.1475</v>
       </c>
       <c r="P480" t="n">
-        <v>0.005760483297796881</v>
+        <v>0.03735074626865664</v>
       </c>
       <c r="Q480" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -36322,7 +36322,7 @@
         <v>10</v>
       </c>
       <c r="D481" t="n">
-        <v>26618.970703125</v>
+        <v>26908.4609375</v>
       </c>
       <c r="E481" t="inlineStr">
         <is>
@@ -36333,10 +36333,10 @@
         <v>10</v>
       </c>
       <c r="G481" t="n">
-        <v>0.7484008528784648</v>
+        <v>0.7654584221748401</v>
       </c>
       <c r="H481" t="n">
-        <v>3.634317697228145</v>
+        <v>3.704179104477612</v>
       </c>
       <c r="I481" t="inlineStr">
         <is>
@@ -36349,22 +36349,22 @@
         </is>
       </c>
       <c r="K481" t="n">
-        <v>3.2625</v>
+        <v>2.8725</v>
       </c>
       <c r="L481" t="n">
         <v>1</v>
       </c>
       <c r="M481" t="n">
-        <v>0.3718176972281451</v>
+        <v>0.8316791044776117</v>
       </c>
       <c r="N481" t="n">
-        <v>0.3718176972281451</v>
+        <v>0.8316791044776117</v>
       </c>
       <c r="O481" t="n">
-        <v>-0.1299999999999999</v>
+        <v>-0.2425000000000002</v>
       </c>
       <c r="P481" t="n">
-        <v>0.01886638237384508</v>
+        <v>0.03376865671641793</v>
       </c>
       <c r="Q481" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -36393,7 +36393,7 @@
         <v>10</v>
       </c>
       <c r="D482" t="n">
-        <v>26801.3828125</v>
+        <v>26740</v>
       </c>
       <c r="E482" t="inlineStr">
         <is>
@@ -36404,10 +36404,10 @@
         <v>10</v>
       </c>
       <c r="G482" t="n">
-        <v>0.7583511016346838</v>
+        <v>0.7547974413646056</v>
       </c>
       <c r="H482" t="n">
-        <v>3.676474769012083</v>
+        <v>3.660656716417911</v>
       </c>
       <c r="I482" t="inlineStr">
         <is>
@@ -36420,22 +36420,22 @@
         </is>
       </c>
       <c r="K482" t="n">
-        <v>3.115</v>
+        <v>2.71</v>
       </c>
       <c r="L482" t="n">
         <v>1</v>
       </c>
       <c r="M482" t="n">
-        <v>0.5614747690120829</v>
+        <v>0.9506567164179103</v>
       </c>
       <c r="N482" t="n">
-        <v>0.5614747690120829</v>
+        <v>0.9506567164179103</v>
       </c>
       <c r="O482" t="n">
-        <v>-0.1475</v>
+        <v>-0.1624999999999996</v>
       </c>
       <c r="P482" t="n">
-        <v>0.0421570717839379</v>
+        <v>-0.0435223880597011</v>
       </c>
       <c r="Q482" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -36464,7 +36464,7 @@
         <v>10</v>
       </c>
       <c r="D483" t="n">
-        <v>26908.4609375</v>
+        <v>26320</v>
       </c>
       <c r="E483" t="inlineStr">
         <is>
@@ -36475,10 +36475,10 @@
         <v>10</v>
       </c>
       <c r="G483" t="n">
-        <v>0.7654584221748401</v>
+        <v>0.7313432835820896</v>
       </c>
       <c r="H483" t="n">
-        <v>3.706524520255864</v>
+        <v>3.565365671641791</v>
       </c>
       <c r="I483" t="inlineStr">
         <is>
@@ -36491,22 +36491,22 @@
         </is>
       </c>
       <c r="K483" t="n">
-        <v>2.8725</v>
+        <v>2.5675</v>
       </c>
       <c r="L483" t="n">
         <v>1</v>
       </c>
       <c r="M483" t="n">
-        <v>0.8340245202558636</v>
+        <v>0.9978656716417911</v>
       </c>
       <c r="N483" t="n">
-        <v>0.8340245202558636</v>
+        <v>0.9978656716417911</v>
       </c>
       <c r="O483" t="n">
-        <v>-0.2425000000000002</v>
+        <v>-0.1425000000000005</v>
       </c>
       <c r="P483" t="n">
-        <v>0.03004975124378051</v>
+        <v>-0.09529104477611972</v>
       </c>
       <c r="Q483" t="inlineStr">
         <is>
@@ -36515,17 +36515,17 @@
       </c>
       <c r="R483" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S483" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -36535,7 +36535,7 @@
         <v>10</v>
       </c>
       <c r="D484" t="n">
-        <v>26740</v>
+        <v>25850</v>
       </c>
       <c r="E484" t="inlineStr">
         <is>
@@ -36546,10 +36546,10 @@
         <v>10</v>
       </c>
       <c r="G484" t="n">
-        <v>0.7547974413646056</v>
+        <v>0.7057569296375267</v>
       </c>
       <c r="H484" t="n">
-        <v>3.661637526652452</v>
+        <v>3.487313432835821</v>
       </c>
       <c r="I484" t="inlineStr">
         <is>
@@ -36562,31 +36562,31 @@
         </is>
       </c>
       <c r="K484" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="L484" t="n">
         <v>1</v>
       </c>
       <c r="M484" t="n">
-        <v>0.9116375266524521</v>
+        <v>0.9673134328358213</v>
       </c>
       <c r="N484" t="n">
-        <v>0.9116375266524521</v>
+        <v>0.9673134328358213</v>
       </c>
       <c r="O484" t="n">
-        <v>-0.1225000000000001</v>
+        <v>-0.04749999999999988</v>
       </c>
       <c r="P484" t="n">
-        <v>-0.04488699360341153</v>
+        <v>-0.07805223880596968</v>
       </c>
       <c r="Q484" t="inlineStr">
         <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
           <t>Descendente</t>
-        </is>
-      </c>
-      <c r="R484" t="inlineStr">
-        <is>
-          <t>Estable</t>
         </is>
       </c>
       <c r="S484" t="b">
@@ -36596,7 +36596,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -36606,7 +36606,7 @@
         <v>9</v>
       </c>
       <c r="D485" t="n">
-        <v>20420</v>
+        <v>19780</v>
       </c>
       <c r="E485" t="inlineStr">
         <is>
@@ -36617,10 +36617,10 @@
         <v>9</v>
       </c>
       <c r="G485" t="n">
-        <v>0.8653149891383056</v>
+        <v>0.8392469225199131</v>
       </c>
       <c r="H485" t="n">
-        <v>2.465856263577118</v>
+        <v>2.363012309920347</v>
       </c>
       <c r="I485" t="inlineStr">
         <is>
@@ -36633,16 +36633,16 @@
         </is>
       </c>
       <c r="K485" t="n">
-        <v>2.0525</v>
+        <v>1.8775</v>
       </c>
       <c r="L485" t="n">
         <v>1</v>
       </c>
       <c r="M485" t="n">
-        <v>0.4133562635771182</v>
+        <v>0.4855123099203476</v>
       </c>
       <c r="N485" t="n">
-        <v>0.4133562635771182</v>
+        <v>0.4855123099203476</v>
       </c>
       <c r="O485" t="inlineStr"/>
       <c r="P485" t="inlineStr"/>
@@ -36661,7 +36661,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -36671,7 +36671,7 @@
         <v>9</v>
       </c>
       <c r="D486" t="n">
-        <v>20360</v>
+        <v>19566.671875</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
@@ -36682,10 +36682,10 @@
         <v>9</v>
       </c>
       <c r="G486" t="n">
-        <v>0.8624185372918175</v>
+        <v>0.8240405503258509</v>
       </c>
       <c r="H486" t="n">
-        <v>2.459302437846971</v>
+        <v>2.30992396813903</v>
       </c>
       <c r="I486" t="inlineStr">
         <is>
@@ -36698,31 +36698,31 @@
         </is>
       </c>
       <c r="K486" t="n">
-        <v>1.9675</v>
+        <v>1.8425</v>
       </c>
       <c r="L486" t="n">
         <v>1</v>
       </c>
       <c r="M486" t="n">
-        <v>0.491802437846971</v>
+        <v>0.4674239681390298</v>
       </c>
       <c r="N486" t="n">
-        <v>0.491802437846971</v>
+        <v>0.4674239681390298</v>
       </c>
       <c r="O486" t="n">
-        <v>-0.08500000000000041</v>
+        <v>-0.03499999999999992</v>
       </c>
       <c r="P486" t="n">
-        <v>-0.006553825730147622</v>
+        <v>-0.05308834178131772</v>
       </c>
       <c r="Q486" t="inlineStr">
         <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="R486" t="inlineStr">
+        <is>
           <t>Descendente</t>
-        </is>
-      </c>
-      <c r="R486" t="inlineStr">
-        <is>
-          <t>Estable</t>
         </is>
       </c>
       <c r="S486" t="b">
@@ -36732,7 +36732,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -36742,7 +36742,7 @@
         <v>9</v>
       </c>
       <c r="D487" t="n">
-        <v>20160</v>
+        <v>19390</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
@@ -36753,10 +36753,10 @@
         <v>9</v>
       </c>
       <c r="G487" t="n">
-        <v>0.8530050687907313</v>
+        <v>0.8160753077480087</v>
       </c>
       <c r="H487" t="n">
-        <v>2.418743664011586</v>
+        <v>2.279905865314989</v>
       </c>
       <c r="I487" t="inlineStr">
         <is>
@@ -36769,26 +36769,26 @@
         </is>
       </c>
       <c r="K487" t="n">
-        <v>1.9</v>
+        <v>1.875</v>
       </c>
       <c r="L487" t="n">
         <v>1</v>
       </c>
       <c r="M487" t="n">
-        <v>0.5187436640115859</v>
+        <v>0.4049058653149893</v>
       </c>
       <c r="N487" t="n">
-        <v>0.5187436640115859</v>
+        <v>0.4049058653149893</v>
       </c>
       <c r="O487" t="n">
-        <v>-0.06749999999999989</v>
+        <v>0.03249999999999997</v>
       </c>
       <c r="P487" t="n">
-        <v>-0.04055877383538498</v>
+        <v>-0.03001810282404049</v>
       </c>
       <c r="Q487" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R487" t="inlineStr">
@@ -36797,13 +36797,13 @@
         </is>
       </c>
       <c r="S487" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -36813,7 +36813,7 @@
         <v>9</v>
       </c>
       <c r="D488" t="n">
-        <v>19780</v>
+        <v>19300</v>
       </c>
       <c r="E488" t="inlineStr">
         <is>
@@ -36824,10 +36824,10 @@
         <v>9</v>
       </c>
       <c r="G488" t="n">
-        <v>0.8392469225199131</v>
+        <v>0.8102824040550326</v>
       </c>
       <c r="H488" t="n">
-        <v>2.363012309920347</v>
+        <v>2.265</v>
       </c>
       <c r="I488" t="inlineStr">
         <is>
@@ -36840,22 +36840,22 @@
         </is>
       </c>
       <c r="K488" t="n">
-        <v>1.8775</v>
+        <v>1.9175</v>
       </c>
       <c r="L488" t="n">
         <v>1</v>
       </c>
       <c r="M488" t="n">
-        <v>0.4855123099203476</v>
+        <v>0.3475000000000001</v>
       </c>
       <c r="N488" t="n">
-        <v>0.4855123099203476</v>
+        <v>0.3475000000000001</v>
       </c>
       <c r="O488" t="n">
-        <v>-0.02249999999999996</v>
+        <v>0.04249999999999998</v>
       </c>
       <c r="P488" t="n">
-        <v>-0.05573135409123831</v>
+        <v>-0.01490586531498916</v>
       </c>
       <c r="Q488" t="inlineStr">
         <is>
@@ -36864,17 +36864,17 @@
       </c>
       <c r="R488" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S488" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -36884,7 +36884,7 @@
         <v>9</v>
       </c>
       <c r="D489" t="n">
-        <v>19566.671875</v>
+        <v>19280</v>
       </c>
       <c r="E489" t="inlineStr">
         <is>
@@ -36895,10 +36895,10 @@
         <v>9</v>
       </c>
       <c r="G489" t="n">
-        <v>0.8240405503258509</v>
+        <v>0.8095582910934106</v>
       </c>
       <c r="H489" t="n">
-        <v>2.30992396813903</v>
+        <v>2.265</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -36911,31 +36911,31 @@
         </is>
       </c>
       <c r="K489" t="n">
-        <v>1.8425</v>
+        <v>2.0025</v>
       </c>
       <c r="L489" t="n">
         <v>1</v>
       </c>
       <c r="M489" t="n">
-        <v>0.4674239681390298</v>
+        <v>0.2624999999999997</v>
       </c>
       <c r="N489" t="n">
-        <v>0.4674239681390298</v>
+        <v>0.2624999999999997</v>
       </c>
       <c r="O489" t="n">
-        <v>-0.03499999999999992</v>
+        <v>0.08499999999999996</v>
       </c>
       <c r="P489" t="n">
-        <v>-0.05308834178131772</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="Q489" t="inlineStr">
         <is>
+          <t>Ascendente</t>
+        </is>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
           <t>Estable</t>
-        </is>
-      </c>
-      <c r="R489" t="inlineStr">
-        <is>
-          <t>Descendente</t>
         </is>
       </c>
       <c r="S489" t="b">
@@ -36945,7 +36945,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -36955,7 +36955,7 @@
         <v>9</v>
       </c>
       <c r="D490" t="n">
-        <v>19390</v>
+        <v>19240</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
@@ -36966,10 +36966,10 @@
         <v>9</v>
       </c>
       <c r="G490" t="n">
-        <v>0.8160753077480087</v>
+        <v>0.8073859522085446</v>
       </c>
       <c r="H490" t="n">
-        <v>2.279905865314989</v>
+        <v>2.258267559739319</v>
       </c>
       <c r="I490" t="inlineStr">
         <is>
@@ -36982,41 +36982,41 @@
         </is>
       </c>
       <c r="K490" t="n">
-        <v>1.875</v>
+        <v>2.0625</v>
       </c>
       <c r="L490" t="n">
         <v>1</v>
       </c>
       <c r="M490" t="n">
-        <v>0.4049058653149893</v>
+        <v>0.1957675597393194</v>
       </c>
       <c r="N490" t="n">
-        <v>0.4049058653149893</v>
+        <v>0.1957675597393194</v>
       </c>
       <c r="O490" t="n">
-        <v>0.03249999999999997</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="P490" t="n">
-        <v>-0.03001810282404049</v>
+        <v>-0.006732440260680317</v>
       </c>
       <c r="Q490" t="inlineStr">
         <is>
+          <t>Ascendente</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="R490" t="inlineStr">
-        <is>
-          <t>Estable</t>
-        </is>
-      </c>
       <c r="S490" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -37026,7 +37026,7 @@
         <v>9</v>
       </c>
       <c r="D491" t="n">
-        <v>19300</v>
+        <v>19180</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
@@ -37037,10 +37037,10 @@
         <v>9</v>
       </c>
       <c r="G491" t="n">
-        <v>0.8102824040550326</v>
+        <v>0.8044895003620565</v>
       </c>
       <c r="H491" t="n">
-        <v>2.265</v>
+        <v>2.229347332850591</v>
       </c>
       <c r="I491" t="inlineStr">
         <is>
@@ -37053,41 +37053,41 @@
         </is>
       </c>
       <c r="K491" t="n">
-        <v>1.9175</v>
+        <v>2.1275</v>
       </c>
       <c r="L491" t="n">
         <v>1</v>
       </c>
       <c r="M491" t="n">
-        <v>0.3475000000000001</v>
+        <v>0.1018473328505909</v>
       </c>
       <c r="N491" t="n">
-        <v>0.3475000000000001</v>
+        <v>0.1018473328505909</v>
       </c>
       <c r="O491" t="n">
-        <v>0.04249999999999998</v>
+        <v>0.06500000000000039</v>
       </c>
       <c r="P491" t="n">
-        <v>-0.01490586531498916</v>
+        <v>-0.02892022688872808</v>
       </c>
       <c r="Q491" t="inlineStr">
         <is>
+          <t>Ascendente</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="R491" t="inlineStr">
-        <is>
-          <t>Estable</t>
-        </is>
-      </c>
       <c r="S491" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -37097,7 +37097,7 @@
         <v>9</v>
       </c>
       <c r="D492" t="n">
-        <v>19280</v>
+        <v>19122.62890625</v>
       </c>
       <c r="E492" t="inlineStr">
         <is>
@@ -37108,38 +37108,38 @@
         <v>9</v>
       </c>
       <c r="G492" t="n">
-        <v>0.8095582910934106</v>
+        <v>0.8001448225923244</v>
       </c>
       <c r="H492" t="n">
+        <v>2.219818971759595</v>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>TAMSHIYACU</t>
+        </is>
+      </c>
+      <c r="K492" t="n">
         <v>2.265</v>
       </c>
-      <c r="I492" t="inlineStr">
-        <is>
-          <t>cdf_empirica_mensual_ordenada</t>
-        </is>
-      </c>
-      <c r="J492" t="inlineStr">
-        <is>
-          <t>TAMSHIYACU</t>
-        </is>
-      </c>
-      <c r="K492" t="n">
-        <v>2.0025</v>
-      </c>
       <c r="L492" t="n">
         <v>1</v>
       </c>
       <c r="M492" t="n">
-        <v>0.2624999999999997</v>
+        <v>-0.04518102824040504</v>
       </c>
       <c r="N492" t="n">
-        <v>0.2624999999999997</v>
+        <v>0.04518102824040504</v>
       </c>
       <c r="O492" t="n">
-        <v>0.08499999999999996</v>
+        <v>0.1374999999999993</v>
       </c>
       <c r="P492" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>-0.00952836109099664</v>
       </c>
       <c r="Q492" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -37168,7 +37168,7 @@
         <v>9</v>
       </c>
       <c r="D493" t="n">
-        <v>19240</v>
+        <v>19010</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
@@ -37179,10 +37179,10 @@
         <v>9</v>
       </c>
       <c r="G493" t="n">
-        <v>0.8073859522085446</v>
+        <v>0.7943519188993483</v>
       </c>
       <c r="H493" t="n">
-        <v>2.258267559739319</v>
+        <v>2.208549360366884</v>
       </c>
       <c r="I493" t="inlineStr">
         <is>
@@ -37195,22 +37195,22 @@
         </is>
       </c>
       <c r="K493" t="n">
-        <v>2.0625</v>
+        <v>2.435</v>
       </c>
       <c r="L493" t="n">
         <v>1</v>
       </c>
       <c r="M493" t="n">
-        <v>0.1957675597393194</v>
+        <v>-0.2264506396331156</v>
       </c>
       <c r="N493" t="n">
-        <v>0.1957675597393194</v>
+        <v>0.2264506396331156</v>
       </c>
       <c r="O493" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.1699999999999999</v>
       </c>
       <c r="P493" t="n">
-        <v>-0.006732440260680317</v>
+        <v>-0.01126961139271065</v>
       </c>
       <c r="Q493" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -37239,7 +37239,7 @@
         <v>9</v>
       </c>
       <c r="D494" t="n">
-        <v>19180</v>
+        <v>18750</v>
       </c>
       <c r="E494" t="inlineStr">
         <is>
@@ -37250,10 +37250,10 @@
         <v>9</v>
       </c>
       <c r="G494" t="n">
-        <v>0.8044895003620565</v>
+        <v>0.7842143374366402</v>
       </c>
       <c r="H494" t="n">
-        <v>2.229347332850591</v>
+        <v>2.1644641564084</v>
       </c>
       <c r="I494" t="inlineStr">
         <is>
@@ -37266,22 +37266,22 @@
         </is>
       </c>
       <c r="K494" t="n">
-        <v>2.1275</v>
+        <v>2.655</v>
       </c>
       <c r="L494" t="n">
         <v>1</v>
       </c>
       <c r="M494" t="n">
-        <v>0.1018473328505909</v>
+        <v>-0.4905358435916001</v>
       </c>
       <c r="N494" t="n">
-        <v>0.1018473328505909</v>
+        <v>0.4905358435916001</v>
       </c>
       <c r="O494" t="n">
-        <v>0.06500000000000039</v>
+        <v>0.2200000000000006</v>
       </c>
       <c r="P494" t="n">
-        <v>-0.02892022688872808</v>
+        <v>-0.04408520395848381</v>
       </c>
       <c r="Q494" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -37310,7 +37310,7 @@
         <v>9</v>
       </c>
       <c r="D495" t="n">
-        <v>19122.62890625</v>
+        <v>18530</v>
       </c>
       <c r="E495" t="inlineStr">
         <is>
@@ -37321,10 +37321,10 @@
         <v>9</v>
       </c>
       <c r="G495" t="n">
-        <v>0.8001448225923244</v>
+        <v>0.7704561911658219</v>
       </c>
       <c r="H495" t="n">
-        <v>2.219818971759595</v>
+        <v>2.119239681390297</v>
       </c>
       <c r="I495" t="inlineStr">
         <is>
@@ -37337,22 +37337,22 @@
         </is>
       </c>
       <c r="K495" t="n">
-        <v>2.265</v>
+        <v>2.8875</v>
       </c>
       <c r="L495" t="n">
         <v>1</v>
       </c>
       <c r="M495" t="n">
-        <v>-0.04518102824040504</v>
+        <v>-0.7682603186097028</v>
       </c>
       <c r="N495" t="n">
-        <v>0.04518102824040504</v>
+        <v>0.7682603186097028</v>
       </c>
       <c r="O495" t="n">
-        <v>0.1374999999999993</v>
+        <v>0.2324999999999995</v>
       </c>
       <c r="P495" t="n">
-        <v>-0.00952836109099664</v>
+        <v>-0.04522447501810323</v>
       </c>
       <c r="Q495" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -37381,7 +37381,7 @@
         <v>9</v>
       </c>
       <c r="D496" t="n">
-        <v>19010</v>
+        <v>18280</v>
       </c>
       <c r="E496" t="inlineStr">
         <is>
@@ -37392,10 +37392,10 @@
         <v>9</v>
       </c>
       <c r="G496" t="n">
-        <v>0.7943519188993483</v>
+        <v>0.7538015930485156</v>
       </c>
       <c r="H496" t="n">
-        <v>2.208549360366884</v>
+        <v>2.077549601737871</v>
       </c>
       <c r="I496" t="inlineStr">
         <is>
@@ -37408,22 +37408,22 @@
         </is>
       </c>
       <c r="K496" t="n">
-        <v>2.435</v>
+        <v>3.0175</v>
       </c>
       <c r="L496" t="n">
         <v>1</v>
       </c>
       <c r="M496" t="n">
-        <v>-0.2264506396331156</v>
+        <v>-0.9399503982621287</v>
       </c>
       <c r="N496" t="n">
-        <v>0.2264506396331156</v>
+        <v>0.9399503982621287</v>
       </c>
       <c r="O496" t="n">
-        <v>0.1699999999999999</v>
+        <v>0.1300000000000003</v>
       </c>
       <c r="P496" t="n">
-        <v>-0.01126961139271065</v>
+        <v>-0.04169007965242555</v>
       </c>
       <c r="Q496" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -37452,7 +37452,7 @@
         <v>9</v>
       </c>
       <c r="D497" t="n">
-        <v>18750</v>
+        <v>17910</v>
       </c>
       <c r="E497" t="inlineStr">
         <is>
@@ -37463,10 +37463,10 @@
         <v>9</v>
       </c>
       <c r="G497" t="n">
-        <v>0.7842143374366402</v>
+        <v>0.7342505430847213</v>
       </c>
       <c r="H497" t="n">
-        <v>2.1644641564084</v>
+        <v>2.009812092686459</v>
       </c>
       <c r="I497" t="inlineStr">
         <is>
@@ -37479,22 +37479,22 @@
         </is>
       </c>
       <c r="K497" t="n">
-        <v>2.655</v>
+        <v>3.1</v>
       </c>
       <c r="L497" t="n">
         <v>1</v>
       </c>
       <c r="M497" t="n">
-        <v>-0.4905358435916001</v>
+        <v>-1.090187907313541</v>
       </c>
       <c r="N497" t="n">
-        <v>0.4905358435916001</v>
+        <v>1.090187907313541</v>
       </c>
       <c r="O497" t="n">
-        <v>0.2200000000000006</v>
+        <v>0.08249999999999957</v>
       </c>
       <c r="P497" t="n">
-        <v>-0.04408520395848381</v>
+        <v>-0.06773750905141229</v>
       </c>
       <c r="Q497" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
       </c>
       <c r="R497" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S497" t="b">
@@ -37513,7 +37513,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -37523,7 +37523,7 @@
         <v>9</v>
       </c>
       <c r="D498" t="n">
-        <v>18530</v>
+        <v>17725.712890625</v>
       </c>
       <c r="E498" t="inlineStr">
         <is>
@@ -37534,10 +37534,10 @@
         <v>9</v>
       </c>
       <c r="G498" t="n">
-        <v>0.7704561911658219</v>
+        <v>0.720492396813903</v>
       </c>
       <c r="H498" t="n">
-        <v>2.119239681390297</v>
+        <v>1.973153511947864</v>
       </c>
       <c r="I498" t="inlineStr">
         <is>
@@ -37550,26 +37550,26 @@
         </is>
       </c>
       <c r="K498" t="n">
-        <v>2.8875</v>
+        <v>3.1025</v>
       </c>
       <c r="L498" t="n">
         <v>1</v>
       </c>
       <c r="M498" t="n">
-        <v>-0.7682603186097028</v>
+        <v>-1.129346488052136</v>
       </c>
       <c r="N498" t="n">
-        <v>0.7682603186097028</v>
+        <v>1.129346488052136</v>
       </c>
       <c r="O498" t="n">
-        <v>0.2324999999999995</v>
+        <v>0.002500000000000391</v>
       </c>
       <c r="P498" t="n">
-        <v>-0.04522447501810323</v>
+        <v>-0.03665858073859485</v>
       </c>
       <c r="Q498" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R498" t="inlineStr">
@@ -37578,13 +37578,13 @@
         </is>
       </c>
       <c r="S498" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -37594,7 +37594,7 @@
         <v>9</v>
       </c>
       <c r="D499" t="n">
-        <v>18280</v>
+        <v>17620</v>
       </c>
       <c r="E499" t="inlineStr">
         <is>
@@ -37605,10 +37605,10 @@
         <v>9</v>
       </c>
       <c r="G499" t="n">
-        <v>0.7538015930485156</v>
+        <v>0.7132512671976828</v>
       </c>
       <c r="H499" t="n">
-        <v>2.077549601737871</v>
+        <v>1.942994931209269</v>
       </c>
       <c r="I499" t="inlineStr">
         <is>
@@ -37621,26 +37621,26 @@
         </is>
       </c>
       <c r="K499" t="n">
-        <v>3.0175</v>
+        <v>3.02</v>
       </c>
       <c r="L499" t="n">
         <v>1</v>
       </c>
       <c r="M499" t="n">
-        <v>-0.9399503982621287</v>
+        <v>-1.077005068790731</v>
       </c>
       <c r="N499" t="n">
-        <v>0.9399503982621287</v>
+        <v>1.077005068790731</v>
       </c>
       <c r="O499" t="n">
-        <v>0.1300000000000003</v>
+        <v>-0.08250000000000046</v>
       </c>
       <c r="P499" t="n">
-        <v>-0.04169007965242555</v>
+        <v>-0.03015858073859556</v>
       </c>
       <c r="Q499" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="R499" t="inlineStr">
@@ -37655,7 +37655,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -37665,7 +37665,7 @@
         <v>9</v>
       </c>
       <c r="D500" t="n">
-        <v>17910</v>
+        <v>17639.984375</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
@@ -37676,10 +37676,10 @@
         <v>9</v>
       </c>
       <c r="G500" t="n">
-        <v>0.7342505430847213</v>
+        <v>0.7139753801593048</v>
       </c>
       <c r="H500" t="n">
-        <v>2.009812092686459</v>
+        <v>1.948147719044171</v>
       </c>
       <c r="I500" t="inlineStr">
         <is>
@@ -37692,31 +37692,31 @@
         </is>
       </c>
       <c r="K500" t="n">
-        <v>3.1</v>
+        <v>2.7575</v>
       </c>
       <c r="L500" t="n">
         <v>1</v>
       </c>
       <c r="M500" t="n">
-        <v>-1.090187907313541</v>
+        <v>-0.8093522809558291</v>
       </c>
       <c r="N500" t="n">
-        <v>1.090187907313541</v>
+        <v>0.8093522809558291</v>
       </c>
       <c r="O500" t="n">
-        <v>0.08249999999999957</v>
+        <v>-0.2624999999999997</v>
       </c>
       <c r="P500" t="n">
-        <v>-0.06773750905141229</v>
+        <v>0.005152787834902028</v>
       </c>
       <c r="Q500" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="R500" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S500" t="b">
@@ -37726,7 +37726,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -37736,7 +37736,7 @@
         <v>9</v>
       </c>
       <c r="D501" t="n">
-        <v>17725.712890625</v>
+        <v>17741.51953125</v>
       </c>
       <c r="E501" t="inlineStr">
         <is>
@@ -37747,10 +37747,10 @@
         <v>9</v>
       </c>
       <c r="G501" t="n">
-        <v>0.720492396813903</v>
+        <v>0.723388848660391</v>
       </c>
       <c r="H501" t="n">
-        <v>1.973153511947864</v>
+        <v>1.980611151339609</v>
       </c>
       <c r="I501" t="inlineStr">
         <is>
@@ -37763,41 +37763,41 @@
         </is>
       </c>
       <c r="K501" t="n">
-        <v>3.1025</v>
+        <v>2.5</v>
       </c>
       <c r="L501" t="n">
         <v>1</v>
       </c>
       <c r="M501" t="n">
-        <v>-1.129346488052136</v>
+        <v>-0.519388848660391</v>
       </c>
       <c r="N501" t="n">
-        <v>1.129346488052136</v>
+        <v>0.519388848660391</v>
       </c>
       <c r="O501" t="n">
-        <v>0.002500000000000391</v>
+        <v>-0.2574999999999998</v>
       </c>
       <c r="P501" t="n">
-        <v>-0.03665858073859485</v>
+        <v>0.03246343229543824</v>
       </c>
       <c r="Q501" t="inlineStr">
         <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R501" t="inlineStr">
+        <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="R501" t="inlineStr">
-        <is>
-          <t>Estable</t>
-        </is>
-      </c>
       <c r="S501" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -37807,7 +37807,7 @@
         <v>9</v>
       </c>
       <c r="D502" t="n">
-        <v>17620</v>
+        <v>17886.734375</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
@@ -37818,10 +37818,10 @@
         <v>9</v>
       </c>
       <c r="G502" t="n">
-        <v>0.7132512671976828</v>
+        <v>0.7320782041998551</v>
       </c>
       <c r="H502" t="n">
-        <v>1.942994931209269</v>
+        <v>2.006941346850108</v>
       </c>
       <c r="I502" t="inlineStr">
         <is>
@@ -37834,22 +37834,22 @@
         </is>
       </c>
       <c r="K502" t="n">
-        <v>3.02</v>
+        <v>2.3875</v>
       </c>
       <c r="L502" t="n">
         <v>1</v>
       </c>
       <c r="M502" t="n">
-        <v>-1.077005068790731</v>
+        <v>-0.3805586531498917</v>
       </c>
       <c r="N502" t="n">
-        <v>1.077005068790731</v>
+        <v>0.3805586531498917</v>
       </c>
       <c r="O502" t="n">
-        <v>-0.08250000000000046</v>
+        <v>-0.1124999999999998</v>
       </c>
       <c r="P502" t="n">
-        <v>-0.03015858073859556</v>
+        <v>0.02633019551049953</v>
       </c>
       <c r="Q502" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -37878,7 +37878,7 @@
         <v>9</v>
       </c>
       <c r="D503" t="n">
-        <v>17639.984375</v>
+        <v>18078.9140625</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
@@ -37889,10 +37889,10 @@
         <v>9</v>
       </c>
       <c r="G503" t="n">
-        <v>0.7139753801593048</v>
+        <v>0.7414916727009413</v>
       </c>
       <c r="H503" t="n">
-        <v>1.948147719044171</v>
+        <v>2.022541636495293</v>
       </c>
       <c r="I503" t="inlineStr">
         <is>
@@ -37905,22 +37905,22 @@
         </is>
       </c>
       <c r="K503" t="n">
-        <v>2.7575</v>
+        <v>2.2575</v>
       </c>
       <c r="L503" t="n">
         <v>1</v>
       </c>
       <c r="M503" t="n">
-        <v>-0.8093522809558291</v>
+        <v>-0.234958363504707</v>
       </c>
       <c r="N503" t="n">
-        <v>0.8093522809558291</v>
+        <v>0.234958363504707</v>
       </c>
       <c r="O503" t="n">
-        <v>-0.2624999999999997</v>
+        <v>-0.1300000000000003</v>
       </c>
       <c r="P503" t="n">
-        <v>0.005152787834902028</v>
+        <v>0.01560028964518434</v>
       </c>
       <c r="Q503" t="inlineStr">
         <is>
@@ -37939,17 +37939,17 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B504" t="n">
         <v>9038269</v>
       </c>
       <c r="C504" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D504" t="n">
-        <v>17741.51953125</v>
+        <v>19130</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
@@ -37957,13 +37957,13 @@
         </is>
       </c>
       <c r="F504" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G504" t="n">
-        <v>0.723388848660391</v>
+        <v>0.7057569296375267</v>
       </c>
       <c r="H504" t="n">
-        <v>1.980611151339609</v>
+        <v>2.634022743425728</v>
       </c>
       <c r="I504" t="inlineStr">
         <is>
@@ -37976,22 +37976,22 @@
         </is>
       </c>
       <c r="K504" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="L504" t="n">
         <v>1</v>
       </c>
       <c r="M504" t="n">
-        <v>-0.519388848660391</v>
+        <v>0.484022743425728</v>
       </c>
       <c r="N504" t="n">
-        <v>0.519388848660391</v>
+        <v>0.484022743425728</v>
       </c>
       <c r="O504" t="n">
-        <v>-0.2574999999999998</v>
+        <v>-0.1074999999999995</v>
       </c>
       <c r="P504" t="n">
-        <v>0.03246343229543824</v>
+        <v>0.6114811069304356</v>
       </c>
       <c r="Q504" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
       </c>
       <c r="R504" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S504" t="b">
@@ -38010,17 +38010,17 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B505" t="n">
         <v>9038269</v>
       </c>
       <c r="C505" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D505" t="n">
-        <v>17886.734375</v>
+        <v>18950</v>
       </c>
       <c r="E505" t="inlineStr">
         <is>
@@ -38028,13 +38028,13 @@
         </is>
       </c>
       <c r="F505" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G505" t="n">
-        <v>0.7320782041998551</v>
+        <v>0.6929637526652452</v>
       </c>
       <c r="H505" t="n">
-        <v>2.006941346850108</v>
+        <v>2.590756929637527</v>
       </c>
       <c r="I505" t="inlineStr">
         <is>
@@ -38047,22 +38047,22 @@
         </is>
       </c>
       <c r="K505" t="n">
-        <v>2.3875</v>
+        <v>2.09</v>
       </c>
       <c r="L505" t="n">
         <v>1</v>
       </c>
       <c r="M505" t="n">
-        <v>-0.3805586531498917</v>
+        <v>0.5007569296375269</v>
       </c>
       <c r="N505" t="n">
-        <v>0.3805586531498917</v>
+        <v>0.5007569296375269</v>
       </c>
       <c r="O505" t="n">
-        <v>-0.1124999999999998</v>
+        <v>-0.0600000000000005</v>
       </c>
       <c r="P505" t="n">
-        <v>0.02633019551049953</v>
+        <v>-0.0432658137882016</v>
       </c>
       <c r="Q505" t="inlineStr">
         <is>
@@ -38081,17 +38081,17 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="B506" t="n">
         <v>9038269</v>
       </c>
       <c r="C506" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D506" t="n">
-        <v>18078.9140625</v>
+        <v>18790</v>
       </c>
       <c r="E506" t="inlineStr">
         <is>
@@ -38099,13 +38099,13 @@
         </is>
       </c>
       <c r="F506" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G506" t="n">
-        <v>0.7414916727009413</v>
+        <v>0.6837242359630419</v>
       </c>
       <c r="H506" t="n">
-        <v>2.022541636495293</v>
+        <v>2.551795782989812</v>
       </c>
       <c r="I506" t="inlineStr">
         <is>
@@ -38118,26 +38118,26 @@
         </is>
       </c>
       <c r="K506" t="n">
-        <v>2.2575</v>
+        <v>2.0475</v>
       </c>
       <c r="L506" t="n">
         <v>1</v>
       </c>
       <c r="M506" t="n">
-        <v>-0.234958363504707</v>
+        <v>0.5042957829898125</v>
       </c>
       <c r="N506" t="n">
-        <v>0.234958363504707</v>
+        <v>0.5042957829898125</v>
       </c>
       <c r="O506" t="n">
-        <v>-0.1300000000000003</v>
+        <v>-0.04249999999999998</v>
       </c>
       <c r="P506" t="n">
-        <v>0.01560028964518434</v>
+        <v>-0.03896114664771444</v>
       </c>
       <c r="Q506" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R506" t="inlineStr">
@@ -38146,13 +38146,13 @@
         </is>
       </c>
       <c r="S506" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -38162,7 +38162,7 @@
         <v>10</v>
       </c>
       <c r="D507" t="n">
-        <v>19130</v>
+        <v>18740</v>
       </c>
       <c r="E507" t="inlineStr">
         <is>
@@ -38173,10 +38173,10 @@
         <v>10</v>
       </c>
       <c r="G507" t="n">
-        <v>0.7057569296375267</v>
+        <v>0.681592039800995</v>
       </c>
       <c r="H507" t="n">
-        <v>2.637945984363895</v>
+        <v>2.546757877280265</v>
       </c>
       <c r="I507" t="inlineStr">
         <is>
@@ -38189,22 +38189,22 @@
         </is>
       </c>
       <c r="K507" t="n">
-        <v>2.15</v>
+        <v>1.8725</v>
       </c>
       <c r="L507" t="n">
         <v>1</v>
       </c>
       <c r="M507" t="n">
-        <v>0.4879459843638947</v>
+        <v>0.6742578772802652</v>
       </c>
       <c r="N507" t="n">
-        <v>0.4879459843638947</v>
+        <v>0.6742578772802652</v>
       </c>
       <c r="O507" t="n">
-        <v>-0.1074999999999995</v>
+        <v>-0.1749999999999998</v>
       </c>
       <c r="P507" t="n">
-        <v>0.6154043478686022</v>
+        <v>-0.005037905709547097</v>
       </c>
       <c r="Q507" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
       </c>
       <c r="R507" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S507" t="b">
@@ -38223,7 +38223,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -38233,7 +38233,7 @@
         <v>10</v>
       </c>
       <c r="D508" t="n">
-        <v>18950</v>
+        <v>18870.7734375</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
@@ -38244,10 +38244,10 @@
         <v>10</v>
       </c>
       <c r="G508" t="n">
-        <v>0.6929637526652452</v>
+        <v>0.6879886282871357</v>
       </c>
       <c r="H508" t="n">
-        <v>2.593827292110874</v>
+        <v>2.572533759772566</v>
       </c>
       <c r="I508" t="inlineStr">
         <is>
@@ -38260,22 +38260,22 @@
         </is>
       </c>
       <c r="K508" t="n">
-        <v>2.09</v>
+        <v>1.7675</v>
       </c>
       <c r="L508" t="n">
         <v>1</v>
       </c>
       <c r="M508" t="n">
-        <v>0.5038272921108744</v>
+        <v>0.8050337597725659</v>
       </c>
       <c r="N508" t="n">
-        <v>0.5038272921108744</v>
+        <v>0.8050337597725659</v>
       </c>
       <c r="O508" t="n">
-        <v>-0.0600000000000005</v>
+        <v>-0.1050000000000002</v>
       </c>
       <c r="P508" t="n">
-        <v>-0.04411869225302079</v>
+        <v>0.02577588249230045</v>
       </c>
       <c r="Q508" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -38304,7 +38304,7 @@
         <v>10</v>
       </c>
       <c r="D509" t="n">
-        <v>18790</v>
+        <v>19274.451171875</v>
       </c>
       <c r="E509" t="inlineStr">
         <is>
@@ -38315,10 +38315,10 @@
         <v>10</v>
       </c>
       <c r="G509" t="n">
-        <v>0.6837242359630419</v>
+        <v>0.7135749822316987</v>
       </c>
       <c r="H509" t="n">
-        <v>2.556012793176972</v>
+        <v>2.671574271499645</v>
       </c>
       <c r="I509" t="inlineStr">
         <is>
@@ -38331,22 +38331,22 @@
         </is>
       </c>
       <c r="K509" t="n">
-        <v>2.0475</v>
+        <v>1.745</v>
       </c>
       <c r="L509" t="n">
         <v>1</v>
       </c>
       <c r="M509" t="n">
-        <v>0.5085127931769722</v>
+        <v>0.9265742714996446</v>
       </c>
       <c r="N509" t="n">
-        <v>0.5085127931769722</v>
+        <v>0.9265742714996446</v>
       </c>
       <c r="O509" t="n">
-        <v>-0.04249999999999998</v>
+        <v>-0.02249999999999974</v>
       </c>
       <c r="P509" t="n">
-        <v>-0.03781449893390221</v>
+        <v>0.09904051172707895</v>
       </c>
       <c r="Q509" t="inlineStr">
         <is>
@@ -38355,17 +38355,17 @@
       </c>
       <c r="R509" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S509" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -38375,7 +38375,7 @@
         <v>10</v>
       </c>
       <c r="D510" t="n">
-        <v>18740</v>
+        <v>19768.615234375</v>
       </c>
       <c r="E510" t="inlineStr">
         <is>
@@ -38386,10 +38386,10 @@
         <v>10</v>
       </c>
       <c r="G510" t="n">
-        <v>0.681592039800995</v>
+        <v>0.7370291400142146</v>
       </c>
       <c r="H510" t="n">
-        <v>2.548880597014925</v>
+        <v>2.748796493721867</v>
       </c>
       <c r="I510" t="inlineStr">
         <is>
@@ -38402,41 +38402,41 @@
         </is>
       </c>
       <c r="K510" t="n">
-        <v>1.8725</v>
+        <v>1.8025</v>
       </c>
       <c r="L510" t="n">
         <v>1</v>
       </c>
       <c r="M510" t="n">
-        <v>0.676380597014925</v>
+        <v>0.9462964937218667</v>
       </c>
       <c r="N510" t="n">
-        <v>0.676380597014925</v>
+        <v>0.9462964937218667</v>
       </c>
       <c r="O510" t="n">
-        <v>-0.1749999999999998</v>
+        <v>0.05750000000000011</v>
       </c>
       <c r="P510" t="n">
-        <v>-0.007132196162046966</v>
+        <v>0.0772222222222223</v>
       </c>
       <c r="Q510" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="R510" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S510" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -38446,7 +38446,7 @@
         <v>10</v>
       </c>
       <c r="D511" t="n">
-        <v>18870.7734375</v>
+        <v>20640</v>
       </c>
       <c r="E511" t="inlineStr">
         <is>
@@ -38457,10 +38457,10 @@
         <v>10</v>
       </c>
       <c r="G511" t="n">
-        <v>0.6879886282871357</v>
+        <v>0.7661691542288557</v>
       </c>
       <c r="H511" t="n">
-        <v>2.575943496801706</v>
+        <v>2.868348258706468</v>
       </c>
       <c r="I511" t="inlineStr">
         <is>
@@ -38473,41 +38473,41 @@
         </is>
       </c>
       <c r="K511" t="n">
-        <v>1.7675</v>
+        <v>1.915</v>
       </c>
       <c r="L511" t="n">
         <v>1</v>
       </c>
       <c r="M511" t="n">
-        <v>0.8084434968017056</v>
+        <v>0.9533482587064681</v>
       </c>
       <c r="N511" t="n">
-        <v>0.8084434968017056</v>
+        <v>0.9533482587064681</v>
       </c>
       <c r="O511" t="n">
-        <v>-0.105</v>
+        <v>0.1124999999999996</v>
       </c>
       <c r="P511" t="n">
-        <v>0.02706289978678056</v>
+        <v>0.119551764984601</v>
       </c>
       <c r="Q511" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="R511" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S511" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -38517,7 +38517,7 @@
         <v>10</v>
       </c>
       <c r="D512" t="n">
-        <v>19274.451171875</v>
+        <v>21420.30859375</v>
       </c>
       <c r="E512" t="inlineStr">
         <is>
@@ -38528,10 +38528,10 @@
         <v>10</v>
       </c>
       <c r="G512" t="n">
-        <v>0.7135749822316987</v>
+        <v>0.7903340440653873</v>
       </c>
       <c r="H512" t="n">
-        <v>2.675575692963752</v>
+        <v>2.998695806680881</v>
       </c>
       <c r="I512" t="inlineStr">
         <is>
@@ -38544,26 +38544,26 @@
         </is>
       </c>
       <c r="K512" t="n">
-        <v>1.745</v>
+        <v>1.9725</v>
       </c>
       <c r="L512" t="n">
         <v>1</v>
       </c>
       <c r="M512" t="n">
-        <v>0.9305756929637523</v>
+        <v>1.026195806680881</v>
       </c>
       <c r="N512" t="n">
-        <v>0.9305756929637523</v>
+        <v>1.026195806680881</v>
       </c>
       <c r="O512" t="n">
-        <v>-0.02249999999999996</v>
+        <v>0.05750000000000033</v>
       </c>
       <c r="P512" t="n">
-        <v>0.09963219616204677</v>
+        <v>0.1303475479744129</v>
       </c>
       <c r="Q512" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="R512" t="inlineStr">
@@ -38572,13 +38572,13 @@
         </is>
       </c>
       <c r="S512" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -38588,7 +38588,7 @@
         <v>10</v>
       </c>
       <c r="D513" t="n">
-        <v>19768.615234375</v>
+        <v>22200.73046875</v>
       </c>
       <c r="E513" t="inlineStr">
         <is>
@@ -38599,10 +38599,10 @@
         <v>10</v>
       </c>
       <c r="G513" t="n">
-        <v>0.7370291400142146</v>
+        <v>0.8180525941719972</v>
       </c>
       <c r="H513" t="n">
-        <v>2.756908315565031</v>
+        <v>3.166718787017294</v>
       </c>
       <c r="I513" t="inlineStr">
         <is>
@@ -38615,41 +38615,41 @@
         </is>
       </c>
       <c r="K513" t="n">
-        <v>1.8025</v>
+        <v>2.01</v>
       </c>
       <c r="L513" t="n">
         <v>1</v>
       </c>
       <c r="M513" t="n">
-        <v>0.9544083155650311</v>
+        <v>1.156718787017295</v>
       </c>
       <c r="N513" t="n">
-        <v>0.9544083155650311</v>
+        <v>1.156718787017295</v>
       </c>
       <c r="O513" t="n">
-        <v>0.05749999999999988</v>
+        <v>0.03749999999999964</v>
       </c>
       <c r="P513" t="n">
-        <v>0.08133262260127871</v>
+        <v>0.1680229803364135</v>
       </c>
       <c r="Q513" t="inlineStr">
         <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="R513" t="inlineStr">
+        <is>
           <t>Ascendente</t>
         </is>
       </c>
-      <c r="R513" t="inlineStr">
-        <is>
-          <t>Ascendente</t>
-        </is>
-      </c>
       <c r="S513" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -38659,7 +38659,7 @@
         <v>10</v>
       </c>
       <c r="D514" t="n">
-        <v>20640</v>
+        <v>22720</v>
       </c>
       <c r="E514" t="inlineStr">
         <is>
@@ -38670,10 +38670,10 @@
         <v>10</v>
       </c>
       <c r="G514" t="n">
-        <v>0.7661691542288557</v>
+        <v>0.8443496801705757</v>
       </c>
       <c r="H514" t="n">
-        <v>2.871305970149253</v>
+        <v>3.289376332622601</v>
       </c>
       <c r="I514" t="inlineStr">
         <is>
@@ -38686,41 +38686,41 @@
         </is>
       </c>
       <c r="K514" t="n">
-        <v>1.9</v>
+        <v>1.8825</v>
       </c>
       <c r="L514" t="n">
         <v>1</v>
       </c>
       <c r="M514" t="n">
-        <v>0.9713059701492535</v>
+        <v>1.406876332622601</v>
       </c>
       <c r="N514" t="n">
-        <v>0.9713059701492535</v>
+        <v>1.406876332622601</v>
       </c>
       <c r="O514" t="n">
-        <v>0.09749999999999992</v>
+        <v>-0.1274999999999997</v>
       </c>
       <c r="P514" t="n">
-        <v>0.1143976545842222</v>
+        <v>0.122657545605307</v>
       </c>
       <c r="Q514" t="inlineStr">
         <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R514" t="inlineStr">
+        <is>
           <t>Ascendente</t>
         </is>
       </c>
-      <c r="R514" t="inlineStr">
-        <is>
-          <t>Ascendente</t>
-        </is>
-      </c>
       <c r="S514" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -38730,7 +38730,7 @@
         <v>9</v>
       </c>
       <c r="D515" t="n">
-        <v>23911.451171875</v>
+        <v>24221.97265625</v>
       </c>
       <c r="E515" t="inlineStr">
         <is>
@@ -38741,10 +38741,10 @@
         <v>9</v>
       </c>
       <c r="G515" t="n">
-        <v>0.8037653874004345</v>
+        <v>0.835626357711803</v>
       </c>
       <c r="H515" t="n">
-        <v>6.616821144098479</v>
+        <v>6.843721940622738</v>
       </c>
       <c r="I515" t="inlineStr">
         <is>
@@ -38757,16 +38757,16 @@
         </is>
       </c>
       <c r="K515" t="n">
-        <v>7.645</v>
+        <v>6.3275</v>
       </c>
       <c r="L515" t="n">
         <v>1</v>
       </c>
       <c r="M515" t="n">
-        <v>-1.028178855901521</v>
+        <v>0.5162219406227386</v>
       </c>
       <c r="N515" t="n">
-        <v>1.028178855901521</v>
+        <v>0.5162219406227386</v>
       </c>
       <c r="O515" t="inlineStr"/>
       <c r="P515" t="inlineStr"/>
@@ -38785,7 +38785,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -38795,7 +38795,7 @@
         <v>9</v>
       </c>
       <c r="D516" t="n">
-        <v>23951.40625</v>
+        <v>24064.072265625</v>
       </c>
       <c r="E516" t="inlineStr">
         <is>
@@ -38806,10 +38806,10 @@
         <v>9</v>
       </c>
       <c r="G516" t="n">
-        <v>0.8102824040550326</v>
+        <v>0.8240405503258509</v>
       </c>
       <c r="H516" t="n">
-        <v>6.637271904417089</v>
+        <v>6.809362780593772</v>
       </c>
       <c r="I516" t="inlineStr">
         <is>
@@ -38822,22 +38822,22 @@
         </is>
       </c>
       <c r="K516" t="n">
-        <v>7.4375</v>
+        <v>6.265</v>
       </c>
       <c r="L516" t="n">
         <v>1</v>
       </c>
       <c r="M516" t="n">
-        <v>-0.8002280955829111</v>
+        <v>0.5443627805937723</v>
       </c>
       <c r="N516" t="n">
-        <v>0.8002280955829111</v>
+        <v>0.5443627805937723</v>
       </c>
       <c r="O516" t="n">
-        <v>-0.2074999999999996</v>
+        <v>-0.0625</v>
       </c>
       <c r="P516" t="n">
-        <v>0.02045076031861015</v>
+        <v>-0.03435916002896633</v>
       </c>
       <c r="Q516" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -38866,7 +38866,7 @@
         <v>9</v>
       </c>
       <c r="D517" t="n">
-        <v>23981.4453125</v>
+        <v>23880.943359375</v>
       </c>
       <c r="E517" t="inlineStr">
         <is>
@@ -38877,10 +38877,10 @@
         <v>9</v>
       </c>
       <c r="G517" t="n">
-        <v>0.8153511947863866</v>
+        <v>0.7994207096307024</v>
       </c>
       <c r="H517" t="n">
-        <v>6.752150615496017</v>
+        <v>6.584610789283128</v>
       </c>
       <c r="I517" t="inlineStr">
         <is>
@@ -38893,31 +38893,31 @@
         </is>
       </c>
       <c r="K517" t="n">
-        <v>7.215000000000001</v>
+        <v>6.2275</v>
       </c>
       <c r="L517" t="n">
         <v>1</v>
       </c>
       <c r="M517" t="n">
-        <v>-0.4628493845039836</v>
+        <v>0.3571107892831282</v>
       </c>
       <c r="N517" t="n">
-        <v>0.4628493845039836</v>
+        <v>0.3571107892831282</v>
       </c>
       <c r="O517" t="n">
-        <v>-0.2224999999999993</v>
+        <v>-0.03749999999999964</v>
       </c>
       <c r="P517" t="n">
-        <v>0.1148787110789282</v>
+        <v>-0.2247519913106437</v>
       </c>
       <c r="Q517" t="inlineStr">
         <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="R517" t="inlineStr">
+        <is>
           <t>Descendente</t>
-        </is>
-      </c>
-      <c r="R517" t="inlineStr">
-        <is>
-          <t>Ascendente</t>
         </is>
       </c>
       <c r="S517" t="b">
@@ -38927,7 +38927,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -38937,7 +38937,7 @@
         <v>9</v>
       </c>
       <c r="D518" t="n">
-        <v>24009.1796875</v>
+        <v>23732.28515625</v>
       </c>
       <c r="E518" t="inlineStr">
         <is>
@@ -38948,10 +38948,10 @@
         <v>9</v>
       </c>
       <c r="G518" t="n">
-        <v>0.8175235336712527</v>
+        <v>0.7921795800144823</v>
       </c>
       <c r="H518" t="n">
-        <v>6.777360608254888</v>
+        <v>6.531996741491673</v>
       </c>
       <c r="I518" t="inlineStr">
         <is>
@@ -38964,31 +38964,31 @@
         </is>
       </c>
       <c r="K518" t="n">
-        <v>7.087499999999999</v>
+        <v>6.225000000000001</v>
       </c>
       <c r="L518" t="n">
         <v>1</v>
       </c>
       <c r="M518" t="n">
-        <v>-0.3101393917451114</v>
+        <v>0.3069967414916723</v>
       </c>
       <c r="N518" t="n">
-        <v>0.3101393917451114</v>
+        <v>0.3069967414916723</v>
       </c>
       <c r="O518" t="n">
-        <v>-0.1275000000000013</v>
+        <v>-0.002499999999999503</v>
       </c>
       <c r="P518" t="n">
-        <v>0.02520999275887092</v>
+        <v>-0.0526140477914554</v>
       </c>
       <c r="Q518" t="inlineStr">
         <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="R518" t="inlineStr">
+        <is>
           <t>Descendente</t>
-        </is>
-      </c>
-      <c r="R518" t="inlineStr">
-        <is>
-          <t>Estable</t>
         </is>
       </c>
       <c r="S518" t="b">
@@ -38998,7 +38998,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -39008,7 +39008,7 @@
         <v>9</v>
       </c>
       <c r="D519" t="n">
-        <v>24063.4609375</v>
+        <v>23685.703125</v>
       </c>
       <c r="E519" t="inlineStr">
         <is>
@@ -39019,10 +39019,10 @@
         <v>9</v>
       </c>
       <c r="G519" t="n">
-        <v>0.8233164373642288</v>
+        <v>0.7885590152063722</v>
       </c>
       <c r="H519" t="n">
-        <v>6.808598841419261</v>
+        <v>6.515219044170891</v>
       </c>
       <c r="I519" t="inlineStr">
         <is>
@@ -39035,26 +39035,26 @@
         </is>
       </c>
       <c r="K519" t="n">
-        <v>6.9525</v>
+        <v>6.4175</v>
       </c>
       <c r="L519" t="n">
         <v>1</v>
       </c>
       <c r="M519" t="n">
-        <v>-0.1439011585807384</v>
+        <v>0.0977190441708915</v>
       </c>
       <c r="N519" t="n">
-        <v>0.1439011585807384</v>
+        <v>0.0977190441708915</v>
       </c>
       <c r="O519" t="n">
-        <v>-0.1349999999999998</v>
+        <v>0.192499999999999</v>
       </c>
       <c r="P519" t="n">
-        <v>0.03123823316437324</v>
+        <v>-0.01677769732078183</v>
       </c>
       <c r="Q519" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="R519" t="inlineStr">
@@ -39069,7 +39069,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -39079,7 +39079,7 @@
         <v>9</v>
       </c>
       <c r="D520" t="n">
-        <v>24158.8984375</v>
+        <v>23768.970703125</v>
       </c>
       <c r="E520" t="inlineStr">
         <is>
@@ -39090,10 +39090,10 @@
         <v>9</v>
       </c>
       <c r="G520" t="n">
-        <v>0.8291093410572049</v>
+        <v>0.7943519188993483</v>
       </c>
       <c r="H520" t="n">
-        <v>6.812355177407674</v>
+        <v>6.545747646632875</v>
       </c>
       <c r="I520" t="inlineStr">
         <is>
@@ -39106,26 +39106,26 @@
         </is>
       </c>
       <c r="K520" t="n">
-        <v>6.835000000000001</v>
+        <v>6.5075</v>
       </c>
       <c r="L520" t="n">
         <v>1</v>
       </c>
       <c r="M520" t="n">
-        <v>-0.02264482259232636</v>
+        <v>0.0382476466328745</v>
       </c>
       <c r="N520" t="n">
-        <v>0.02264482259232636</v>
+        <v>0.0382476466328745</v>
       </c>
       <c r="O520" t="n">
-        <v>-0.1174999999999988</v>
+        <v>0.09000000000000075</v>
       </c>
       <c r="P520" t="n">
-        <v>0.003756335988413184</v>
+        <v>0.03052860246198374</v>
       </c>
       <c r="Q520" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="R520" t="inlineStr">
@@ -39140,7 +39140,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -39150,7 +39150,7 @@
         <v>9</v>
       </c>
       <c r="D521" t="n">
-        <v>24263.53125</v>
+        <v>23898.845703125</v>
       </c>
       <c r="E521" t="inlineStr">
         <is>
@@ -39161,10 +39161,10 @@
         <v>9</v>
       </c>
       <c r="G521" t="n">
-        <v>0.8385228095582911</v>
+        <v>0.8023171614771905</v>
       </c>
       <c r="H521" t="n">
-        <v>6.860528602461984</v>
+        <v>6.606889934829834</v>
       </c>
       <c r="I521" t="inlineStr">
         <is>
@@ -39177,41 +39177,41 @@
         </is>
       </c>
       <c r="K521" t="n">
-        <v>6.6375</v>
+        <v>6.63</v>
       </c>
       <c r="L521" t="n">
         <v>1</v>
       </c>
       <c r="M521" t="n">
-        <v>0.2230286024619836</v>
+        <v>-0.02311006517016612</v>
       </c>
       <c r="N521" t="n">
-        <v>0.2230286024619836</v>
+        <v>0.02311006517016612</v>
       </c>
       <c r="O521" t="n">
-        <v>-0.1975000000000007</v>
+        <v>0.1224999999999996</v>
       </c>
       <c r="P521" t="n">
-        <v>0.04817342505430933</v>
+        <v>0.06114228819695899</v>
       </c>
       <c r="Q521" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="R521" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S521" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -39221,7 +39221,7 @@
         <v>9</v>
       </c>
       <c r="D522" t="n">
-        <v>24323.658203125</v>
+        <v>23970.509765625</v>
       </c>
       <c r="E522" t="inlineStr">
         <is>
@@ -39232,10 +39232,10 @@
         <v>9</v>
       </c>
       <c r="G522" t="n">
-        <v>0.8464880521361332</v>
+        <v>0.8131788559015206</v>
       </c>
       <c r="H522" t="n">
-        <v>6.902404055032584</v>
+        <v>6.702833091962345</v>
       </c>
       <c r="I522" t="inlineStr">
         <is>
@@ -39248,41 +39248,41 @@
         </is>
       </c>
       <c r="K522" t="n">
-        <v>6.5275</v>
+        <v>6.75</v>
       </c>
       <c r="L522" t="n">
         <v>1</v>
       </c>
       <c r="M522" t="n">
-        <v>0.3749040550325846</v>
+        <v>-0.04716690803765466</v>
       </c>
       <c r="N522" t="n">
-        <v>0.3749040550325846</v>
+        <v>0.04716690803765466</v>
       </c>
       <c r="O522" t="n">
-        <v>-0.1100000000000003</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="P522" t="n">
-        <v>0.04187545257060066</v>
+        <v>0.09594315713251156</v>
       </c>
       <c r="Q522" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="R522" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S522" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -39292,7 +39292,7 @@
         <v>9</v>
       </c>
       <c r="D523" t="n">
-        <v>24311.998046875</v>
+        <v>23966.36328125</v>
       </c>
       <c r="E523" t="inlineStr">
         <is>
@@ -39303,10 +39303,10 @@
         <v>9</v>
       </c>
       <c r="G523" t="n">
-        <v>0.8435916002896452</v>
+        <v>0.8117306299782766</v>
       </c>
       <c r="H523" t="n">
-        <v>6.874972845763939</v>
+        <v>6.66845582910934</v>
       </c>
       <c r="I523" t="inlineStr">
         <is>
@@ -39319,26 +39319,26 @@
         </is>
       </c>
       <c r="K523" t="n">
-        <v>6.455</v>
+        <v>6.81</v>
       </c>
       <c r="L523" t="n">
         <v>1</v>
       </c>
       <c r="M523" t="n">
-        <v>0.4199728457639393</v>
+        <v>-0.1415441708906595</v>
       </c>
       <c r="N523" t="n">
-        <v>0.4199728457639393</v>
+        <v>0.1415441708906595</v>
       </c>
       <c r="O523" t="n">
-        <v>-0.07249999999999979</v>
+        <v>0.05999999999999961</v>
       </c>
       <c r="P523" t="n">
-        <v>-0.02743120926864506</v>
+        <v>-0.03437726285300524</v>
       </c>
       <c r="Q523" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="R523" t="inlineStr">
@@ -39353,7 +39353,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -39363,7 +39363,7 @@
         <v>9</v>
       </c>
       <c r="D524" t="n">
-        <v>24221.97265625</v>
+        <v>23891.98828125</v>
       </c>
       <c r="E524" t="inlineStr">
         <is>
@@ -39374,10 +39374,10 @@
         <v>9</v>
       </c>
       <c r="G524" t="n">
-        <v>0.835626357711803</v>
+        <v>0.8015930485155685</v>
       </c>
       <c r="H524" t="n">
-        <v>6.843721940622738</v>
+        <v>6.60192433019551</v>
       </c>
       <c r="I524" t="inlineStr">
         <is>
@@ -39390,31 +39390,31 @@
         </is>
       </c>
       <c r="K524" t="n">
-        <v>6.3275</v>
+        <v>7.0025</v>
       </c>
       <c r="L524" t="n">
         <v>1</v>
       </c>
       <c r="M524" t="n">
-        <v>0.5162219406227386</v>
+        <v>-0.40057566980449</v>
       </c>
       <c r="N524" t="n">
-        <v>0.5162219406227386</v>
+        <v>0.40057566980449</v>
       </c>
       <c r="O524" t="n">
-        <v>-0.1275000000000004</v>
+        <v>0.1925000000000008</v>
       </c>
       <c r="P524" t="n">
-        <v>-0.0312509051412011</v>
+        <v>-0.0665314989138297</v>
       </c>
       <c r="Q524" t="inlineStr">
         <is>
+          <t>Ascendente</t>
+        </is>
+      </c>
+      <c r="R524" t="inlineStr">
+        <is>
           <t>Descendente</t>
-        </is>
-      </c>
-      <c r="R524" t="inlineStr">
-        <is>
-          <t>Estable</t>
         </is>
       </c>
       <c r="S524" t="b">
@@ -39424,7 +39424,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -39434,7 +39434,7 @@
         <v>9</v>
       </c>
       <c r="D525" t="n">
-        <v>24064.072265625</v>
+        <v>23712.396484375</v>
       </c>
       <c r="E525" t="inlineStr">
         <is>
@@ -39445,10 +39445,10 @@
         <v>9</v>
       </c>
       <c r="G525" t="n">
-        <v>0.8240405503258509</v>
+        <v>0.7907313540912382</v>
       </c>
       <c r="H525" t="n">
-        <v>6.809362780593772</v>
+        <v>6.524386314265025</v>
       </c>
       <c r="I525" t="inlineStr">
         <is>
@@ -39461,31 +39461,31 @@
         </is>
       </c>
       <c r="K525" t="n">
-        <v>6.265</v>
+        <v>7.137499999999999</v>
       </c>
       <c r="L525" t="n">
         <v>1</v>
       </c>
       <c r="M525" t="n">
-        <v>0.5443627805937723</v>
+        <v>-0.6131136857349739</v>
       </c>
       <c r="N525" t="n">
-        <v>0.5443627805937723</v>
+        <v>0.6131136857349739</v>
       </c>
       <c r="O525" t="n">
-        <v>-0.0625</v>
+        <v>0.1349999999999989</v>
       </c>
       <c r="P525" t="n">
-        <v>-0.03435916002896633</v>
+        <v>-0.07753801593048504</v>
       </c>
       <c r="Q525" t="inlineStr">
         <is>
+          <t>Ascendente</t>
+        </is>
+      </c>
+      <c r="R525" t="inlineStr">
+        <is>
           <t>Descendente</t>
-        </is>
-      </c>
-      <c r="R525" t="inlineStr">
-        <is>
-          <t>Estable</t>
         </is>
       </c>
       <c r="S525" t="b">
@@ -39495,7 +39495,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -39505,7 +39505,7 @@
         <v>9</v>
       </c>
       <c r="D526" t="n">
-        <v>23880.943359375</v>
+        <v>23416.142578125</v>
       </c>
       <c r="E526" t="inlineStr">
         <is>
@@ -39516,10 +39516,10 @@
         <v>9</v>
       </c>
       <c r="G526" t="n">
-        <v>0.7994207096307024</v>
+        <v>0.7682838522809559</v>
       </c>
       <c r="H526" t="n">
-        <v>6.584610789283128</v>
+        <v>6.337210354815351</v>
       </c>
       <c r="I526" t="inlineStr">
         <is>
@@ -39532,26 +39532,26 @@
         </is>
       </c>
       <c r="K526" t="n">
-        <v>6.2275</v>
+        <v>7.2225</v>
       </c>
       <c r="L526" t="n">
         <v>1</v>
       </c>
       <c r="M526" t="n">
-        <v>0.3571107892831282</v>
+        <v>-0.885289645184649</v>
       </c>
       <c r="N526" t="n">
-        <v>0.3571107892831282</v>
+        <v>0.885289645184649</v>
       </c>
       <c r="O526" t="n">
-        <v>-0.03749999999999964</v>
+        <v>0.08500000000000085</v>
       </c>
       <c r="P526" t="n">
-        <v>-0.2247519913106437</v>
+        <v>-0.1871759594496742</v>
       </c>
       <c r="Q526" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="R526" t="inlineStr">
@@ -39566,7 +39566,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -39576,7 +39576,7 @@
         <v>9</v>
       </c>
       <c r="D527" t="n">
-        <v>23732.28515625</v>
+        <v>23058.701171875</v>
       </c>
       <c r="E527" t="inlineStr">
         <is>
@@ -39587,10 +39587,10 @@
         <v>9</v>
       </c>
       <c r="G527" t="n">
-        <v>0.7921795800144823</v>
+        <v>0.7465604634322954</v>
       </c>
       <c r="H527" t="n">
-        <v>6.531996741491673</v>
+        <v>6.151259956553223</v>
       </c>
       <c r="I527" t="inlineStr">
         <is>
@@ -39603,22 +39603,22 @@
         </is>
       </c>
       <c r="K527" t="n">
-        <v>6.225000000000001</v>
+        <v>7.2725</v>
       </c>
       <c r="L527" t="n">
         <v>1</v>
       </c>
       <c r="M527" t="n">
-        <v>0.3069967414916723</v>
+        <v>-1.121240043446777</v>
       </c>
       <c r="N527" t="n">
-        <v>0.3069967414916723</v>
+        <v>1.121240043446777</v>
       </c>
       <c r="O527" t="n">
-        <v>-0.002499999999999503</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="P527" t="n">
-        <v>-0.0526140477914554</v>
+        <v>-0.1859503982621282</v>
       </c>
       <c r="Q527" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -39647,7 +39647,7 @@
         <v>9</v>
       </c>
       <c r="D528" t="n">
-        <v>23685.703125</v>
+        <v>22731.326171875</v>
       </c>
       <c r="E528" t="inlineStr">
         <is>
@@ -39658,10 +39658,10 @@
         <v>9</v>
       </c>
       <c r="G528" t="n">
-        <v>0.7885590152063722</v>
+        <v>0.7154236060825488</v>
       </c>
       <c r="H528" t="n">
-        <v>6.515219044170891</v>
+        <v>5.710419985517741</v>
       </c>
       <c r="I528" t="inlineStr">
         <is>
@@ -39674,22 +39674,22 @@
         </is>
       </c>
       <c r="K528" t="n">
-        <v>6.4175</v>
+        <v>7.37</v>
       </c>
       <c r="L528" t="n">
         <v>1</v>
       </c>
       <c r="M528" t="n">
-        <v>0.0977190441708915</v>
+        <v>-1.659580014482259</v>
       </c>
       <c r="N528" t="n">
-        <v>0.0977190441708915</v>
+        <v>1.659580014482259</v>
       </c>
       <c r="O528" t="n">
-        <v>0.192499999999999</v>
+        <v>0.09750000000000014</v>
       </c>
       <c r="P528" t="n">
-        <v>-0.01677769732078183</v>
+        <v>-0.4408399710354818</v>
       </c>
       <c r="Q528" t="inlineStr">
         <is>
@@ -39698,7 +39698,7 @@
       </c>
       <c r="R528" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S528" t="b">
@@ -39708,7 +39708,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -39718,7 +39718,7 @@
         <v>9</v>
       </c>
       <c r="D529" t="n">
-        <v>23768.970703125</v>
+        <v>22546.1484375</v>
       </c>
       <c r="E529" t="inlineStr">
         <is>
@@ -39729,10 +39729,10 @@
         <v>9</v>
       </c>
       <c r="G529" t="n">
-        <v>0.7943519188993483</v>
+        <v>0.6900796524257784</v>
       </c>
       <c r="H529" t="n">
-        <v>6.545747646632875</v>
+        <v>5.099225199131063</v>
       </c>
       <c r="I529" t="inlineStr">
         <is>
@@ -39745,31 +39745,31 @@
         </is>
       </c>
       <c r="K529" t="n">
-        <v>6.5075</v>
+        <v>7.37</v>
       </c>
       <c r="L529" t="n">
         <v>1</v>
       </c>
       <c r="M529" t="n">
-        <v>0.0382476466328745</v>
+        <v>-2.270774800868937</v>
       </c>
       <c r="N529" t="n">
-        <v>0.0382476466328745</v>
+        <v>2.270774800868937</v>
       </c>
       <c r="O529" t="n">
-        <v>0.09000000000000075</v>
+        <v>0</v>
       </c>
       <c r="P529" t="n">
-        <v>0.03052860246198374</v>
+        <v>-0.6111947863866778</v>
       </c>
       <c r="Q529" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R529" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S529" t="b">
@@ -39779,7 +39779,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -39789,7 +39789,7 @@
         <v>9</v>
       </c>
       <c r="D530" t="n">
-        <v>23898.845703125</v>
+        <v>22595.015625</v>
       </c>
       <c r="E530" t="inlineStr">
         <is>
@@ -39800,10 +39800,10 @@
         <v>9</v>
       </c>
       <c r="G530" t="n">
-        <v>0.8023171614771905</v>
+        <v>0.6973207820419985</v>
       </c>
       <c r="H530" t="n">
-        <v>6.606889934829834</v>
+        <v>5.318081100651701</v>
       </c>
       <c r="I530" t="inlineStr">
         <is>
@@ -39816,41 +39816,41 @@
         </is>
       </c>
       <c r="K530" t="n">
-        <v>6.63</v>
+        <v>7.209999999999999</v>
       </c>
       <c r="L530" t="n">
         <v>1</v>
       </c>
       <c r="M530" t="n">
-        <v>-0.02311006517016612</v>
+        <v>-1.891918899348298</v>
       </c>
       <c r="N530" t="n">
-        <v>0.02311006517016612</v>
+        <v>1.891918899348298</v>
       </c>
       <c r="O530" t="n">
-        <v>0.1224999999999996</v>
+        <v>-0.160000000000001</v>
       </c>
       <c r="P530" t="n">
-        <v>0.06114228819695899</v>
+        <v>0.2188559015206382</v>
       </c>
       <c r="Q530" t="inlineStr">
         <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R530" t="inlineStr">
+        <is>
           <t>Ascendente</t>
         </is>
       </c>
-      <c r="R530" t="inlineStr">
-        <is>
-          <t>Ascendente</t>
-        </is>
-      </c>
       <c r="S530" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -39860,7 +39860,7 @@
         <v>9</v>
       </c>
       <c r="D531" t="n">
-        <v>23970.509765625</v>
+        <v>22859.333984375</v>
       </c>
       <c r="E531" t="inlineStr">
         <is>
@@ -39871,10 +39871,10 @@
         <v>9</v>
       </c>
       <c r="G531" t="n">
-        <v>0.8131788559015206</v>
+        <v>0.7255611875452571</v>
       </c>
       <c r="H531" t="n">
-        <v>6.702833091962345</v>
+        <v>5.800467052860246</v>
       </c>
       <c r="I531" t="inlineStr">
         <is>
@@ -39887,41 +39887,41 @@
         </is>
       </c>
       <c r="K531" t="n">
-        <v>6.75</v>
+        <v>7.04</v>
       </c>
       <c r="L531" t="n">
         <v>1</v>
       </c>
       <c r="M531" t="n">
-        <v>-0.04716690803765466</v>
+        <v>-1.239532947139754</v>
       </c>
       <c r="N531" t="n">
-        <v>0.04716690803765466</v>
+        <v>1.239532947139754</v>
       </c>
       <c r="O531" t="n">
-        <v>0.1200000000000001</v>
+        <v>-0.169999999999999</v>
       </c>
       <c r="P531" t="n">
-        <v>0.09594315713251156</v>
+        <v>0.4823859522085447</v>
       </c>
       <c r="Q531" t="inlineStr">
         <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R531" t="inlineStr">
+        <is>
           <t>Ascendente</t>
         </is>
       </c>
-      <c r="R531" t="inlineStr">
-        <is>
-          <t>Ascendente</t>
-        </is>
-      </c>
       <c r="S531" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -39931,7 +39931,7 @@
         <v>9</v>
       </c>
       <c r="D532" t="n">
-        <v>23966.36328125</v>
+        <v>23283.712890625</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
@@ -39942,10 +39942,10 @@
         <v>9</v>
       </c>
       <c r="G532" t="n">
-        <v>0.8117306299782766</v>
+        <v>0.7610427226647357</v>
       </c>
       <c r="H532" t="n">
-        <v>6.66845582910934</v>
+        <v>6.298350832729906</v>
       </c>
       <c r="I532" t="inlineStr">
         <is>
@@ -39958,31 +39958,31 @@
         </is>
       </c>
       <c r="K532" t="n">
-        <v>6.81</v>
+        <v>6.805</v>
       </c>
       <c r="L532" t="n">
         <v>1</v>
       </c>
       <c r="M532" t="n">
-        <v>-0.1415441708906595</v>
+        <v>-0.5066491672700932</v>
       </c>
       <c r="N532" t="n">
-        <v>0.1415441708906595</v>
+        <v>0.5066491672700932</v>
       </c>
       <c r="O532" t="n">
-        <v>0.05999999999999961</v>
+        <v>-0.2350000000000003</v>
       </c>
       <c r="P532" t="n">
-        <v>-0.03437726285300524</v>
+        <v>0.4978837798696603</v>
       </c>
       <c r="Q532" t="inlineStr">
         <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R532" t="inlineStr">
+        <is>
           <t>Ascendente</t>
-        </is>
-      </c>
-      <c r="R532" t="inlineStr">
-        <is>
-          <t>Estable</t>
         </is>
       </c>
       <c r="S532" t="b">
@@ -39992,7 +39992,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -40002,7 +40002,7 @@
         <v>9</v>
       </c>
       <c r="D533" t="n">
-        <v>23891.98828125</v>
+        <v>23728.486328125</v>
       </c>
       <c r="E533" t="inlineStr">
         <is>
@@ -40013,10 +40013,10 @@
         <v>9</v>
       </c>
       <c r="G533" t="n">
-        <v>0.8015930485155685</v>
+        <v>0.7914554670528603</v>
       </c>
       <c r="H533" t="n">
-        <v>6.60192433019551</v>
+        <v>6.527442070963071</v>
       </c>
       <c r="I533" t="inlineStr">
         <is>
@@ -40029,31 +40029,31 @@
         </is>
       </c>
       <c r="K533" t="n">
-        <v>7.0025</v>
+        <v>6.5975</v>
       </c>
       <c r="L533" t="n">
         <v>1</v>
       </c>
       <c r="M533" t="n">
-        <v>-0.40057566980449</v>
+        <v>-0.07005792903692942</v>
       </c>
       <c r="N533" t="n">
-        <v>0.40057566980449</v>
+        <v>0.07005792903692942</v>
       </c>
       <c r="O533" t="n">
-        <v>0.1925000000000008</v>
+        <v>-0.2074999999999996</v>
       </c>
       <c r="P533" t="n">
-        <v>-0.0665314989138297</v>
+        <v>0.2290912382331642</v>
       </c>
       <c r="Q533" t="inlineStr">
         <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R533" t="inlineStr">
+        <is>
           <t>Ascendente</t>
-        </is>
-      </c>
-      <c r="R533" t="inlineStr">
-        <is>
-          <t>Descendente</t>
         </is>
       </c>
       <c r="S533" t="b">
@@ -40063,17 +40063,17 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B534" t="n">
         <v>9036459</v>
       </c>
       <c r="C534" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D534" t="n">
-        <v>23712.396484375</v>
+        <v>23912.447265625</v>
       </c>
       <c r="E534" t="inlineStr">
         <is>
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="F534" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G534" t="n">
-        <v>0.7907313540912382</v>
+        <v>0.7640369580668088</v>
       </c>
       <c r="H534" t="n">
-        <v>6.524386314265025</v>
+        <v>6.02</v>
       </c>
       <c r="I534" t="inlineStr">
         <is>
@@ -40100,26 +40100,26 @@
         </is>
       </c>
       <c r="K534" t="n">
-        <v>7.137499999999999</v>
+        <v>6.49</v>
       </c>
       <c r="L534" t="n">
         <v>1</v>
       </c>
       <c r="M534" t="n">
-        <v>-0.6131136857349739</v>
+        <v>-0.4700000000000006</v>
       </c>
       <c r="N534" t="n">
-        <v>0.6131136857349739</v>
+        <v>0.4700000000000006</v>
       </c>
       <c r="O534" t="n">
-        <v>0.1349999999999989</v>
+        <v>-0.1074999999999999</v>
       </c>
       <c r="P534" t="n">
-        <v>-0.07753801593048504</v>
+        <v>-0.5074420709630711</v>
       </c>
       <c r="Q534" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="R534" t="inlineStr">
@@ -40128,23 +40128,23 @@
         </is>
       </c>
       <c r="S534" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B535" t="n">
         <v>9036459</v>
       </c>
       <c r="C535" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D535" t="n">
-        <v>23416.142578125</v>
+        <v>23735.55859375</v>
       </c>
       <c r="E535" t="inlineStr">
         <is>
@@ -40152,13 +40152,13 @@
         </is>
       </c>
       <c r="F535" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G535" t="n">
-        <v>0.7682838522809559</v>
+        <v>0.7526652452025586</v>
       </c>
       <c r="H535" t="n">
-        <v>6.337210354815351</v>
+        <v>5.999725479744137</v>
       </c>
       <c r="I535" t="inlineStr">
         <is>
@@ -40171,31 +40171,31 @@
         </is>
       </c>
       <c r="K535" t="n">
-        <v>7.2225</v>
+        <v>6.390000000000001</v>
       </c>
       <c r="L535" t="n">
         <v>1</v>
       </c>
       <c r="M535" t="n">
-        <v>-0.885289645184649</v>
+        <v>-0.390274520255864</v>
       </c>
       <c r="N535" t="n">
-        <v>0.885289645184649</v>
+        <v>0.390274520255864</v>
       </c>
       <c r="O535" t="n">
-        <v>0.08500000000000085</v>
+        <v>-0.09999999999999964</v>
       </c>
       <c r="P535" t="n">
-        <v>-0.1871759594496742</v>
+        <v>-0.02027452025586296</v>
       </c>
       <c r="Q535" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="R535" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S535" t="b">
@@ -40205,17 +40205,17 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="B536" t="n">
         <v>9036459</v>
       </c>
       <c r="C536" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D536" t="n">
-        <v>23058.701171875</v>
+        <v>23376.720703125</v>
       </c>
       <c r="E536" t="inlineStr">
         <is>
@@ -40223,13 +40223,13 @@
         </is>
       </c>
       <c r="F536" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G536" t="n">
-        <v>0.7465604634322954</v>
+        <v>0.7270788912579957</v>
       </c>
       <c r="H536" t="n">
-        <v>6.151259956553223</v>
+        <v>5.90615671641791</v>
       </c>
       <c r="I536" t="inlineStr">
         <is>
@@ -40242,26 +40242,26 @@
         </is>
       </c>
       <c r="K536" t="n">
-        <v>7.2725</v>
+        <v>6.34</v>
       </c>
       <c r="L536" t="n">
         <v>1</v>
       </c>
       <c r="M536" t="n">
-        <v>-1.121240043446777</v>
+        <v>-0.4338432835820898</v>
       </c>
       <c r="N536" t="n">
-        <v>1.121240043446777</v>
+        <v>0.4338432835820898</v>
       </c>
       <c r="O536" t="n">
-        <v>0.04999999999999982</v>
+        <v>-0.05000000000000071</v>
       </c>
       <c r="P536" t="n">
-        <v>-0.1859503982621282</v>
+        <v>-0.09356876332622655</v>
       </c>
       <c r="Q536" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="R536" t="inlineStr">
@@ -40270,23 +40270,23 @@
         </is>
       </c>
       <c r="S536" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="B537" t="n">
         <v>9036459</v>
       </c>
       <c r="C537" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D537" t="n">
-        <v>22731.326171875</v>
+        <v>23038.732421875</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
@@ -40294,13 +40294,13 @@
         </is>
       </c>
       <c r="F537" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G537" t="n">
-        <v>0.7154236060825488</v>
+        <v>0.6993603411513859</v>
       </c>
       <c r="H537" t="n">
-        <v>5.710419985517741</v>
+        <v>5.776908315565031</v>
       </c>
       <c r="I537" t="inlineStr">
         <is>
@@ -40313,26 +40313,26 @@
         </is>
       </c>
       <c r="K537" t="n">
-        <v>7.37</v>
+        <v>6.272499999999999</v>
       </c>
       <c r="L537" t="n">
         <v>1</v>
       </c>
       <c r="M537" t="n">
-        <v>-1.659580014482259</v>
+        <v>-0.4955916844349684</v>
       </c>
       <c r="N537" t="n">
-        <v>1.659580014482259</v>
+        <v>0.4955916844349684</v>
       </c>
       <c r="O537" t="n">
-        <v>0.09750000000000014</v>
+        <v>-0.06750000000000078</v>
       </c>
       <c r="P537" t="n">
-        <v>-0.4408399710354818</v>
+        <v>-0.1292484008528794</v>
       </c>
       <c r="Q537" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="R537" t="inlineStr">
@@ -40341,23 +40341,23 @@
         </is>
       </c>
       <c r="S537" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B538" t="n">
         <v>9036459</v>
       </c>
       <c r="C538" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D538" t="n">
-        <v>22546.1484375</v>
+        <v>22813.505859375</v>
       </c>
       <c r="E538" t="inlineStr">
         <is>
@@ -40365,13 +40365,13 @@
         </is>
       </c>
       <c r="F538" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G538" t="n">
-        <v>0.6900796524257784</v>
+        <v>0.6780383795309168</v>
       </c>
       <c r="H538" t="n">
-        <v>5.099225199131063</v>
+        <v>5.627889125799573</v>
       </c>
       <c r="I538" t="inlineStr">
         <is>
@@ -40384,26 +40384,26 @@
         </is>
       </c>
       <c r="K538" t="n">
-        <v>7.37</v>
+        <v>6.1925</v>
       </c>
       <c r="L538" t="n">
         <v>1</v>
       </c>
       <c r="M538" t="n">
-        <v>-2.270774800868937</v>
+        <v>-0.5646108742004268</v>
       </c>
       <c r="N538" t="n">
-        <v>2.270774800868937</v>
+        <v>0.5646108742004268</v>
       </c>
       <c r="O538" t="n">
-        <v>0</v>
+        <v>-0.07999999999999918</v>
       </c>
       <c r="P538" t="n">
-        <v>-0.6111947863866778</v>
+        <v>-0.1490191897654576</v>
       </c>
       <c r="Q538" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="R538" t="inlineStr">
@@ -40412,23 +40412,23 @@
         </is>
       </c>
       <c r="S538" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B539" t="n">
         <v>9036459</v>
       </c>
       <c r="C539" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D539" t="n">
-        <v>22595.015625</v>
+        <v>22760.013671875</v>
       </c>
       <c r="E539" t="inlineStr">
         <is>
@@ -40436,13 +40436,13 @@
         </is>
       </c>
       <c r="F539" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G539" t="n">
-        <v>0.6973207820419985</v>
+        <v>0.673773987206823</v>
       </c>
       <c r="H539" t="n">
-        <v>5.318081100651701</v>
+        <v>5.602430703624733</v>
       </c>
       <c r="I539" t="inlineStr">
         <is>
@@ -40455,22 +40455,22 @@
         </is>
       </c>
       <c r="K539" t="n">
-        <v>7.209999999999999</v>
+        <v>6.02</v>
       </c>
       <c r="L539" t="n">
         <v>1</v>
       </c>
       <c r="M539" t="n">
-        <v>-1.891918899348298</v>
+        <v>-0.4175692963752677</v>
       </c>
       <c r="N539" t="n">
-        <v>1.891918899348298</v>
+        <v>0.4175692963752677</v>
       </c>
       <c r="O539" t="n">
-        <v>-0.160000000000001</v>
+        <v>-0.1724999999999994</v>
       </c>
       <c r="P539" t="n">
-        <v>0.2188559015206382</v>
+        <v>-0.0254584221748404</v>
       </c>
       <c r="Q539" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
       </c>
       <c r="R539" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S539" t="b">
@@ -40489,17 +40489,17 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B540" t="n">
         <v>9036459</v>
       </c>
       <c r="C540" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D540" t="n">
-        <v>22859.333984375</v>
+        <v>22902.693359375</v>
       </c>
       <c r="E540" t="inlineStr">
         <is>
@@ -40507,13 +40507,13 @@
         </is>
       </c>
       <c r="F540" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G540" t="n">
-        <v>0.7255611875452571</v>
+        <v>0.6879886282871357</v>
       </c>
       <c r="H540" t="n">
-        <v>5.800467052860246</v>
+        <v>5.6772921108742</v>
       </c>
       <c r="I540" t="inlineStr">
         <is>
@@ -40526,22 +40526,22 @@
         </is>
       </c>
       <c r="K540" t="n">
-        <v>7.04</v>
+        <v>5.85</v>
       </c>
       <c r="L540" t="n">
         <v>1</v>
       </c>
       <c r="M540" t="n">
-        <v>-1.239532947139754</v>
+        <v>-0.1727078891257996</v>
       </c>
       <c r="N540" t="n">
-        <v>1.239532947139754</v>
+        <v>0.1727078891257996</v>
       </c>
       <c r="O540" t="n">
-        <v>-0.169999999999999</v>
+        <v>-0.1700000000000008</v>
       </c>
       <c r="P540" t="n">
-        <v>0.4823859522085447</v>
+        <v>0.07486140724946733</v>
       </c>
       <c r="Q540" t="inlineStr">
         <is>
@@ -40560,17 +40560,17 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B541" t="n">
         <v>9036459</v>
       </c>
       <c r="C541" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D541" t="n">
-        <v>23283.712890625</v>
+        <v>23174.3984375</v>
       </c>
       <c r="E541" t="inlineStr">
         <is>
@@ -40578,13 +40578,13 @@
         </is>
       </c>
       <c r="F541" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G541" t="n">
-        <v>0.7610427226647357</v>
+        <v>0.7114427860696517</v>
       </c>
       <c r="H541" t="n">
-        <v>6.298350832729906</v>
+        <v>5.841542288557213</v>
       </c>
       <c r="I541" t="inlineStr">
         <is>
@@ -40597,26 +40597,26 @@
         </is>
       </c>
       <c r="K541" t="n">
-        <v>6.805</v>
+        <v>5.9225</v>
       </c>
       <c r="L541" t="n">
         <v>1</v>
       </c>
       <c r="M541" t="n">
-        <v>-0.5066491672700932</v>
+        <v>-0.08095771144278707</v>
       </c>
       <c r="N541" t="n">
-        <v>0.5066491672700932</v>
+        <v>0.08095771144278707</v>
       </c>
       <c r="O541" t="n">
-        <v>-0.2350000000000003</v>
+        <v>0.07250000000000068</v>
       </c>
       <c r="P541" t="n">
-        <v>0.4978837798696603</v>
+        <v>0.1642501776830132</v>
       </c>
       <c r="Q541" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="R541" t="inlineStr">
@@ -40625,23 +40625,23 @@
         </is>
       </c>
       <c r="S541" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B542" t="n">
         <v>9036459</v>
       </c>
       <c r="C542" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D542" t="n">
-        <v>23728.486328125</v>
+        <v>23490.265625</v>
       </c>
       <c r="E542" t="inlineStr">
         <is>
@@ -40649,13 +40649,13 @@
         </is>
       </c>
       <c r="F542" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G542" t="n">
-        <v>0.7914554670528603</v>
+        <v>0.7384506041222459</v>
       </c>
       <c r="H542" t="n">
-        <v>6.527442070963071</v>
+        <v>5.9786105188344</v>
       </c>
       <c r="I542" t="inlineStr">
         <is>
@@ -40668,26 +40668,26 @@
         </is>
       </c>
       <c r="K542" t="n">
-        <v>6.5975</v>
+        <v>5.9975</v>
       </c>
       <c r="L542" t="n">
         <v>1</v>
       </c>
       <c r="M542" t="n">
-        <v>-0.07005792903692942</v>
+        <v>-0.01888948116560041</v>
       </c>
       <c r="N542" t="n">
-        <v>0.07005792903692942</v>
+        <v>0.01888948116560041</v>
       </c>
       <c r="O542" t="n">
-        <v>-0.2074999999999996</v>
+        <v>0.07500000000000018</v>
       </c>
       <c r="P542" t="n">
-        <v>0.2290912382331642</v>
+        <v>0.1370682302771868</v>
       </c>
       <c r="Q542" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="R542" t="inlineStr">
@@ -40696,13 +40696,13 @@
         </is>
       </c>
       <c r="S542" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -40712,7 +40712,7 @@
         <v>10</v>
       </c>
       <c r="D543" t="n">
-        <v>23912.447265625</v>
+        <v>23828.6640625</v>
       </c>
       <c r="E543" t="inlineStr">
         <is>
@@ -40723,10 +40723,10 @@
         <v>10</v>
       </c>
       <c r="G543" t="n">
-        <v>0.7640369580668088</v>
+        <v>0.7569296375266524</v>
       </c>
       <c r="H543" t="n">
-        <v>5.988059701492538</v>
+        <v>6.007862473347548</v>
       </c>
       <c r="I543" t="inlineStr">
         <is>
@@ -40739,31 +40739,31 @@
         </is>
       </c>
       <c r="K543" t="n">
-        <v>6.49</v>
+        <v>6.0125</v>
       </c>
       <c r="L543" t="n">
         <v>1</v>
       </c>
       <c r="M543" t="n">
-        <v>-0.5019402985074626</v>
+        <v>-0.004637526652452095</v>
       </c>
       <c r="N543" t="n">
-        <v>0.5019402985074626</v>
+        <v>0.004637526652452095</v>
       </c>
       <c r="O543" t="n">
-        <v>-0.1074999999999999</v>
+        <v>0.01499999999999968</v>
       </c>
       <c r="P543" t="n">
-        <v>-0.5393823694705331</v>
+        <v>0.02925195451314799</v>
       </c>
       <c r="Q543" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R543" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S543" t="b">
@@ -40773,7 +40773,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -40783,7 +40783,7 @@
         <v>10</v>
       </c>
       <c r="D544" t="n">
-        <v>23735.55859375</v>
+        <v>24189.279296875</v>
       </c>
       <c r="E544" t="inlineStr">
         <is>
@@ -40794,10 +40794,10 @@
         <v>10</v>
       </c>
       <c r="G544" t="n">
-        <v>0.7526652452025586</v>
+        <v>0.7853589196872779</v>
       </c>
       <c r="H544" t="n">
-        <v>5.883955223880597</v>
+        <v>6.16930881307747</v>
       </c>
       <c r="I544" t="inlineStr">
         <is>
@@ -40810,41 +40810,41 @@
         </is>
       </c>
       <c r="K544" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="L544" t="n">
         <v>1</v>
       </c>
       <c r="M544" t="n">
-        <v>-0.4960447761194029</v>
+        <v>0.1693088130774703</v>
       </c>
       <c r="N544" t="n">
-        <v>0.4960447761194029</v>
+        <v>0.1693088130774703</v>
       </c>
       <c r="O544" t="n">
-        <v>-0.1100000000000003</v>
+        <v>-0.01250000000000018</v>
       </c>
       <c r="P544" t="n">
-        <v>-0.1041044776119406</v>
+        <v>0.1614463397299222</v>
       </c>
       <c r="Q544" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R544" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S544" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -40854,7 +40854,7 @@
         <v>9</v>
       </c>
       <c r="D545" t="n">
-        <v>1882.029541015625</v>
+        <v>1471.796875</v>
       </c>
       <c r="E545" t="inlineStr">
         <is>
@@ -40865,10 +40865,10 @@
         <v>9</v>
       </c>
       <c r="G545" t="n">
-        <v>0.7711803041274439</v>
+        <v>0.4105720492396814</v>
       </c>
       <c r="H545" t="n">
-        <v>129.28698044895</v>
+        <v>128.0324330195511</v>
       </c>
       <c r="I545" t="inlineStr">
         <is>
@@ -40881,16 +40881,16 @@
         </is>
       </c>
       <c r="K545" t="n">
-        <v>129.8</v>
+        <v>127.65</v>
       </c>
       <c r="L545" t="n">
         <v>1</v>
       </c>
       <c r="M545" t="n">
-        <v>-0.5130195510499789</v>
+        <v>0.3824330195510584</v>
       </c>
       <c r="N545" t="n">
-        <v>0.5130195510499789</v>
+        <v>0.3824330195510584</v>
       </c>
       <c r="O545" t="inlineStr"/>
       <c r="P545" t="inlineStr"/>
@@ -40909,7 +40909,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -40919,7 +40919,7 @@
         <v>9</v>
       </c>
       <c r="D546" t="n">
-        <v>1768.240478515625</v>
+        <v>1474.109497070312</v>
       </c>
       <c r="E546" t="inlineStr">
         <is>
@@ -40930,10 +40930,10 @@
         <v>9</v>
       </c>
       <c r="G546" t="n">
-        <v>0.6980448950036205</v>
+        <v>0.4134685010861694</v>
       </c>
       <c r="H546" t="n">
-        <v>128.9424927588704</v>
+        <v>128.0425242577842</v>
       </c>
       <c r="I546" t="inlineStr">
         <is>
@@ -40946,31 +40946,31 @@
         </is>
       </c>
       <c r="K546" t="n">
-        <v>129.72</v>
+        <v>127.64</v>
       </c>
       <c r="L546" t="n">
         <v>1</v>
       </c>
       <c r="M546" t="n">
-        <v>-0.7775072411296264</v>
+        <v>0.4025242577842079</v>
       </c>
       <c r="N546" t="n">
-        <v>0.7775072411296264</v>
+        <v>0.4025242577842079</v>
       </c>
       <c r="O546" t="n">
-        <v>-0.08000000000001251</v>
+        <v>-0.01000000000000512</v>
       </c>
       <c r="P546" t="n">
-        <v>-0.3444876900796601</v>
+        <v>0.0100912382331444</v>
       </c>
       <c r="Q546" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R546" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S546" t="b">
@@ -40980,7 +40980,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -40990,7 +40990,7 @@
         <v>9</v>
       </c>
       <c r="D547" t="n">
-        <v>1675.415771484375</v>
+        <v>1478.184326171875</v>
       </c>
       <c r="E547" t="inlineStr">
         <is>
@@ -41001,10 +41001,10 @@
         <v>9</v>
       </c>
       <c r="G547" t="n">
-        <v>0.6220130340333092</v>
+        <v>0.4192614047791455</v>
       </c>
       <c r="H547" t="n">
-        <v>128.7406074503178</v>
+        <v>128.0736278059377</v>
       </c>
       <c r="I547" t="inlineStr">
         <is>
@@ -41017,31 +41017,31 @@
         </is>
       </c>
       <c r="K547" t="n">
-        <v>129.68</v>
+        <v>127.35</v>
       </c>
       <c r="L547" t="n">
         <v>1</v>
       </c>
       <c r="M547" t="n">
-        <v>-0.9393925496821964</v>
+        <v>0.7236278059377241</v>
       </c>
       <c r="N547" t="n">
-        <v>0.9393925496821964</v>
+        <v>0.7236278059377241</v>
       </c>
       <c r="O547" t="n">
-        <v>-0.03999999999999204</v>
+        <v>-0.2900000000000063</v>
       </c>
       <c r="P547" t="n">
-        <v>-0.201885308552562</v>
+        <v>0.03110354815351002</v>
       </c>
       <c r="Q547" t="inlineStr">
         <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R547" t="inlineStr">
+        <is>
           <t>Estable</t>
-        </is>
-      </c>
-      <c r="R547" t="inlineStr">
-        <is>
-          <t>Descendente</t>
         </is>
       </c>
       <c r="S547" t="b">
@@ -41051,7 +41051,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -41061,7 +41061,7 @@
         <v>9</v>
       </c>
       <c r="D548" t="n">
-        <v>1607.37841796875</v>
+        <v>1480.848876953125</v>
       </c>
       <c r="E548" t="inlineStr">
         <is>
@@ -41072,10 +41072,10 @@
         <v>9</v>
       </c>
       <c r="G548" t="n">
-        <v>0.559739319333816</v>
+        <v>0.4221578566256336</v>
       </c>
       <c r="H548" t="n">
-        <v>128.4956886314265</v>
+        <v>128.0778324885349</v>
       </c>
       <c r="I548" t="inlineStr">
         <is>
@@ -41088,31 +41088,31 @@
         </is>
       </c>
       <c r="K548" t="n">
-        <v>128.7</v>
+        <v>127.3</v>
       </c>
       <c r="L548" t="n">
         <v>1</v>
       </c>
       <c r="M548" t="n">
-        <v>-0.2043113685734852</v>
+        <v>0.7778324885348837</v>
       </c>
       <c r="N548" t="n">
-        <v>0.2043113685734852</v>
+        <v>0.7778324885348837</v>
       </c>
       <c r="O548" t="n">
-        <v>-0.9800000000000182</v>
+        <v>-0.04999999999999716</v>
       </c>
       <c r="P548" t="n">
-        <v>-0.244918818891307</v>
+        <v>0.004204682597162446</v>
       </c>
       <c r="Q548" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R548" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S548" t="b">
@@ -41122,7 +41122,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -41132,7 +41132,7 @@
         <v>9</v>
       </c>
       <c r="D549" t="n">
-        <v>1559.032592773438</v>
+        <v>1487.517944335938</v>
       </c>
       <c r="E549" t="inlineStr">
         <is>
@@ -41143,10 +41143,10 @@
         <v>9</v>
       </c>
       <c r="G549" t="n">
-        <v>0.5061549601737871</v>
+        <v>0.4322954380883418</v>
       </c>
       <c r="H549" t="n">
-        <v>128.3496524257784</v>
+        <v>128.0946638046964</v>
       </c>
       <c r="I549" t="inlineStr">
         <is>
@@ -41159,41 +41159,41 @@
         </is>
       </c>
       <c r="K549" t="n">
-        <v>128.1</v>
+        <v>129.6</v>
       </c>
       <c r="L549" t="n">
         <v>1</v>
       </c>
       <c r="M549" t="n">
-        <v>0.2496524257784358</v>
+        <v>-1.505336195303613</v>
       </c>
       <c r="N549" t="n">
-        <v>0.2496524257784358</v>
+        <v>1.505336195303613</v>
       </c>
       <c r="O549" t="n">
-        <v>-0.5999999999999943</v>
+        <v>2.299999999999997</v>
       </c>
       <c r="P549" t="n">
-        <v>-0.1460362056480733</v>
+        <v>0.01683131616150035</v>
       </c>
       <c r="Q549" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="R549" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S549" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -41203,7 +41203,7 @@
         <v>9</v>
       </c>
       <c r="D550" t="n">
-        <v>1524.2138671875</v>
+        <v>1524.831298828125</v>
       </c>
       <c r="E550" t="inlineStr">
         <is>
@@ -41214,10 +41214,10 @@
         <v>9</v>
       </c>
       <c r="G550" t="n">
-        <v>0.4721216509775525</v>
+        <v>0.4742939898624186</v>
       </c>
       <c r="H550" t="n">
-        <v>128.1976816316679</v>
+        <v>128.1992583876418</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -41230,22 +41230,22 @@
         </is>
       </c>
       <c r="K550" t="n">
-        <v>127.45</v>
+        <v>129.5</v>
       </c>
       <c r="L550" t="n">
         <v>1</v>
       </c>
       <c r="M550" t="n">
-        <v>0.7476816316678736</v>
+        <v>-1.300741612358195</v>
       </c>
       <c r="N550" t="n">
-        <v>0.7476816316678736</v>
+        <v>1.300741612358195</v>
       </c>
       <c r="O550" t="n">
-        <v>-0.6499999999999915</v>
+        <v>-0.09999999999999432</v>
       </c>
       <c r="P550" t="n">
-        <v>-0.1519707941105537</v>
+        <v>0.104594582945424</v>
       </c>
       <c r="Q550" t="inlineStr">
         <is>
@@ -41254,17 +41254,17 @@
       </c>
       <c r="R550" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S550" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -41274,7 +41274,7 @@
         <v>9</v>
       </c>
       <c r="D551" t="n">
-        <v>1499.664916992188</v>
+        <v>1635.493530273438</v>
       </c>
       <c r="E551" t="inlineStr">
         <is>
@@ -41285,10 +41285,10 @@
         <v>9</v>
       </c>
       <c r="G551" t="n">
-        <v>0.445329471397538</v>
+        <v>0.5836350470673425</v>
       </c>
       <c r="H551" t="n">
-        <v>128.1288196958726</v>
+        <v>128.5933431738428</v>
       </c>
       <c r="I551" t="inlineStr">
         <is>
@@ -41301,31 +41301,31 @@
         </is>
       </c>
       <c r="K551" t="n">
-        <v>127.2</v>
+        <v>129.59</v>
       </c>
       <c r="L551" t="n">
         <v>1</v>
       </c>
       <c r="M551" t="n">
-        <v>0.9288196958725479</v>
+        <v>-0.9966568261571922</v>
       </c>
       <c r="N551" t="n">
-        <v>0.9288196958725479</v>
+        <v>0.9966568261571922</v>
       </c>
       <c r="O551" t="n">
-        <v>-0.25</v>
+        <v>0.09000000000000341</v>
       </c>
       <c r="P551" t="n">
-        <v>-0.06886193579532573</v>
+        <v>0.394084786201006</v>
       </c>
       <c r="Q551" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="R551" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S551" t="b">
@@ -41335,7 +41335,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -41345,7 +41345,7 @@
         <v>9</v>
       </c>
       <c r="D552" t="n">
-        <v>1483.4921875</v>
+        <v>1827.105346679688</v>
       </c>
       <c r="E552" t="inlineStr">
         <is>
@@ -41356,10 +41356,10 @@
         <v>9</v>
       </c>
       <c r="G552" t="n">
-        <v>0.4265025343953657</v>
+        <v>0.7270094134685011</v>
       </c>
       <c r="H552" t="n">
-        <v>128.0910597910417</v>
+        <v>129.0345039826213</v>
       </c>
       <c r="I552" t="inlineStr">
         <is>
@@ -41372,31 +41372,31 @@
         </is>
       </c>
       <c r="K552" t="n">
-        <v>127.26</v>
+        <v>129.3</v>
       </c>
       <c r="L552" t="n">
         <v>1</v>
       </c>
       <c r="M552" t="n">
-        <v>0.8310597910416817</v>
+        <v>-0.2654960173787231</v>
       </c>
       <c r="N552" t="n">
-        <v>0.8310597910416817</v>
+        <v>0.2654960173787231</v>
       </c>
       <c r="O552" t="n">
-        <v>0.06000000000000227</v>
+        <v>-0.289999999999992</v>
       </c>
       <c r="P552" t="n">
-        <v>-0.03775990483086389</v>
+        <v>0.4411608087784771</v>
       </c>
       <c r="Q552" t="inlineStr">
         <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R552" t="inlineStr">
+        <is>
           <t>Ascendente</t>
-        </is>
-      </c>
-      <c r="R552" t="inlineStr">
-        <is>
-          <t>Estable</t>
         </is>
       </c>
       <c r="S552" t="b">
@@ -41406,7 +41406,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -41416,7 +41416,7 @@
         <v>9</v>
       </c>
       <c r="D553" t="n">
-        <v>1474.3740234375</v>
+        <v>2023.500366210938</v>
       </c>
       <c r="E553" t="inlineStr">
         <is>
@@ -41427,10 +41427,10 @@
         <v>9</v>
       </c>
       <c r="G553" t="n">
-        <v>0.4149167270094135</v>
+        <v>0.8414192614047792</v>
       </c>
       <c r="H553" t="n">
-        <v>128.0475698769008</v>
+        <v>129.4732570601014</v>
       </c>
       <c r="I553" t="inlineStr">
         <is>
@@ -41443,22 +41443,22 @@
         </is>
       </c>
       <c r="K553" t="n">
-        <v>127.34</v>
+        <v>129.5</v>
       </c>
       <c r="L553" t="n">
         <v>1</v>
       </c>
       <c r="M553" t="n">
-        <v>0.7075698769008056</v>
+        <v>-0.02674293989863941</v>
       </c>
       <c r="N553" t="n">
-        <v>0.7075698769008056</v>
+        <v>0.02674293989863941</v>
       </c>
       <c r="O553" t="n">
-        <v>0.07999999999999829</v>
+        <v>0.1999999999999886</v>
       </c>
       <c r="P553" t="n">
-        <v>-0.04348991414087777</v>
+        <v>0.4387530774800723</v>
       </c>
       <c r="Q553" t="inlineStr">
         <is>
@@ -41467,17 +41467,17 @@
       </c>
       <c r="R553" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S553" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -41487,7 +41487,7 @@
         <v>9</v>
       </c>
       <c r="D554" t="n">
-        <v>1471.796875</v>
+        <v>2127.298583984375</v>
       </c>
       <c r="E554" t="inlineStr">
         <is>
@@ -41498,10 +41498,10 @@
         <v>9</v>
       </c>
       <c r="G554" t="n">
-        <v>0.4105720492396814</v>
+        <v>0.8783490224475018</v>
       </c>
       <c r="H554" t="n">
-        <v>128.0324330195511</v>
+        <v>129.5970419985518</v>
       </c>
       <c r="I554" t="inlineStr">
         <is>
@@ -41514,31 +41514,31 @@
         </is>
       </c>
       <c r="K554" t="n">
-        <v>127.65</v>
+        <v>129.44</v>
       </c>
       <c r="L554" t="n">
         <v>1</v>
       </c>
       <c r="M554" t="n">
-        <v>0.3824330195510584</v>
+        <v>0.1570419985517617</v>
       </c>
       <c r="N554" t="n">
-        <v>0.3824330195510584</v>
+        <v>0.1570419985517617</v>
       </c>
       <c r="O554" t="n">
-        <v>0.3100000000000023</v>
+        <v>-0.06000000000000227</v>
       </c>
       <c r="P554" t="n">
-        <v>-0.01513685734974501</v>
+        <v>0.1237849384503988</v>
       </c>
       <c r="Q554" t="inlineStr">
         <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R554" t="inlineStr">
+        <is>
           <t>Ascendente</t>
-        </is>
-      </c>
-      <c r="R554" t="inlineStr">
-        <is>
-          <t>Estable</t>
         </is>
       </c>
       <c r="S554" t="b">
@@ -41548,7 +41548,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -41558,7 +41558,7 @@
         <v>9</v>
       </c>
       <c r="D555" t="n">
-        <v>1474.109497070312</v>
+        <v>2119.77880859375</v>
       </c>
       <c r="E555" t="inlineStr">
         <is>
@@ -41569,10 +41569,10 @@
         <v>9</v>
       </c>
       <c r="G555" t="n">
-        <v>0.4134685010861694</v>
+        <v>0.8769007965242578</v>
       </c>
       <c r="H555" t="n">
-        <v>128.0425242577842</v>
+        <v>129.5957805937726</v>
       </c>
       <c r="I555" t="inlineStr">
         <is>
@@ -41585,41 +41585,41 @@
         </is>
       </c>
       <c r="K555" t="n">
-        <v>127.64</v>
+        <v>129.7</v>
       </c>
       <c r="L555" t="n">
         <v>1</v>
       </c>
       <c r="M555" t="n">
-        <v>0.4025242577842079</v>
+        <v>-0.1042194062273722</v>
       </c>
       <c r="N555" t="n">
-        <v>0.4025242577842079</v>
+        <v>0.1042194062273722</v>
       </c>
       <c r="O555" t="n">
-        <v>-0.01000000000000512</v>
+        <v>0.2599999999999909</v>
       </c>
       <c r="P555" t="n">
-        <v>0.0100912382331444</v>
+        <v>-0.001261404779143049</v>
       </c>
       <c r="Q555" t="inlineStr">
         <is>
+          <t>Ascendente</t>
+        </is>
+      </c>
+      <c r="R555" t="inlineStr">
+        <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="R555" t="inlineStr">
-        <is>
-          <t>Estable</t>
-        </is>
-      </c>
       <c r="S555" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -41629,7 +41629,7 @@
         <v>9</v>
       </c>
       <c r="D556" t="n">
-        <v>1478.184326171875</v>
+        <v>2044.919555664062</v>
       </c>
       <c r="E556" t="inlineStr">
         <is>
@@ -41640,10 +41640,10 @@
         <v>9</v>
       </c>
       <c r="G556" t="n">
-        <v>0.4192614047791455</v>
+        <v>0.8508327299058653</v>
       </c>
       <c r="H556" t="n">
-        <v>128.0736278059377</v>
+        <v>129.49179217958</v>
       </c>
       <c r="I556" t="inlineStr">
         <is>
@@ -41656,22 +41656,22 @@
         </is>
       </c>
       <c r="K556" t="n">
-        <v>127.35</v>
+        <v>129.4</v>
       </c>
       <c r="L556" t="n">
         <v>1</v>
       </c>
       <c r="M556" t="n">
-        <v>0.7236278059377241</v>
+        <v>0.09179217958001118</v>
       </c>
       <c r="N556" t="n">
-        <v>0.7236278059377241</v>
+        <v>0.09179217958001118</v>
       </c>
       <c r="O556" t="n">
-        <v>-0.2900000000000063</v>
+        <v>-0.2999999999999829</v>
       </c>
       <c r="P556" t="n">
-        <v>0.03110354815351002</v>
+        <v>-0.1039884141925995</v>
       </c>
       <c r="Q556" t="inlineStr">
         <is>
@@ -41680,17 +41680,17 @@
       </c>
       <c r="R556" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S556" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -41700,7 +41700,7 @@
         <v>9</v>
       </c>
       <c r="D557" t="n">
-        <v>1480.848876953125</v>
+        <v>1945.693725585938</v>
       </c>
       <c r="E557" t="inlineStr">
         <is>
@@ -41711,10 +41711,10 @@
         <v>9</v>
       </c>
       <c r="G557" t="n">
-        <v>0.4221578566256336</v>
+        <v>0.8110065170166546</v>
       </c>
       <c r="H557" t="n">
-        <v>128.0778324885349</v>
+        <v>129.3720702008461</v>
       </c>
       <c r="I557" t="inlineStr">
         <is>
@@ -41727,31 +41727,31 @@
         </is>
       </c>
       <c r="K557" t="n">
-        <v>127.3</v>
+        <v>128.7</v>
       </c>
       <c r="L557" t="n">
         <v>1</v>
       </c>
       <c r="M557" t="n">
-        <v>0.7778324885348837</v>
+        <v>0.6720702008460933</v>
       </c>
       <c r="N557" t="n">
-        <v>0.7778324885348837</v>
+        <v>0.6720702008460933</v>
       </c>
       <c r="O557" t="n">
-        <v>-0.04999999999999716</v>
+        <v>-0.7000000000000171</v>
       </c>
       <c r="P557" t="n">
-        <v>0.004204682597162446</v>
+        <v>-0.119721978733935</v>
       </c>
       <c r="Q557" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="R557" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S557" t="b">
@@ -41761,7 +41761,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -41771,7 +41771,7 @@
         <v>9</v>
       </c>
       <c r="D558" t="n">
-        <v>1487.517944335938</v>
+        <v>1845.803955078125</v>
       </c>
       <c r="E558" t="inlineStr">
         <is>
@@ -41782,10 +41782,10 @@
         <v>9</v>
       </c>
       <c r="G558" t="n">
-        <v>0.4322954380883418</v>
+        <v>0.7407675597393193</v>
       </c>
       <c r="H558" t="n">
-        <v>128.0946638046964</v>
+        <v>129.1220854453295</v>
       </c>
       <c r="I558" t="inlineStr">
         <is>
@@ -41798,41 +41798,41 @@
         </is>
       </c>
       <c r="K558" t="n">
-        <v>129.6</v>
+        <v>128.45</v>
       </c>
       <c r="L558" t="n">
         <v>1</v>
       </c>
       <c r="M558" t="n">
-        <v>-1.505336195303613</v>
+        <v>0.6720854453294862</v>
       </c>
       <c r="N558" t="n">
-        <v>1.505336195303613</v>
+        <v>0.6720854453294862</v>
       </c>
       <c r="O558" t="n">
-        <v>2.299999999999997</v>
+        <v>-0.25</v>
       </c>
       <c r="P558" t="n">
-        <v>0.01683131616150035</v>
+        <v>-0.249984755516607</v>
       </c>
       <c r="Q558" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="R558" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S558" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -41842,7 +41842,7 @@
         <v>9</v>
       </c>
       <c r="D559" t="n">
-        <v>1524.831298828125</v>
+        <v>1757.952026367188</v>
       </c>
       <c r="E559" t="inlineStr">
         <is>
@@ -41853,10 +41853,10 @@
         <v>9</v>
       </c>
       <c r="G559" t="n">
-        <v>0.4742939898624186</v>
+        <v>0.6879073135409124</v>
       </c>
       <c r="H559" t="n">
-        <v>128.1992583876418</v>
+        <v>128.9058363504707</v>
       </c>
       <c r="I559" t="inlineStr">
         <is>
@@ -41869,22 +41869,22 @@
         </is>
       </c>
       <c r="K559" t="n">
-        <v>129.5</v>
+        <v>128.36</v>
       </c>
       <c r="L559" t="n">
         <v>1</v>
       </c>
       <c r="M559" t="n">
-        <v>-1.300741612358195</v>
+        <v>0.5458363504706654</v>
       </c>
       <c r="N559" t="n">
-        <v>1.300741612358195</v>
+        <v>0.5458363504706654</v>
       </c>
       <c r="O559" t="n">
-        <v>-0.09999999999999432</v>
+        <v>-0.08999999999997499</v>
       </c>
       <c r="P559" t="n">
-        <v>0.104594582945424</v>
+        <v>-0.2162490948587958</v>
       </c>
       <c r="Q559" t="inlineStr">
         <is>
@@ -41893,17 +41893,17 @@
       </c>
       <c r="R559" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S559" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -41913,7 +41913,7 @@
         <v>9</v>
       </c>
       <c r="D560" t="n">
-        <v>1635.493530273438</v>
+        <v>1692.794311523438</v>
       </c>
       <c r="E560" t="inlineStr">
         <is>
@@ -41924,10 +41924,10 @@
         <v>9</v>
       </c>
       <c r="G560" t="n">
-        <v>0.5836350470673425</v>
+        <v>0.6415640839971035</v>
       </c>
       <c r="H560" t="n">
-        <v>128.5933431738428</v>
+        <v>128.7902543446778</v>
       </c>
       <c r="I560" t="inlineStr">
         <is>
@@ -41940,22 +41940,22 @@
         </is>
       </c>
       <c r="K560" t="n">
-        <v>129.59</v>
+        <v>128.45</v>
       </c>
       <c r="L560" t="n">
         <v>1</v>
       </c>
       <c r="M560" t="n">
-        <v>-0.9966568261571922</v>
+        <v>0.3402543446777884</v>
       </c>
       <c r="N560" t="n">
-        <v>0.9966568261571922</v>
+        <v>0.3402543446777884</v>
       </c>
       <c r="O560" t="n">
-        <v>0.09000000000000341</v>
+        <v>0.08999999999997499</v>
       </c>
       <c r="P560" t="n">
-        <v>0.394084786201006</v>
+        <v>-0.115582005792902</v>
       </c>
       <c r="Q560" t="inlineStr">
         <is>
@@ -41964,17 +41964,17 @@
       </c>
       <c r="R560" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S560" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -41984,7 +41984,7 @@
         <v>9</v>
       </c>
       <c r="D561" t="n">
-        <v>1827.105346679688</v>
+        <v>1657.840209960938</v>
       </c>
       <c r="E561" t="inlineStr">
         <is>
@@ -41995,10 +41995,10 @@
         <v>9</v>
       </c>
       <c r="G561" t="n">
-        <v>0.7270094134685011</v>
+        <v>0.6060825488776249</v>
       </c>
       <c r="H561" t="n">
-        <v>129.0345039826213</v>
+        <v>128.6870870910408</v>
       </c>
       <c r="I561" t="inlineStr">
         <is>
@@ -42011,31 +42011,31 @@
         </is>
       </c>
       <c r="K561" t="n">
-        <v>129.3</v>
+        <v>128.49</v>
       </c>
       <c r="L561" t="n">
         <v>1</v>
       </c>
       <c r="M561" t="n">
-        <v>-0.2654960173787231</v>
+        <v>0.1970870910407427</v>
       </c>
       <c r="N561" t="n">
-        <v>0.2654960173787231</v>
+        <v>0.1970870910407427</v>
       </c>
       <c r="O561" t="n">
-        <v>-0.289999999999992</v>
+        <v>0.04000000000002046</v>
       </c>
       <c r="P561" t="n">
-        <v>0.4411608087784771</v>
+        <v>-0.1031672536370252</v>
       </c>
       <c r="Q561" t="inlineStr">
         <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="R561" t="inlineStr">
+        <is>
           <t>Descendente</t>
-        </is>
-      </c>
-      <c r="R561" t="inlineStr">
-        <is>
-          <t>Ascendente</t>
         </is>
       </c>
       <c r="S561" t="b">
@@ -42045,7 +42045,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -42055,7 +42055,7 @@
         <v>9</v>
       </c>
       <c r="D562" t="n">
-        <v>2023.500366210938</v>
+        <v>1657.227905273438</v>
       </c>
       <c r="E562" t="inlineStr">
         <is>
@@ -42066,10 +42066,10 @@
         <v>9</v>
       </c>
       <c r="G562" t="n">
-        <v>0.8414192614047792</v>
+        <v>0.6046343229543809</v>
       </c>
       <c r="H562" t="n">
-        <v>129.4732570601014</v>
+        <v>128.6847936278059</v>
       </c>
       <c r="I562" t="inlineStr">
         <is>
@@ -42082,22 +42082,22 @@
         </is>
       </c>
       <c r="K562" t="n">
-        <v>129.5</v>
+        <v>128.6</v>
       </c>
       <c r="L562" t="n">
         <v>1</v>
       </c>
       <c r="M562" t="n">
-        <v>-0.02674293989863941</v>
+        <v>0.08479362780593647</v>
       </c>
       <c r="N562" t="n">
-        <v>0.02674293989863941</v>
+        <v>0.08479362780593647</v>
       </c>
       <c r="O562" t="n">
-        <v>0.1999999999999886</v>
+        <v>0.1099999999999852</v>
       </c>
       <c r="P562" t="n">
-        <v>0.4387530774800723</v>
+        <v>-0.002293463234821047</v>
       </c>
       <c r="Q562" t="inlineStr">
         <is>
@@ -42106,17 +42106,17 @@
       </c>
       <c r="R562" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S562" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -42126,7 +42126,7 @@
         <v>9</v>
       </c>
       <c r="D563" t="n">
-        <v>2127.298583984375</v>
+        <v>1697.664672851562</v>
       </c>
       <c r="E563" t="inlineStr">
         <is>
@@ -42137,10 +42137,10 @@
         <v>9</v>
       </c>
       <c r="G563" t="n">
-        <v>0.8783490224475018</v>
+        <v>0.6451846488052136</v>
       </c>
       <c r="H563" t="n">
-        <v>129.5970419985518</v>
+        <v>128.79616717958</v>
       </c>
       <c r="I563" t="inlineStr">
         <is>
@@ -42153,26 +42153,26 @@
         </is>
       </c>
       <c r="K563" t="n">
-        <v>129.44</v>
+        <v>129.15</v>
       </c>
       <c r="L563" t="n">
         <v>1</v>
       </c>
       <c r="M563" t="n">
-        <v>0.1570419985517617</v>
+        <v>-0.3538328204199672</v>
       </c>
       <c r="N563" t="n">
-        <v>0.1570419985517617</v>
+        <v>0.3538328204199672</v>
       </c>
       <c r="O563" t="n">
-        <v>-0.06000000000000227</v>
+        <v>0.5500000000000114</v>
       </c>
       <c r="P563" t="n">
-        <v>0.1237849384503988</v>
+        <v>0.1113735517741077</v>
       </c>
       <c r="Q563" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="R563" t="inlineStr">
@@ -42181,23 +42181,23 @@
         </is>
       </c>
       <c r="S563" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B564" t="n">
         <v>9046779</v>
       </c>
       <c r="C564" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D564" t="n">
-        <v>2119.77880859375</v>
+        <v>1789.900512695312</v>
       </c>
       <c r="E564" t="inlineStr">
         <is>
@@ -42205,13 +42205,13 @@
         </is>
       </c>
       <c r="F564" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G564" t="n">
-        <v>0.8769007965242578</v>
+        <v>0.1719971570717839</v>
       </c>
       <c r="H564" t="n">
-        <v>129.5957805937726</v>
+        <v>128.5351769722814</v>
       </c>
       <c r="I564" t="inlineStr">
         <is>
@@ -42224,22 +42224,22 @@
         </is>
       </c>
       <c r="K564" t="n">
-        <v>129.7</v>
+        <v>129.6</v>
       </c>
       <c r="L564" t="n">
         <v>1</v>
       </c>
       <c r="M564" t="n">
-        <v>-0.1042194062273722</v>
+        <v>-1.064823027718546</v>
       </c>
       <c r="N564" t="n">
-        <v>0.1042194062273722</v>
+        <v>1.064823027718546</v>
       </c>
       <c r="O564" t="n">
-        <v>0.2599999999999909</v>
+        <v>0.4499999999999886</v>
       </c>
       <c r="P564" t="n">
-        <v>-0.001261404779143049</v>
+        <v>-0.2609902072985903</v>
       </c>
       <c r="Q564" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
       </c>
       <c r="R564" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S564" t="b">
@@ -42258,17 +42258,17 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B565" t="n">
         <v>9046779</v>
       </c>
       <c r="C565" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D565" t="n">
-        <v>2044.919555664062</v>
+        <v>1917.7978515625</v>
       </c>
       <c r="E565" t="inlineStr">
         <is>
@@ -42276,13 +42276,13 @@
         </is>
       </c>
       <c r="F565" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G565" t="n">
-        <v>0.8508327299058653</v>
+        <v>0.2423596304193319</v>
       </c>
       <c r="H565" t="n">
-        <v>129.49179217958</v>
+        <v>128.8017294479981</v>
       </c>
       <c r="I565" t="inlineStr">
         <is>
@@ -42295,22 +42295,22 @@
         </is>
       </c>
       <c r="K565" t="n">
-        <v>129.4</v>
+        <v>129.46</v>
       </c>
       <c r="L565" t="n">
         <v>1</v>
       </c>
       <c r="M565" t="n">
-        <v>0.09179217958001118</v>
+        <v>-0.6582705520018806</v>
       </c>
       <c r="N565" t="n">
-        <v>0.09179217958001118</v>
+        <v>0.6582705520018806</v>
       </c>
       <c r="O565" t="n">
-        <v>-0.2999999999999829</v>
+        <v>-0.1399999999999864</v>
       </c>
       <c r="P565" t="n">
-        <v>-0.1039884141925995</v>
+        <v>0.2665524757166793</v>
       </c>
       <c r="Q565" t="inlineStr">
         <is>
@@ -42319,27 +42319,27 @@
       </c>
       <c r="R565" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S565" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="B566" t="n">
         <v>9046779</v>
       </c>
       <c r="C566" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D566" t="n">
-        <v>1945.693725585938</v>
+        <v>2018.260131835938</v>
       </c>
       <c r="E566" t="inlineStr">
         <is>
@@ -42347,13 +42347,13 @@
         </is>
       </c>
       <c r="F566" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G566" t="n">
-        <v>0.8110065170166546</v>
+        <v>0.3120113717128642</v>
       </c>
       <c r="H566" t="n">
-        <v>129.3720702008461</v>
+        <v>129.0875280739161</v>
       </c>
       <c r="I566" t="inlineStr">
         <is>
@@ -42366,22 +42366,22 @@
         </is>
       </c>
       <c r="K566" t="n">
-        <v>128.7</v>
+        <v>129.16</v>
       </c>
       <c r="L566" t="n">
         <v>1</v>
       </c>
       <c r="M566" t="n">
-        <v>0.6720702008460933</v>
+        <v>-0.07247192608386399</v>
       </c>
       <c r="N566" t="n">
-        <v>0.6720702008460933</v>
+        <v>0.07247192608386399</v>
       </c>
       <c r="O566" t="n">
-        <v>-0.7000000000000171</v>
+        <v>-0.3000000000000114</v>
       </c>
       <c r="P566" t="n">
-        <v>-0.119721978733935</v>
+        <v>0.2857986259180052</v>
       </c>
       <c r="Q566" t="inlineStr">
         <is>
@@ -42390,27 +42390,27 @@
       </c>
       <c r="R566" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S566" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="B567" t="n">
         <v>9046779</v>
       </c>
       <c r="C567" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D567" t="n">
-        <v>1845.803955078125</v>
+        <v>2048.108154296875</v>
       </c>
       <c r="E567" t="inlineStr">
         <is>
@@ -42418,13 +42418,13 @@
         </is>
       </c>
       <c r="F567" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G567" t="n">
-        <v>0.7407675597393193</v>
+        <v>0.3383084577114428</v>
       </c>
       <c r="H567" t="n">
-        <v>129.1220854453295</v>
+        <v>129.1920995024876</v>
       </c>
       <c r="I567" t="inlineStr">
         <is>
@@ -42437,22 +42437,22 @@
         </is>
       </c>
       <c r="K567" t="n">
-        <v>128.45</v>
+        <v>129.04</v>
       </c>
       <c r="L567" t="n">
         <v>1</v>
       </c>
       <c r="M567" t="n">
-        <v>0.6720854453294862</v>
+        <v>0.1520995024875731</v>
       </c>
       <c r="N567" t="n">
-        <v>0.6720854453294862</v>
+        <v>0.1520995024875731</v>
       </c>
       <c r="O567" t="n">
-        <v>-0.25</v>
+        <v>-0.1200000000000045</v>
       </c>
       <c r="P567" t="n">
-        <v>-0.249984755516607</v>
+        <v>0.1045714285714325</v>
       </c>
       <c r="Q567" t="inlineStr">
         <is>
@@ -42461,27 +42461,27 @@
       </c>
       <c r="R567" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S567" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B568" t="n">
         <v>9046779</v>
       </c>
       <c r="C568" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D568" t="n">
-        <v>1757.952026367188</v>
+        <v>2026.685180664062</v>
       </c>
       <c r="E568" t="inlineStr">
         <is>
@@ -42489,13 +42489,13 @@
         </is>
       </c>
       <c r="F568" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G568" t="n">
-        <v>0.6879073135409124</v>
+        <v>0.3212508884150675</v>
       </c>
       <c r="H568" t="n">
-        <v>128.9058363504707</v>
+        <v>129.1301468846245</v>
       </c>
       <c r="I568" t="inlineStr">
         <is>
@@ -42508,51 +42508,51 @@
         </is>
       </c>
       <c r="K568" t="n">
-        <v>128.36</v>
+        <v>129.23</v>
       </c>
       <c r="L568" t="n">
         <v>1</v>
       </c>
       <c r="M568" t="n">
-        <v>0.5458363504706654</v>
+        <v>-0.09985311537550956</v>
       </c>
       <c r="N568" t="n">
-        <v>0.5458363504706654</v>
+        <v>0.09985311537550956</v>
       </c>
       <c r="O568" t="n">
-        <v>-0.08999999999997499</v>
+        <v>0.1899999999999977</v>
       </c>
       <c r="P568" t="n">
-        <v>-0.2162490948587958</v>
+        <v>-0.06195261786308492</v>
       </c>
       <c r="Q568" t="inlineStr">
         <is>
+          <t>Ascendente</t>
+        </is>
+      </c>
+      <c r="R568" t="inlineStr">
+        <is>
           <t>Descendente</t>
         </is>
       </c>
-      <c r="R568" t="inlineStr">
-        <is>
-          <t>Descendente</t>
-        </is>
-      </c>
       <c r="S568" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B569" t="n">
         <v>9046779</v>
       </c>
       <c r="C569" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D569" t="n">
-        <v>1692.794311523438</v>
+        <v>1989.22216796875</v>
       </c>
       <c r="E569" t="inlineStr">
         <is>
@@ -42560,13 +42560,13 @@
         </is>
       </c>
       <c r="F569" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G569" t="n">
-        <v>0.6415640839971035</v>
+        <v>0.2928216062544421</v>
       </c>
       <c r="H569" t="n">
-        <v>128.7902543446778</v>
+        <v>128.9949597251836</v>
       </c>
       <c r="I569" t="inlineStr">
         <is>
@@ -42579,26 +42579,26 @@
         </is>
       </c>
       <c r="K569" t="n">
-        <v>128.45</v>
+        <v>128.8</v>
       </c>
       <c r="L569" t="n">
         <v>1</v>
       </c>
       <c r="M569" t="n">
-        <v>0.3402543446777884</v>
+        <v>0.1949597251835939</v>
       </c>
       <c r="N569" t="n">
-        <v>0.3402543446777884</v>
+        <v>0.1949597251835939</v>
       </c>
       <c r="O569" t="n">
-        <v>0.08999999999997499</v>
+        <v>-0.4299999999999784</v>
       </c>
       <c r="P569" t="n">
-        <v>-0.115582005792902</v>
+        <v>-0.1351871594408749</v>
       </c>
       <c r="Q569" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="R569" t="inlineStr">
@@ -42607,23 +42607,23 @@
         </is>
       </c>
       <c r="S569" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B570" t="n">
         <v>9046779</v>
       </c>
       <c r="C570" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D570" t="n">
-        <v>1657.840209960938</v>
+        <v>1947.940551757812</v>
       </c>
       <c r="E570" t="inlineStr">
         <is>
@@ -42631,13 +42631,13 @@
         </is>
       </c>
       <c r="F570" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G570" t="n">
-        <v>0.6060825488776249</v>
+        <v>0.2622601279317697</v>
       </c>
       <c r="H570" t="n">
-        <v>128.6870870910408</v>
+        <v>128.8607675906183</v>
       </c>
       <c r="I570" t="inlineStr">
         <is>
@@ -42650,26 +42650,26 @@
         </is>
       </c>
       <c r="K570" t="n">
-        <v>128.49</v>
+        <v>128.5</v>
       </c>
       <c r="L570" t="n">
         <v>1</v>
       </c>
       <c r="M570" t="n">
-        <v>0.1970870910407427</v>
+        <v>0.3607675906183374</v>
       </c>
       <c r="N570" t="n">
-        <v>0.1970870910407427</v>
+        <v>0.3607675906183374</v>
       </c>
       <c r="O570" t="n">
-        <v>0.04000000000002046</v>
+        <v>-0.3000000000000114</v>
       </c>
       <c r="P570" t="n">
-        <v>-0.1031672536370252</v>
+        <v>-0.1341921345652679</v>
       </c>
       <c r="Q570" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="R570" t="inlineStr">
@@ -42678,23 +42678,23 @@
         </is>
       </c>
       <c r="S570" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B571" t="n">
         <v>9046779</v>
       </c>
       <c r="C571" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D571" t="n">
-        <v>1657.227905273438</v>
+        <v>1907.248779296875</v>
       </c>
       <c r="E571" t="inlineStr">
         <is>
@@ -42702,13 +42702,13 @@
         </is>
       </c>
       <c r="F571" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G571" t="n">
-        <v>0.6046343229543809</v>
+        <v>0.2373845060412225</v>
       </c>
       <c r="H571" t="n">
-        <v>128.6847936278059</v>
+        <v>128.7980678749112</v>
       </c>
       <c r="I571" t="inlineStr">
         <is>
@@ -42721,51 +42721,51 @@
         </is>
       </c>
       <c r="K571" t="n">
-        <v>128.6</v>
+        <v>128</v>
       </c>
       <c r="L571" t="n">
         <v>1</v>
       </c>
       <c r="M571" t="n">
-        <v>0.08479362780593647</v>
+        <v>0.7980678749111689</v>
       </c>
       <c r="N571" t="n">
-        <v>0.08479362780593647</v>
+        <v>0.7980678749111689</v>
       </c>
       <c r="O571" t="n">
-        <v>0.1099999999999852</v>
+        <v>-0.5</v>
       </c>
       <c r="P571" t="n">
-        <v>-0.002293463234821047</v>
+        <v>-0.06269971570716848</v>
       </c>
       <c r="Q571" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="R571" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S571" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B572" t="n">
         <v>9046779</v>
       </c>
       <c r="C572" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D572" t="n">
-        <v>1697.664672851562</v>
+        <v>1872.346069335938</v>
       </c>
       <c r="E572" t="inlineStr">
         <is>
@@ -42773,13 +42773,13 @@
         </is>
       </c>
       <c r="F572" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G572" t="n">
-        <v>0.6451846488052136</v>
+        <v>0.2132196162046908</v>
       </c>
       <c r="H572" t="n">
-        <v>128.79616717958</v>
+        <v>128.7476929637527</v>
       </c>
       <c r="I572" t="inlineStr">
         <is>
@@ -42792,41 +42792,41 @@
         </is>
       </c>
       <c r="K572" t="n">
-        <v>129.15</v>
+        <v>127.96</v>
       </c>
       <c r="L572" t="n">
         <v>1</v>
       </c>
       <c r="M572" t="n">
-        <v>-0.3538328204199672</v>
+        <v>0.7876929637526615</v>
       </c>
       <c r="N572" t="n">
-        <v>0.3538328204199672</v>
+        <v>0.7876929637526615</v>
       </c>
       <c r="O572" t="n">
-        <v>0.5500000000000114</v>
+        <v>-0.04000000000000625</v>
       </c>
       <c r="P572" t="n">
-        <v>0.1113735517741077</v>
+        <v>-0.05037491115851367</v>
       </c>
       <c r="Q572" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R572" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S572" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -42836,7 +42836,7 @@
         <v>10</v>
       </c>
       <c r="D573" t="n">
-        <v>1789.900512695312</v>
+        <v>1839.430419921875</v>
       </c>
       <c r="E573" t="inlineStr">
         <is>
@@ -42847,10 +42847,10 @@
         <v>10</v>
       </c>
       <c r="G573" t="n">
-        <v>0.1719971570717839</v>
+        <v>0.1926083866382374</v>
       </c>
       <c r="H573" t="n">
-        <v>128.5488571428571</v>
+        <v>128.6734399431414</v>
       </c>
       <c r="I573" t="inlineStr">
         <is>
@@ -42863,22 +42863,22 @@
         </is>
       </c>
       <c r="K573" t="n">
-        <v>129.6</v>
+        <v>128.3</v>
       </c>
       <c r="L573" t="n">
         <v>1</v>
       </c>
       <c r="M573" t="n">
-        <v>-1.05114285714285</v>
+        <v>0.3734399431414204</v>
       </c>
       <c r="N573" t="n">
-        <v>1.05114285714285</v>
+        <v>0.3734399431414204</v>
       </c>
       <c r="O573" t="n">
-        <v>0.4499999999999886</v>
+        <v>0.3400000000000176</v>
       </c>
       <c r="P573" t="n">
-        <v>-0.2473100367228938</v>
+        <v>-0.07425302061122352</v>
       </c>
       <c r="Q573" t="inlineStr">
         <is>
@@ -42897,7 +42897,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -42907,7 +42907,7 @@
         <v>10</v>
       </c>
       <c r="D574" t="n">
-        <v>1917.7978515625</v>
+        <v>1806.540405273438</v>
       </c>
       <c r="E574" t="inlineStr">
         <is>
@@ -42918,10 +42918,10 @@
         <v>10</v>
       </c>
       <c r="G574" t="n">
-        <v>0.2423596304193319</v>
+        <v>0.1798152096659559</v>
       </c>
       <c r="H574" t="n">
-        <v>128.8101904761905</v>
+        <v>128.5897634277592</v>
       </c>
       <c r="I574" t="inlineStr">
         <is>
@@ -42934,31 +42934,31 @@
         </is>
       </c>
       <c r="K574" t="n">
-        <v>129.46</v>
+        <v>128.96</v>
       </c>
       <c r="L574" t="n">
         <v>1</v>
       </c>
       <c r="M574" t="n">
-        <v>-0.6498095238095232</v>
+        <v>-0.3702365722408274</v>
       </c>
       <c r="N574" t="n">
-        <v>0.6498095238095232</v>
+        <v>0.3702365722408274</v>
       </c>
       <c r="O574" t="n">
-        <v>-0.1399999999999864</v>
+        <v>0.6599999999999966</v>
       </c>
       <c r="P574" t="n">
-        <v>0.2613333333333401</v>
+        <v>-0.08367651538225118</v>
       </c>
       <c r="Q574" t="inlineStr">
         <is>
+          <t>Ascendente</t>
+        </is>
+      </c>
+      <c r="R574" t="inlineStr">
+        <is>
           <t>Descendente</t>
-        </is>
-      </c>
-      <c r="R574" t="inlineStr">
-        <is>
-          <t>Ascendente</t>
         </is>
       </c>
       <c r="S574" t="b">
@@ -44320,22 +44320,22 @@
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.366</v>
+        <v>3.365</v>
       </c>
       <c r="G18" t="n">
-        <v>3.82</v>
+        <v>3.817</v>
       </c>
       <c r="H18" t="n">
-        <v>4.297</v>
+        <v>4.291</v>
       </c>
       <c r="I18" t="n">
-        <v>3.366</v>
+        <v>3.365</v>
       </c>
       <c r="J18" t="n">
-        <v>4.251</v>
+        <v>4.248</v>
       </c>
       <c r="K18" t="n">
-        <v>0.885</v>
+        <v>0.883</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -44344,23 +44344,23 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>0.522</v>
+        <v>0.581</v>
       </c>
       <c r="P18" t="n">
-        <v>0.459</v>
+        <v>0.516</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.106</v>
+        <v>0.177</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.403</v>
+        <v>-0.465</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -44396,22 +44396,22 @@
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.252</v>
+        <v>3.248</v>
       </c>
       <c r="G19" t="n">
-        <v>3.307</v>
+        <v>3.304</v>
       </c>
       <c r="H19" t="n">
-        <v>3.336</v>
+        <v>3.332</v>
       </c>
       <c r="I19" t="n">
-        <v>3.322</v>
+        <v>3.32</v>
       </c>
       <c r="J19" t="n">
-        <v>3.269</v>
+        <v>3.266</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.053</v>
+        <v>-0.054</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -44420,23 +44420,23 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="N19" t="n">
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>0.649</v>
+        <v>0.736</v>
       </c>
       <c r="P19" t="n">
-        <v>0.575</v>
+        <v>0.645</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.061</v>
+        <v>0.131</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.806</v>
+        <v>-0.679</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -44472,22 +44472,22 @@
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>6.336</v>
+        <v>6.27</v>
       </c>
       <c r="G20" t="n">
-        <v>6.78</v>
+        <v>6.629</v>
       </c>
       <c r="H20" t="n">
-        <v>7.401</v>
+        <v>7.389</v>
       </c>
       <c r="I20" t="n">
-        <v>6.43</v>
+        <v>6.349</v>
       </c>
       <c r="J20" t="n">
-        <v>6.852</v>
+        <v>6.767</v>
       </c>
       <c r="K20" t="n">
-        <v>0.422</v>
+        <v>0.417</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -44496,23 +44496,23 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="N20" t="n">
         <v>30</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.776</v>
       </c>
       <c r="P20" t="n">
-        <v>0.584</v>
+        <v>0.532</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.392</v>
+        <v>-0.396</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.365</v>
+        <v>-0.062</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -44548,22 +44548,22 @@
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.581</v>
+        <v>128.545</v>
       </c>
       <c r="G21" t="n">
-        <v>129.102</v>
+        <v>129.084</v>
       </c>
       <c r="H21" t="n">
-        <v>129.799</v>
+        <v>129.795</v>
       </c>
       <c r="I21" t="n">
-        <v>128.581</v>
+        <v>128.545</v>
       </c>
       <c r="J21" t="n">
-        <v>129.618</v>
+        <v>129.609</v>
       </c>
       <c r="K21" t="n">
-        <v>1.037</v>
+        <v>1.063</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -44572,23 +44572,23 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="N21" t="n">
         <v>30</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.614</v>
       </c>
       <c r="P21" t="n">
-        <v>0.573</v>
+        <v>0.484</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.006</v>
+        <v>0.03</v>
       </c>
       <c r="R21" t="n">
-        <v>0.451</v>
+        <v>0.403</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>

--- a/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
+++ b/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>56.475</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>4.04</v>
@@ -1014,31 +1014,31 @@
         <v>2.73</v>
       </c>
       <c r="J6" t="n">
-        <v>-52.435</v>
+        <v>0.04</v>
       </c>
       <c r="K6" t="n">
         <v>1.393</v>
       </c>
       <c r="L6" t="n">
-        <v>-37.631</v>
+        <v>-0.923</v>
       </c>
       <c r="M6" t="n">
-        <v>37.653</v>
+        <v>0.976</v>
       </c>
       <c r="N6" t="n">
-        <v>44.832</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.126</v>
+        <v>0.58</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.428</v>
+        <v>-6.859</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.739</v>
+        <v>-0.371</v>
       </c>
       <c r="R6" t="n">
-        <v>34.483</v>
+        <v>31.034</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1049,16 +1049,16 @@
         <v>10053</v>
       </c>
       <c r="U6" t="n">
-        <v>0.153</v>
+        <v>0.855</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.611</v>
+        <v>0.71</v>
       </c>
       <c r="W6" t="n">
-        <v>0.151</v>
+        <v>0.855</v>
       </c>
       <c r="X6" t="n">
-        <v>16.975</v>
+        <v>1.616</v>
       </c>
     </row>
     <row r="7">
@@ -10938,16 +10938,16 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>56.475</v>
+        <v>4</v>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-55.13830919623462</v>
+        <v>-2.663309196234612</v>
       </c>
       <c r="N122" t="n">
-        <v>55.13830919623462</v>
+        <v>2.663309196234612</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
@@ -11003,19 +11003,19 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>56.395</v>
+        <v>3.92</v>
       </c>
       <c r="L123" t="n">
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-55.00959087617669</v>
+        <v>-2.534590876176682</v>
       </c>
       <c r="N123" t="n">
-        <v>55.00959087617669</v>
+        <v>2.534590876176682</v>
       </c>
       <c r="O123" t="n">
-        <v>-0.07999999999999829</v>
+        <v>-0.08000000000000007</v>
       </c>
       <c r="P123" t="n">
         <v>0.04871832005792998</v>
@@ -11074,19 +11074,19 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>56.335</v>
+        <v>3.86</v>
       </c>
       <c r="L124" t="n">
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-54.85215423606083</v>
+        <v>-2.377154236060823</v>
       </c>
       <c r="N124" t="n">
-        <v>54.85215423606083</v>
+        <v>2.377154236060823</v>
       </c>
       <c r="O124" t="n">
-        <v>-0.06000000000000227</v>
+        <v>-0.06000000000000005</v>
       </c>
       <c r="P124" t="n">
         <v>0.09743664011585884</v>
@@ -11145,19 +11145,19 @@
         </is>
       </c>
       <c r="K125" t="n">
-        <v>56.285</v>
+        <v>3.81</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-54.46479724837075</v>
+        <v>-1.98979724837075</v>
       </c>
       <c r="N125" t="n">
-        <v>54.46479724837075</v>
+        <v>1.98979724837075</v>
       </c>
       <c r="O125" t="n">
-        <v>-0.04999999999999716</v>
+        <v>-0.04999999999999982</v>
       </c>
       <c r="P125" t="n">
         <v>0.3373569876900735</v>
@@ -11216,19 +11216,19 @@
         </is>
       </c>
       <c r="K126" t="n">
-        <v>56.315</v>
+        <v>3.84</v>
       </c>
       <c r="L126" t="n">
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-54.15200458604876</v>
+        <v>-1.677004586048759</v>
       </c>
       <c r="N126" t="n">
-        <v>54.15200458604876</v>
+        <v>1.677004586048759</v>
       </c>
       <c r="O126" t="n">
-        <v>0.03000000000000114</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="P126" t="n">
         <v>0.3427926623219912</v>
@@ -11287,19 +11287,19 @@
         </is>
       </c>
       <c r="K127" t="n">
-        <v>56.325</v>
+        <v>3.85</v>
       </c>
       <c r="L127" t="n">
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-53.86499999999999</v>
+        <v>-1.39</v>
       </c>
       <c r="N127" t="n">
-        <v>53.86499999999999</v>
+        <v>1.39</v>
       </c>
       <c r="O127" t="n">
-        <v>0.009999999999990905</v>
+        <v>0.01000000000000023</v>
       </c>
       <c r="P127" t="n">
         <v>0.2970045860487587</v>
@@ -11358,19 +11358,19 @@
         </is>
       </c>
       <c r="K128" t="n">
-        <v>56.405</v>
+        <v>3.93</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-53.82179217958002</v>
+        <v>-1.346792179580014</v>
       </c>
       <c r="N128" t="n">
-        <v>53.82179217958002</v>
+        <v>1.346792179580014</v>
       </c>
       <c r="O128" t="n">
-        <v>0.0800000000000054</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="P128" t="n">
         <v>0.1232078204199865</v>
@@ -11429,19 +11429,19 @@
         </is>
       </c>
       <c r="K129" t="n">
-        <v>56.505</v>
+        <v>4.03</v>
       </c>
       <c r="L129" t="n">
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-53.59665821868212</v>
+        <v>-1.121658218682117</v>
       </c>
       <c r="N129" t="n">
-        <v>53.59665821868212</v>
+        <v>1.121658218682117</v>
       </c>
       <c r="O129" t="n">
-        <v>0.1000000000000014</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="P129" t="n">
         <v>0.3251339608978965</v>
@@ -11500,19 +11500,19 @@
         </is>
       </c>
       <c r="K130" t="n">
-        <v>56.625</v>
+        <v>4.15</v>
       </c>
       <c r="L130" t="n">
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-53.02024257784215</v>
+        <v>-0.5452425778421475</v>
       </c>
       <c r="N130" t="n">
-        <v>53.02024257784215</v>
+        <v>0.5452425778421475</v>
       </c>
       <c r="O130" t="n">
-        <v>0.1199999999999974</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="P130" t="n">
         <v>0.69641564083997</v>
@@ -11558,7 +11558,7 @@
         <v>0.5655322230267922</v>
       </c>
       <c r="H131" t="n">
-        <v>4.155375331885105</v>
+        <v>4.116125995655316</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -11571,35 +11571,35 @@
         </is>
       </c>
       <c r="K131" t="n">
-        <v>56.68000000000001</v>
+        <v>4.18</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-52.5246246681149</v>
+        <v>-0.06387400434468393</v>
       </c>
       <c r="N131" t="n">
-        <v>52.5246246681149</v>
+        <v>0.06387400434468393</v>
       </c>
       <c r="O131" t="n">
-        <v>0.05500000000000682</v>
+        <v>0.02999999999999936</v>
       </c>
       <c r="P131" t="n">
-        <v>0.5506179097272526</v>
+        <v>0.5113685734974629</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
           <t>Ascendente</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr">
-        <is>
-          <t>Ascendente</t>
-        </is>
-      </c>
       <c r="S131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -11629,7 +11629,7 @@
         <v>0.6053584359160029</v>
       </c>
       <c r="H132" t="n">
-        <v>4.28</v>
+        <v>4.235266111513395</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -11642,22 +11642,22 @@
         </is>
       </c>
       <c r="K132" t="n">
-        <v>56.935</v>
+        <v>4.46</v>
       </c>
       <c r="L132" t="n">
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-52.65499999999999</v>
+        <v>-0.2247338884866048</v>
       </c>
       <c r="N132" t="n">
-        <v>52.65499999999999</v>
+        <v>0.2247338884866048</v>
       </c>
       <c r="O132" t="n">
-        <v>0.2549999999999883</v>
+        <v>0.2800000000000002</v>
       </c>
       <c r="P132" t="n">
-        <v>0.1246246681148948</v>
+        <v>0.1191401158580794</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>0.5843591600289645</v>
       </c>
       <c r="H133" t="n">
-        <v>4.197230267921797</v>
+        <v>4.179999999999996</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -11713,22 +11713,22 @@
         </is>
       </c>
       <c r="K133" t="n">
-        <v>57.295</v>
+        <v>4.82</v>
       </c>
       <c r="L133" t="n">
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-53.09776973207821</v>
+        <v>-0.6400000000000041</v>
       </c>
       <c r="N133" t="n">
-        <v>53.09776973207821</v>
+        <v>0.6400000000000041</v>
       </c>
       <c r="O133" t="n">
-        <v>0.3600000000000065</v>
+        <v>0.3600000000000003</v>
       </c>
       <c r="P133" t="n">
-        <v>-0.08276973207820326</v>
+        <v>-0.055266111513399</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>0.5257060101375814</v>
       </c>
       <c r="H134" t="n">
-        <v>4.020296886314261</v>
+        <v>3.991187545257056</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -11784,22 +11784,22 @@
         </is>
       </c>
       <c r="K134" t="n">
-        <v>57.415</v>
+        <v>4.94</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-53.39470311368574</v>
+        <v>-0.9488124547429448</v>
       </c>
       <c r="N134" t="n">
-        <v>53.39470311368574</v>
+        <v>0.9488124547429448</v>
       </c>
       <c r="O134" t="n">
-        <v>0.1199999999999974</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="P134" t="n">
-        <v>-0.1769333816075358</v>
+        <v>-0.1888124547429406</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -11855,22 +11855,22 @@
         </is>
       </c>
       <c r="K135" t="n">
-        <v>57.495</v>
+        <v>5.02</v>
       </c>
       <c r="L135" t="n">
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-53.75715061549602</v>
+        <v>-1.28215061549602</v>
       </c>
       <c r="N135" t="n">
-        <v>53.75715061549602</v>
+        <v>1.28215061549602</v>
       </c>
       <c r="O135" t="n">
-        <v>0.07999999999999829</v>
+        <v>0.07999999999999918</v>
       </c>
       <c r="P135" t="n">
-        <v>-0.2824475018102817</v>
+        <v>-0.253338160753076</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>57.565</v>
+        <v>5.09</v>
       </c>
       <c r="L136" t="n">
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-54.279283128168</v>
+        <v>-1.804283128167998</v>
       </c>
       <c r="N136" t="n">
-        <v>54.279283128168</v>
+        <v>1.804283128167998</v>
       </c>
       <c r="O136" t="n">
-        <v>0.07000000000000739</v>
+        <v>0.07000000000000028</v>
       </c>
       <c r="P136" t="n">
         <v>-0.452132512671978</v>
@@ -11997,19 +11997,19 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>57.615</v>
+        <v>5.14</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-54.44760680666184</v>
+        <v>-1.972606806661838</v>
       </c>
       <c r="N137" t="n">
-        <v>54.44760680666184</v>
+        <v>1.972606806661838</v>
       </c>
       <c r="O137" t="n">
-        <v>0.04999999999999716</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="P137" t="n">
         <v>-0.11832367849384</v>
@@ -12055,7 +12055,7 @@
         <v>0.4721216509775525</v>
       </c>
       <c r="H138" t="n">
-        <v>3.808108616944244</v>
+        <v>3.810000000000001</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -12068,22 +12068,22 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>57.565</v>
+        <v>5.09</v>
       </c>
       <c r="L138" t="n">
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-53.75689138305576</v>
+        <v>-1.279999999999999</v>
       </c>
       <c r="N138" t="n">
-        <v>53.75689138305576</v>
+        <v>1.279999999999999</v>
       </c>
       <c r="O138" t="n">
-        <v>-0.04999999999999716</v>
+        <v>-0.04999999999999982</v>
       </c>
       <c r="P138" t="n">
-        <v>0.6407154236060828</v>
+        <v>0.6426068066618393</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>0.6893555394641564</v>
       </c>
       <c r="H139" t="n">
-        <v>4.560000000000002</v>
+        <v>4.50937002172338</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -12139,22 +12139,22 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>57.425</v>
+        <v>4.95</v>
       </c>
       <c r="L139" t="n">
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-52.865</v>
+        <v>-0.4406299782766201</v>
       </c>
       <c r="N139" t="n">
-        <v>52.865</v>
+        <v>0.4406299782766201</v>
       </c>
       <c r="O139" t="n">
-        <v>-0.1400000000000006</v>
+        <v>-0.1399999999999997</v>
       </c>
       <c r="P139" t="n">
-        <v>0.7518913830557579</v>
+        <v>0.6993700217233791</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>0.78059377262853</v>
       </c>
       <c r="H140" t="n">
-        <v>5.039917451122374</v>
+        <v>4.841597875935315</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -12210,22 +12210,22 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>57.295</v>
+        <v>4.82</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-52.25508254887762</v>
+        <v>0.02159787593531437</v>
       </c>
       <c r="N140" t="n">
-        <v>52.25508254887762</v>
+        <v>0.02159787593531437</v>
       </c>
       <c r="O140" t="n">
-        <v>-0.1300000000000026</v>
+        <v>-0.1299999999999999</v>
       </c>
       <c r="P140" t="n">
-        <v>0.4799174511223718</v>
+        <v>0.3322278542119346</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>0.7907313540912382</v>
       </c>
       <c r="H141" t="n">
-        <v>5.113350229302434</v>
+        <v>4.870025343953657</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -12281,22 +12281,22 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>57.195</v>
+        <v>4.72</v>
       </c>
       <c r="L141" t="n">
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-52.08164977069757</v>
+        <v>0.150025343953657</v>
       </c>
       <c r="N141" t="n">
-        <v>52.08164977069757</v>
+        <v>0.150025343953657</v>
       </c>
       <c r="O141" t="n">
-        <v>-0.1000000000000014</v>
+        <v>-0.1000000000000005</v>
       </c>
       <c r="P141" t="n">
-        <v>0.07343277818006033</v>
+        <v>0.02842746801834206</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S141" t="b">
@@ -12339,7 +12339,7 @@
         <v>0.7668356263577119</v>
       </c>
       <c r="H142" t="n">
-        <v>4.949771904417092</v>
+        <v>4.816362539222782</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -12352,22 +12352,22 @@
         </is>
       </c>
       <c r="K142" t="n">
-        <v>56.995</v>
+        <v>4.52</v>
       </c>
       <c r="L142" t="n">
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-52.04522809558291</v>
+        <v>0.2963625392227822</v>
       </c>
       <c r="N142" t="n">
-        <v>52.04522809558291</v>
+        <v>0.2963625392227822</v>
       </c>
       <c r="O142" t="n">
-        <v>-0.2000000000000028</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="P142" t="n">
-        <v>-0.1635783248853429</v>
+        <v>-0.05366280473087492</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
@@ -12435,10 +12435,10 @@
         <v>0.1990405117270786</v>
       </c>
       <c r="O143" t="n">
-        <v>-52.655</v>
+        <v>-0.1799999999999997</v>
       </c>
       <c r="P143" t="n">
-        <v>-0.4107313926900131</v>
+        <v>-0.2773220274957033</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -43411,19 +43411,19 @@
         <v>0.738</v>
       </c>
       <c r="G6" t="n">
-        <v>2.616</v>
+        <v>2.612</v>
       </c>
       <c r="H6" t="n">
-        <v>6.191</v>
+        <v>6.124</v>
       </c>
       <c r="I6" t="n">
         <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>4.145</v>
+        <v>4.132</v>
       </c>
       <c r="K6" t="n">
-        <v>2.445</v>
+        <v>2.432</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -43439,16 +43439,16 @@
         <v>30</v>
       </c>
       <c r="O6" t="n">
-        <v>44.832</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>37.653</v>
+        <v>0.976</v>
       </c>
       <c r="Q6" t="n">
-        <v>-37.631</v>
+        <v>-0.923</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.739</v>
+        <v>-0.371</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>

--- a/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
+++ b/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
@@ -489,7 +489,7 @@
         <v>334560</v>
       </c>
       <c r="E2" t="n">
-        <v>332982</v>
+        <v>332983</v>
       </c>
       <c r="F2" t="n">
         <v>600</v>
@@ -511,7 +511,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
     </row>
@@ -1758,19 +1758,19 @@
         <v>1.381</v>
       </c>
       <c r="L15" t="n">
-        <v>0.593</v>
+        <v>0.592</v>
       </c>
       <c r="M15" t="n">
-        <v>1.215</v>
+        <v>1.214</v>
       </c>
       <c r="N15" t="n">
-        <v>1.355</v>
+        <v>1.354</v>
       </c>
       <c r="O15" t="n">
         <v>-0.878</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.616</v>
+        <v>-3.613</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.882</v>
@@ -30816,7 +30816,7 @@
         <v>0.6452296819787986</v>
       </c>
       <c r="H403" t="n">
-        <v>5.490580918727916</v>
+        <v>5.489785630153122</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -30835,16 +30835,16 @@
         <v>1</v>
       </c>
       <c r="M403" t="n">
-        <v>0.555580918727915</v>
+        <v>0.5547856301531215</v>
       </c>
       <c r="N403" t="n">
-        <v>0.555580918727915</v>
+        <v>0.5547856301531215</v>
       </c>
       <c r="O403" t="n">
         <v>-0.1124999999999989</v>
       </c>
       <c r="P403" t="n">
-        <v>0.4380809187279153</v>
+        <v>0.4372856301531218</v>
       </c>
       <c r="Q403" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>0.6381625441696113</v>
       </c>
       <c r="H404" t="n">
-        <v>5.457587750294464</v>
+        <v>5.456381625441696</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -30906,16 +30906,16 @@
         <v>1</v>
       </c>
       <c r="M404" t="n">
-        <v>0.5550877502944642</v>
+        <v>0.5538816254416963</v>
       </c>
       <c r="N404" t="n">
-        <v>0.5550877502944642</v>
+        <v>0.5538816254416963</v>
       </c>
       <c r="O404" t="n">
         <v>-0.03250000000000064</v>
       </c>
       <c r="P404" t="n">
-        <v>-0.03299316843345146</v>
+        <v>-0.03340400471142591</v>
       </c>
       <c r="Q404" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>0.6402826855123674</v>
       </c>
       <c r="H405" t="n">
-        <v>5.465701413427562</v>
+        <v>5.464802120141343</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -30977,16 +30977,16 @@
         <v>1</v>
       </c>
       <c r="M405" t="n">
-        <v>0.6182014134275615</v>
+        <v>0.6173021201413427</v>
       </c>
       <c r="N405" t="n">
-        <v>0.6182014134275615</v>
+        <v>0.6173021201413427</v>
       </c>
       <c r="O405" t="n">
         <v>-0.05499999999999972</v>
       </c>
       <c r="P405" t="n">
-        <v>0.008113663133097582</v>
+        <v>0.008420494699646675</v>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>0.6593639575971731</v>
       </c>
       <c r="H406" t="n">
-        <v>5.558296819787985</v>
+        <v>5.557445229681979</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -31048,16 +31048,16 @@
         <v>1</v>
       </c>
       <c r="M406" t="n">
-        <v>0.8507968197879858</v>
+        <v>0.8499452296819792</v>
       </c>
       <c r="N406" t="n">
-        <v>0.8507968197879858</v>
+        <v>0.8499452296819792</v>
       </c>
       <c r="O406" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P406" t="n">
-        <v>0.09259540636042374</v>
+        <v>0.09264310954063593</v>
       </c>
       <c r="Q406" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>0.7010600706713781</v>
       </c>
       <c r="H407" t="n">
-        <v>5.748007067137809</v>
+        <v>5.747010600706714</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
@@ -31119,16 +31119,16 @@
         <v>1</v>
       </c>
       <c r="M407" t="n">
-        <v>1.100507067137809</v>
+        <v>1.099510600706714</v>
       </c>
       <c r="N407" t="n">
-        <v>1.100507067137809</v>
+        <v>1.099510600706714</v>
       </c>
       <c r="O407" t="n">
         <v>-0.05999999999999961</v>
       </c>
       <c r="P407" t="n">
-        <v>0.189710247349824</v>
+        <v>0.1895653710247354</v>
       </c>
       <c r="Q407" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>0.7477031802120141</v>
       </c>
       <c r="H408" t="n">
-        <v>5.981486219081272</v>
+        <v>5.980729328621909</v>
       </c>
       <c r="I408" t="inlineStr">
         <is>
@@ -31190,16 +31190,16 @@
         <v>1</v>
       </c>
       <c r="M408" t="n">
-        <v>1.193986219081272</v>
+        <v>1.193229328621909</v>
       </c>
       <c r="N408" t="n">
-        <v>1.193986219081272</v>
+        <v>1.193229328621909</v>
       </c>
       <c r="O408" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P408" t="n">
-        <v>0.2334791519434622</v>
+        <v>0.2337187279151944</v>
       </c>
       <c r="Q408" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>0.7795053003533569</v>
       </c>
       <c r="H409" t="n">
-        <v>6.115590106007066</v>
+        <v>6.1133851590106</v>
       </c>
       <c r="I409" t="inlineStr">
         <is>
@@ -31261,16 +31261,16 @@
         <v>1</v>
       </c>
       <c r="M409" t="n">
-        <v>1.075590106007067</v>
+        <v>1.073385159010601</v>
       </c>
       <c r="N409" t="n">
-        <v>1.075590106007067</v>
+        <v>1.073385159010601</v>
       </c>
       <c r="O409" t="n">
         <v>0.2524999999999995</v>
       </c>
       <c r="P409" t="n">
-        <v>0.1341038869257947</v>
+        <v>0.1326558303886918</v>
       </c>
       <c r="Q409" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>0.7978798586572439</v>
       </c>
       <c r="H410" t="n">
-        <v>6.231191519434629</v>
+        <v>6.230787279151944</v>
       </c>
       <c r="I410" t="inlineStr">
         <is>
@@ -31332,16 +31332,16 @@
         <v>1</v>
       </c>
       <c r="M410" t="n">
-        <v>1.16619151943463</v>
+        <v>1.165787279151944</v>
       </c>
       <c r="N410" t="n">
-        <v>1.16619151943463</v>
+        <v>1.165787279151944</v>
       </c>
       <c r="O410" t="n">
         <v>0.02500000000000036</v>
       </c>
       <c r="P410" t="n">
-        <v>0.1156014134275631</v>
+        <v>0.1174021201413433</v>
       </c>
       <c r="Q410" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>0.8148409893992933</v>
       </c>
       <c r="H411" t="n">
-        <v>6.331259363957597</v>
+        <v>6.330889045936396</v>
       </c>
       <c r="I411" t="inlineStr">
         <is>
@@ -31403,16 +31403,16 @@
         <v>1</v>
       </c>
       <c r="M411" t="n">
-        <v>1.338759363957596</v>
+        <v>1.338389045936395</v>
       </c>
       <c r="N411" t="n">
-        <v>1.338759363957596</v>
+        <v>1.338389045936395</v>
       </c>
       <c r="O411" t="n">
         <v>-0.0724999999999989</v>
       </c>
       <c r="P411" t="n">
-        <v>0.1000678445229672</v>
+        <v>0.1001017667844524</v>
       </c>
       <c r="Q411" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>0.8197879858657244</v>
       </c>
       <c r="H412" t="n">
-        <v>6.366918727915195</v>
+        <v>6.366378091872792</v>
       </c>
       <c r="I412" t="inlineStr">
         <is>
@@ -31474,16 +31474,16 @@
         <v>1</v>
       </c>
       <c r="M412" t="n">
-        <v>1.544418727915195</v>
+        <v>1.543878091872792</v>
       </c>
       <c r="N412" t="n">
-        <v>1.544418727915195</v>
+        <v>1.543878091872792</v>
       </c>
       <c r="O412" t="n">
         <v>-0.1700000000000008</v>
       </c>
       <c r="P412" t="n">
-        <v>0.03565936395759817</v>
+        <v>0.03548904593639612</v>
       </c>
       <c r="Q412" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>0.8240282685512368</v>
       </c>
       <c r="H413" t="n">
-        <v>6.396296113074205</v>
+        <v>6.395944169611307</v>
       </c>
       <c r="I413" t="inlineStr">
         <is>
@@ -31545,16 +31545,16 @@
         <v>1</v>
       </c>
       <c r="M413" t="n">
-        <v>1.756296113074205</v>
+        <v>1.755944169611308</v>
       </c>
       <c r="N413" t="n">
-        <v>1.756296113074205</v>
+        <v>1.755944169611308</v>
       </c>
       <c r="O413" t="n">
         <v>-0.1825000000000001</v>
       </c>
       <c r="P413" t="n">
-        <v>0.02937738515900978</v>
+        <v>0.02956607773851516</v>
       </c>
       <c r="Q413" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>0.8219081272084806</v>
       </c>
       <c r="H414" t="n">
-        <v>6.391073027090695</v>
+        <v>6.390776207302709</v>
       </c>
       <c r="I414" t="inlineStr">
         <is>
@@ -31616,16 +31616,16 @@
         <v>1</v>
       </c>
       <c r="M414" t="n">
-        <v>1.941073027090694</v>
+        <v>1.940776207302708</v>
       </c>
       <c r="N414" t="n">
-        <v>1.941073027090694</v>
+        <v>1.940776207302708</v>
       </c>
       <c r="O414" t="n">
         <v>-0.1899999999999986</v>
       </c>
       <c r="P414" t="n">
-        <v>-0.005223085983510067</v>
+        <v>-0.005167962308598284</v>
       </c>
       <c r="Q414" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>0.8190812720848056</v>
       </c>
       <c r="H415" t="n">
-        <v>6.363190812720848</v>
+        <v>6.362286219081272</v>
       </c>
       <c r="I415" t="inlineStr">
         <is>
@@ -31687,16 +31687,16 @@
         <v>1</v>
       </c>
       <c r="M415" t="n">
-        <v>2.003190812720849</v>
+        <v>2.002286219081273</v>
       </c>
       <c r="N415" t="n">
-        <v>2.003190812720849</v>
+        <v>2.002286219081273</v>
       </c>
       <c r="O415" t="n">
         <v>-0.09000000000000163</v>
       </c>
       <c r="P415" t="n">
-        <v>-0.02788221436984628</v>
+        <v>-0.02848998822143667</v>
       </c>
       <c r="Q415" t="inlineStr">
         <is>
@@ -31739,7 +31739,7 @@
         <v>0.815547703180212</v>
       </c>
       <c r="H416" t="n">
-        <v>6.334524381625442</v>
+        <v>6.333786572438163</v>
       </c>
       <c r="I416" t="inlineStr">
         <is>
@@ -31758,16 +31758,16 @@
         <v>1</v>
       </c>
       <c r="M416" t="n">
-        <v>1.974524381625441</v>
+        <v>1.973786572438162</v>
       </c>
       <c r="N416" t="n">
-        <v>1.974524381625441</v>
+        <v>1.973786572438162</v>
       </c>
       <c r="O416" t="n">
         <v>8.881784197001252e-16</v>
       </c>
       <c r="P416" t="n">
-        <v>-0.02866643109540679</v>
+        <v>-0.02849964664310978</v>
       </c>
       <c r="Q416" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>0.8106007067137809</v>
       </c>
       <c r="H417" t="n">
-        <v>6.308106007067138</v>
+        <v>6.307159010600706</v>
       </c>
       <c r="I417" t="inlineStr">
         <is>
@@ -31829,16 +31829,16 @@
         <v>1</v>
       </c>
       <c r="M417" t="n">
-        <v>1.915606007067137</v>
+        <v>1.914659010600706</v>
       </c>
       <c r="N417" t="n">
-        <v>1.915606007067137</v>
+        <v>1.914659010600706</v>
       </c>
       <c r="O417" t="n">
         <v>0.03249999999999975</v>
       </c>
       <c r="P417" t="n">
-        <v>-0.02641837455830398</v>
+        <v>-0.02662756183745607</v>
       </c>
       <c r="Q417" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>0.8035335689045936</v>
       </c>
       <c r="H418" t="n">
-        <v>6.275152953054013</v>
+        <v>6.274872286723877</v>
       </c>
       <c r="I418" t="inlineStr">
         <is>
@@ -31900,16 +31900,16 @@
         <v>1</v>
       </c>
       <c r="M418" t="n">
-        <v>1.887652953054013</v>
+        <v>1.887372286723877</v>
       </c>
       <c r="N418" t="n">
-        <v>1.887652953054013</v>
+        <v>1.887372286723877</v>
       </c>
       <c r="O418" t="n">
         <v>-0.004999999999999893</v>
       </c>
       <c r="P418" t="n">
-        <v>-0.03295305401312465</v>
+        <v>-0.03228672387682963</v>
       </c>
       <c r="Q418" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>0.8021201413427562</v>
       </c>
       <c r="H419" t="n">
-        <v>6.272291771832408</v>
+        <v>6.272009086320041</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>
@@ -31971,16 +31971,16 @@
         <v>1</v>
       </c>
       <c r="M419" t="n">
-        <v>1.877291771832407</v>
+        <v>1.87700908632004</v>
       </c>
       <c r="N419" t="n">
-        <v>1.877291771832407</v>
+        <v>1.87700908632004</v>
       </c>
       <c r="O419" t="n">
         <v>0.007500000000000284</v>
       </c>
       <c r="P419" t="n">
-        <v>-0.002861181221605058</v>
+        <v>-0.002863200403836252</v>
       </c>
       <c r="Q419" t="inlineStr">
         <is>
@@ -32023,7 +32023,7 @@
         <v>0.8007067137809187</v>
       </c>
       <c r="H420" t="n">
-        <v>6.269202826855123</v>
+        <v>6.268804240282686</v>
       </c>
       <c r="I420" t="inlineStr">
         <is>
@@ -32042,16 +32042,16 @@
         <v>1</v>
       </c>
       <c r="M420" t="n">
-        <v>1.909202826855123</v>
+        <v>1.908804240282685</v>
       </c>
       <c r="N420" t="n">
-        <v>1.909202826855123</v>
+        <v>1.908804240282685</v>
       </c>
       <c r="O420" t="n">
         <v>-0.03500000000000014</v>
       </c>
       <c r="P420" t="n">
-        <v>-0.003088944977284847</v>
+        <v>-0.003204846037355047</v>
       </c>
       <c r="Q420" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>0.8014134275618374</v>
       </c>
       <c r="H421" t="n">
-        <v>6.270861181221605</v>
+        <v>6.270577486118122</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
@@ -32113,16 +32113,16 @@
         <v>1</v>
       </c>
       <c r="M421" t="n">
-        <v>1.840861181221604</v>
+        <v>1.840577486118121</v>
       </c>
       <c r="N421" t="n">
-        <v>1.840861181221604</v>
+        <v>1.840577486118121</v>
       </c>
       <c r="O421" t="n">
         <v>0.07000000000000028</v>
       </c>
       <c r="P421" t="n">
-        <v>0.001658354366481873</v>
+        <v>0.001773245835436477</v>
       </c>
       <c r="Q421" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>3.626</v>
       </c>
       <c r="G15" t="n">
-        <v>4.278</v>
+        <v>4.279</v>
       </c>
       <c r="H15" t="n">
         <v>5.399</v>
@@ -46021,10 +46021,10 @@
         <v>3.626</v>
       </c>
       <c r="J15" t="n">
-        <v>5.398</v>
+        <v>5.397</v>
       </c>
       <c r="K15" t="n">
-        <v>1.772</v>
+        <v>1.771</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -46040,13 +46040,13 @@
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>1.355</v>
+        <v>1.354</v>
       </c>
       <c r="P15" t="n">
-        <v>1.215</v>
+        <v>1.214</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.593</v>
+        <v>0.592</v>
       </c>
       <c r="R15" t="n">
         <v>-0.882</v>
